--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5283,31 +5283,113 @@
       <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2892.7</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2935.7</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2906.1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2917.7</v>
+      </c>
+      <c r="F58" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="H58" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2797.3</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2800.08</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2859.35</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2918.62</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2949.65</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2980.67</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3068.2</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I58" s="13" t="n">
-        <v>2797.3</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>2800.08</v>
-      </c>
-      <c r="K58" s="13" t="n">
-        <v>2859.35</v>
-      </c>
-      <c r="L58" s="13" t="n">
-        <v>2918.62</v>
-      </c>
-      <c r="M58" s="13" t="n">
-        <v>2949.65</v>
-      </c>
-      <c r="N58" s="13" t="n">
-        <v>2980.67</v>
-      </c>
-      <c r="O58" s="13" t="n">
-        <v>3068.2</v>
+      <c r="I59" s="13" t="n">
+        <v>2876.5</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>2886.5</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>2902.9</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>2919.3</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>2932.5</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>2945.7</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>2965.3</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -666,25 +669,25 @@
         <v>117.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2102.5</v>
+        <v>2107.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2181.65</v>
+        <v>2183.6</v>
       </c>
       <c r="K2" t="n">
-        <v>2233.8</v>
+        <v>2235.1</v>
       </c>
       <c r="L2" t="n">
-        <v>2285.95</v>
+        <v>2286.6</v>
       </c>
       <c r="M2" t="n">
-        <v>2351.6</v>
+        <v>2350.3</v>
       </c>
       <c r="N2" t="n">
-        <v>2417.25</v>
+        <v>2414</v>
       </c>
       <c r="O2" t="n">
-        <v>2455.9</v>
+        <v>2453.3</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5289,25 +5292,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2892.7</v>
+        <v>2917.2</v>
       </c>
       <c r="C58" t="n">
-        <v>2935.7</v>
+        <v>2918.3</v>
       </c>
       <c r="D58" t="n">
-        <v>2906.1</v>
+        <v>2913.4</v>
       </c>
       <c r="E58" t="n">
-        <v>2917.7</v>
+        <v/>
       </c>
       <c r="F58" t="n">
-        <v>13.2</v>
+        <v/>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0045</v>
+        <v/>
       </c>
       <c r="H58" t="n">
-        <v>29.6</v>
+        <v>4.9</v>
       </c>
       <c r="I58" t="n">
         <v>2797.3</v>
@@ -5330,8 +5333,10 @@
       <c r="O58" t="n">
         <v>3068.2</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5339,9 +5344,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5360,36 +5365,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="13" t="n">
-        <v>2876.5</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>2886.5</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>2902.9</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>2919.3</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>2932.5</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>2945.7</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>2965.3</v>
+      <c r="I59" s="14" t="n">
+        <v>2908.5</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>2923.2</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5298,7 +5298,7 @@
         <v>2918.3</v>
       </c>
       <c r="D58" t="n">
-        <v>2913.4</v>
+        <v>2911.6</v>
       </c>
       <c r="E58" t="n">
         <v/>
@@ -5310,7 +5310,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>4.9</v>
+        <v>6.7</v>
       </c>
       <c r="I58" t="n">
         <v>2797.3</v>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="I59" s="14" t="n">
-        <v>2908.5</v>
+        <v>2904.9</v>
       </c>
       <c r="J59" s="14" t="n">
         <v/>
@@ -5394,7 +5394,7 @@
         <v/>
       </c>
       <c r="O59" s="14" t="n">
-        <v>2923.2</v>
+        <v>2925</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5292,25 +5289,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2917.2</v>
+        <v>2892.7</v>
       </c>
       <c r="C58" t="n">
-        <v>2918.3</v>
+        <v>2913.5</v>
       </c>
       <c r="D58" t="n">
-        <v>2911.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>2894.1</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-10.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0036</v>
       </c>
       <c r="H58" t="n">
-        <v>6.7</v>
+        <v>29.2</v>
       </c>
       <c r="I58" t="n">
         <v>2797.3</v>
@@ -5333,10 +5330,8 @@
       <c r="O58" t="n">
         <v>3068.2</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5344,9 +5339,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5363,38 +5358,34 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="14" t="n">
-        <v>2904.9</v>
-      </c>
-      <c r="J59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="14" t="n">
-        <v>2925</v>
+      <c r="I59" s="13" t="n">
+        <v>2855.1</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>2862.5</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>2879.5</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>2896.5</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>2908.7</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>2920.9</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>2942.7</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5292,22 +5292,22 @@
         <v>2892.7</v>
       </c>
       <c r="C58" t="n">
-        <v>2913.5</v>
+        <v>2918.3</v>
       </c>
       <c r="D58" t="n">
-        <v>2884.3</v>
+        <v>2883.6</v>
       </c>
       <c r="E58" t="n">
-        <v>2894.1</v>
+        <v>2896.6</v>
       </c>
       <c r="F58" t="n">
-        <v>-10.4</v>
+        <v>-7.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0027</v>
       </c>
       <c r="H58" t="n">
-        <v>29.2</v>
+        <v>34.7</v>
       </c>
       <c r="I58" t="n">
         <v>2797.3</v>
@@ -5367,25 +5367,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2855.1</v>
+        <v>2848.9</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2862.5</v>
+        <v>2859.73</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2879.5</v>
+        <v>2879.25</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2896.5</v>
+        <v>2898.78</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2908.7</v>
+        <v>2913.95</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2920.9</v>
+        <v>2929.13</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2942.7</v>
+        <v>2953</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>117.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2107.7</v>
+        <v>2225.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2183.6</v>
+        <v>2227.7</v>
       </c>
       <c r="K2" t="n">
-        <v>2235.1</v>
+        <v>2264.5</v>
       </c>
       <c r="L2" t="n">
-        <v>2286.6</v>
+        <v>2301.3</v>
       </c>
       <c r="M2" t="n">
-        <v>2350.3</v>
+        <v>2320.9</v>
       </c>
       <c r="N2" t="n">
-        <v>2414</v>
+        <v>2340.5</v>
       </c>
       <c r="O2" t="n">
-        <v>2453.3</v>
+        <v>2394.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,8 +692,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -702,21 +704,29 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5292,22 +5302,22 @@
         <v>2892.7</v>
       </c>
       <c r="C58" t="n">
-        <v>2918.3</v>
+        <v>2913.5</v>
       </c>
       <c r="D58" t="n">
-        <v>2883.6</v>
+        <v>2884.3</v>
       </c>
       <c r="E58" t="n">
-        <v>2896.6</v>
+        <v>2896.2</v>
       </c>
       <c r="F58" t="n">
-        <v>-7.9</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.0029</v>
       </c>
       <c r="H58" t="n">
-        <v>34.7</v>
+        <v>29.2</v>
       </c>
       <c r="I58" t="n">
         <v>2797.3</v>
@@ -5367,25 +5377,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2848.9</v>
+        <v>2855.1</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2859.73</v>
+        <v>2865.65</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2879.25</v>
+        <v>2881.6</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2898.78</v>
+        <v>2897.55</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2913.95</v>
+        <v>2910.8</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2929.13</v>
+        <v>2924.05</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2953</v>
+        <v>2942.7</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5305,19 +5305,19 @@
         <v>2913.5</v>
       </c>
       <c r="D58" t="n">
-        <v>2884.3</v>
+        <v>2862.7</v>
       </c>
       <c r="E58" t="n">
-        <v>2896.2</v>
+        <v>2898.9</v>
       </c>
       <c r="F58" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5.6</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0019</v>
       </c>
       <c r="H58" t="n">
-        <v>29.2</v>
+        <v>50.8</v>
       </c>
       <c r="I58" t="n">
         <v>2797.3</v>
@@ -5377,25 +5377,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2855.1</v>
+        <v>2811.9</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2865.65</v>
+        <v>2853.5</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2881.6</v>
+        <v>2873.5</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2897.55</v>
+        <v>2893.5</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2910.8</v>
+        <v>2924.3</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2924.05</v>
+        <v>2955.1</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2942.7</v>
+        <v>2964.3</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5308,13 +5308,13 @@
         <v>2862.7</v>
       </c>
       <c r="E58" t="n">
-        <v>2898.9</v>
+        <v>2900.4</v>
       </c>
       <c r="F58" t="n">
-        <v>-5.6</v>
+        <v>-4.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0019</v>
+        <v>-0.0014</v>
       </c>
       <c r="H58" t="n">
         <v>50.8</v>
@@ -5380,19 +5380,19 @@
         <v>2811.9</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2853.5</v>
+        <v>2855.75</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2873.5</v>
+        <v>2875</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2893.5</v>
+        <v>2894.25</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2924.3</v>
+        <v>2925.8</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2955.1</v>
+        <v>2957.35</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>2964.3</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5308,13 +5308,13 @@
         <v>2862.7</v>
       </c>
       <c r="E58" t="n">
-        <v>2900.4</v>
+        <v>2903.7</v>
       </c>
       <c r="F58" t="n">
-        <v>-4.1</v>
+        <v>-0.8</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0003</v>
       </c>
       <c r="H58" t="n">
         <v>50.8</v>
@@ -5380,19 +5380,19 @@
         <v>2811.9</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2855.75</v>
+        <v>2860.7</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2875</v>
+        <v>2878.3</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2894.25</v>
+        <v>2895.9</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2925.8</v>
+        <v>2929.1</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2957.35</v>
+        <v>2962.3</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>2964.3</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5308,10 +5308,10 @@
         <v>2862.7</v>
       </c>
       <c r="E58" t="n">
-        <v>2903.7</v>
+        <v>2903.6</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="G58" s="5" t="n">
         <v>-0.0003</v>
@@ -5380,19 +5380,19 @@
         <v>2811.9</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2860.7</v>
+        <v>2860.55</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2878.3</v>
+        <v>2878.2</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2895.9</v>
+        <v>2895.85</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2929.1</v>
+        <v>2929</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2962.3</v>
+        <v>2962.15</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>2964.3</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5308,13 +5308,13 @@
         <v>2862.7</v>
       </c>
       <c r="E58" t="n">
-        <v>2903.6</v>
+        <v>2880.9</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.9</v>
+        <v>-23.6</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0081</v>
       </c>
       <c r="H58" t="n">
         <v>50.8</v>
@@ -5346,12 +5346,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5380,19 +5382,19 @@
         <v>2811.9</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2860.55</v>
+        <v>2826.5</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2878.2</v>
+        <v>2855.5</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2895.85</v>
+        <v>2884.5</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2929</v>
+        <v>2906.3</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2962.15</v>
+        <v>2928.1</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>2964.3</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>117.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2225.3</v>
+        <v>2226.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2227.7</v>
+        <v>2229.07</v>
       </c>
       <c r="K2" t="n">
-        <v>2264.5</v>
+        <v>2265.05</v>
       </c>
       <c r="L2" t="n">
-        <v>2301.3</v>
+        <v>2301.02</v>
       </c>
       <c r="M2" t="n">
-        <v>2320.9</v>
+        <v>2320.35</v>
       </c>
       <c r="N2" t="n">
-        <v>2340.5</v>
+        <v>2339.67</v>
       </c>
       <c r="O2" t="n">
-        <v>2394.5</v>
+        <v>2392.3</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5308,13 +5308,13 @@
         <v>2862.7</v>
       </c>
       <c r="E58" t="n">
-        <v>2880.9</v>
+        <v>2900.4</v>
       </c>
       <c r="F58" t="n">
-        <v>-23.6</v>
+        <v>-4.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0014</v>
       </c>
       <c r="H58" t="n">
         <v>50.8</v>
@@ -5346,14 +5346,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5382,19 +5380,19 @@
         <v>2811.9</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2826.5</v>
+        <v>2855.75</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2855.5</v>
+        <v>2875</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2884.5</v>
+        <v>2894.25</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2906.3</v>
+        <v>2925.8</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2928.1</v>
+        <v>2957.35</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>2964.3</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5305,19 +5305,19 @@
         <v>2913.5</v>
       </c>
       <c r="D58" t="n">
-        <v>2862.7</v>
+        <v>2831.9</v>
       </c>
       <c r="E58" t="n">
-        <v>2900.4</v>
+        <v>2893.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-4.1</v>
+        <v>-11</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0038</v>
       </c>
       <c r="H58" t="n">
-        <v>50.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I58" t="n">
         <v>2797.3</v>
@@ -5346,8 +5346,10 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
@@ -5377,25 +5379,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2811.9</v>
+        <v>2750.3</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2855.75</v>
+        <v>2822.3</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2875</v>
+        <v>2852.7</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2894.25</v>
+        <v>2883.1</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2925.8</v>
+        <v>2934.3</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2957.35</v>
+        <v>2985.5</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2964.3</v>
+        <v>2995.1</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5308,13 +5308,13 @@
         <v>2831.9</v>
       </c>
       <c r="E58" t="n">
-        <v>2893.5</v>
+        <v>2892.2</v>
       </c>
       <c r="F58" t="n">
-        <v>-11</v>
+        <v>-12.3</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0042</v>
       </c>
       <c r="H58" t="n">
         <v>81.59999999999999</v>
@@ -5382,19 +5382,19 @@
         <v>2750.3</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2822.3</v>
+        <v>2820.35</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2852.7</v>
+        <v>2851.4</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2883.1</v>
+        <v>2882.45</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2934.3</v>
+        <v>2933</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2985.5</v>
+        <v>2983.55</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>2995.1</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,25 +659,25 @@
         <v>117.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2226.4</v>
+        <v>2243.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2229.07</v>
+        <v>2250.82</v>
       </c>
       <c r="K2" t="n">
-        <v>2265.05</v>
+        <v>2273.75</v>
       </c>
       <c r="L2" t="n">
-        <v>2301.02</v>
+        <v>2296.67</v>
       </c>
       <c r="M2" t="n">
-        <v>2320.35</v>
+        <v>2311.65</v>
       </c>
       <c r="N2" t="n">
-        <v>2339.67</v>
+        <v>2326.63</v>
       </c>
       <c r="O2" t="n">
-        <v>2392.3</v>
+        <v>2357.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5308,13 +5301,13 @@
         <v>2831.9</v>
       </c>
       <c r="E58" t="n">
-        <v>2892.2</v>
+        <v>2890.9</v>
       </c>
       <c r="F58" t="n">
-        <v>-12.3</v>
+        <v>-13.6</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0047</v>
       </c>
       <c r="H58" t="n">
         <v>81.59999999999999</v>
@@ -5371,34 +5364,6 @@
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>2750.3</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>2820.35</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>2851.4</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>2882.45</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>2933</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>2983.55</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>2995.1</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2289.5</v>
+        <v>2369.3</v>
       </c>
       <c r="C2" t="n">
-        <v>2374.9</v>
+        <v>2398.6</v>
       </c>
       <c r="D2" t="n">
-        <v>2257.8</v>
+        <v>2330.8</v>
       </c>
       <c r="E2" t="n">
-        <v>2368.9</v>
+        <v>2369.8</v>
       </c>
       <c r="F2" t="n">
-        <v>76.2</v>
+        <v>0.9</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0332</v>
+        <v>0.0004</v>
       </c>
       <c r="H2" t="n">
-        <v>117.1</v>
+        <v>67.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2243.8</v>
+        <v>2140.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2250.82</v>
+        <v>2278.08</v>
       </c>
       <c r="K2" t="n">
-        <v>2273.75</v>
+        <v>2310.35</v>
       </c>
       <c r="L2" t="n">
-        <v>2296.67</v>
+        <v>2342.62</v>
       </c>
       <c r="M2" t="n">
-        <v>2311.65</v>
+        <v>2427.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2326.63</v>
+        <v>2512.27</v>
       </c>
       <c r="O2" t="n">
-        <v>2357.5</v>
+        <v>2492</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,89 +685,77 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2369.3</v>
+        <v>2373</v>
       </c>
       <c r="C3" t="n">
-        <v>2398.6</v>
+        <v>2413.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2330.8</v>
+        <v>2326.1</v>
       </c>
       <c r="E3" t="n">
-        <v>2369.8</v>
+        <v>2393.5</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9</v>
+        <v>23.7</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.01</v>
       </c>
       <c r="H3" t="n">
-        <v>67.8</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>2140.7</v>
+        <v>2263</v>
       </c>
       <c r="J3" t="n">
-        <v>2278.08</v>
+        <v>2304.55</v>
       </c>
       <c r="K3" t="n">
-        <v>2310.35</v>
+        <v>2335.9</v>
       </c>
       <c r="L3" t="n">
-        <v>2342.62</v>
+        <v>2367.25</v>
       </c>
       <c r="M3" t="n">
-        <v>2427.45</v>
+        <v>2403.7</v>
       </c>
       <c r="N3" t="n">
-        <v>2512.27</v>
+        <v>2440.15</v>
       </c>
       <c r="O3" t="n">
-        <v>2492</v>
+        <v>2466.4</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -775,16 +763,20 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -797,55 +789,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2373</v>
+        <v>2391.8</v>
       </c>
       <c r="C4" t="n">
-        <v>2413.5</v>
+        <v>2424.7</v>
       </c>
       <c r="D4" t="n">
-        <v>2326.1</v>
+        <v>2369.9</v>
       </c>
       <c r="E4" t="n">
-        <v>2393.5</v>
+        <v>2397.9</v>
       </c>
       <c r="F4" t="n">
-        <v>23.7</v>
+        <v>4.4</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0018</v>
       </c>
       <c r="H4" t="n">
-        <v>87.40000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="I4" t="n">
-        <v>2263</v>
+        <v>2238.7</v>
       </c>
       <c r="J4" t="n">
-        <v>2304.55</v>
+        <v>2317.95</v>
       </c>
       <c r="K4" t="n">
-        <v>2335.9</v>
+        <v>2349.8</v>
       </c>
       <c r="L4" t="n">
-        <v>2367.25</v>
+        <v>2381.65</v>
       </c>
       <c r="M4" t="n">
-        <v>2403.7</v>
+        <v>2437.2</v>
       </c>
       <c r="N4" t="n">
-        <v>2440.15</v>
+        <v>2492.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2466.4</v>
+        <v>2500.9</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,20 +849,16 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -879,59 +871,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2391.8</v>
+        <v>2398</v>
       </c>
       <c r="C5" t="n">
-        <v>2424.7</v>
+        <v>2485.1</v>
       </c>
       <c r="D5" t="n">
-        <v>2369.9</v>
+        <v>2388.3</v>
       </c>
       <c r="E5" t="n">
-        <v>2397.9</v>
+        <v>2472.04</v>
       </c>
       <c r="F5" t="n">
-        <v>4.4</v>
+        <v>74.14</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0309</v>
       </c>
       <c r="H5" t="n">
-        <v>54.8</v>
+        <v>96.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2238.7</v>
+        <v>2315.1</v>
       </c>
       <c r="J5" t="n">
-        <v>2317.95</v>
+        <v>2343.4</v>
       </c>
       <c r="K5" t="n">
-        <v>2349.8</v>
+        <v>2370.5</v>
       </c>
       <c r="L5" t="n">
-        <v>2381.65</v>
+        <v>2397.6</v>
       </c>
       <c r="M5" t="n">
-        <v>2437.2</v>
+        <v>2425.3</v>
       </c>
       <c r="N5" t="n">
-        <v>2492.75</v>
+        <v>2453</v>
       </c>
       <c r="O5" t="n">
-        <v>2500.9</v>
+        <v>2479.5</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -944,17 +932,23 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -966,50 +960,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2398</v>
+        <v>2469.5</v>
       </c>
       <c r="C6" t="n">
-        <v>2485.1</v>
+        <v>2510.3</v>
       </c>
       <c r="D6" t="n">
-        <v>2388.3</v>
+        <v>2412.1</v>
       </c>
       <c r="E6" t="n">
-        <v>2472.04</v>
+        <v>2450.4</v>
       </c>
       <c r="F6" t="n">
-        <v>74.14</v>
+        <v>-21.64</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0309</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>96.8</v>
+        <v>98.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2315.1</v>
+        <v>2291.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2343.4</v>
+        <v>2392.91</v>
       </c>
       <c r="K6" t="n">
-        <v>2370.5</v>
+        <v>2423.64</v>
       </c>
       <c r="L6" t="n">
-        <v>2397.6</v>
+        <v>2454.37</v>
       </c>
       <c r="M6" t="n">
-        <v>2425.3</v>
+        <v>2520.44</v>
       </c>
       <c r="N6" t="n">
-        <v>2453</v>
+        <v>2586.51</v>
       </c>
       <c r="O6" t="n">
-        <v>2479.5</v>
+        <v>2581.9</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1017,83 +1011,83 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2469.5</v>
+        <v>2449.2</v>
       </c>
       <c r="C7" t="n">
-        <v>2510.3</v>
+        <v>2515</v>
       </c>
       <c r="D7" t="n">
-        <v>2412.1</v>
+        <v>2424.7</v>
       </c>
       <c r="E7" t="n">
-        <v>2450.4</v>
+        <v>2492.1</v>
       </c>
       <c r="F7" t="n">
-        <v>-21.64</v>
+        <v>41.7</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="H7" t="n">
-        <v>98.2</v>
+        <v>90.3</v>
       </c>
       <c r="I7" t="n">
-        <v>2291.5</v>
+        <v>2313.9</v>
       </c>
       <c r="J7" t="n">
-        <v>2392.91</v>
+        <v>2346.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2423.64</v>
+        <v>2401.3</v>
       </c>
       <c r="L7" t="n">
-        <v>2454.37</v>
+        <v>2455.8</v>
       </c>
       <c r="M7" t="n">
-        <v>2520.44</v>
+        <v>2499.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2586.51</v>
+        <v>2543.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2581.9</v>
+        <v>2608.5</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1101,18 +1095,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1125,164 +1119,166 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2449.2</v>
+        <v>2491.9</v>
       </c>
       <c r="C8" t="n">
-        <v>2515</v>
+        <v>2518.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2424.7</v>
+        <v>2381.8</v>
       </c>
       <c r="E8" t="n">
-        <v>2492.1</v>
+        <v>2408.5</v>
       </c>
       <c r="F8" t="n">
-        <v>41.7</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.017</v>
+        <v>-0.0335</v>
       </c>
       <c r="H8" t="n">
-        <v>90.3</v>
+        <v>136.7</v>
       </c>
       <c r="I8" t="n">
-        <v>2313.9</v>
+        <v>2334.4</v>
       </c>
       <c r="J8" t="n">
-        <v>2346.8</v>
+        <v>2412.93</v>
       </c>
       <c r="K8" t="n">
-        <v>2401.3</v>
+        <v>2446.95</v>
       </c>
       <c r="L8" t="n">
-        <v>2455.8</v>
+        <v>2480.98</v>
       </c>
       <c r="M8" t="n">
-        <v>2499.5</v>
+        <v>2537.25</v>
       </c>
       <c r="N8" t="n">
-        <v>2543.2</v>
+        <v>2593.53</v>
       </c>
       <c r="O8" t="n">
-        <v>2608.5</v>
+        <v>2605.3</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2491.9</v>
+        <v>2421.6</v>
       </c>
       <c r="C9" t="n">
-        <v>2518.5</v>
+        <v>2559.9</v>
       </c>
       <c r="D9" t="n">
-        <v>2381.8</v>
+        <v>2421.6</v>
       </c>
       <c r="E9" t="n">
-        <v>2408.5</v>
+        <v>2464.4</v>
       </c>
       <c r="F9" t="n">
-        <v>-83.59999999999999</v>
+        <v>55.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0335</v>
+        <v>0.0232</v>
       </c>
       <c r="H9" t="n">
-        <v>136.7</v>
+        <v>138.3</v>
       </c>
       <c r="I9" t="n">
-        <v>2334.4</v>
+        <v>2245.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2412.93</v>
+        <v>2250.98</v>
       </c>
       <c r="K9" t="n">
-        <v>2446.95</v>
+        <v>2340.15</v>
       </c>
       <c r="L9" t="n">
-        <v>2480.98</v>
+        <v>2429.33</v>
       </c>
       <c r="M9" t="n">
-        <v>2537.25</v>
+        <v>2476.85</v>
       </c>
       <c r="N9" t="n">
-        <v>2593.53</v>
+        <v>2524.37</v>
       </c>
       <c r="O9" t="n">
-        <v>2605.3</v>
+        <v>2655.2</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1293,57 +1289,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2421.6</v>
+        <v>2473.7</v>
       </c>
       <c r="C10" t="n">
-        <v>2559.9</v>
+        <v>2544</v>
       </c>
       <c r="D10" t="n">
-        <v>2421.6</v>
+        <v>2436.9</v>
       </c>
       <c r="E10" t="n">
-        <v>2464.4</v>
+        <v>2523.7</v>
       </c>
       <c r="F10" t="n">
-        <v>55.9</v>
+        <v>59.3</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0232</v>
+        <v>0.0241</v>
       </c>
       <c r="H10" t="n">
-        <v>138.3</v>
+        <v>107.1</v>
       </c>
       <c r="I10" t="n">
-        <v>2245.1</v>
+        <v>2283.3</v>
       </c>
       <c r="J10" t="n">
-        <v>2250.98</v>
+        <v>2312.93</v>
       </c>
       <c r="K10" t="n">
-        <v>2340.15</v>
+        <v>2395.25</v>
       </c>
       <c r="L10" t="n">
-        <v>2429.33</v>
+        <v>2477.57</v>
       </c>
       <c r="M10" t="n">
-        <v>2476.85</v>
+        <v>2533.55</v>
       </c>
       <c r="N10" t="n">
-        <v>2524.37</v>
+        <v>2589.52</v>
       </c>
       <c r="O10" t="n">
-        <v>2655.2</v>
+        <v>2698.2</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1364,10 +1360,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1379,57 +1373,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2473.7</v>
+        <v>2551.8</v>
       </c>
       <c r="C11" t="n">
-        <v>2544</v>
+        <v>2566.5</v>
       </c>
       <c r="D11" t="n">
-        <v>2436.9</v>
+        <v>2463</v>
       </c>
       <c r="E11" t="n">
-        <v>2523.7</v>
+        <v>2489.9</v>
       </c>
       <c r="F11" t="n">
-        <v>59.3</v>
+        <v>-33.8</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0241</v>
+        <v>-0.0134</v>
       </c>
       <c r="H11" t="n">
-        <v>107.1</v>
+        <v>103.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2283.3</v>
+        <v>2329.8</v>
       </c>
       <c r="J11" t="n">
-        <v>2312.93</v>
+        <v>2433.22</v>
       </c>
       <c r="K11" t="n">
-        <v>2395.25</v>
+        <v>2470.15</v>
       </c>
       <c r="L11" t="n">
-        <v>2477.57</v>
+        <v>2507.07</v>
       </c>
       <c r="M11" t="n">
-        <v>2533.55</v>
+        <v>2577.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2589.52</v>
+        <v>2647.43</v>
       </c>
       <c r="O11" t="n">
-        <v>2698.2</v>
+        <v>2651.1</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1437,18 +1431,18 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1470,50 +1464,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2551.8</v>
+        <v>2489.1</v>
       </c>
       <c r="C12" t="n">
-        <v>2566.5</v>
+        <v>2500.4</v>
       </c>
       <c r="D12" t="n">
-        <v>2463</v>
+        <v>2386.6</v>
       </c>
       <c r="E12" t="n">
-        <v>2489.9</v>
+        <v>2440.6</v>
       </c>
       <c r="F12" t="n">
-        <v>-33.8</v>
+        <v>-49.3</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0134</v>
+        <v>-0.0198</v>
       </c>
       <c r="H12" t="n">
-        <v>103.5</v>
+        <v>113.8</v>
       </c>
       <c r="I12" t="n">
-        <v>2329.8</v>
+        <v>2359.5</v>
       </c>
       <c r="J12" t="n">
-        <v>2433.22</v>
+        <v>2373.97</v>
       </c>
       <c r="K12" t="n">
-        <v>2470.15</v>
+        <v>2438.15</v>
       </c>
       <c r="L12" t="n">
-        <v>2507.07</v>
+        <v>2502.32</v>
       </c>
       <c r="M12" t="n">
-        <v>2577.25</v>
+        <v>2541.65</v>
       </c>
       <c r="N12" t="n">
-        <v>2647.43</v>
+        <v>2580.97</v>
       </c>
       <c r="O12" t="n">
-        <v>2651.1</v>
+        <v>2670</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1523,12 +1517,12 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1545,59 +1539,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2489.1</v>
+        <v>2455.2</v>
       </c>
       <c r="C13" t="n">
-        <v>2500.4</v>
+        <v>2487.6</v>
       </c>
       <c r="D13" t="n">
-        <v>2386.6</v>
+        <v>2353.8</v>
       </c>
       <c r="E13" t="n">
-        <v>2440.6</v>
+        <v>2396</v>
       </c>
       <c r="F13" t="n">
-        <v>-49.3</v>
+        <v>-44.6</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0198</v>
+        <v>-0.0183</v>
       </c>
       <c r="H13" t="n">
-        <v>113.8</v>
+        <v>133.8</v>
       </c>
       <c r="I13" t="n">
-        <v>2359.5</v>
+        <v>2272.8</v>
       </c>
       <c r="J13" t="n">
-        <v>2373.97</v>
+        <v>2325.35</v>
       </c>
       <c r="K13" t="n">
-        <v>2438.15</v>
+        <v>2383.7</v>
       </c>
       <c r="L13" t="n">
-        <v>2502.32</v>
+        <v>2442.05</v>
       </c>
       <c r="M13" t="n">
-        <v>2541.65</v>
+        <v>2497.5</v>
       </c>
       <c r="N13" t="n">
-        <v>2580.97</v>
+        <v>2552.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2670</v>
+        <v>2614.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1634,50 +1624,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2455.2</v>
+        <v>2397</v>
       </c>
       <c r="C14" t="n">
-        <v>2487.6</v>
+        <v>2411.9</v>
       </c>
       <c r="D14" t="n">
-        <v>2353.8</v>
+        <v>2300.7</v>
       </c>
       <c r="E14" t="n">
-        <v>2396</v>
+        <v>2375.3</v>
       </c>
       <c r="F14" t="n">
-        <v>-44.6</v>
+        <v>-20.7</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.0086</v>
       </c>
       <c r="H14" t="n">
-        <v>133.8</v>
+        <v>111.2</v>
       </c>
       <c r="I14" t="n">
-        <v>2272.8</v>
+        <v>2220</v>
       </c>
       <c r="J14" t="n">
-        <v>2325.35</v>
+        <v>2249.85</v>
       </c>
       <c r="K14" t="n">
-        <v>2383.7</v>
+        <v>2329.1</v>
       </c>
       <c r="L14" t="n">
-        <v>2442.05</v>
+        <v>2408.35</v>
       </c>
       <c r="M14" t="n">
-        <v>2497.5</v>
+        <v>2462.9</v>
       </c>
       <c r="N14" t="n">
-        <v>2552.95</v>
+        <v>2517.45</v>
       </c>
       <c r="O14" t="n">
-        <v>2614.2</v>
+        <v>2621.4</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1687,12 +1677,12 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1714,50 +1704,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2397</v>
+        <v>2387.8</v>
       </c>
       <c r="C15" t="n">
-        <v>2411.9</v>
+        <v>2508.1</v>
       </c>
       <c r="D15" t="n">
-        <v>2300.7</v>
+        <v>2370.3</v>
       </c>
       <c r="E15" t="n">
-        <v>2375.3</v>
+        <v>2505.1</v>
       </c>
       <c r="F15" t="n">
-        <v>-20.7</v>
+        <v>129.8</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0546</v>
       </c>
       <c r="H15" t="n">
-        <v>111.2</v>
+        <v>137.8</v>
       </c>
       <c r="I15" t="n">
-        <v>2220</v>
+        <v>2189.5</v>
       </c>
       <c r="J15" t="n">
-        <v>2249.85</v>
+        <v>2273.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2329.1</v>
+        <v>2319.7</v>
       </c>
       <c r="L15" t="n">
-        <v>2408.35</v>
+        <v>2365.8</v>
       </c>
       <c r="M15" t="n">
-        <v>2462.9</v>
+        <v>2430.9</v>
       </c>
       <c r="N15" t="n">
-        <v>2517.45</v>
+        <v>2496</v>
       </c>
       <c r="O15" t="n">
-        <v>2621.4</v>
+        <v>2523.1</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1765,28 +1755,30 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1794,50 +1786,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2387.8</v>
+        <v>2501</v>
       </c>
       <c r="C16" t="n">
-        <v>2508.1</v>
+        <v>2544.2</v>
       </c>
       <c r="D16" t="n">
-        <v>2370.3</v>
+        <v>2468.1</v>
       </c>
       <c r="E16" t="n">
-        <v>2505.1</v>
+        <v>2524.4</v>
       </c>
       <c r="F16" t="n">
-        <v>129.8</v>
+        <v>19.3</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0077</v>
       </c>
       <c r="H16" t="n">
-        <v>137.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2189.5</v>
+        <v>2232.5</v>
       </c>
       <c r="J16" t="n">
-        <v>2273.6</v>
+        <v>2400.25</v>
       </c>
       <c r="K16" t="n">
-        <v>2319.7</v>
+        <v>2436.2</v>
       </c>
       <c r="L16" t="n">
-        <v>2365.8</v>
+        <v>2472.15</v>
       </c>
       <c r="M16" t="n">
-        <v>2430.9</v>
+        <v>2574</v>
       </c>
       <c r="N16" t="n">
-        <v>2496</v>
+        <v>2675.85</v>
       </c>
       <c r="O16" t="n">
-        <v>2523.1</v>
+        <v>2645.9</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1855,13 +1847,11 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1876,50 +1866,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2501</v>
+        <v>2528</v>
       </c>
       <c r="C17" t="n">
-        <v>2544.2</v>
+        <v>2605</v>
       </c>
       <c r="D17" t="n">
-        <v>2468.1</v>
+        <v>2516.6</v>
       </c>
       <c r="E17" t="n">
-        <v>2524.4</v>
+        <v>2553.7</v>
       </c>
       <c r="F17" t="n">
-        <v>19.3</v>
+        <v>29.3</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0116</v>
       </c>
       <c r="H17" t="n">
-        <v>76.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>2232.5</v>
+        <v>2392</v>
       </c>
       <c r="J17" t="n">
-        <v>2400.25</v>
+        <v>2457.42</v>
       </c>
       <c r="K17" t="n">
-        <v>2436.2</v>
+        <v>2486.35</v>
       </c>
       <c r="L17" t="n">
-        <v>2472.15</v>
+        <v>2515.27</v>
       </c>
       <c r="M17" t="n">
-        <v>2574</v>
+        <v>2562.45</v>
       </c>
       <c r="N17" t="n">
-        <v>2675.85</v>
+        <v>2609.62</v>
       </c>
       <c r="O17" t="n">
-        <v>2645.9</v>
+        <v>2620.3</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1956,50 +1946,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2528</v>
+        <v>2552.8</v>
       </c>
       <c r="C18" t="n">
-        <v>2605</v>
+        <v>2577.3</v>
       </c>
       <c r="D18" t="n">
-        <v>2516.6</v>
+        <v>2489.4</v>
       </c>
       <c r="E18" t="n">
-        <v>2553.7</v>
+        <v>2509.56</v>
       </c>
       <c r="F18" t="n">
-        <v>29.3</v>
+        <v>-44.14</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0116</v>
+        <v>-0.0173</v>
       </c>
       <c r="H18" t="n">
-        <v>88.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>2392</v>
+        <v>2428.2</v>
       </c>
       <c r="J18" t="n">
-        <v>2457.42</v>
+        <v>2461.75</v>
       </c>
       <c r="K18" t="n">
-        <v>2486.35</v>
+        <v>2509.5</v>
       </c>
       <c r="L18" t="n">
-        <v>2515.27</v>
+        <v>2557.25</v>
       </c>
       <c r="M18" t="n">
-        <v>2562.45</v>
+        <v>2597.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2609.62</v>
+        <v>2638.55</v>
       </c>
       <c r="O18" t="n">
-        <v>2620.3</v>
+        <v>2693.4</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2007,19 +1997,19 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2031,55 +2021,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2552.8</v>
+        <v>2550</v>
       </c>
       <c r="C19" t="n">
-        <v>2577.3</v>
+        <v>2590.3</v>
       </c>
       <c r="D19" t="n">
-        <v>2489.4</v>
+        <v>2540.8</v>
       </c>
       <c r="E19" t="n">
-        <v>2509.56</v>
+        <v>2551.4</v>
       </c>
       <c r="F19" t="n">
-        <v>-44.14</v>
+        <v>41.84</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0173</v>
+        <v>0.0167</v>
       </c>
       <c r="H19" t="n">
-        <v>87.90000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="I19" t="n">
-        <v>2428.2</v>
+        <v>2401.5</v>
       </c>
       <c r="J19" t="n">
-        <v>2461.75</v>
+        <v>2409.76</v>
       </c>
       <c r="K19" t="n">
-        <v>2509.5</v>
+        <v>2465.61</v>
       </c>
       <c r="L19" t="n">
-        <v>2557.25</v>
+        <v>2521.46</v>
       </c>
       <c r="M19" t="n">
-        <v>2597.9</v>
+        <v>2553.51</v>
       </c>
       <c r="N19" t="n">
-        <v>2638.55</v>
+        <v>2585.57</v>
       </c>
       <c r="O19" t="n">
-        <v>2693.4</v>
+        <v>2665.2</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2087,21 +2081,23 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2111,83 +2107,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2550</v>
+        <v>2551.6</v>
       </c>
       <c r="C20" t="n">
-        <v>2590.3</v>
+        <v>2556.9</v>
       </c>
       <c r="D20" t="n">
-        <v>2540.8</v>
+        <v>2493.5</v>
       </c>
       <c r="E20" t="n">
-        <v>2551.4</v>
+        <v>2522.5</v>
       </c>
       <c r="F20" t="n">
-        <v>41.84</v>
+        <v>-28.9</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0167</v>
+        <v>-0.0113</v>
       </c>
       <c r="H20" t="n">
-        <v>49.5</v>
+        <v>63.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2401.5</v>
+        <v>2491.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2409.76</v>
+        <v>2494.82</v>
       </c>
       <c r="K20" t="n">
-        <v>2465.61</v>
+        <v>2526.65</v>
       </c>
       <c r="L20" t="n">
-        <v>2521.46</v>
+        <v>2558.47</v>
       </c>
       <c r="M20" t="n">
-        <v>2553.51</v>
+        <v>2576.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2585.57</v>
+        <v>2593.82</v>
       </c>
       <c r="O20" t="n">
-        <v>2665.2</v>
+        <v>2639.8</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2197,141 +2189,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2551.6</v>
+        <v>2524.2</v>
       </c>
       <c r="C21" t="n">
-        <v>2556.9</v>
+        <v>2650.3</v>
       </c>
       <c r="D21" t="n">
-        <v>2493.5</v>
+        <v>2517.2</v>
       </c>
       <c r="E21" t="n">
-        <v>2522.5</v>
+        <v>2636.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-28.9</v>
+        <v>114.4</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0113</v>
+        <v>0.0454</v>
       </c>
       <c r="H21" t="n">
-        <v>63.4</v>
+        <v>133.1</v>
       </c>
       <c r="I21" t="n">
-        <v>2491.3</v>
+        <v>2430.1</v>
       </c>
       <c r="J21" t="n">
-        <v>2494.82</v>
+        <v>2457.75</v>
       </c>
       <c r="K21" t="n">
-        <v>2526.65</v>
+        <v>2490.8</v>
       </c>
       <c r="L21" t="n">
-        <v>2558.47</v>
+        <v>2523.85</v>
       </c>
       <c r="M21" t="n">
-        <v>2576.15</v>
+        <v>2554.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2593.82</v>
+        <v>2584.55</v>
       </c>
       <c r="O21" t="n">
-        <v>2639.8</v>
+        <v>2620.3</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2524.2</v>
+        <v>2638.9</v>
       </c>
       <c r="C22" t="n">
-        <v>2650.3</v>
+        <v>2705.6</v>
       </c>
       <c r="D22" t="n">
-        <v>2517.2</v>
+        <v>2616.3</v>
       </c>
       <c r="E22" t="n">
-        <v>2636.9</v>
+        <v>2691.2</v>
       </c>
       <c r="F22" t="n">
-        <v>114.4</v>
+        <v>54.3</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0454</v>
+        <v>0.0206</v>
       </c>
       <c r="H22" t="n">
-        <v>133.1</v>
+        <v>89.3</v>
       </c>
       <c r="I22" t="n">
-        <v>2430.1</v>
+        <v>2384.1</v>
       </c>
       <c r="J22" t="n">
-        <v>2457.75</v>
+        <v>2530.37</v>
       </c>
       <c r="K22" t="n">
-        <v>2490.8</v>
+        <v>2570.35</v>
       </c>
       <c r="L22" t="n">
-        <v>2523.85</v>
+        <v>2610.32</v>
       </c>
       <c r="M22" t="n">
-        <v>2554.2</v>
+        <v>2703.45</v>
       </c>
       <c r="N22" t="n">
-        <v>2584.55</v>
+        <v>2796.57</v>
       </c>
       <c r="O22" t="n">
-        <v>2620.3</v>
+        <v>2783.4</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2349,18 +2343,14 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2372,50 +2362,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2638.9</v>
+        <v>2670</v>
       </c>
       <c r="C23" t="n">
-        <v>2705.6</v>
+        <v>2749.2</v>
       </c>
       <c r="D23" t="n">
-        <v>2616.3</v>
+        <v>2631</v>
       </c>
       <c r="E23" t="n">
-        <v>2691.2</v>
+        <v>2679.6</v>
       </c>
       <c r="F23" t="n">
-        <v>54.3</v>
+        <v>-11.6</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0206</v>
+        <v>-0.0043</v>
       </c>
       <c r="H23" t="n">
-        <v>89.3</v>
+        <v>118.2</v>
       </c>
       <c r="I23" t="n">
-        <v>2384.1</v>
+        <v>2527</v>
       </c>
       <c r="J23" t="n">
-        <v>2530.37</v>
+        <v>2617.02</v>
       </c>
       <c r="K23" t="n">
-        <v>2570.35</v>
+        <v>2646.55</v>
       </c>
       <c r="L23" t="n">
-        <v>2610.32</v>
+        <v>2676.08</v>
       </c>
       <c r="M23" t="n">
-        <v>2703.45</v>
+        <v>2735.85</v>
       </c>
       <c r="N23" t="n">
-        <v>2796.57</v>
+        <v>2795.62</v>
       </c>
       <c r="O23" t="n">
-        <v>2783.4</v>
+        <v>2794.9</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2423,17 +2413,19 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U23" s="8" t="n">
@@ -2447,55 +2439,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2670</v>
+        <v>2661</v>
       </c>
       <c r="C24" t="n">
-        <v>2749.2</v>
+        <v>2697.9</v>
       </c>
       <c r="D24" t="n">
-        <v>2631</v>
+        <v>2607.5</v>
       </c>
       <c r="E24" t="n">
-        <v>2679.6</v>
+        <v>2624.6</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.6</v>
+        <v>-55</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0205</v>
       </c>
       <c r="H24" t="n">
-        <v>118.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>2527</v>
+        <v>2512.8</v>
       </c>
       <c r="J24" t="n">
-        <v>2617.02</v>
+        <v>2556.15</v>
       </c>
       <c r="K24" t="n">
-        <v>2646.55</v>
+        <v>2620.5</v>
       </c>
       <c r="L24" t="n">
-        <v>2676.08</v>
+        <v>2684.85</v>
       </c>
       <c r="M24" t="n">
-        <v>2735.85</v>
+        <v>2738.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2795.62</v>
+        <v>2792.55</v>
       </c>
       <c r="O24" t="n">
-        <v>2794.9</v>
+        <v>2867.4</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2505,18 +2501,16 @@
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2531,57 +2525,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2661</v>
+        <v>2615</v>
       </c>
       <c r="C25" t="n">
-        <v>2697.9</v>
+        <v>2684.1</v>
       </c>
       <c r="D25" t="n">
-        <v>2607.5</v>
+        <v>2566.8</v>
       </c>
       <c r="E25" t="n">
-        <v>2624.6</v>
+        <v>2677.9</v>
       </c>
       <c r="F25" t="n">
-        <v>-55</v>
+        <v>53.3</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0205</v>
+        <v>0.0203</v>
       </c>
       <c r="H25" t="n">
-        <v>90.40000000000001</v>
+        <v>117.3</v>
       </c>
       <c r="I25" t="n">
-        <v>2512.8</v>
+        <v>2517.1</v>
       </c>
       <c r="J25" t="n">
-        <v>2556.15</v>
+        <v>2520.15</v>
       </c>
       <c r="K25" t="n">
-        <v>2620.5</v>
+        <v>2579.4</v>
       </c>
       <c r="L25" t="n">
-        <v>2684.85</v>
+        <v>2638.65</v>
       </c>
       <c r="M25" t="n">
-        <v>2738.7</v>
+        <v>2669.8</v>
       </c>
       <c r="N25" t="n">
-        <v>2792.55</v>
+        <v>2700.95</v>
       </c>
       <c r="O25" t="n">
-        <v>2867.4</v>
+        <v>2788.3</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2591,17 +2585,19 @@
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2615,57 +2611,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2615</v>
+        <v>2677</v>
       </c>
       <c r="C26" t="n">
-        <v>2684.1</v>
+        <v>2720</v>
       </c>
       <c r="D26" t="n">
-        <v>2566.8</v>
+        <v>2607.3</v>
       </c>
       <c r="E26" t="n">
-        <v>2677.9</v>
+        <v>2653.1</v>
       </c>
       <c r="F26" t="n">
-        <v>53.3</v>
+        <v>-24.8</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0203</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>117.3</v>
+        <v>112.7</v>
       </c>
       <c r="I26" t="n">
-        <v>2517.1</v>
+        <v>2449.5</v>
       </c>
       <c r="J26" t="n">
-        <v>2520.15</v>
+        <v>2586.82</v>
       </c>
       <c r="K26" t="n">
-        <v>2579.4</v>
+        <v>2619.25</v>
       </c>
       <c r="L26" t="n">
-        <v>2638.65</v>
+        <v>2651.67</v>
       </c>
       <c r="M26" t="n">
-        <v>2669.8</v>
+        <v>2736.55</v>
       </c>
       <c r="N26" t="n">
-        <v>2700.95</v>
+        <v>2821.42</v>
       </c>
       <c r="O26" t="n">
-        <v>2788.3</v>
+        <v>2801.4</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2680,13 +2676,11 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2701,57 +2695,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2677</v>
+        <v>2650.9</v>
       </c>
       <c r="C27" t="n">
-        <v>2720</v>
+        <v>2696</v>
       </c>
       <c r="D27" t="n">
-        <v>2607.3</v>
+        <v>2613.7</v>
       </c>
       <c r="E27" t="n">
-        <v>2653.1</v>
+        <v>2668.8</v>
       </c>
       <c r="F27" t="n">
-        <v>-24.8</v>
+        <v>15.7</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H27" t="n">
-        <v>112.7</v>
+        <v>82.3</v>
       </c>
       <c r="I27" t="n">
-        <v>2449.5</v>
+        <v>2494.6</v>
       </c>
       <c r="J27" t="n">
-        <v>2586.82</v>
+        <v>2535.13</v>
       </c>
       <c r="K27" t="n">
-        <v>2619.25</v>
+        <v>2596.75</v>
       </c>
       <c r="L27" t="n">
-        <v>2651.67</v>
+        <v>2658.38</v>
       </c>
       <c r="M27" t="n">
-        <v>2736.55</v>
+        <v>2709.45</v>
       </c>
       <c r="N27" t="n">
-        <v>2821.42</v>
+        <v>2760.53</v>
       </c>
       <c r="O27" t="n">
-        <v>2801.4</v>
+        <v>2832.7</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2759,10 +2753,8 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
@@ -2792,50 +2784,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2650.9</v>
+        <v>2666.5</v>
       </c>
       <c r="C28" t="n">
-        <v>2696</v>
+        <v>2683.4</v>
       </c>
       <c r="D28" t="n">
-        <v>2613.7</v>
+        <v>2602.7</v>
       </c>
       <c r="E28" t="n">
-        <v>2668.8</v>
+        <v>2634.7</v>
       </c>
       <c r="F28" t="n">
-        <v>15.7</v>
+        <v>-34.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0128</v>
       </c>
       <c r="H28" t="n">
-        <v>82.3</v>
+        <v>80.7</v>
       </c>
       <c r="I28" t="n">
-        <v>2494.6</v>
+        <v>2531.4</v>
       </c>
       <c r="J28" t="n">
-        <v>2535.13</v>
+        <v>2593.48</v>
       </c>
       <c r="K28" t="n">
-        <v>2596.75</v>
+        <v>2627.65</v>
       </c>
       <c r="L28" t="n">
-        <v>2658.38</v>
+        <v>2661.83</v>
       </c>
       <c r="M28" t="n">
-        <v>2709.45</v>
+        <v>2709.95</v>
       </c>
       <c r="N28" t="n">
-        <v>2760.53</v>
+        <v>2758.08</v>
       </c>
       <c r="O28" t="n">
-        <v>2832.7</v>
+        <v>2778.3</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2843,12 +2835,14 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2867,67 +2861,71 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2666.5</v>
+        <v>2608.8</v>
       </c>
       <c r="C29" t="n">
-        <v>2683.4</v>
+        <v>2663.3</v>
       </c>
       <c r="D29" t="n">
-        <v>2602.7</v>
+        <v>2516.6</v>
       </c>
       <c r="E29" t="n">
-        <v>2634.7</v>
+        <v>2526.7</v>
       </c>
       <c r="F29" t="n">
-        <v>-34.1</v>
+        <v>-108</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0128</v>
+        <v>-0.041</v>
       </c>
       <c r="H29" t="n">
-        <v>80.7</v>
+        <v>146.7</v>
       </c>
       <c r="I29" t="n">
-        <v>2531.4</v>
+        <v>2522</v>
       </c>
       <c r="J29" t="n">
-        <v>2593.48</v>
+        <v>2549.83</v>
       </c>
       <c r="K29" t="n">
-        <v>2627.65</v>
+        <v>2594.35</v>
       </c>
       <c r="L29" t="n">
-        <v>2661.83</v>
+        <v>2638.87</v>
       </c>
       <c r="M29" t="n">
-        <v>2709.95</v>
+        <v>2675.05</v>
       </c>
       <c r="N29" t="n">
-        <v>2758.08</v>
+        <v>2711.22</v>
       </c>
       <c r="O29" t="n">
-        <v>2778.3</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+        <v>2764.1</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
@@ -2944,78 +2942,70 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2608.8</v>
+        <v>2499.2</v>
       </c>
       <c r="C30" t="n">
-        <v>2663.3</v>
+        <v>2594.4</v>
       </c>
       <c r="D30" t="n">
-        <v>2516.6</v>
+        <v>2416.9</v>
       </c>
       <c r="E30" t="n">
-        <v>2526.7</v>
+        <v>2480.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-108</v>
+        <v>-45.8</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.041</v>
+        <v>-0.0181</v>
       </c>
       <c r="H30" t="n">
-        <v>146.7</v>
+        <v>177.5</v>
       </c>
       <c r="I30" t="n">
-        <v>2522</v>
+        <v>2369.9</v>
       </c>
       <c r="J30" t="n">
-        <v>2549.83</v>
+        <v>2348.37</v>
       </c>
       <c r="K30" t="n">
-        <v>2594.35</v>
+        <v>2453.35</v>
       </c>
       <c r="L30" t="n">
-        <v>2638.87</v>
+        <v>2558.33</v>
       </c>
       <c r="M30" t="n">
-        <v>2675.05</v>
+        <v>2600.05</v>
       </c>
       <c r="N30" t="n">
-        <v>2711.22</v>
+        <v>2641.77</v>
       </c>
       <c r="O30" t="n">
-        <v>2764.1</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
+        <v>2810</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
@@ -3042,50 +3032,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2499.2</v>
+        <v>2468.5</v>
       </c>
       <c r="C31" t="n">
-        <v>2594.4</v>
+        <v>2547.9</v>
       </c>
       <c r="D31" t="n">
-        <v>2416.9</v>
+        <v>2442</v>
       </c>
       <c r="E31" t="n">
-        <v>2480.9</v>
+        <v>2496.4</v>
       </c>
       <c r="F31" t="n">
-        <v>-45.8</v>
+        <v>15.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0181</v>
+        <v>0.0062</v>
       </c>
       <c r="H31" t="n">
-        <v>177.5</v>
+        <v>105.9</v>
       </c>
       <c r="I31" t="n">
-        <v>2369.9</v>
+        <v>2239.4</v>
       </c>
       <c r="J31" t="n">
-        <v>2348.37</v>
+        <v>2291.02</v>
       </c>
       <c r="K31" t="n">
-        <v>2453.35</v>
+        <v>2392.15</v>
       </c>
       <c r="L31" t="n">
-        <v>2558.33</v>
+        <v>2493.27</v>
       </c>
       <c r="M31" t="n">
-        <v>2600.05</v>
+        <v>2569.65</v>
       </c>
       <c r="N31" t="n">
-        <v>2641.77</v>
+        <v>2646.02</v>
       </c>
       <c r="O31" t="n">
-        <v>2810</v>
+        <v>2771.9</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3093,14 +3083,12 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3117,55 +3105,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2468.5</v>
+        <v>2429.1</v>
       </c>
       <c r="C32" t="n">
-        <v>2547.9</v>
+        <v>2574.5</v>
       </c>
       <c r="D32" t="n">
-        <v>2442</v>
+        <v>2415.3</v>
       </c>
       <c r="E32" t="n">
-        <v>2496.4</v>
+        <v>2464</v>
       </c>
       <c r="F32" t="n">
-        <v>15.5</v>
+        <v>-32.4</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.013</v>
       </c>
       <c r="H32" t="n">
-        <v>105.9</v>
+        <v>159.2</v>
       </c>
       <c r="I32" t="n">
-        <v>2239.4</v>
+        <v>2336.1</v>
       </c>
       <c r="J32" t="n">
-        <v>2291.02</v>
+        <v>2391.22</v>
       </c>
       <c r="K32" t="n">
-        <v>2392.15</v>
+        <v>2443.45</v>
       </c>
       <c r="L32" t="n">
-        <v>2493.27</v>
+        <v>2495.67</v>
       </c>
       <c r="M32" t="n">
-        <v>2569.65</v>
+        <v>2549.35</v>
       </c>
       <c r="N32" t="n">
-        <v>2646.02</v>
+        <v>2603.02</v>
       </c>
       <c r="O32" t="n">
-        <v>2771.9</v>
+        <v>2653.8</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3173,16 +3165,20 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3197,57 +3193,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2429.1</v>
+        <v>2445</v>
       </c>
       <c r="C33" t="n">
-        <v>2574.5</v>
+        <v>2557</v>
       </c>
       <c r="D33" t="n">
-        <v>2415.3</v>
+        <v>2409.4</v>
       </c>
       <c r="E33" t="n">
-        <v>2464</v>
+        <v>2531.7</v>
       </c>
       <c r="F33" t="n">
-        <v>-32.4</v>
+        <v>67.7</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.013</v>
+        <v>0.0275</v>
       </c>
       <c r="H33" t="n">
-        <v>159.2</v>
+        <v>147.6</v>
       </c>
       <c r="I33" t="n">
-        <v>2336.1</v>
+        <v>2256.1</v>
       </c>
       <c r="J33" t="n">
-        <v>2391.22</v>
+        <v>2289.35</v>
       </c>
       <c r="K33" t="n">
-        <v>2443.45</v>
+        <v>2384.4</v>
       </c>
       <c r="L33" t="n">
-        <v>2495.67</v>
+        <v>2479.45</v>
       </c>
       <c r="M33" t="n">
-        <v>2549.35</v>
+        <v>2543.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2603.02</v>
+        <v>2607.75</v>
       </c>
       <c r="O33" t="n">
-        <v>2653.8</v>
+        <v>2733.7</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3255,19 +3251,17 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="U33" s="8" t="n">
@@ -3290,50 +3284,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2445</v>
+        <v>2527.9</v>
       </c>
       <c r="C34" t="n">
-        <v>2557</v>
+        <v>2674.5</v>
       </c>
       <c r="D34" t="n">
-        <v>2409.4</v>
+        <v>2511.4</v>
       </c>
       <c r="E34" t="n">
-        <v>2531.7</v>
+        <v>2644.4</v>
       </c>
       <c r="F34" t="n">
-        <v>67.7</v>
+        <v>112.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0445</v>
       </c>
       <c r="H34" t="n">
-        <v>147.6</v>
+        <v>163.1</v>
       </c>
       <c r="I34" t="n">
-        <v>2256.1</v>
+        <v>2261.8</v>
       </c>
       <c r="J34" t="n">
-        <v>2289.35</v>
+        <v>2408.35</v>
       </c>
       <c r="K34" t="n">
-        <v>2384.4</v>
+        <v>2457.9</v>
       </c>
       <c r="L34" t="n">
-        <v>2479.45</v>
+        <v>2507.45</v>
       </c>
       <c r="M34" t="n">
-        <v>2543.6</v>
+        <v>2605.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2607.75</v>
+        <v>2703.55</v>
       </c>
       <c r="O34" t="n">
-        <v>2733.7</v>
+        <v>2704.6</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3367,57 +3361,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2527.9</v>
+        <v>2607.8</v>
       </c>
       <c r="C35" t="n">
-        <v>2674.5</v>
+        <v>2807.8</v>
       </c>
       <c r="D35" t="n">
-        <v>2511.4</v>
+        <v>2591.8</v>
       </c>
       <c r="E35" t="n">
-        <v>2644.4</v>
+        <v>2788.9</v>
       </c>
       <c r="F35" t="n">
-        <v>112.7</v>
+        <v>144.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0445</v>
+        <v>0.0546</v>
       </c>
       <c r="H35" t="n">
-        <v>163.1</v>
+        <v>216</v>
       </c>
       <c r="I35" t="n">
-        <v>2261.8</v>
+        <v>2348.3</v>
       </c>
       <c r="J35" t="n">
-        <v>2408.35</v>
+        <v>2507.02</v>
       </c>
       <c r="K35" t="n">
-        <v>2457.9</v>
+        <v>2562.85</v>
       </c>
       <c r="L35" t="n">
-        <v>2507.45</v>
+        <v>2618.67</v>
       </c>
       <c r="M35" t="n">
-        <v>2605.5</v>
+        <v>2725.95</v>
       </c>
       <c r="N35" t="n">
-        <v>2703.55</v>
+        <v>2833.22</v>
       </c>
       <c r="O35" t="n">
-        <v>2704.6</v>
+        <v>2837.6</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3435,11 +3429,13 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3458,50 +3454,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2607.8</v>
+        <v>2758.7</v>
       </c>
       <c r="C36" t="n">
-        <v>2807.8</v>
+        <v>2828.7</v>
       </c>
       <c r="D36" t="n">
-        <v>2591.8</v>
+        <v>2745.9</v>
       </c>
       <c r="E36" t="n">
-        <v>2788.9</v>
+        <v>2796.1</v>
       </c>
       <c r="F36" t="n">
-        <v>144.5</v>
+        <v>7.2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0026</v>
       </c>
       <c r="H36" t="n">
-        <v>216</v>
+        <v>82.8</v>
       </c>
       <c r="I36" t="n">
-        <v>2348.3</v>
+        <v>2375.8</v>
       </c>
       <c r="J36" t="n">
-        <v>2507.02</v>
+        <v>2617.45</v>
       </c>
       <c r="K36" t="n">
-        <v>2562.85</v>
+        <v>2680.9</v>
       </c>
       <c r="L36" t="n">
-        <v>2618.67</v>
+        <v>2744.35</v>
       </c>
       <c r="M36" t="n">
-        <v>2725.95</v>
+        <v>2896.9</v>
       </c>
       <c r="N36" t="n">
-        <v>2833.22</v>
+        <v>3049.45</v>
       </c>
       <c r="O36" t="n">
-        <v>2837.6</v>
+        <v>3023.8</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3514,18 +3510,14 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3544,50 +3536,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2758.7</v>
+        <v>2792.7</v>
       </c>
       <c r="C37" t="n">
-        <v>2828.7</v>
+        <v>2825</v>
       </c>
       <c r="D37" t="n">
-        <v>2745.9</v>
+        <v>2726.1</v>
       </c>
       <c r="E37" t="n">
-        <v>2796.1</v>
+        <v>2819.3</v>
       </c>
       <c r="F37" t="n">
-        <v>7.2</v>
+        <v>23.2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0083</v>
       </c>
       <c r="H37" t="n">
-        <v>82.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>2375.8</v>
+        <v>2663.1</v>
       </c>
       <c r="J37" t="n">
-        <v>2617.45</v>
+        <v>2717.7</v>
       </c>
       <c r="K37" t="n">
-        <v>2680.9</v>
+        <v>2754.7</v>
       </c>
       <c r="L37" t="n">
-        <v>2744.35</v>
+        <v>2791.7</v>
       </c>
       <c r="M37" t="n">
-        <v>2896.9</v>
+        <v>2837.5</v>
       </c>
       <c r="N37" t="n">
-        <v>3049.45</v>
+        <v>2883.3</v>
       </c>
       <c r="O37" t="n">
-        <v>3023.8</v>
+        <v>2911.5</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3595,16 +3587,20 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3619,57 +3615,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2792.7</v>
+        <v>2825.9</v>
       </c>
       <c r="C38" t="n">
-        <v>2825</v>
+        <v>2918.4</v>
       </c>
       <c r="D38" t="n">
-        <v>2726.1</v>
+        <v>2786.8</v>
       </c>
       <c r="E38" t="n">
-        <v>2819.3</v>
+        <v>2867.6</v>
       </c>
       <c r="F38" t="n">
-        <v>23.2</v>
+        <v>48.3</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0171</v>
       </c>
       <c r="H38" t="n">
-        <v>98.90000000000001</v>
+        <v>131.6</v>
       </c>
       <c r="I38" t="n">
-        <v>2663.1</v>
+        <v>2627.2</v>
       </c>
       <c r="J38" t="n">
-        <v>2717.7</v>
+        <v>2742.28</v>
       </c>
       <c r="K38" t="n">
-        <v>2754.7</v>
+        <v>2769.85</v>
       </c>
       <c r="L38" t="n">
-        <v>2791.7</v>
+        <v>2797.43</v>
       </c>
       <c r="M38" t="n">
-        <v>2837.5</v>
+        <v>2868.75</v>
       </c>
       <c r="N38" t="n">
-        <v>2883.3</v>
+        <v>2940.07</v>
       </c>
       <c r="O38" t="n">
-        <v>2911.5</v>
+        <v>2923.9</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3677,10 +3673,8 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
@@ -3705,57 +3699,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2825.9</v>
+        <v>2863</v>
       </c>
       <c r="C39" t="n">
-        <v>2918.4</v>
+        <v>2896.2</v>
       </c>
       <c r="D39" t="n">
-        <v>2786.8</v>
+        <v>2787.9</v>
       </c>
       <c r="E39" t="n">
-        <v>2867.6</v>
+        <v>2799.6</v>
       </c>
       <c r="F39" t="n">
-        <v>48.3</v>
+        <v>-68</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0171</v>
+        <v>-0.0237</v>
       </c>
       <c r="H39" t="n">
-        <v>131.6</v>
+        <v>108.3</v>
       </c>
       <c r="I39" t="n">
-        <v>2627.2</v>
+        <v>2655.2</v>
       </c>
       <c r="J39" t="n">
-        <v>2742.28</v>
+        <v>2743.5</v>
       </c>
       <c r="K39" t="n">
-        <v>2769.85</v>
+        <v>2801.8</v>
       </c>
       <c r="L39" t="n">
-        <v>2797.43</v>
+        <v>2860.1</v>
       </c>
       <c r="M39" t="n">
-        <v>2868.75</v>
+        <v>2933.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2940.07</v>
+        <v>3006.7</v>
       </c>
       <c r="O39" t="n">
-        <v>2923.9</v>
+        <v>3050</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3763,19 +3757,19 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3789,57 +3783,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2863</v>
+        <v>2788.8</v>
       </c>
       <c r="C40" t="n">
-        <v>2896.2</v>
+        <v>2887</v>
       </c>
       <c r="D40" t="n">
-        <v>2787.9</v>
+        <v>2728.4</v>
       </c>
       <c r="E40" t="n">
-        <v>2799.6</v>
+        <v>2872.1</v>
       </c>
       <c r="F40" t="n">
-        <v>-68</v>
+        <v>72.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0259</v>
       </c>
       <c r="H40" t="n">
-        <v>108.3</v>
+        <v>158.6</v>
       </c>
       <c r="I40" t="n">
-        <v>2655.2</v>
+        <v>2679.6</v>
       </c>
       <c r="J40" t="n">
-        <v>2743.5</v>
+        <v>2670.08</v>
       </c>
       <c r="K40" t="n">
-        <v>2801.8</v>
+        <v>2745.45</v>
       </c>
       <c r="L40" t="n">
-        <v>2860.1</v>
+        <v>2820.83</v>
       </c>
       <c r="M40" t="n">
-        <v>2933.4</v>
+        <v>2853.75</v>
       </c>
       <c r="N40" t="n">
-        <v>3006.7</v>
+        <v>2886.68</v>
       </c>
       <c r="O40" t="n">
-        <v>3050</v>
+        <v>3004.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3849,19 +3843,23 @@
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3880,50 +3878,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2788.8</v>
+        <v>2888</v>
       </c>
       <c r="C41" t="n">
-        <v>2887</v>
+        <v>2952</v>
       </c>
       <c r="D41" t="n">
-        <v>2728.4</v>
+        <v>2887.9</v>
       </c>
       <c r="E41" t="n">
-        <v>2872.1</v>
+        <v>2924.3</v>
       </c>
       <c r="F41" t="n">
-        <v>72.5</v>
+        <v>52.2</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0259</v>
+        <v>0.0182</v>
       </c>
       <c r="H41" t="n">
-        <v>158.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>2679.6</v>
+        <v>2569.8</v>
       </c>
       <c r="J41" t="n">
-        <v>2670.08</v>
+        <v>2745.7</v>
       </c>
       <c r="K41" t="n">
-        <v>2745.45</v>
+        <v>2792.8</v>
       </c>
       <c r="L41" t="n">
-        <v>2820.83</v>
+        <v>2839.9</v>
       </c>
       <c r="M41" t="n">
-        <v>2853.75</v>
+        <v>2951.4</v>
       </c>
       <c r="N41" t="n">
-        <v>2886.68</v>
+        <v>3062.9</v>
       </c>
       <c r="O41" t="n">
-        <v>3004.5</v>
+        <v>3045.6</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3931,10 +3929,8 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
@@ -3943,14 +3939,12 @@
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
@@ -3961,77 +3955,81 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2888</v>
+        <v>2920.5</v>
       </c>
       <c r="C42" t="n">
-        <v>2952</v>
+        <v>2948.3</v>
       </c>
       <c r="D42" t="n">
-        <v>2887.9</v>
+        <v>2812.4</v>
       </c>
       <c r="E42" t="n">
-        <v>2924.3</v>
+        <v>2834.8</v>
       </c>
       <c r="F42" t="n">
-        <v>52.2</v>
+        <v>-89.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0182</v>
+        <v>-0.0306</v>
       </c>
       <c r="H42" t="n">
-        <v>64.09999999999999</v>
+        <v>135.9</v>
       </c>
       <c r="I42" t="n">
-        <v>2569.8</v>
+        <v>2823.8</v>
       </c>
       <c r="J42" t="n">
-        <v>2745.7</v>
+        <v>2862.38</v>
       </c>
       <c r="K42" t="n">
-        <v>2792.8</v>
+        <v>2892.25</v>
       </c>
       <c r="L42" t="n">
-        <v>2839.9</v>
+        <v>2922.12</v>
       </c>
       <c r="M42" t="n">
-        <v>2951.4</v>
+        <v>2956.35</v>
       </c>
       <c r="N42" t="n">
-        <v>3062.9</v>
+        <v>2990.58</v>
       </c>
       <c r="O42" t="n">
-        <v>3045.6</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+        <v>3016.1</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4043,86 +4041,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2920.5</v>
+        <v>2816.3</v>
       </c>
       <c r="C43" t="n">
-        <v>2948.3</v>
+        <v>2974.2</v>
       </c>
       <c r="D43" t="n">
-        <v>2812.4</v>
+        <v>2793.7</v>
       </c>
       <c r="E43" t="n">
-        <v>2834.8</v>
+        <v>2947</v>
       </c>
       <c r="F43" t="n">
-        <v>-89.5</v>
+        <v>112.2</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0306</v>
+        <v>0.0396</v>
       </c>
       <c r="H43" t="n">
-        <v>135.9</v>
+        <v>180.5</v>
       </c>
       <c r="I43" t="n">
-        <v>2823.8</v>
+        <v>2676.5</v>
       </c>
       <c r="J43" t="n">
-        <v>2862.38</v>
+        <v>2676.12</v>
       </c>
       <c r="K43" t="n">
-        <v>2892.25</v>
+        <v>2766.85</v>
       </c>
       <c r="L43" t="n">
-        <v>2922.12</v>
+        <v>2857.58</v>
       </c>
       <c r="M43" t="n">
-        <v>2956.35</v>
+        <v>2902.75</v>
       </c>
       <c r="N43" t="n">
-        <v>2990.58</v>
+        <v>2947.93</v>
       </c>
       <c r="O43" t="n">
-        <v>3016.1</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
+        <v>3084.2</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
@@ -4131,55 +4123,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2816.3</v>
+        <v>2984</v>
       </c>
       <c r="C44" t="n">
-        <v>2974.2</v>
+        <v>3005</v>
       </c>
       <c r="D44" t="n">
-        <v>2793.7</v>
+        <v>2910.3</v>
       </c>
       <c r="E44" t="n">
-        <v>2947</v>
+        <v>2995.6</v>
       </c>
       <c r="F44" t="n">
-        <v>112.2</v>
+        <v>48.6</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.0165</v>
       </c>
       <c r="H44" t="n">
-        <v>180.5</v>
+        <v>94.7</v>
       </c>
       <c r="I44" t="n">
-        <v>2676.5</v>
+        <v>2613.2</v>
       </c>
       <c r="J44" t="n">
-        <v>2676.12</v>
+        <v>2798.03</v>
       </c>
       <c r="K44" t="n">
-        <v>2766.85</v>
+        <v>2856.75</v>
       </c>
       <c r="L44" t="n">
-        <v>2857.58</v>
+        <v>2915.47</v>
       </c>
       <c r="M44" t="n">
-        <v>2902.75</v>
+        <v>3037.25</v>
       </c>
       <c r="N44" t="n">
-        <v>2947.93</v>
+        <v>3159.03</v>
       </c>
       <c r="O44" t="n">
-        <v>3084.2</v>
+        <v>3154.7</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4197,14 +4193,12 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4215,57 +4209,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2984</v>
+        <v>2989.9</v>
       </c>
       <c r="C45" t="n">
-        <v>3005</v>
+        <v>3062.4</v>
       </c>
       <c r="D45" t="n">
-        <v>2910.3</v>
+        <v>2965.2</v>
       </c>
       <c r="E45" t="n">
-        <v>2995.6</v>
+        <v>3022.6</v>
       </c>
       <c r="F45" t="n">
-        <v>48.6</v>
+        <v>27</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>94.7</v>
+        <v>97.2</v>
       </c>
       <c r="I45" t="n">
-        <v>2613.2</v>
+        <v>2815.6</v>
       </c>
       <c r="J45" t="n">
-        <v>2798.03</v>
+        <v>2919.88</v>
       </c>
       <c r="K45" t="n">
-        <v>2856.75</v>
+        <v>2948.25</v>
       </c>
       <c r="L45" t="n">
-        <v>2915.47</v>
+        <v>2976.63</v>
       </c>
       <c r="M45" t="n">
-        <v>3037.25</v>
+        <v>3042.95</v>
       </c>
       <c r="N45" t="n">
-        <v>3159.03</v>
+        <v>3109.28</v>
       </c>
       <c r="O45" t="n">
-        <v>3154.7</v>
+        <v>3099.7</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4306,50 +4300,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2989.9</v>
+        <v>3020.9</v>
       </c>
       <c r="C46" t="n">
-        <v>3062.4</v>
+        <v>3068.4</v>
       </c>
       <c r="D46" t="n">
-        <v>2965.2</v>
+        <v>2987.8</v>
       </c>
       <c r="E46" t="n">
-        <v>3022.6</v>
+        <v>3023.5</v>
       </c>
       <c r="F46" t="n">
-        <v>27</v>
+        <v>0.9</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0003</v>
       </c>
       <c r="H46" t="n">
-        <v>97.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>2815.6</v>
+        <v>2868</v>
       </c>
       <c r="J46" t="n">
-        <v>2919.88</v>
+        <v>2929.8</v>
       </c>
       <c r="K46" t="n">
-        <v>2948.25</v>
+        <v>2974</v>
       </c>
       <c r="L46" t="n">
-        <v>2976.63</v>
+        <v>3018.2</v>
       </c>
       <c r="M46" t="n">
-        <v>3042.95</v>
+        <v>3071.2</v>
       </c>
       <c r="N46" t="n">
-        <v>3109.28</v>
+        <v>3124.2</v>
       </c>
       <c r="O46" t="n">
-        <v>3099.7</v>
+        <v>3159.6</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4362,13 +4356,11 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4390,50 +4382,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3020.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C47" t="n">
-        <v>3068.4</v>
+        <v>3042.6</v>
       </c>
       <c r="D47" t="n">
-        <v>2987.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E47" t="n">
-        <v>3023.5</v>
+        <v>2994</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9</v>
+        <v>-29.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0098</v>
       </c>
       <c r="H47" t="n">
-        <v>80.59999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="I47" t="n">
-        <v>2868</v>
+        <v>2907.2</v>
       </c>
       <c r="J47" t="n">
-        <v>2929.8</v>
+        <v>2940.6</v>
       </c>
       <c r="K47" t="n">
-        <v>2974</v>
+        <v>2983.2</v>
       </c>
       <c r="L47" t="n">
-        <v>3018.2</v>
+        <v>3025.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3071.2</v>
+        <v>3063.8</v>
       </c>
       <c r="N47" t="n">
-        <v>3124.2</v>
+        <v>3101.8</v>
       </c>
       <c r="O47" t="n">
-        <v>3159.6</v>
+        <v>3149</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4441,12 +4433,14 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4463,59 +4457,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3019.7</v>
+        <v>2984.7</v>
       </c>
       <c r="C48" t="n">
-        <v>3042.6</v>
+        <v>3029.8</v>
       </c>
       <c r="D48" t="n">
-        <v>2943.4</v>
+        <v>2949.3</v>
       </c>
       <c r="E48" t="n">
-        <v>2994</v>
+        <v>2973.5</v>
       </c>
       <c r="F48" t="n">
-        <v>-29.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0068</v>
       </c>
       <c r="H48" t="n">
-        <v>99.2</v>
+        <v>80.5</v>
       </c>
       <c r="I48" t="n">
-        <v>2907.2</v>
+        <v>2844.2</v>
       </c>
       <c r="J48" t="n">
-        <v>2940.6</v>
+        <v>2895.3</v>
       </c>
       <c r="K48" t="n">
-        <v>2983.2</v>
+        <v>2944.4</v>
       </c>
       <c r="L48" t="n">
-        <v>3025.8</v>
+        <v>2993.5</v>
       </c>
       <c r="M48" t="n">
-        <v>3063.8</v>
+        <v>3043.6</v>
       </c>
       <c r="N48" t="n">
-        <v>3101.8</v>
+        <v>3093.7</v>
       </c>
       <c r="O48" t="n">
-        <v>3149</v>
+        <v>3141.8</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4523,14 +4513,12 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4547,55 +4535,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2984.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C49" t="n">
-        <v>3029.8</v>
+        <v>2999.8</v>
       </c>
       <c r="D49" t="n">
-        <v>2949.3</v>
+        <v>2932.1</v>
       </c>
       <c r="E49" t="n">
-        <v>2973.5</v>
+        <v>2941.3</v>
       </c>
       <c r="F49" t="n">
-        <v>-20.5</v>
+        <v>-32.2</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0068</v>
+        <v>-0.0108</v>
       </c>
       <c r="H49" t="n">
-        <v>80.5</v>
+        <v>67.7</v>
       </c>
       <c r="I49" t="n">
-        <v>2844.2</v>
+        <v>2868.8</v>
       </c>
       <c r="J49" t="n">
-        <v>2895.3</v>
+        <v>2884.97</v>
       </c>
       <c r="K49" t="n">
-        <v>2944.4</v>
+        <v>2933.25</v>
       </c>
       <c r="L49" t="n">
-        <v>2993.5</v>
+        <v>2981.53</v>
       </c>
       <c r="M49" t="n">
-        <v>3043.6</v>
+        <v>3013.75</v>
       </c>
       <c r="N49" t="n">
-        <v>3093.7</v>
+        <v>3045.97</v>
       </c>
       <c r="O49" t="n">
-        <v>3141.8</v>
+        <v>3110.3</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4603,12 +4595,14 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4625,59 +4619,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2964.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C50" t="n">
-        <v>2999.8</v>
+        <v>2985.9</v>
       </c>
       <c r="D50" t="n">
-        <v>2932.1</v>
+        <v>2902.3</v>
       </c>
       <c r="E50" t="n">
-        <v>2941.3</v>
+        <v>2938</v>
       </c>
       <c r="F50" t="n">
-        <v>-32.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0011</v>
       </c>
       <c r="H50" t="n">
-        <v>67.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>2868.8</v>
+        <v>2864.4</v>
       </c>
       <c r="J50" t="n">
-        <v>2884.97</v>
+        <v>2861.28</v>
       </c>
       <c r="K50" t="n">
-        <v>2933.25</v>
+        <v>2907.45</v>
       </c>
       <c r="L50" t="n">
-        <v>2981.53</v>
+        <v>2953.63</v>
       </c>
       <c r="M50" t="n">
-        <v>3013.75</v>
+        <v>2975.15</v>
       </c>
       <c r="N50" t="n">
-        <v>3045.97</v>
+        <v>2996.67</v>
       </c>
       <c r="O50" t="n">
-        <v>3110.3</v>
+        <v>3067.5</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4687,16 +4677,18 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4714,50 +4706,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2955.5</v>
+        <v>2950</v>
       </c>
       <c r="C51" t="n">
-        <v>2985.9</v>
+        <v>3058.3</v>
       </c>
       <c r="D51" t="n">
-        <v>2902.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E51" t="n">
-        <v>2938</v>
+        <v>3041.6</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.3</v>
+        <v>103.6</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0353</v>
       </c>
       <c r="H51" t="n">
-        <v>83.59999999999999</v>
+        <v>109.9</v>
       </c>
       <c r="I51" t="n">
-        <v>2864.4</v>
+        <v>2818.7</v>
       </c>
       <c r="J51" t="n">
-        <v>2861.28</v>
+        <v>2851.35</v>
       </c>
       <c r="K51" t="n">
-        <v>2907.45</v>
+        <v>2896.2</v>
       </c>
       <c r="L51" t="n">
-        <v>2953.63</v>
+        <v>2941.05</v>
       </c>
       <c r="M51" t="n">
-        <v>2975.15</v>
+        <v>2979.8</v>
       </c>
       <c r="N51" t="n">
-        <v>2996.67</v>
+        <v>3018.55</v>
       </c>
       <c r="O51" t="n">
-        <v>3067.5</v>
+        <v>3069.5</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4765,30 +4757,30 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W51" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr"/>
@@ -4796,50 +4788,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2950</v>
+        <v>3038.9</v>
       </c>
       <c r="C52" t="n">
-        <v>3058.3</v>
+        <v>3076.3</v>
       </c>
       <c r="D52" t="n">
-        <v>2948.4</v>
+        <v>3016</v>
       </c>
       <c r="E52" t="n">
-        <v>3041.6</v>
+        <v>3074.9</v>
       </c>
       <c r="F52" t="n">
-        <v>103.6</v>
+        <v>33.3</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.0109</v>
       </c>
       <c r="H52" t="n">
-        <v>109.9</v>
+        <v>60.3</v>
       </c>
       <c r="I52" t="n">
-        <v>2818.7</v>
+        <v>2838.5</v>
       </c>
       <c r="J52" t="n">
-        <v>2851.35</v>
+        <v>2950.83</v>
       </c>
       <c r="K52" t="n">
-        <v>2896.2</v>
+        <v>2986.65</v>
       </c>
       <c r="L52" t="n">
-        <v>2941.05</v>
+        <v>3022.48</v>
       </c>
       <c r="M52" t="n">
-        <v>2979.8</v>
+        <v>3096.55</v>
       </c>
       <c r="N52" t="n">
-        <v>3018.55</v>
+        <v>3170.63</v>
       </c>
       <c r="O52" t="n">
-        <v>3069.5</v>
+        <v>3168.2</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4857,13 +4849,11 @@
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4878,144 +4868,148 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3038.9</v>
+        <v>3073.5</v>
       </c>
       <c r="C53" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D53" t="n">
-        <v>3016</v>
+        <v>2993.2</v>
       </c>
       <c r="E53" t="n">
-        <v>3074.9</v>
+        <v>3022.1</v>
       </c>
       <c r="F53" t="n">
-        <v>33.3</v>
+        <v>-52.8</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.0172</v>
       </c>
       <c r="H53" t="n">
-        <v>60.3</v>
+        <v>86.7</v>
       </c>
       <c r="I53" t="n">
-        <v>2838.5</v>
+        <v>2955.7</v>
       </c>
       <c r="J53" t="n">
-        <v>2950.83</v>
+        <v>3028.97</v>
       </c>
       <c r="K53" t="n">
-        <v>2986.65</v>
+        <v>3044.75</v>
       </c>
       <c r="L53" t="n">
-        <v>3022.48</v>
+        <v>3060.52</v>
       </c>
       <c r="M53" t="n">
-        <v>3096.55</v>
+        <v>3105.05</v>
       </c>
       <c r="N53" t="n">
-        <v>3170.63</v>
+        <v>3149.57</v>
       </c>
       <c r="O53" t="n">
-        <v>3168.2</v>
+        <v>3136.6</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="Q53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3073.5</v>
+        <v>3023</v>
       </c>
       <c r="C54" t="n">
-        <v>3079.9</v>
+        <v>3028.9</v>
       </c>
       <c r="D54" t="n">
-        <v>2993.2</v>
+        <v>2976.6</v>
       </c>
       <c r="E54" t="n">
-        <v>3022.1</v>
+        <v>2977.5</v>
       </c>
       <c r="F54" t="n">
-        <v>-52.8</v>
+        <v>-44.6</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0172</v>
+        <v>-0.0148</v>
       </c>
       <c r="H54" t="n">
-        <v>86.7</v>
+        <v>52.3</v>
       </c>
       <c r="I54" t="n">
-        <v>2955.7</v>
+        <v>2906.5</v>
       </c>
       <c r="J54" t="n">
-        <v>3028.97</v>
+        <v>2928.18</v>
       </c>
       <c r="K54" t="n">
-        <v>3044.75</v>
+        <v>2978.75</v>
       </c>
       <c r="L54" t="n">
-        <v>3060.52</v>
+        <v>3029.33</v>
       </c>
       <c r="M54" t="n">
-        <v>3105.05</v>
+        <v>3065.45</v>
       </c>
       <c r="N54" t="n">
-        <v>3149.57</v>
+        <v>3101.58</v>
       </c>
       <c r="O54" t="n">
-        <v>3136.6</v>
+        <v>3166.6</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5035,74 +5029,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3023</v>
+        <v>2971</v>
       </c>
       <c r="C55" t="n">
-        <v>3028.9</v>
+        <v>2983.3</v>
       </c>
       <c r="D55" t="n">
+        <v>2914.5</v>
+      </c>
+      <c r="E55" t="n">
         <v>2976.6</v>
       </c>
-      <c r="E55" t="n">
-        <v>2977.5</v>
-      </c>
       <c r="F55" t="n">
-        <v>-44.6</v>
+        <v>-0.9</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0148</v>
+        <v>-0.0003</v>
       </c>
       <c r="H55" t="n">
-        <v>52.3</v>
+        <v>68.8</v>
       </c>
       <c r="I55" t="n">
-        <v>2906.5</v>
+        <v>2924.3</v>
       </c>
       <c r="J55" t="n">
-        <v>2928.18</v>
+        <v>2912.58</v>
       </c>
       <c r="K55" t="n">
-        <v>2978.75</v>
+        <v>2951.35</v>
       </c>
       <c r="L55" t="n">
-        <v>3029.33</v>
+        <v>2990.12</v>
       </c>
       <c r="M55" t="n">
-        <v>3065.45</v>
+        <v>3003.65</v>
       </c>
       <c r="N55" t="n">
-        <v>3101.58</v>
+        <v>3017.17</v>
       </c>
       <c r="O55" t="n">
-        <v>3166.6</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
+        <v>3081.2</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5124,67 +5116,67 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2971</v>
+        <v>2974.7</v>
       </c>
       <c r="C56" t="n">
-        <v>2983.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D56" t="n">
-        <v>2914.5</v>
+        <v>2887.6</v>
       </c>
       <c r="E56" t="n">
-        <v>2976.6</v>
+        <v>2904.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.9</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0242</v>
       </c>
       <c r="H56" t="n">
-        <v>68.8</v>
+        <v>90.3</v>
       </c>
       <c r="I56" t="n">
-        <v>2924.3</v>
+        <v>2845.7</v>
       </c>
       <c r="J56" t="n">
-        <v>2912.58</v>
+        <v>2921.65</v>
       </c>
       <c r="K56" t="n">
-        <v>2951.35</v>
+        <v>2942.2</v>
       </c>
       <c r="L56" t="n">
-        <v>2990.12</v>
+        <v>2962.75</v>
       </c>
       <c r="M56" t="n">
-        <v>3003.65</v>
+        <v>3011</v>
       </c>
       <c r="N56" t="n">
-        <v>3017.17</v>
+        <v>3059.25</v>
       </c>
       <c r="O56" t="n">
-        <v>3081.2</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
+        <v>3052.1</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5206,64 +5198,62 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2974.7</v>
+        <v>2892.7</v>
       </c>
       <c r="C57" t="n">
-        <v>2977.9</v>
+        <v>2913.5</v>
       </c>
       <c r="D57" t="n">
-        <v>2887.6</v>
+        <v>2831.9</v>
       </c>
       <c r="E57" t="n">
-        <v>2904.5</v>
+        <v>2881.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-72.09999999999999</v>
+        <v>-23</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0242</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>90.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>2845.7</v>
+        <v>2797.3</v>
       </c>
       <c r="J57" t="n">
-        <v>2921.65</v>
+        <v>2800.08</v>
       </c>
       <c r="K57" t="n">
-        <v>2942.2</v>
+        <v>2859.35</v>
       </c>
       <c r="L57" t="n">
-        <v>2962.75</v>
+        <v>2918.62</v>
       </c>
       <c r="M57" t="n">
-        <v>3011</v>
+        <v>2949.65</v>
       </c>
       <c r="N57" t="n">
-        <v>3059.25</v>
+        <v>2980.67</v>
       </c>
       <c r="O57" t="n">
-        <v>3052.1</v>
+        <v>3068.2</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5284,86 +5274,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2892.7</v>
-      </c>
-      <c r="C58" t="n">
-        <v>2913.5</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2831.9</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2890.9</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-13.6</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0047</v>
-      </c>
-      <c r="H58" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2797.3</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2800.08</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2859.35</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2918.62</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2949.65</v>
-      </c>
-      <c r="N58" t="n">
-        <v>2980.67</v>
-      </c>
-      <c r="O58" t="n">
-        <v>3068.2</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5211,13 +5211,13 @@
         <v>2831.9</v>
       </c>
       <c r="E57" t="n">
-        <v>2881.5</v>
+        <v>2873.23</v>
       </c>
       <c r="F57" t="n">
-        <v>-23</v>
+        <v>-31.27</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0108</v>
       </c>
       <c r="H57" t="n">
         <v>81.59999999999999</v>
@@ -5274,6 +5274,90 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2897.8</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2899.1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2897.8</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2898.8</v>
+      </c>
+      <c r="F58" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2750.3</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2791.89</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2832.43</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2872.96</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2914.03</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2955.1</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2995.1</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5282,25 +5282,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2897.8</v>
+        <v>2879.5</v>
       </c>
       <c r="C58" t="n">
-        <v>2899.1</v>
+        <v>2925.6</v>
       </c>
       <c r="D58" t="n">
-        <v>2897.8</v>
+        <v>2876.6</v>
       </c>
       <c r="E58" t="n">
-        <v>2898.8</v>
+        <v>2924</v>
       </c>
       <c r="F58" t="n">
-        <v>25.57</v>
+        <v>50.77</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0089</v>
+        <v>0.0177</v>
       </c>
       <c r="H58" t="n">
-        <v>1.3</v>
+        <v>49</v>
       </c>
       <c r="I58" t="n">
         <v>2750.3</v>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5285,22 +5285,22 @@
         <v>2879.5</v>
       </c>
       <c r="C58" t="n">
-        <v>2925.6</v>
+        <v>2931.2</v>
       </c>
       <c r="D58" t="n">
         <v>2876.6</v>
       </c>
       <c r="E58" t="n">
-        <v>2924</v>
+        <v>2904.8</v>
       </c>
       <c r="F58" t="n">
-        <v>50.77</v>
+        <v>31.57</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0177</v>
+        <v>0.011</v>
       </c>
       <c r="H58" t="n">
-        <v>49</v>
+        <v>54.6</v>
       </c>
       <c r="I58" t="n">
         <v>2750.3</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5285,22 +5285,22 @@
         <v>2879.5</v>
       </c>
       <c r="C58" t="n">
-        <v>2931.2</v>
+        <v>2914.3</v>
       </c>
       <c r="D58" t="n">
         <v>2876.6</v>
       </c>
       <c r="E58" t="n">
-        <v>2904.8</v>
+        <v>2913</v>
       </c>
       <c r="F58" t="n">
-        <v>31.57</v>
+        <v>39.77</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.011</v>
+        <v>0.0138</v>
       </c>
       <c r="H58" t="n">
-        <v>54.6</v>
+        <v>37.7</v>
       </c>
       <c r="I58" t="n">
         <v>2750.3</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5285,22 +5285,22 @@
         <v>2879.5</v>
       </c>
       <c r="C58" t="n">
-        <v>2914.3</v>
+        <v>2915.2</v>
       </c>
       <c r="D58" t="n">
         <v>2876.6</v>
       </c>
       <c r="E58" t="n">
-        <v>2913</v>
+        <v>2910.5</v>
       </c>
       <c r="F58" t="n">
-        <v>39.77</v>
+        <v>37.27</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.013</v>
       </c>
       <c r="H58" t="n">
-        <v>37.7</v>
+        <v>38.6</v>
       </c>
       <c r="I58" t="n">
         <v>2750.3</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5291,13 +5291,13 @@
         <v>2876.6</v>
       </c>
       <c r="E58" t="n">
-        <v>2910.5</v>
+        <v>2910.1</v>
       </c>
       <c r="F58" t="n">
-        <v>37.27</v>
+        <v>36.87</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0128</v>
       </c>
       <c r="H58" t="n">
         <v>38.6</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5291,13 +5291,13 @@
         <v>2876.6</v>
       </c>
       <c r="E58" t="n">
-        <v>2910.1</v>
+        <v>2911.4</v>
       </c>
       <c r="F58" t="n">
-        <v>36.87</v>
+        <v>38.17</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0133</v>
       </c>
       <c r="H58" t="n">
         <v>38.6</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5291,13 +5291,13 @@
         <v>2876.6</v>
       </c>
       <c r="E58" t="n">
-        <v>2911.4</v>
+        <v>2912.2</v>
       </c>
       <c r="F58" t="n">
-        <v>38.17</v>
+        <v>38.97</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0136</v>
       </c>
       <c r="H58" t="n">
         <v>38.6</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5285,22 +5285,22 @@
         <v>2879.5</v>
       </c>
       <c r="C58" t="n">
-        <v>2915.2</v>
+        <v>2931.2</v>
       </c>
       <c r="D58" t="n">
         <v>2876.6</v>
       </c>
       <c r="E58" t="n">
-        <v>2912.2</v>
+        <v>2897.2</v>
       </c>
       <c r="F58" t="n">
-        <v>38.97</v>
+        <v>23.97</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0083</v>
       </c>
       <c r="H58" t="n">
-        <v>38.6</v>
+        <v>54.6</v>
       </c>
       <c r="I58" t="n">
         <v>2750.3</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5288,19 +5288,19 @@
         <v>2931.2</v>
       </c>
       <c r="D58" t="n">
-        <v>2876.6</v>
+        <v>2859.8</v>
       </c>
       <c r="E58" t="n">
-        <v>2897.2</v>
+        <v>2861</v>
       </c>
       <c r="F58" t="n">
-        <v>23.97</v>
+        <v>-12.23</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H58" t="n">
-        <v>54.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I58" t="n">
         <v>2750.3</v>
@@ -5332,14 +5332,14 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>67.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2140.7</v>
+        <v>2141.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2278.08</v>
+        <v>2278.3</v>
       </c>
       <c r="K2" t="n">
-        <v>2310.35</v>
+        <v>2310.5</v>
       </c>
       <c r="L2" t="n">
-        <v>2342.62</v>
+        <v>2342.7</v>
       </c>
       <c r="M2" t="n">
-        <v>2427.45</v>
+        <v>2427.3</v>
       </c>
       <c r="N2" t="n">
-        <v>2512.27</v>
+        <v>2511.9</v>
       </c>
       <c r="O2" t="n">
-        <v>2492</v>
+        <v>2491.7</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5288,19 +5288,19 @@
         <v>2931.2</v>
       </c>
       <c r="D58" t="n">
-        <v>2859.8</v>
+        <v>2853.2</v>
       </c>
       <c r="E58" t="n">
-        <v>2861</v>
+        <v>2853.2</v>
       </c>
       <c r="F58" t="n">
-        <v>-12.23</v>
+        <v>-20.03</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.007</v>
       </c>
       <c r="H58" t="n">
-        <v>71.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="I58" t="n">
         <v>2750.3</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2369.3</v>
+        <v>2373</v>
       </c>
       <c r="C2" t="n">
-        <v>2398.6</v>
+        <v>2413.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2330.8</v>
+        <v>2326.1</v>
       </c>
       <c r="E2" t="n">
-        <v>2369.8</v>
+        <v>2393.5</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9</v>
+        <v>23.7</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.01</v>
       </c>
       <c r="H2" t="n">
-        <v>67.8</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>2141.3</v>
+        <v>2263</v>
       </c>
       <c r="J2" t="n">
-        <v>2278.3</v>
+        <v>2304.55</v>
       </c>
       <c r="K2" t="n">
-        <v>2310.5</v>
+        <v>2335.9</v>
       </c>
       <c r="L2" t="n">
-        <v>2342.7</v>
+        <v>2367.25</v>
       </c>
       <c r="M2" t="n">
-        <v>2427.3</v>
+        <v>2403.7</v>
       </c>
       <c r="N2" t="n">
-        <v>2511.9</v>
+        <v>2440.15</v>
       </c>
       <c r="O2" t="n">
-        <v>2491.7</v>
+        <v>2466.4</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,16 +685,20 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -707,55 +711,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2373</v>
+        <v>2391.8</v>
       </c>
       <c r="C3" t="n">
-        <v>2413.5</v>
+        <v>2424.7</v>
       </c>
       <c r="D3" t="n">
-        <v>2326.1</v>
+        <v>2369.9</v>
       </c>
       <c r="E3" t="n">
-        <v>2393.5</v>
+        <v>2397.9</v>
       </c>
       <c r="F3" t="n">
-        <v>23.7</v>
+        <v>4.4</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0018</v>
       </c>
       <c r="H3" t="n">
-        <v>87.40000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="I3" t="n">
-        <v>2263</v>
+        <v>2238.7</v>
       </c>
       <c r="J3" t="n">
-        <v>2304.55</v>
+        <v>2317.95</v>
       </c>
       <c r="K3" t="n">
-        <v>2335.9</v>
+        <v>2349.8</v>
       </c>
       <c r="L3" t="n">
-        <v>2367.25</v>
+        <v>2381.65</v>
       </c>
       <c r="M3" t="n">
-        <v>2403.7</v>
+        <v>2437.2</v>
       </c>
       <c r="N3" t="n">
-        <v>2440.15</v>
+        <v>2492.75</v>
       </c>
       <c r="O3" t="n">
-        <v>2466.4</v>
+        <v>2500.9</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -763,20 +771,16 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -789,59 +793,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2391.8</v>
+        <v>2398</v>
       </c>
       <c r="C4" t="n">
-        <v>2424.7</v>
+        <v>2485.1</v>
       </c>
       <c r="D4" t="n">
-        <v>2369.9</v>
+        <v>2388.3</v>
       </c>
       <c r="E4" t="n">
-        <v>2397.9</v>
+        <v>2472.04</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4</v>
+        <v>74.14</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0309</v>
       </c>
       <c r="H4" t="n">
-        <v>54.8</v>
+        <v>96.8</v>
       </c>
       <c r="I4" t="n">
-        <v>2238.7</v>
+        <v>2315.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2317.95</v>
+        <v>2343.4</v>
       </c>
       <c r="K4" t="n">
-        <v>2349.8</v>
+        <v>2370.5</v>
       </c>
       <c r="L4" t="n">
-        <v>2381.65</v>
+        <v>2397.6</v>
       </c>
       <c r="M4" t="n">
-        <v>2437.2</v>
+        <v>2425.3</v>
       </c>
       <c r="N4" t="n">
-        <v>2492.75</v>
+        <v>2453</v>
       </c>
       <c r="O4" t="n">
-        <v>2500.9</v>
+        <v>2479.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -854,17 +854,23 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -876,50 +882,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2398</v>
+        <v>2469.5</v>
       </c>
       <c r="C5" t="n">
-        <v>2485.1</v>
+        <v>2510.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2388.3</v>
+        <v>2412.1</v>
       </c>
       <c r="E5" t="n">
-        <v>2472.04</v>
+        <v>2450.4</v>
       </c>
       <c r="F5" t="n">
-        <v>74.14</v>
+        <v>-21.64</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0309</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>96.8</v>
+        <v>98.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2315.1</v>
+        <v>2291.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2343.4</v>
+        <v>2392.91</v>
       </c>
       <c r="K5" t="n">
-        <v>2370.5</v>
+        <v>2423.64</v>
       </c>
       <c r="L5" t="n">
-        <v>2397.6</v>
+        <v>2454.37</v>
       </c>
       <c r="M5" t="n">
-        <v>2425.3</v>
+        <v>2520.44</v>
       </c>
       <c r="N5" t="n">
-        <v>2453</v>
+        <v>2586.51</v>
       </c>
       <c r="O5" t="n">
-        <v>2479.5</v>
+        <v>2581.9</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -927,83 +933,83 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2469.5</v>
+        <v>2449.2</v>
       </c>
       <c r="C6" t="n">
-        <v>2510.3</v>
+        <v>2515</v>
       </c>
       <c r="D6" t="n">
-        <v>2412.1</v>
+        <v>2424.7</v>
       </c>
       <c r="E6" t="n">
-        <v>2450.4</v>
+        <v>2492.1</v>
       </c>
       <c r="F6" t="n">
-        <v>-21.64</v>
+        <v>41.7</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="H6" t="n">
-        <v>98.2</v>
+        <v>90.3</v>
       </c>
       <c r="I6" t="n">
-        <v>2291.5</v>
+        <v>2313.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2392.91</v>
+        <v>2346.8</v>
       </c>
       <c r="K6" t="n">
-        <v>2423.64</v>
+        <v>2401.3</v>
       </c>
       <c r="L6" t="n">
-        <v>2454.37</v>
+        <v>2455.8</v>
       </c>
       <c r="M6" t="n">
-        <v>2520.44</v>
+        <v>2499.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2586.51</v>
+        <v>2543.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2581.9</v>
+        <v>2608.5</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1011,18 +1017,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1035,164 +1041,166 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2449.2</v>
+        <v>2491.9</v>
       </c>
       <c r="C7" t="n">
-        <v>2515</v>
+        <v>2518.5</v>
       </c>
       <c r="D7" t="n">
-        <v>2424.7</v>
+        <v>2381.8</v>
       </c>
       <c r="E7" t="n">
-        <v>2492.1</v>
+        <v>2408.5</v>
       </c>
       <c r="F7" t="n">
-        <v>41.7</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.017</v>
+        <v>-0.0335</v>
       </c>
       <c r="H7" t="n">
-        <v>90.3</v>
+        <v>136.7</v>
       </c>
       <c r="I7" t="n">
-        <v>2313.9</v>
+        <v>2334.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2346.8</v>
+        <v>2412.93</v>
       </c>
       <c r="K7" t="n">
-        <v>2401.3</v>
+        <v>2446.95</v>
       </c>
       <c r="L7" t="n">
-        <v>2455.8</v>
+        <v>2480.98</v>
       </c>
       <c r="M7" t="n">
-        <v>2499.5</v>
+        <v>2537.25</v>
       </c>
       <c r="N7" t="n">
-        <v>2543.2</v>
+        <v>2593.53</v>
       </c>
       <c r="O7" t="n">
-        <v>2608.5</v>
+        <v>2605.3</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2491.9</v>
+        <v>2421.6</v>
       </c>
       <c r="C8" t="n">
-        <v>2518.5</v>
+        <v>2559.9</v>
       </c>
       <c r="D8" t="n">
-        <v>2381.8</v>
+        <v>2421.6</v>
       </c>
       <c r="E8" t="n">
-        <v>2408.5</v>
+        <v>2464.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-83.59999999999999</v>
+        <v>55.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0335</v>
+        <v>0.0232</v>
       </c>
       <c r="H8" t="n">
-        <v>136.7</v>
+        <v>138.3</v>
       </c>
       <c r="I8" t="n">
-        <v>2334.4</v>
+        <v>2245.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2412.93</v>
+        <v>2250.98</v>
       </c>
       <c r="K8" t="n">
-        <v>2446.95</v>
+        <v>2340.15</v>
       </c>
       <c r="L8" t="n">
-        <v>2480.98</v>
+        <v>2429.33</v>
       </c>
       <c r="M8" t="n">
-        <v>2537.25</v>
+        <v>2476.85</v>
       </c>
       <c r="N8" t="n">
-        <v>2593.53</v>
+        <v>2524.37</v>
       </c>
       <c r="O8" t="n">
-        <v>2605.3</v>
+        <v>2655.2</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1203,57 +1211,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2421.6</v>
+        <v>2473.7</v>
       </c>
       <c r="C9" t="n">
-        <v>2559.9</v>
+        <v>2544</v>
       </c>
       <c r="D9" t="n">
-        <v>2421.6</v>
+        <v>2436.9</v>
       </c>
       <c r="E9" t="n">
-        <v>2464.4</v>
+        <v>2523.7</v>
       </c>
       <c r="F9" t="n">
-        <v>55.9</v>
+        <v>59.3</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0232</v>
+        <v>0.0241</v>
       </c>
       <c r="H9" t="n">
-        <v>138.3</v>
+        <v>107.1</v>
       </c>
       <c r="I9" t="n">
-        <v>2245.1</v>
+        <v>2283.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2250.98</v>
+        <v>2312.93</v>
       </c>
       <c r="K9" t="n">
-        <v>2340.15</v>
+        <v>2395.25</v>
       </c>
       <c r="L9" t="n">
-        <v>2429.33</v>
+        <v>2477.57</v>
       </c>
       <c r="M9" t="n">
-        <v>2476.85</v>
+        <v>2533.55</v>
       </c>
       <c r="N9" t="n">
-        <v>2524.37</v>
+        <v>2589.52</v>
       </c>
       <c r="O9" t="n">
-        <v>2655.2</v>
+        <v>2698.2</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1274,10 +1282,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1289,57 +1295,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2473.7</v>
+        <v>2551.8</v>
       </c>
       <c r="C10" t="n">
-        <v>2544</v>
+        <v>2566.5</v>
       </c>
       <c r="D10" t="n">
-        <v>2436.9</v>
+        <v>2463</v>
       </c>
       <c r="E10" t="n">
-        <v>2523.7</v>
+        <v>2489.9</v>
       </c>
       <c r="F10" t="n">
-        <v>59.3</v>
+        <v>-33.8</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0241</v>
+        <v>-0.0134</v>
       </c>
       <c r="H10" t="n">
-        <v>107.1</v>
+        <v>103.5</v>
       </c>
       <c r="I10" t="n">
-        <v>2283.3</v>
+        <v>2329.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2312.93</v>
+        <v>2433.22</v>
       </c>
       <c r="K10" t="n">
-        <v>2395.25</v>
+        <v>2470.15</v>
       </c>
       <c r="L10" t="n">
-        <v>2477.57</v>
+        <v>2507.07</v>
       </c>
       <c r="M10" t="n">
-        <v>2533.55</v>
+        <v>2577.25</v>
       </c>
       <c r="N10" t="n">
-        <v>2589.52</v>
+        <v>2647.43</v>
       </c>
       <c r="O10" t="n">
-        <v>2698.2</v>
+        <v>2651.1</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1347,18 +1353,18 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1380,50 +1386,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2551.8</v>
+        <v>2489.1</v>
       </c>
       <c r="C11" t="n">
-        <v>2566.5</v>
+        <v>2500.4</v>
       </c>
       <c r="D11" t="n">
-        <v>2463</v>
+        <v>2386.6</v>
       </c>
       <c r="E11" t="n">
-        <v>2489.9</v>
+        <v>2440.6</v>
       </c>
       <c r="F11" t="n">
-        <v>-33.8</v>
+        <v>-49.3</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0134</v>
+        <v>-0.0198</v>
       </c>
       <c r="H11" t="n">
-        <v>103.5</v>
+        <v>113.8</v>
       </c>
       <c r="I11" t="n">
-        <v>2329.8</v>
+        <v>2359.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2433.22</v>
+        <v>2373.97</v>
       </c>
       <c r="K11" t="n">
-        <v>2470.15</v>
+        <v>2438.15</v>
       </c>
       <c r="L11" t="n">
-        <v>2507.07</v>
+        <v>2502.32</v>
       </c>
       <c r="M11" t="n">
-        <v>2577.25</v>
+        <v>2541.65</v>
       </c>
       <c r="N11" t="n">
-        <v>2647.43</v>
+        <v>2580.97</v>
       </c>
       <c r="O11" t="n">
-        <v>2651.1</v>
+        <v>2670</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1433,12 +1439,12 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1455,59 +1461,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2489.1</v>
+        <v>2455.2</v>
       </c>
       <c r="C12" t="n">
-        <v>2500.4</v>
+        <v>2487.6</v>
       </c>
       <c r="D12" t="n">
-        <v>2386.6</v>
+        <v>2353.8</v>
       </c>
       <c r="E12" t="n">
-        <v>2440.6</v>
+        <v>2396</v>
       </c>
       <c r="F12" t="n">
-        <v>-49.3</v>
+        <v>-44.6</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0198</v>
+        <v>-0.0183</v>
       </c>
       <c r="H12" t="n">
-        <v>113.8</v>
+        <v>133.8</v>
       </c>
       <c r="I12" t="n">
-        <v>2359.5</v>
+        <v>2272.8</v>
       </c>
       <c r="J12" t="n">
-        <v>2373.97</v>
+        <v>2325.35</v>
       </c>
       <c r="K12" t="n">
-        <v>2438.15</v>
+        <v>2383.7</v>
       </c>
       <c r="L12" t="n">
-        <v>2502.32</v>
+        <v>2442.05</v>
       </c>
       <c r="M12" t="n">
-        <v>2541.65</v>
+        <v>2497.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2580.97</v>
+        <v>2552.95</v>
       </c>
       <c r="O12" t="n">
-        <v>2670</v>
+        <v>2614.2</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1544,50 +1546,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2455.2</v>
+        <v>2397</v>
       </c>
       <c r="C13" t="n">
-        <v>2487.6</v>
+        <v>2411.9</v>
       </c>
       <c r="D13" t="n">
-        <v>2353.8</v>
+        <v>2300.7</v>
       </c>
       <c r="E13" t="n">
-        <v>2396</v>
+        <v>2375.3</v>
       </c>
       <c r="F13" t="n">
-        <v>-44.6</v>
+        <v>-20.7</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.0086</v>
       </c>
       <c r="H13" t="n">
-        <v>133.8</v>
+        <v>111.2</v>
       </c>
       <c r="I13" t="n">
-        <v>2272.8</v>
+        <v>2220</v>
       </c>
       <c r="J13" t="n">
-        <v>2325.35</v>
+        <v>2249.85</v>
       </c>
       <c r="K13" t="n">
-        <v>2383.7</v>
+        <v>2329.1</v>
       </c>
       <c r="L13" t="n">
-        <v>2442.05</v>
+        <v>2408.35</v>
       </c>
       <c r="M13" t="n">
-        <v>2497.5</v>
+        <v>2462.9</v>
       </c>
       <c r="N13" t="n">
-        <v>2552.95</v>
+        <v>2517.45</v>
       </c>
       <c r="O13" t="n">
-        <v>2614.2</v>
+        <v>2621.4</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1597,12 +1599,12 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1624,50 +1626,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2397</v>
+        <v>2387.8</v>
       </c>
       <c r="C14" t="n">
-        <v>2411.9</v>
+        <v>2508.1</v>
       </c>
       <c r="D14" t="n">
-        <v>2300.7</v>
+        <v>2370.3</v>
       </c>
       <c r="E14" t="n">
-        <v>2375.3</v>
+        <v>2505.1</v>
       </c>
       <c r="F14" t="n">
-        <v>-20.7</v>
+        <v>129.8</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0546</v>
       </c>
       <c r="H14" t="n">
-        <v>111.2</v>
+        <v>137.8</v>
       </c>
       <c r="I14" t="n">
-        <v>2220</v>
+        <v>2189.5</v>
       </c>
       <c r="J14" t="n">
-        <v>2249.85</v>
+        <v>2273.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2329.1</v>
+        <v>2319.7</v>
       </c>
       <c r="L14" t="n">
-        <v>2408.35</v>
+        <v>2365.8</v>
       </c>
       <c r="M14" t="n">
-        <v>2462.9</v>
+        <v>2430.9</v>
       </c>
       <c r="N14" t="n">
-        <v>2517.45</v>
+        <v>2496</v>
       </c>
       <c r="O14" t="n">
-        <v>2621.4</v>
+        <v>2523.1</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1675,28 +1677,30 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1704,50 +1708,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2387.8</v>
+        <v>2501</v>
       </c>
       <c r="C15" t="n">
-        <v>2508.1</v>
+        <v>2544.2</v>
       </c>
       <c r="D15" t="n">
-        <v>2370.3</v>
+        <v>2468.1</v>
       </c>
       <c r="E15" t="n">
-        <v>2505.1</v>
+        <v>2524.4</v>
       </c>
       <c r="F15" t="n">
-        <v>129.8</v>
+        <v>19.3</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0077</v>
       </c>
       <c r="H15" t="n">
-        <v>137.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>2189.5</v>
+        <v>2232.5</v>
       </c>
       <c r="J15" t="n">
-        <v>2273.6</v>
+        <v>2400.25</v>
       </c>
       <c r="K15" t="n">
-        <v>2319.7</v>
+        <v>2436.2</v>
       </c>
       <c r="L15" t="n">
-        <v>2365.8</v>
+        <v>2472.15</v>
       </c>
       <c r="M15" t="n">
-        <v>2430.9</v>
+        <v>2574</v>
       </c>
       <c r="N15" t="n">
-        <v>2496</v>
+        <v>2675.85</v>
       </c>
       <c r="O15" t="n">
-        <v>2523.1</v>
+        <v>2645.9</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1765,13 +1769,11 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1786,50 +1788,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2501</v>
+        <v>2528</v>
       </c>
       <c r="C16" t="n">
-        <v>2544.2</v>
+        <v>2605</v>
       </c>
       <c r="D16" t="n">
-        <v>2468.1</v>
+        <v>2516.6</v>
       </c>
       <c r="E16" t="n">
-        <v>2524.4</v>
+        <v>2553.7</v>
       </c>
       <c r="F16" t="n">
-        <v>19.3</v>
+        <v>29.3</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0116</v>
       </c>
       <c r="H16" t="n">
-        <v>76.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>2232.5</v>
+        <v>2392</v>
       </c>
       <c r="J16" t="n">
-        <v>2400.25</v>
+        <v>2457.42</v>
       </c>
       <c r="K16" t="n">
-        <v>2436.2</v>
+        <v>2486.35</v>
       </c>
       <c r="L16" t="n">
-        <v>2472.15</v>
+        <v>2515.27</v>
       </c>
       <c r="M16" t="n">
-        <v>2574</v>
+        <v>2562.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2675.85</v>
+        <v>2609.62</v>
       </c>
       <c r="O16" t="n">
-        <v>2645.9</v>
+        <v>2620.3</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1866,50 +1868,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2528</v>
+        <v>2552.8</v>
       </c>
       <c r="C17" t="n">
-        <v>2605</v>
+        <v>2577.3</v>
       </c>
       <c r="D17" t="n">
-        <v>2516.6</v>
+        <v>2489.4</v>
       </c>
       <c r="E17" t="n">
-        <v>2553.7</v>
+        <v>2509.56</v>
       </c>
       <c r="F17" t="n">
-        <v>29.3</v>
+        <v>-44.14</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0116</v>
+        <v>-0.0173</v>
       </c>
       <c r="H17" t="n">
-        <v>88.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>2392</v>
+        <v>2428.2</v>
       </c>
       <c r="J17" t="n">
-        <v>2457.42</v>
+        <v>2461.75</v>
       </c>
       <c r="K17" t="n">
-        <v>2486.35</v>
+        <v>2509.5</v>
       </c>
       <c r="L17" t="n">
-        <v>2515.27</v>
+        <v>2557.25</v>
       </c>
       <c r="M17" t="n">
-        <v>2562.45</v>
+        <v>2597.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2609.62</v>
+        <v>2638.55</v>
       </c>
       <c r="O17" t="n">
-        <v>2620.3</v>
+        <v>2693.4</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1917,19 +1919,19 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1941,55 +1943,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2552.8</v>
+        <v>2550</v>
       </c>
       <c r="C18" t="n">
-        <v>2577.3</v>
+        <v>2590.3</v>
       </c>
       <c r="D18" t="n">
-        <v>2489.4</v>
+        <v>2540.8</v>
       </c>
       <c r="E18" t="n">
-        <v>2509.56</v>
+        <v>2551.4</v>
       </c>
       <c r="F18" t="n">
-        <v>-44.14</v>
+        <v>41.84</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0173</v>
+        <v>0.0167</v>
       </c>
       <c r="H18" t="n">
-        <v>87.90000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="I18" t="n">
-        <v>2428.2</v>
+        <v>2401.5</v>
       </c>
       <c r="J18" t="n">
-        <v>2461.75</v>
+        <v>2409.76</v>
       </c>
       <c r="K18" t="n">
-        <v>2509.5</v>
+        <v>2465.61</v>
       </c>
       <c r="L18" t="n">
-        <v>2557.25</v>
+        <v>2521.46</v>
       </c>
       <c r="M18" t="n">
-        <v>2597.9</v>
+        <v>2553.51</v>
       </c>
       <c r="N18" t="n">
-        <v>2638.55</v>
+        <v>2585.57</v>
       </c>
       <c r="O18" t="n">
-        <v>2693.4</v>
+        <v>2665.2</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -1997,21 +2003,23 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2021,83 +2029,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2550</v>
+        <v>2551.6</v>
       </c>
       <c r="C19" t="n">
-        <v>2590.3</v>
+        <v>2556.9</v>
       </c>
       <c r="D19" t="n">
-        <v>2540.8</v>
+        <v>2493.5</v>
       </c>
       <c r="E19" t="n">
-        <v>2551.4</v>
+        <v>2522.5</v>
       </c>
       <c r="F19" t="n">
-        <v>41.84</v>
+        <v>-28.9</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0167</v>
+        <v>-0.0113</v>
       </c>
       <c r="H19" t="n">
-        <v>49.5</v>
+        <v>63.4</v>
       </c>
       <c r="I19" t="n">
-        <v>2401.5</v>
+        <v>2491.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2409.76</v>
+        <v>2494.82</v>
       </c>
       <c r="K19" t="n">
-        <v>2465.61</v>
+        <v>2526.65</v>
       </c>
       <c r="L19" t="n">
-        <v>2521.46</v>
+        <v>2558.47</v>
       </c>
       <c r="M19" t="n">
-        <v>2553.51</v>
+        <v>2576.15</v>
       </c>
       <c r="N19" t="n">
-        <v>2585.57</v>
+        <v>2593.82</v>
       </c>
       <c r="O19" t="n">
-        <v>2665.2</v>
+        <v>2639.8</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2107,141 +2111,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2551.6</v>
+        <v>2524.2</v>
       </c>
       <c r="C20" t="n">
-        <v>2556.9</v>
+        <v>2650.3</v>
       </c>
       <c r="D20" t="n">
-        <v>2493.5</v>
+        <v>2517.2</v>
       </c>
       <c r="E20" t="n">
-        <v>2522.5</v>
+        <v>2636.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-28.9</v>
+        <v>114.4</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0113</v>
+        <v>0.0454</v>
       </c>
       <c r="H20" t="n">
-        <v>63.4</v>
+        <v>133.1</v>
       </c>
       <c r="I20" t="n">
-        <v>2491.3</v>
+        <v>2430.1</v>
       </c>
       <c r="J20" t="n">
-        <v>2494.82</v>
+        <v>2457.75</v>
       </c>
       <c r="K20" t="n">
-        <v>2526.65</v>
+        <v>2490.8</v>
       </c>
       <c r="L20" t="n">
-        <v>2558.47</v>
+        <v>2523.85</v>
       </c>
       <c r="M20" t="n">
-        <v>2576.15</v>
+        <v>2554.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2593.82</v>
+        <v>2584.55</v>
       </c>
       <c r="O20" t="n">
-        <v>2639.8</v>
+        <v>2620.3</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2524.2</v>
+        <v>2638.9</v>
       </c>
       <c r="C21" t="n">
-        <v>2650.3</v>
+        <v>2705.6</v>
       </c>
       <c r="D21" t="n">
-        <v>2517.2</v>
+        <v>2616.3</v>
       </c>
       <c r="E21" t="n">
-        <v>2636.9</v>
+        <v>2691.2</v>
       </c>
       <c r="F21" t="n">
-        <v>114.4</v>
+        <v>54.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0454</v>
+        <v>0.0206</v>
       </c>
       <c r="H21" t="n">
-        <v>133.1</v>
+        <v>89.3</v>
       </c>
       <c r="I21" t="n">
-        <v>2430.1</v>
+        <v>2384.1</v>
       </c>
       <c r="J21" t="n">
-        <v>2457.75</v>
+        <v>2530.37</v>
       </c>
       <c r="K21" t="n">
-        <v>2490.8</v>
+        <v>2570.35</v>
       </c>
       <c r="L21" t="n">
-        <v>2523.85</v>
+        <v>2610.32</v>
       </c>
       <c r="M21" t="n">
-        <v>2554.2</v>
+        <v>2703.45</v>
       </c>
       <c r="N21" t="n">
-        <v>2584.55</v>
+        <v>2796.57</v>
       </c>
       <c r="O21" t="n">
-        <v>2620.3</v>
+        <v>2783.4</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2259,18 +2265,14 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2282,50 +2284,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2638.9</v>
+        <v>2670</v>
       </c>
       <c r="C22" t="n">
-        <v>2705.6</v>
+        <v>2749.2</v>
       </c>
       <c r="D22" t="n">
-        <v>2616.3</v>
+        <v>2631</v>
       </c>
       <c r="E22" t="n">
-        <v>2691.2</v>
+        <v>2679.6</v>
       </c>
       <c r="F22" t="n">
-        <v>54.3</v>
+        <v>-11.6</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0206</v>
+        <v>-0.0043</v>
       </c>
       <c r="H22" t="n">
-        <v>89.3</v>
+        <v>118.2</v>
       </c>
       <c r="I22" t="n">
-        <v>2384.1</v>
+        <v>2527</v>
       </c>
       <c r="J22" t="n">
-        <v>2530.37</v>
+        <v>2617.02</v>
       </c>
       <c r="K22" t="n">
-        <v>2570.35</v>
+        <v>2646.55</v>
       </c>
       <c r="L22" t="n">
-        <v>2610.32</v>
+        <v>2676.08</v>
       </c>
       <c r="M22" t="n">
-        <v>2703.45</v>
+        <v>2735.85</v>
       </c>
       <c r="N22" t="n">
-        <v>2796.57</v>
+        <v>2795.62</v>
       </c>
       <c r="O22" t="n">
-        <v>2783.4</v>
+        <v>2794.9</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2333,17 +2335,19 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U22" s="8" t="n">
@@ -2357,55 +2361,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2670</v>
+        <v>2661</v>
       </c>
       <c r="C23" t="n">
-        <v>2749.2</v>
+        <v>2697.9</v>
       </c>
       <c r="D23" t="n">
-        <v>2631</v>
+        <v>2607.5</v>
       </c>
       <c r="E23" t="n">
-        <v>2679.6</v>
+        <v>2624.6</v>
       </c>
       <c r="F23" t="n">
-        <v>-11.6</v>
+        <v>-55</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0205</v>
       </c>
       <c r="H23" t="n">
-        <v>118.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>2527</v>
+        <v>2512.8</v>
       </c>
       <c r="J23" t="n">
-        <v>2617.02</v>
+        <v>2556.15</v>
       </c>
       <c r="K23" t="n">
-        <v>2646.55</v>
+        <v>2620.5</v>
       </c>
       <c r="L23" t="n">
-        <v>2676.08</v>
+        <v>2684.85</v>
       </c>
       <c r="M23" t="n">
-        <v>2735.85</v>
+        <v>2738.7</v>
       </c>
       <c r="N23" t="n">
-        <v>2795.62</v>
+        <v>2792.55</v>
       </c>
       <c r="O23" t="n">
-        <v>2794.9</v>
+        <v>2867.4</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2415,18 +2423,16 @@
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2441,57 +2447,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2661</v>
+        <v>2615</v>
       </c>
       <c r="C24" t="n">
-        <v>2697.9</v>
+        <v>2684.1</v>
       </c>
       <c r="D24" t="n">
-        <v>2607.5</v>
+        <v>2566.8</v>
       </c>
       <c r="E24" t="n">
-        <v>2624.6</v>
+        <v>2677.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-55</v>
+        <v>53.3</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0205</v>
+        <v>0.0203</v>
       </c>
       <c r="H24" t="n">
-        <v>90.40000000000001</v>
+        <v>117.3</v>
       </c>
       <c r="I24" t="n">
-        <v>2512.8</v>
+        <v>2517.1</v>
       </c>
       <c r="J24" t="n">
-        <v>2556.15</v>
+        <v>2520.15</v>
       </c>
       <c r="K24" t="n">
-        <v>2620.5</v>
+        <v>2579.4</v>
       </c>
       <c r="L24" t="n">
-        <v>2684.85</v>
+        <v>2638.65</v>
       </c>
       <c r="M24" t="n">
-        <v>2738.7</v>
+        <v>2669.8</v>
       </c>
       <c r="N24" t="n">
-        <v>2792.55</v>
+        <v>2700.95</v>
       </c>
       <c r="O24" t="n">
-        <v>2867.4</v>
+        <v>2788.3</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2501,17 +2507,19 @@
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2525,57 +2533,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2615</v>
+        <v>2677</v>
       </c>
       <c r="C25" t="n">
-        <v>2684.1</v>
+        <v>2720</v>
       </c>
       <c r="D25" t="n">
-        <v>2566.8</v>
+        <v>2607.3</v>
       </c>
       <c r="E25" t="n">
-        <v>2677.9</v>
+        <v>2653.1</v>
       </c>
       <c r="F25" t="n">
-        <v>53.3</v>
+        <v>-24.8</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0203</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>117.3</v>
+        <v>112.7</v>
       </c>
       <c r="I25" t="n">
-        <v>2517.1</v>
+        <v>2449.5</v>
       </c>
       <c r="J25" t="n">
-        <v>2520.15</v>
+        <v>2586.82</v>
       </c>
       <c r="K25" t="n">
-        <v>2579.4</v>
+        <v>2619.25</v>
       </c>
       <c r="L25" t="n">
-        <v>2638.65</v>
+        <v>2651.67</v>
       </c>
       <c r="M25" t="n">
-        <v>2669.8</v>
+        <v>2736.55</v>
       </c>
       <c r="N25" t="n">
-        <v>2700.95</v>
+        <v>2821.42</v>
       </c>
       <c r="O25" t="n">
-        <v>2788.3</v>
+        <v>2801.4</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2590,13 +2598,11 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2611,57 +2617,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2677</v>
+        <v>2650.9</v>
       </c>
       <c r="C26" t="n">
-        <v>2720</v>
+        <v>2696</v>
       </c>
       <c r="D26" t="n">
-        <v>2607.3</v>
+        <v>2613.7</v>
       </c>
       <c r="E26" t="n">
-        <v>2653.1</v>
+        <v>2668.8</v>
       </c>
       <c r="F26" t="n">
-        <v>-24.8</v>
+        <v>15.7</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H26" t="n">
-        <v>112.7</v>
+        <v>82.3</v>
       </c>
       <c r="I26" t="n">
-        <v>2449.5</v>
+        <v>2494.6</v>
       </c>
       <c r="J26" t="n">
-        <v>2586.82</v>
+        <v>2535.13</v>
       </c>
       <c r="K26" t="n">
-        <v>2619.25</v>
+        <v>2596.75</v>
       </c>
       <c r="L26" t="n">
-        <v>2651.67</v>
+        <v>2658.38</v>
       </c>
       <c r="M26" t="n">
-        <v>2736.55</v>
+        <v>2709.45</v>
       </c>
       <c r="N26" t="n">
-        <v>2821.42</v>
+        <v>2760.53</v>
       </c>
       <c r="O26" t="n">
-        <v>2801.4</v>
+        <v>2832.7</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2669,10 +2675,8 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
@@ -2702,50 +2706,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2650.9</v>
+        <v>2666.5</v>
       </c>
       <c r="C27" t="n">
-        <v>2696</v>
+        <v>2683.4</v>
       </c>
       <c r="D27" t="n">
-        <v>2613.7</v>
+        <v>2602.7</v>
       </c>
       <c r="E27" t="n">
-        <v>2668.8</v>
+        <v>2634.7</v>
       </c>
       <c r="F27" t="n">
-        <v>15.7</v>
+        <v>-34.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0128</v>
       </c>
       <c r="H27" t="n">
-        <v>82.3</v>
+        <v>80.7</v>
       </c>
       <c r="I27" t="n">
-        <v>2494.6</v>
+        <v>2531.4</v>
       </c>
       <c r="J27" t="n">
-        <v>2535.13</v>
+        <v>2593.48</v>
       </c>
       <c r="K27" t="n">
-        <v>2596.75</v>
+        <v>2627.65</v>
       </c>
       <c r="L27" t="n">
-        <v>2658.38</v>
+        <v>2661.83</v>
       </c>
       <c r="M27" t="n">
-        <v>2709.45</v>
+        <v>2709.95</v>
       </c>
       <c r="N27" t="n">
-        <v>2760.53</v>
+        <v>2758.08</v>
       </c>
       <c r="O27" t="n">
-        <v>2832.7</v>
+        <v>2778.3</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2753,12 +2757,14 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2777,67 +2783,71 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2666.5</v>
+        <v>2608.8</v>
       </c>
       <c r="C28" t="n">
-        <v>2683.4</v>
+        <v>2663.3</v>
       </c>
       <c r="D28" t="n">
-        <v>2602.7</v>
+        <v>2516.6</v>
       </c>
       <c r="E28" t="n">
-        <v>2634.7</v>
+        <v>2526.7</v>
       </c>
       <c r="F28" t="n">
-        <v>-34.1</v>
+        <v>-108</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0128</v>
+        <v>-0.041</v>
       </c>
       <c r="H28" t="n">
-        <v>80.7</v>
+        <v>146.7</v>
       </c>
       <c r="I28" t="n">
-        <v>2531.4</v>
+        <v>2522</v>
       </c>
       <c r="J28" t="n">
-        <v>2593.48</v>
+        <v>2549.83</v>
       </c>
       <c r="K28" t="n">
-        <v>2627.65</v>
+        <v>2594.35</v>
       </c>
       <c r="L28" t="n">
-        <v>2661.83</v>
+        <v>2638.87</v>
       </c>
       <c r="M28" t="n">
-        <v>2709.95</v>
+        <v>2675.05</v>
       </c>
       <c r="N28" t="n">
-        <v>2758.08</v>
+        <v>2711.22</v>
       </c>
       <c r="O28" t="n">
-        <v>2778.3</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+        <v>2764.1</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
@@ -2854,78 +2864,70 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2608.8</v>
+        <v>2499.2</v>
       </c>
       <c r="C29" t="n">
-        <v>2663.3</v>
+        <v>2594.4</v>
       </c>
       <c r="D29" t="n">
-        <v>2516.6</v>
+        <v>2416.9</v>
       </c>
       <c r="E29" t="n">
-        <v>2526.7</v>
+        <v>2480.9</v>
       </c>
       <c r="F29" t="n">
-        <v>-108</v>
+        <v>-45.8</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.041</v>
+        <v>-0.0181</v>
       </c>
       <c r="H29" t="n">
-        <v>146.7</v>
+        <v>177.5</v>
       </c>
       <c r="I29" t="n">
-        <v>2522</v>
+        <v>2369.9</v>
       </c>
       <c r="J29" t="n">
-        <v>2549.83</v>
+        <v>2348.37</v>
       </c>
       <c r="K29" t="n">
-        <v>2594.35</v>
+        <v>2453.35</v>
       </c>
       <c r="L29" t="n">
-        <v>2638.87</v>
+        <v>2558.33</v>
       </c>
       <c r="M29" t="n">
-        <v>2675.05</v>
+        <v>2600.05</v>
       </c>
       <c r="N29" t="n">
-        <v>2711.22</v>
+        <v>2641.77</v>
       </c>
       <c r="O29" t="n">
-        <v>2764.1</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
+        <v>2810</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
@@ -2952,50 +2954,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2499.2</v>
+        <v>2468.5</v>
       </c>
       <c r="C30" t="n">
-        <v>2594.4</v>
+        <v>2547.9</v>
       </c>
       <c r="D30" t="n">
-        <v>2416.9</v>
+        <v>2442</v>
       </c>
       <c r="E30" t="n">
-        <v>2480.9</v>
+        <v>2496.4</v>
       </c>
       <c r="F30" t="n">
-        <v>-45.8</v>
+        <v>15.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0181</v>
+        <v>0.0062</v>
       </c>
       <c r="H30" t="n">
-        <v>177.5</v>
+        <v>105.9</v>
       </c>
       <c r="I30" t="n">
-        <v>2369.9</v>
+        <v>2239.4</v>
       </c>
       <c r="J30" t="n">
-        <v>2348.37</v>
+        <v>2291.02</v>
       </c>
       <c r="K30" t="n">
-        <v>2453.35</v>
+        <v>2392.15</v>
       </c>
       <c r="L30" t="n">
-        <v>2558.33</v>
+        <v>2493.27</v>
       </c>
       <c r="M30" t="n">
-        <v>2600.05</v>
+        <v>2569.65</v>
       </c>
       <c r="N30" t="n">
-        <v>2641.77</v>
+        <v>2646.02</v>
       </c>
       <c r="O30" t="n">
-        <v>2810</v>
+        <v>2771.9</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3003,14 +3005,12 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3027,55 +3027,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2468.5</v>
+        <v>2429.1</v>
       </c>
       <c r="C31" t="n">
-        <v>2547.9</v>
+        <v>2574.5</v>
       </c>
       <c r="D31" t="n">
-        <v>2442</v>
+        <v>2415.3</v>
       </c>
       <c r="E31" t="n">
-        <v>2496.4</v>
+        <v>2464</v>
       </c>
       <c r="F31" t="n">
-        <v>15.5</v>
+        <v>-32.4</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.013</v>
       </c>
       <c r="H31" t="n">
-        <v>105.9</v>
+        <v>159.2</v>
       </c>
       <c r="I31" t="n">
-        <v>2239.4</v>
+        <v>2336.1</v>
       </c>
       <c r="J31" t="n">
-        <v>2291.02</v>
+        <v>2391.22</v>
       </c>
       <c r="K31" t="n">
-        <v>2392.15</v>
+        <v>2443.45</v>
       </c>
       <c r="L31" t="n">
-        <v>2493.27</v>
+        <v>2495.67</v>
       </c>
       <c r="M31" t="n">
-        <v>2569.65</v>
+        <v>2549.35</v>
       </c>
       <c r="N31" t="n">
-        <v>2646.02</v>
+        <v>2603.02</v>
       </c>
       <c r="O31" t="n">
-        <v>2771.9</v>
+        <v>2653.8</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3083,16 +3087,20 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3107,57 +3115,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2429.1</v>
+        <v>2445</v>
       </c>
       <c r="C32" t="n">
-        <v>2574.5</v>
+        <v>2557</v>
       </c>
       <c r="D32" t="n">
-        <v>2415.3</v>
+        <v>2409.4</v>
       </c>
       <c r="E32" t="n">
-        <v>2464</v>
+        <v>2531.7</v>
       </c>
       <c r="F32" t="n">
-        <v>-32.4</v>
+        <v>67.7</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.013</v>
+        <v>0.0275</v>
       </c>
       <c r="H32" t="n">
-        <v>159.2</v>
+        <v>147.6</v>
       </c>
       <c r="I32" t="n">
-        <v>2336.1</v>
+        <v>2256.1</v>
       </c>
       <c r="J32" t="n">
-        <v>2391.22</v>
+        <v>2289.35</v>
       </c>
       <c r="K32" t="n">
-        <v>2443.45</v>
+        <v>2384.4</v>
       </c>
       <c r="L32" t="n">
-        <v>2495.67</v>
+        <v>2479.45</v>
       </c>
       <c r="M32" t="n">
-        <v>2549.35</v>
+        <v>2543.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2603.02</v>
+        <v>2607.75</v>
       </c>
       <c r="O32" t="n">
-        <v>2653.8</v>
+        <v>2733.7</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3165,19 +3173,17 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="U32" s="8" t="n">
@@ -3200,50 +3206,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2445</v>
+        <v>2527.9</v>
       </c>
       <c r="C33" t="n">
-        <v>2557</v>
+        <v>2674.5</v>
       </c>
       <c r="D33" t="n">
-        <v>2409.4</v>
+        <v>2511.4</v>
       </c>
       <c r="E33" t="n">
-        <v>2531.7</v>
+        <v>2644.4</v>
       </c>
       <c r="F33" t="n">
-        <v>67.7</v>
+        <v>112.7</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0445</v>
       </c>
       <c r="H33" t="n">
-        <v>147.6</v>
+        <v>163.1</v>
       </c>
       <c r="I33" t="n">
-        <v>2256.1</v>
+        <v>2261.8</v>
       </c>
       <c r="J33" t="n">
-        <v>2289.35</v>
+        <v>2408.35</v>
       </c>
       <c r="K33" t="n">
-        <v>2384.4</v>
+        <v>2457.9</v>
       </c>
       <c r="L33" t="n">
-        <v>2479.45</v>
+        <v>2507.45</v>
       </c>
       <c r="M33" t="n">
-        <v>2543.6</v>
+        <v>2605.5</v>
       </c>
       <c r="N33" t="n">
-        <v>2607.75</v>
+        <v>2703.55</v>
       </c>
       <c r="O33" t="n">
-        <v>2733.7</v>
+        <v>2704.6</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3277,57 +3283,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2527.9</v>
+        <v>2607.8</v>
       </c>
       <c r="C34" t="n">
-        <v>2674.5</v>
+        <v>2807.8</v>
       </c>
       <c r="D34" t="n">
-        <v>2511.4</v>
+        <v>2591.8</v>
       </c>
       <c r="E34" t="n">
-        <v>2644.4</v>
+        <v>2788.9</v>
       </c>
       <c r="F34" t="n">
-        <v>112.7</v>
+        <v>144.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0445</v>
+        <v>0.0546</v>
       </c>
       <c r="H34" t="n">
-        <v>163.1</v>
+        <v>216</v>
       </c>
       <c r="I34" t="n">
-        <v>2261.8</v>
+        <v>2348.3</v>
       </c>
       <c r="J34" t="n">
-        <v>2408.35</v>
+        <v>2507.02</v>
       </c>
       <c r="K34" t="n">
-        <v>2457.9</v>
+        <v>2562.85</v>
       </c>
       <c r="L34" t="n">
-        <v>2507.45</v>
+        <v>2618.67</v>
       </c>
       <c r="M34" t="n">
-        <v>2605.5</v>
+        <v>2725.95</v>
       </c>
       <c r="N34" t="n">
-        <v>2703.55</v>
+        <v>2833.22</v>
       </c>
       <c r="O34" t="n">
-        <v>2704.6</v>
+        <v>2837.6</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3345,11 +3351,13 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3368,50 +3376,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2607.8</v>
+        <v>2758.7</v>
       </c>
       <c r="C35" t="n">
-        <v>2807.8</v>
+        <v>2828.7</v>
       </c>
       <c r="D35" t="n">
-        <v>2591.8</v>
+        <v>2745.9</v>
       </c>
       <c r="E35" t="n">
-        <v>2788.9</v>
+        <v>2796.1</v>
       </c>
       <c r="F35" t="n">
-        <v>144.5</v>
+        <v>7.2</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0026</v>
       </c>
       <c r="H35" t="n">
-        <v>216</v>
+        <v>82.8</v>
       </c>
       <c r="I35" t="n">
-        <v>2348.3</v>
+        <v>2375.8</v>
       </c>
       <c r="J35" t="n">
-        <v>2507.02</v>
+        <v>2617.45</v>
       </c>
       <c r="K35" t="n">
-        <v>2562.85</v>
+        <v>2680.9</v>
       </c>
       <c r="L35" t="n">
-        <v>2618.67</v>
+        <v>2744.35</v>
       </c>
       <c r="M35" t="n">
-        <v>2725.95</v>
+        <v>2896.9</v>
       </c>
       <c r="N35" t="n">
-        <v>2833.22</v>
+        <v>3049.45</v>
       </c>
       <c r="O35" t="n">
-        <v>2837.6</v>
+        <v>3023.8</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3424,18 +3432,14 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3454,50 +3458,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2758.7</v>
+        <v>2792.7</v>
       </c>
       <c r="C36" t="n">
-        <v>2828.7</v>
+        <v>2825</v>
       </c>
       <c r="D36" t="n">
-        <v>2745.9</v>
+        <v>2726.1</v>
       </c>
       <c r="E36" t="n">
-        <v>2796.1</v>
+        <v>2819.3</v>
       </c>
       <c r="F36" t="n">
-        <v>7.2</v>
+        <v>23.2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0083</v>
       </c>
       <c r="H36" t="n">
-        <v>82.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>2375.8</v>
+        <v>2663.1</v>
       </c>
       <c r="J36" t="n">
-        <v>2617.45</v>
+        <v>2717.7</v>
       </c>
       <c r="K36" t="n">
-        <v>2680.9</v>
+        <v>2754.7</v>
       </c>
       <c r="L36" t="n">
-        <v>2744.35</v>
+        <v>2791.7</v>
       </c>
       <c r="M36" t="n">
-        <v>2896.9</v>
+        <v>2837.5</v>
       </c>
       <c r="N36" t="n">
-        <v>3049.45</v>
+        <v>2883.3</v>
       </c>
       <c r="O36" t="n">
-        <v>3023.8</v>
+        <v>2911.5</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3505,16 +3509,20 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3529,57 +3537,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2792.7</v>
+        <v>2825.9</v>
       </c>
       <c r="C37" t="n">
-        <v>2825</v>
+        <v>2918.4</v>
       </c>
       <c r="D37" t="n">
-        <v>2726.1</v>
+        <v>2786.8</v>
       </c>
       <c r="E37" t="n">
-        <v>2819.3</v>
+        <v>2867.6</v>
       </c>
       <c r="F37" t="n">
-        <v>23.2</v>
+        <v>48.3</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0171</v>
       </c>
       <c r="H37" t="n">
-        <v>98.90000000000001</v>
+        <v>131.6</v>
       </c>
       <c r="I37" t="n">
-        <v>2663.1</v>
+        <v>2627.2</v>
       </c>
       <c r="J37" t="n">
-        <v>2717.7</v>
+        <v>2742.28</v>
       </c>
       <c r="K37" t="n">
-        <v>2754.7</v>
+        <v>2769.85</v>
       </c>
       <c r="L37" t="n">
-        <v>2791.7</v>
+        <v>2797.43</v>
       </c>
       <c r="M37" t="n">
-        <v>2837.5</v>
+        <v>2868.75</v>
       </c>
       <c r="N37" t="n">
-        <v>2883.3</v>
+        <v>2940.07</v>
       </c>
       <c r="O37" t="n">
-        <v>2911.5</v>
+        <v>2923.9</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3587,10 +3595,8 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
@@ -3615,57 +3621,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2825.9</v>
+        <v>2863</v>
       </c>
       <c r="C38" t="n">
-        <v>2918.4</v>
+        <v>2896.2</v>
       </c>
       <c r="D38" t="n">
-        <v>2786.8</v>
+        <v>2787.9</v>
       </c>
       <c r="E38" t="n">
-        <v>2867.6</v>
+        <v>2799.6</v>
       </c>
       <c r="F38" t="n">
-        <v>48.3</v>
+        <v>-68</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0171</v>
+        <v>-0.0237</v>
       </c>
       <c r="H38" t="n">
-        <v>131.6</v>
+        <v>108.3</v>
       </c>
       <c r="I38" t="n">
-        <v>2627.2</v>
+        <v>2655.2</v>
       </c>
       <c r="J38" t="n">
-        <v>2742.28</v>
+        <v>2743.5</v>
       </c>
       <c r="K38" t="n">
-        <v>2769.85</v>
+        <v>2801.8</v>
       </c>
       <c r="L38" t="n">
-        <v>2797.43</v>
+        <v>2860.1</v>
       </c>
       <c r="M38" t="n">
-        <v>2868.75</v>
+        <v>2933.4</v>
       </c>
       <c r="N38" t="n">
-        <v>2940.07</v>
+        <v>3006.7</v>
       </c>
       <c r="O38" t="n">
-        <v>2923.9</v>
+        <v>3050</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3673,19 +3679,19 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3699,57 +3705,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2863</v>
+        <v>2788.8</v>
       </c>
       <c r="C39" t="n">
-        <v>2896.2</v>
+        <v>2887</v>
       </c>
       <c r="D39" t="n">
-        <v>2787.9</v>
+        <v>2728.4</v>
       </c>
       <c r="E39" t="n">
-        <v>2799.6</v>
+        <v>2872.1</v>
       </c>
       <c r="F39" t="n">
-        <v>-68</v>
+        <v>72.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0259</v>
       </c>
       <c r="H39" t="n">
-        <v>108.3</v>
+        <v>158.6</v>
       </c>
       <c r="I39" t="n">
-        <v>2655.2</v>
+        <v>2679.6</v>
       </c>
       <c r="J39" t="n">
-        <v>2743.5</v>
+        <v>2670.08</v>
       </c>
       <c r="K39" t="n">
-        <v>2801.8</v>
+        <v>2745.45</v>
       </c>
       <c r="L39" t="n">
-        <v>2860.1</v>
+        <v>2820.83</v>
       </c>
       <c r="M39" t="n">
-        <v>2933.4</v>
+        <v>2853.75</v>
       </c>
       <c r="N39" t="n">
-        <v>3006.7</v>
+        <v>2886.68</v>
       </c>
       <c r="O39" t="n">
-        <v>3050</v>
+        <v>3004.5</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3759,19 +3765,23 @@
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3790,50 +3800,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2788.8</v>
+        <v>2888</v>
       </c>
       <c r="C40" t="n">
-        <v>2887</v>
+        <v>2952</v>
       </c>
       <c r="D40" t="n">
-        <v>2728.4</v>
+        <v>2887.9</v>
       </c>
       <c r="E40" t="n">
-        <v>2872.1</v>
+        <v>2924.3</v>
       </c>
       <c r="F40" t="n">
-        <v>72.5</v>
+        <v>52.2</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0259</v>
+        <v>0.0182</v>
       </c>
       <c r="H40" t="n">
-        <v>158.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>2679.6</v>
+        <v>2569.8</v>
       </c>
       <c r="J40" t="n">
-        <v>2670.08</v>
+        <v>2745.7</v>
       </c>
       <c r="K40" t="n">
-        <v>2745.45</v>
+        <v>2792.8</v>
       </c>
       <c r="L40" t="n">
-        <v>2820.83</v>
+        <v>2839.9</v>
       </c>
       <c r="M40" t="n">
-        <v>2853.75</v>
+        <v>2951.4</v>
       </c>
       <c r="N40" t="n">
-        <v>2886.68</v>
+        <v>3062.9</v>
       </c>
       <c r="O40" t="n">
-        <v>3004.5</v>
+        <v>3045.6</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3841,10 +3851,8 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
@@ -3853,14 +3861,12 @@
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3871,77 +3877,81 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2888</v>
+        <v>2920.5</v>
       </c>
       <c r="C41" t="n">
-        <v>2952</v>
+        <v>2948.3</v>
       </c>
       <c r="D41" t="n">
-        <v>2887.9</v>
+        <v>2812.4</v>
       </c>
       <c r="E41" t="n">
-        <v>2924.3</v>
+        <v>2834.8</v>
       </c>
       <c r="F41" t="n">
-        <v>52.2</v>
+        <v>-89.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0182</v>
+        <v>-0.0306</v>
       </c>
       <c r="H41" t="n">
-        <v>64.09999999999999</v>
+        <v>135.9</v>
       </c>
       <c r="I41" t="n">
-        <v>2569.8</v>
+        <v>2823.8</v>
       </c>
       <c r="J41" t="n">
-        <v>2745.7</v>
+        <v>2862.38</v>
       </c>
       <c r="K41" t="n">
-        <v>2792.8</v>
+        <v>2892.25</v>
       </c>
       <c r="L41" t="n">
-        <v>2839.9</v>
+        <v>2922.12</v>
       </c>
       <c r="M41" t="n">
-        <v>2951.4</v>
+        <v>2956.35</v>
       </c>
       <c r="N41" t="n">
-        <v>3062.9</v>
+        <v>2990.58</v>
       </c>
       <c r="O41" t="n">
-        <v>3045.6</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+        <v>3016.1</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3953,86 +3963,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2920.5</v>
+        <v>2816.3</v>
       </c>
       <c r="C42" t="n">
-        <v>2948.3</v>
+        <v>2974.2</v>
       </c>
       <c r="D42" t="n">
-        <v>2812.4</v>
+        <v>2793.7</v>
       </c>
       <c r="E42" t="n">
-        <v>2834.8</v>
+        <v>2947</v>
       </c>
       <c r="F42" t="n">
-        <v>-89.5</v>
+        <v>112.2</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0306</v>
+        <v>0.0396</v>
       </c>
       <c r="H42" t="n">
-        <v>135.9</v>
+        <v>180.5</v>
       </c>
       <c r="I42" t="n">
-        <v>2823.8</v>
+        <v>2676.5</v>
       </c>
       <c r="J42" t="n">
-        <v>2862.38</v>
+        <v>2676.12</v>
       </c>
       <c r="K42" t="n">
-        <v>2892.25</v>
+        <v>2766.85</v>
       </c>
       <c r="L42" t="n">
-        <v>2922.12</v>
+        <v>2857.58</v>
       </c>
       <c r="M42" t="n">
-        <v>2956.35</v>
+        <v>2902.75</v>
       </c>
       <c r="N42" t="n">
-        <v>2990.58</v>
+        <v>2947.93</v>
       </c>
       <c r="O42" t="n">
-        <v>3016.1</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
+        <v>3084.2</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4041,55 +4045,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2816.3</v>
+        <v>2984</v>
       </c>
       <c r="C43" t="n">
-        <v>2974.2</v>
+        <v>3005</v>
       </c>
       <c r="D43" t="n">
-        <v>2793.7</v>
+        <v>2910.3</v>
       </c>
       <c r="E43" t="n">
-        <v>2947</v>
+        <v>2995.6</v>
       </c>
       <c r="F43" t="n">
-        <v>112.2</v>
+        <v>48.6</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.0165</v>
       </c>
       <c r="H43" t="n">
-        <v>180.5</v>
+        <v>94.7</v>
       </c>
       <c r="I43" t="n">
-        <v>2676.5</v>
+        <v>2613.2</v>
       </c>
       <c r="J43" t="n">
-        <v>2676.12</v>
+        <v>2798.03</v>
       </c>
       <c r="K43" t="n">
-        <v>2766.85</v>
+        <v>2856.75</v>
       </c>
       <c r="L43" t="n">
-        <v>2857.58</v>
+        <v>2915.47</v>
       </c>
       <c r="M43" t="n">
-        <v>2902.75</v>
+        <v>3037.25</v>
       </c>
       <c r="N43" t="n">
-        <v>2947.93</v>
+        <v>3159.03</v>
       </c>
       <c r="O43" t="n">
-        <v>3084.2</v>
+        <v>3154.7</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4107,14 +4115,12 @@
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
@@ -4125,57 +4131,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2984</v>
+        <v>2989.9</v>
       </c>
       <c r="C44" t="n">
-        <v>3005</v>
+        <v>3062.4</v>
       </c>
       <c r="D44" t="n">
-        <v>2910.3</v>
+        <v>2965.2</v>
       </c>
       <c r="E44" t="n">
-        <v>2995.6</v>
+        <v>3022.6</v>
       </c>
       <c r="F44" t="n">
-        <v>48.6</v>
+        <v>27</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>94.7</v>
+        <v>97.2</v>
       </c>
       <c r="I44" t="n">
-        <v>2613.2</v>
+        <v>2815.6</v>
       </c>
       <c r="J44" t="n">
-        <v>2798.03</v>
+        <v>2919.88</v>
       </c>
       <c r="K44" t="n">
-        <v>2856.75</v>
+        <v>2948.25</v>
       </c>
       <c r="L44" t="n">
-        <v>2915.47</v>
+        <v>2976.63</v>
       </c>
       <c r="M44" t="n">
-        <v>3037.25</v>
+        <v>3042.95</v>
       </c>
       <c r="N44" t="n">
-        <v>3159.03</v>
+        <v>3109.28</v>
       </c>
       <c r="O44" t="n">
-        <v>3154.7</v>
+        <v>3099.7</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4216,50 +4222,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2989.9</v>
+        <v>3020.9</v>
       </c>
       <c r="C45" t="n">
-        <v>3062.4</v>
+        <v>3068.4</v>
       </c>
       <c r="D45" t="n">
-        <v>2965.2</v>
+        <v>2987.8</v>
       </c>
       <c r="E45" t="n">
-        <v>3022.6</v>
+        <v>3023.5</v>
       </c>
       <c r="F45" t="n">
-        <v>27</v>
+        <v>0.9</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0003</v>
       </c>
       <c r="H45" t="n">
-        <v>97.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>2815.6</v>
+        <v>2868</v>
       </c>
       <c r="J45" t="n">
-        <v>2919.88</v>
+        <v>2929.8</v>
       </c>
       <c r="K45" t="n">
-        <v>2948.25</v>
+        <v>2974</v>
       </c>
       <c r="L45" t="n">
-        <v>2976.63</v>
+        <v>3018.2</v>
       </c>
       <c r="M45" t="n">
-        <v>3042.95</v>
+        <v>3071.2</v>
       </c>
       <c r="N45" t="n">
-        <v>3109.28</v>
+        <v>3124.2</v>
       </c>
       <c r="O45" t="n">
-        <v>3099.7</v>
+        <v>3159.6</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4272,13 +4278,11 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4300,50 +4304,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3020.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C46" t="n">
-        <v>3068.4</v>
+        <v>3042.6</v>
       </c>
       <c r="D46" t="n">
-        <v>2987.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E46" t="n">
-        <v>3023.5</v>
+        <v>2994</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9</v>
+        <v>-29.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0098</v>
       </c>
       <c r="H46" t="n">
-        <v>80.59999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="I46" t="n">
-        <v>2868</v>
+        <v>2907.2</v>
       </c>
       <c r="J46" t="n">
-        <v>2929.8</v>
+        <v>2940.6</v>
       </c>
       <c r="K46" t="n">
-        <v>2974</v>
+        <v>2983.2</v>
       </c>
       <c r="L46" t="n">
-        <v>3018.2</v>
+        <v>3025.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3071.2</v>
+        <v>3063.8</v>
       </c>
       <c r="N46" t="n">
-        <v>3124.2</v>
+        <v>3101.8</v>
       </c>
       <c r="O46" t="n">
-        <v>3159.6</v>
+        <v>3149</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4351,12 +4355,14 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4373,59 +4379,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3019.7</v>
+        <v>2984.7</v>
       </c>
       <c r="C47" t="n">
-        <v>3042.6</v>
+        <v>3029.8</v>
       </c>
       <c r="D47" t="n">
-        <v>2943.4</v>
+        <v>2949.3</v>
       </c>
       <c r="E47" t="n">
-        <v>2994</v>
+        <v>2973.5</v>
       </c>
       <c r="F47" t="n">
-        <v>-29.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0068</v>
       </c>
       <c r="H47" t="n">
-        <v>99.2</v>
+        <v>80.5</v>
       </c>
       <c r="I47" t="n">
-        <v>2907.2</v>
+        <v>2844.2</v>
       </c>
       <c r="J47" t="n">
-        <v>2940.6</v>
+        <v>2895.3</v>
       </c>
       <c r="K47" t="n">
-        <v>2983.2</v>
+        <v>2944.4</v>
       </c>
       <c r="L47" t="n">
-        <v>3025.8</v>
+        <v>2993.5</v>
       </c>
       <c r="M47" t="n">
-        <v>3063.8</v>
+        <v>3043.6</v>
       </c>
       <c r="N47" t="n">
-        <v>3101.8</v>
+        <v>3093.7</v>
       </c>
       <c r="O47" t="n">
-        <v>3149</v>
+        <v>3141.8</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4433,14 +4435,12 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4457,55 +4457,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2984.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C48" t="n">
-        <v>3029.8</v>
+        <v>2999.8</v>
       </c>
       <c r="D48" t="n">
-        <v>2949.3</v>
+        <v>2932.1</v>
       </c>
       <c r="E48" t="n">
-        <v>2973.5</v>
+        <v>2941.3</v>
       </c>
       <c r="F48" t="n">
-        <v>-20.5</v>
+        <v>-32.2</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0068</v>
+        <v>-0.0108</v>
       </c>
       <c r="H48" t="n">
-        <v>80.5</v>
+        <v>67.7</v>
       </c>
       <c r="I48" t="n">
-        <v>2844.2</v>
+        <v>2868.8</v>
       </c>
       <c r="J48" t="n">
-        <v>2895.3</v>
+        <v>2884.97</v>
       </c>
       <c r="K48" t="n">
-        <v>2944.4</v>
+        <v>2933.25</v>
       </c>
       <c r="L48" t="n">
-        <v>2993.5</v>
+        <v>2981.53</v>
       </c>
       <c r="M48" t="n">
-        <v>3043.6</v>
+        <v>3013.75</v>
       </c>
       <c r="N48" t="n">
-        <v>3093.7</v>
+        <v>3045.97</v>
       </c>
       <c r="O48" t="n">
-        <v>3141.8</v>
+        <v>3110.3</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4513,12 +4517,14 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4535,59 +4541,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2964.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C49" t="n">
-        <v>2999.8</v>
+        <v>2985.9</v>
       </c>
       <c r="D49" t="n">
-        <v>2932.1</v>
+        <v>2902.3</v>
       </c>
       <c r="E49" t="n">
-        <v>2941.3</v>
+        <v>2938</v>
       </c>
       <c r="F49" t="n">
-        <v>-32.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0011</v>
       </c>
       <c r="H49" t="n">
-        <v>67.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>2868.8</v>
+        <v>2864.4</v>
       </c>
       <c r="J49" t="n">
-        <v>2884.97</v>
+        <v>2861.28</v>
       </c>
       <c r="K49" t="n">
-        <v>2933.25</v>
+        <v>2907.45</v>
       </c>
       <c r="L49" t="n">
-        <v>2981.53</v>
+        <v>2953.63</v>
       </c>
       <c r="M49" t="n">
-        <v>3013.75</v>
+        <v>2975.15</v>
       </c>
       <c r="N49" t="n">
-        <v>3045.97</v>
+        <v>2996.67</v>
       </c>
       <c r="O49" t="n">
-        <v>3110.3</v>
+        <v>3067.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4597,16 +4599,18 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4624,50 +4628,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2955.5</v>
+        <v>2950</v>
       </c>
       <c r="C50" t="n">
-        <v>2985.9</v>
+        <v>3058.3</v>
       </c>
       <c r="D50" t="n">
-        <v>2902.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E50" t="n">
-        <v>2938</v>
+        <v>3041.6</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.3</v>
+        <v>103.6</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0353</v>
       </c>
       <c r="H50" t="n">
-        <v>83.59999999999999</v>
+        <v>109.9</v>
       </c>
       <c r="I50" t="n">
-        <v>2864.4</v>
+        <v>2818.7</v>
       </c>
       <c r="J50" t="n">
-        <v>2861.28</v>
+        <v>2851.35</v>
       </c>
       <c r="K50" t="n">
-        <v>2907.45</v>
+        <v>2896.2</v>
       </c>
       <c r="L50" t="n">
-        <v>2953.63</v>
+        <v>2941.05</v>
       </c>
       <c r="M50" t="n">
-        <v>2975.15</v>
+        <v>2979.8</v>
       </c>
       <c r="N50" t="n">
-        <v>2996.67</v>
+        <v>3018.55</v>
       </c>
       <c r="O50" t="n">
-        <v>3067.5</v>
+        <v>3069.5</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4675,30 +4679,30 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr"/>
@@ -4706,50 +4710,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2950</v>
+        <v>3038.9</v>
       </c>
       <c r="C51" t="n">
-        <v>3058.3</v>
+        <v>3076.3</v>
       </c>
       <c r="D51" t="n">
-        <v>2948.4</v>
+        <v>3016</v>
       </c>
       <c r="E51" t="n">
-        <v>3041.6</v>
+        <v>3074.9</v>
       </c>
       <c r="F51" t="n">
-        <v>103.6</v>
+        <v>33.3</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.0109</v>
       </c>
       <c r="H51" t="n">
-        <v>109.9</v>
+        <v>60.3</v>
       </c>
       <c r="I51" t="n">
-        <v>2818.7</v>
+        <v>2838.5</v>
       </c>
       <c r="J51" t="n">
-        <v>2851.35</v>
+        <v>2950.83</v>
       </c>
       <c r="K51" t="n">
-        <v>2896.2</v>
+        <v>2986.65</v>
       </c>
       <c r="L51" t="n">
-        <v>2941.05</v>
+        <v>3022.48</v>
       </c>
       <c r="M51" t="n">
-        <v>2979.8</v>
+        <v>3096.55</v>
       </c>
       <c r="N51" t="n">
-        <v>3018.55</v>
+        <v>3170.63</v>
       </c>
       <c r="O51" t="n">
-        <v>3069.5</v>
+        <v>3168.2</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4767,13 +4771,11 @@
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4788,144 +4790,148 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3038.9</v>
+        <v>3073.5</v>
       </c>
       <c r="C52" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D52" t="n">
-        <v>3016</v>
+        <v>2993.2</v>
       </c>
       <c r="E52" t="n">
-        <v>3074.9</v>
+        <v>3022.1</v>
       </c>
       <c r="F52" t="n">
-        <v>33.3</v>
+        <v>-52.8</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.0172</v>
       </c>
       <c r="H52" t="n">
-        <v>60.3</v>
+        <v>86.7</v>
       </c>
       <c r="I52" t="n">
-        <v>2838.5</v>
+        <v>2955.7</v>
       </c>
       <c r="J52" t="n">
-        <v>2950.83</v>
+        <v>3028.97</v>
       </c>
       <c r="K52" t="n">
-        <v>2986.65</v>
+        <v>3044.75</v>
       </c>
       <c r="L52" t="n">
-        <v>3022.48</v>
+        <v>3060.52</v>
       </c>
       <c r="M52" t="n">
-        <v>3096.55</v>
+        <v>3105.05</v>
       </c>
       <c r="N52" t="n">
-        <v>3170.63</v>
+        <v>3149.57</v>
       </c>
       <c r="O52" t="n">
-        <v>3168.2</v>
+        <v>3136.6</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
+      <c r="Q52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3073.5</v>
+        <v>3023</v>
       </c>
       <c r="C53" t="n">
-        <v>3079.9</v>
+        <v>3028.9</v>
       </c>
       <c r="D53" t="n">
-        <v>2993.2</v>
+        <v>2976.6</v>
       </c>
       <c r="E53" t="n">
-        <v>3022.1</v>
+        <v>2977.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-52.8</v>
+        <v>-44.6</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0172</v>
+        <v>-0.0148</v>
       </c>
       <c r="H53" t="n">
-        <v>86.7</v>
+        <v>52.3</v>
       </c>
       <c r="I53" t="n">
-        <v>2955.7</v>
+        <v>2906.5</v>
       </c>
       <c r="J53" t="n">
-        <v>3028.97</v>
+        <v>2928.18</v>
       </c>
       <c r="K53" t="n">
-        <v>3044.75</v>
+        <v>2978.75</v>
       </c>
       <c r="L53" t="n">
-        <v>3060.52</v>
+        <v>3029.33</v>
       </c>
       <c r="M53" t="n">
-        <v>3105.05</v>
+        <v>3065.45</v>
       </c>
       <c r="N53" t="n">
-        <v>3149.57</v>
+        <v>3101.58</v>
       </c>
       <c r="O53" t="n">
-        <v>3136.6</v>
+        <v>3166.6</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4945,74 +4951,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3023</v>
+        <v>2971</v>
       </c>
       <c r="C54" t="n">
-        <v>3028.9</v>
+        <v>2983.3</v>
       </c>
       <c r="D54" t="n">
+        <v>2914.5</v>
+      </c>
+      <c r="E54" t="n">
         <v>2976.6</v>
       </c>
-      <c r="E54" t="n">
-        <v>2977.5</v>
-      </c>
       <c r="F54" t="n">
-        <v>-44.6</v>
+        <v>-0.9</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0148</v>
+        <v>-0.0003</v>
       </c>
       <c r="H54" t="n">
-        <v>52.3</v>
+        <v>68.8</v>
       </c>
       <c r="I54" t="n">
-        <v>2906.5</v>
+        <v>2924.3</v>
       </c>
       <c r="J54" t="n">
-        <v>2928.18</v>
+        <v>2912.58</v>
       </c>
       <c r="K54" t="n">
-        <v>2978.75</v>
+        <v>2951.35</v>
       </c>
       <c r="L54" t="n">
-        <v>3029.33</v>
+        <v>2990.12</v>
       </c>
       <c r="M54" t="n">
-        <v>3065.45</v>
+        <v>3003.65</v>
       </c>
       <c r="N54" t="n">
-        <v>3101.58</v>
+        <v>3017.17</v>
       </c>
       <c r="O54" t="n">
-        <v>3166.6</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
+        <v>3081.2</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5034,67 +5038,67 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2971</v>
+        <v>2974.7</v>
       </c>
       <c r="C55" t="n">
-        <v>2983.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D55" t="n">
-        <v>2914.5</v>
+        <v>2887.6</v>
       </c>
       <c r="E55" t="n">
-        <v>2976.6</v>
+        <v>2904.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.9</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0242</v>
       </c>
       <c r="H55" t="n">
-        <v>68.8</v>
+        <v>90.3</v>
       </c>
       <c r="I55" t="n">
-        <v>2924.3</v>
+        <v>2845.7</v>
       </c>
       <c r="J55" t="n">
-        <v>2912.58</v>
+        <v>2921.65</v>
       </c>
       <c r="K55" t="n">
-        <v>2951.35</v>
+        <v>2942.2</v>
       </c>
       <c r="L55" t="n">
-        <v>2990.12</v>
+        <v>2962.75</v>
       </c>
       <c r="M55" t="n">
-        <v>3003.65</v>
+        <v>3011</v>
       </c>
       <c r="N55" t="n">
-        <v>3017.17</v>
+        <v>3059.25</v>
       </c>
       <c r="O55" t="n">
-        <v>3081.2</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
+        <v>3052.1</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5116,62 +5120,60 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2974.7</v>
+        <v>2892.7</v>
       </c>
       <c r="C56" t="n">
-        <v>2977.9</v>
+        <v>2913.5</v>
       </c>
       <c r="D56" t="n">
-        <v>2887.6</v>
+        <v>2831.9</v>
       </c>
       <c r="E56" t="n">
-        <v>2904.5</v>
+        <v>2873.23</v>
       </c>
       <c r="F56" t="n">
-        <v>-72.09999999999999</v>
+        <v>-31.27</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0242</v>
+        <v>-0.0108</v>
       </c>
       <c r="H56" t="n">
-        <v>90.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>2845.7</v>
+        <v>2797.3</v>
       </c>
       <c r="J56" t="n">
-        <v>2921.65</v>
+        <v>2800.08</v>
       </c>
       <c r="K56" t="n">
-        <v>2942.2</v>
+        <v>2859.35</v>
       </c>
       <c r="L56" t="n">
-        <v>2962.75</v>
+        <v>2918.62</v>
       </c>
       <c r="M56" t="n">
-        <v>3011</v>
+        <v>2949.65</v>
       </c>
       <c r="N56" t="n">
-        <v>3059.25</v>
+        <v>2980.67</v>
       </c>
       <c r="O56" t="n">
-        <v>3052.1</v>
+        <v>3068.2</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
@@ -5198,50 +5200,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2892.7</v>
+        <v>2879.5</v>
       </c>
       <c r="C57" t="n">
-        <v>2913.5</v>
+        <v>2931.2</v>
       </c>
       <c r="D57" t="n">
-        <v>2831.9</v>
+        <v>2829.9</v>
       </c>
       <c r="E57" t="n">
-        <v>2873.23</v>
+        <v>2859.3</v>
       </c>
       <c r="F57" t="n">
-        <v>-31.27</v>
+        <v>-13.93</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0048</v>
       </c>
       <c r="H57" t="n">
-        <v>81.59999999999999</v>
+        <v>101.3</v>
       </c>
       <c r="I57" t="n">
-        <v>2797.3</v>
+        <v>2750.3</v>
       </c>
       <c r="J57" t="n">
-        <v>2800.08</v>
+        <v>2791.89</v>
       </c>
       <c r="K57" t="n">
-        <v>2859.35</v>
+        <v>2832.43</v>
       </c>
       <c r="L57" t="n">
-        <v>2918.62</v>
+        <v>2872.96</v>
       </c>
       <c r="M57" t="n">
-        <v>2949.65</v>
+        <v>2914.03</v>
       </c>
       <c r="N57" t="n">
-        <v>2980.67</v>
+        <v>2955.1</v>
       </c>
       <c r="O57" t="n">
-        <v>3068.2</v>
+        <v>2995.1</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5251,16 +5253,18 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5273,89 +5277,9 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2879.5</v>
-      </c>
-      <c r="C58" t="n">
-        <v>2931.2</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2853.2</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2853.2</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-20.03</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.007</v>
-      </c>
-      <c r="H58" t="n">
-        <v>78</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2750.3</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2791.89</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2832.43</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2872.96</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2914.03</v>
-      </c>
-      <c r="N58" t="n">
-        <v>2955.1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>2995.1</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5283,6 +5283,90 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2839.6</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2841.2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2837.5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2837.8</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2728.6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2747.38</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2808.65</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2869.92</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2909.95</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2949.98</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3032.5</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5290,25 +5290,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2839.6</v>
+        <v>2857.7</v>
       </c>
       <c r="C58" t="n">
-        <v>2841.2</v>
+        <v>2858.8</v>
       </c>
       <c r="D58" t="n">
-        <v>2837.5</v>
+        <v>2826.8</v>
       </c>
       <c r="E58" t="n">
-        <v>2837.8</v>
+        <v>2834.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-21.5</v>
+        <v>-25.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0075</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>3.7</v>
+        <v>32</v>
       </c>
       <c r="I58" t="n">
         <v>2728.6</v>
@@ -5361,11 +5361,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>87.40000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>2263</v>
+        <v>2311.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2304.55</v>
+        <v>2322.7</v>
       </c>
       <c r="K2" t="n">
-        <v>2335.9</v>
+        <v>2348</v>
       </c>
       <c r="L2" t="n">
-        <v>2367.25</v>
+        <v>2373.3</v>
       </c>
       <c r="M2" t="n">
-        <v>2403.7</v>
+        <v>2391.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2440.15</v>
+        <v>2409.9</v>
       </c>
       <c r="O2" t="n">
-        <v>2466.4</v>
+        <v>2442.2</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,8 +700,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5296,19 +5298,19 @@
         <v>2858.8</v>
       </c>
       <c r="D58" t="n">
-        <v>2826.8</v>
+        <v>2811.9</v>
       </c>
       <c r="E58" t="n">
-        <v>2834.1</v>
+        <v>2821.2</v>
       </c>
       <c r="F58" t="n">
-        <v>-25.2</v>
+        <v>-38.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0133</v>
       </c>
       <c r="H58" t="n">
-        <v>32</v>
+        <v>46.9</v>
       </c>
       <c r="I58" t="n">
         <v>2728.6</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -659,31 +659,33 @@
         <v>87.40000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>2311.4</v>
+        <v>2325.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2322.7</v>
+        <v>2328.1</v>
       </c>
       <c r="K2" t="n">
-        <v>2348</v>
+        <v>2351.6</v>
       </c>
       <c r="L2" t="n">
-        <v>2373.3</v>
+        <v>2375.1</v>
       </c>
       <c r="M2" t="n">
-        <v>2391.6</v>
+        <v>2388</v>
       </c>
       <c r="N2" t="n">
-        <v>2409.9</v>
+        <v>2400.9</v>
       </c>
       <c r="O2" t="n">
-        <v>2442.2</v>
+        <v>2435</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -5301,13 +5303,13 @@
         <v>2811.9</v>
       </c>
       <c r="E58" t="n">
-        <v>2821.2</v>
+        <v>2830.4</v>
       </c>
       <c r="F58" t="n">
-        <v>-38.1</v>
+        <v>-28.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0133</v>
+        <v>-0.0101</v>
       </c>
       <c r="H58" t="n">
         <v>46.9</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,78 +634,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2373</v>
+        <v>2391.8</v>
       </c>
       <c r="C2" t="n">
-        <v>2413.5</v>
+        <v>2424.7</v>
       </c>
       <c r="D2" t="n">
-        <v>2326.1</v>
+        <v>2369.9</v>
       </c>
       <c r="E2" t="n">
-        <v>2393.5</v>
+        <v>2397.9</v>
       </c>
       <c r="F2" t="n">
-        <v>23.7</v>
+        <v>4.4</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0018</v>
       </c>
       <c r="H2" t="n">
-        <v>87.40000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2325.8</v>
+        <v>2238.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2328.1</v>
+        <v>2317.95</v>
       </c>
       <c r="K2" t="n">
-        <v>2351.6</v>
+        <v>2349.8</v>
       </c>
       <c r="L2" t="n">
-        <v>2375.1</v>
+        <v>2381.65</v>
       </c>
       <c r="M2" t="n">
-        <v>2388</v>
+        <v>2437.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2400.9</v>
+        <v>2492.75</v>
       </c>
       <c r="O2" t="n">
-        <v>2435</v>
+        <v>2500.9</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -715,59 +707,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2391.8</v>
+        <v>2398</v>
       </c>
       <c r="C3" t="n">
-        <v>2424.7</v>
+        <v>2485.1</v>
       </c>
       <c r="D3" t="n">
-        <v>2369.9</v>
+        <v>2388.3</v>
       </c>
       <c r="E3" t="n">
-        <v>2397.9</v>
+        <v>2472.04</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4</v>
+        <v>74.14</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0309</v>
       </c>
       <c r="H3" t="n">
-        <v>54.8</v>
+        <v>96.8</v>
       </c>
       <c r="I3" t="n">
-        <v>2238.7</v>
+        <v>2315.1</v>
       </c>
       <c r="J3" t="n">
-        <v>2317.95</v>
+        <v>2343.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2349.8</v>
+        <v>2370.5</v>
       </c>
       <c r="L3" t="n">
-        <v>2381.65</v>
+        <v>2397.6</v>
       </c>
       <c r="M3" t="n">
-        <v>2437.2</v>
+        <v>2425.3</v>
       </c>
       <c r="N3" t="n">
-        <v>2492.75</v>
+        <v>2453</v>
       </c>
       <c r="O3" t="n">
-        <v>2500.9</v>
+        <v>2479.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -780,17 +768,23 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -802,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2398</v>
+        <v>2469.5</v>
       </c>
       <c r="C4" t="n">
-        <v>2485.1</v>
+        <v>2510.3</v>
       </c>
       <c r="D4" t="n">
-        <v>2388.3</v>
+        <v>2412.1</v>
       </c>
       <c r="E4" t="n">
-        <v>2472.04</v>
+        <v>2450.4</v>
       </c>
       <c r="F4" t="n">
-        <v>74.14</v>
+        <v>-21.64</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0309</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>96.8</v>
+        <v>98.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2315.1</v>
+        <v>2291.5</v>
       </c>
       <c r="J4" t="n">
-        <v>2343.4</v>
+        <v>2392.91</v>
       </c>
       <c r="K4" t="n">
-        <v>2370.5</v>
+        <v>2423.64</v>
       </c>
       <c r="L4" t="n">
-        <v>2397.6</v>
+        <v>2454.37</v>
       </c>
       <c r="M4" t="n">
-        <v>2425.3</v>
+        <v>2520.44</v>
       </c>
       <c r="N4" t="n">
-        <v>2453</v>
+        <v>2586.51</v>
       </c>
       <c r="O4" t="n">
-        <v>2479.5</v>
+        <v>2581.9</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,83 +847,83 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2469.5</v>
+        <v>2449.2</v>
       </c>
       <c r="C5" t="n">
-        <v>2510.3</v>
+        <v>2515</v>
       </c>
       <c r="D5" t="n">
-        <v>2412.1</v>
+        <v>2424.7</v>
       </c>
       <c r="E5" t="n">
-        <v>2450.4</v>
+        <v>2492.1</v>
       </c>
       <c r="F5" t="n">
-        <v>-21.64</v>
+        <v>41.7</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="H5" t="n">
-        <v>98.2</v>
+        <v>90.3</v>
       </c>
       <c r="I5" t="n">
-        <v>2291.5</v>
+        <v>2313.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2392.91</v>
+        <v>2346.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2423.64</v>
+        <v>2401.3</v>
       </c>
       <c r="L5" t="n">
-        <v>2454.37</v>
+        <v>2455.8</v>
       </c>
       <c r="M5" t="n">
-        <v>2520.44</v>
+        <v>2499.5</v>
       </c>
       <c r="N5" t="n">
-        <v>2586.51</v>
+        <v>2543.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2581.9</v>
+        <v>2608.5</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -937,18 +931,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -961,164 +955,166 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2449.2</v>
+        <v>2491.9</v>
       </c>
       <c r="C6" t="n">
-        <v>2515</v>
+        <v>2518.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2424.7</v>
+        <v>2381.8</v>
       </c>
       <c r="E6" t="n">
-        <v>2492.1</v>
+        <v>2408.5</v>
       </c>
       <c r="F6" t="n">
-        <v>41.7</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.017</v>
+        <v>-0.0335</v>
       </c>
       <c r="H6" t="n">
-        <v>90.3</v>
+        <v>136.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2313.9</v>
+        <v>2334.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2346.8</v>
+        <v>2412.93</v>
       </c>
       <c r="K6" t="n">
-        <v>2401.3</v>
+        <v>2446.95</v>
       </c>
       <c r="L6" t="n">
-        <v>2455.8</v>
+        <v>2480.98</v>
       </c>
       <c r="M6" t="n">
-        <v>2499.5</v>
+        <v>2537.25</v>
       </c>
       <c r="N6" t="n">
-        <v>2543.2</v>
+        <v>2593.53</v>
       </c>
       <c r="O6" t="n">
-        <v>2608.5</v>
+        <v>2605.3</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2491.9</v>
+        <v>2421.6</v>
       </c>
       <c r="C7" t="n">
-        <v>2518.5</v>
+        <v>2559.9</v>
       </c>
       <c r="D7" t="n">
-        <v>2381.8</v>
+        <v>2421.6</v>
       </c>
       <c r="E7" t="n">
-        <v>2408.5</v>
+        <v>2464.4</v>
       </c>
       <c r="F7" t="n">
-        <v>-83.59999999999999</v>
+        <v>55.9</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0335</v>
+        <v>0.0232</v>
       </c>
       <c r="H7" t="n">
-        <v>136.7</v>
+        <v>138.3</v>
       </c>
       <c r="I7" t="n">
-        <v>2334.4</v>
+        <v>2245.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2412.93</v>
+        <v>2250.98</v>
       </c>
       <c r="K7" t="n">
-        <v>2446.95</v>
+        <v>2340.15</v>
       </c>
       <c r="L7" t="n">
-        <v>2480.98</v>
+        <v>2429.33</v>
       </c>
       <c r="M7" t="n">
-        <v>2537.25</v>
+        <v>2476.85</v>
       </c>
       <c r="N7" t="n">
-        <v>2593.53</v>
+        <v>2524.37</v>
       </c>
       <c r="O7" t="n">
-        <v>2605.3</v>
+        <v>2655.2</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1129,57 +1125,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2421.6</v>
+        <v>2473.7</v>
       </c>
       <c r="C8" t="n">
-        <v>2559.9</v>
+        <v>2544</v>
       </c>
       <c r="D8" t="n">
-        <v>2421.6</v>
+        <v>2436.9</v>
       </c>
       <c r="E8" t="n">
-        <v>2464.4</v>
+        <v>2523.7</v>
       </c>
       <c r="F8" t="n">
-        <v>55.9</v>
+        <v>59.3</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0232</v>
+        <v>0.0241</v>
       </c>
       <c r="H8" t="n">
-        <v>138.3</v>
+        <v>107.1</v>
       </c>
       <c r="I8" t="n">
-        <v>2245.1</v>
+        <v>2283.3</v>
       </c>
       <c r="J8" t="n">
-        <v>2250.98</v>
+        <v>2312.93</v>
       </c>
       <c r="K8" t="n">
-        <v>2340.15</v>
+        <v>2395.25</v>
       </c>
       <c r="L8" t="n">
-        <v>2429.33</v>
+        <v>2477.57</v>
       </c>
       <c r="M8" t="n">
-        <v>2476.85</v>
+        <v>2533.55</v>
       </c>
       <c r="N8" t="n">
-        <v>2524.37</v>
+        <v>2589.52</v>
       </c>
       <c r="O8" t="n">
-        <v>2655.2</v>
+        <v>2698.2</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1200,10 +1196,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1215,57 +1209,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2473.7</v>
+        <v>2551.8</v>
       </c>
       <c r="C9" t="n">
-        <v>2544</v>
+        <v>2566.5</v>
       </c>
       <c r="D9" t="n">
-        <v>2436.9</v>
+        <v>2463</v>
       </c>
       <c r="E9" t="n">
-        <v>2523.7</v>
+        <v>2489.9</v>
       </c>
       <c r="F9" t="n">
-        <v>59.3</v>
+        <v>-33.8</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0241</v>
+        <v>-0.0134</v>
       </c>
       <c r="H9" t="n">
-        <v>107.1</v>
+        <v>103.5</v>
       </c>
       <c r="I9" t="n">
-        <v>2283.3</v>
+        <v>2329.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2312.93</v>
+        <v>2433.22</v>
       </c>
       <c r="K9" t="n">
-        <v>2395.25</v>
+        <v>2470.15</v>
       </c>
       <c r="L9" t="n">
-        <v>2477.57</v>
+        <v>2507.07</v>
       </c>
       <c r="M9" t="n">
-        <v>2533.55</v>
+        <v>2577.25</v>
       </c>
       <c r="N9" t="n">
-        <v>2589.52</v>
+        <v>2647.43</v>
       </c>
       <c r="O9" t="n">
-        <v>2698.2</v>
+        <v>2651.1</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,18 +1267,18 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1306,50 +1300,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2551.8</v>
+        <v>2489.1</v>
       </c>
       <c r="C10" t="n">
-        <v>2566.5</v>
+        <v>2500.4</v>
       </c>
       <c r="D10" t="n">
-        <v>2463</v>
+        <v>2386.6</v>
       </c>
       <c r="E10" t="n">
-        <v>2489.9</v>
+        <v>2440.6</v>
       </c>
       <c r="F10" t="n">
-        <v>-33.8</v>
+        <v>-49.3</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0134</v>
+        <v>-0.0198</v>
       </c>
       <c r="H10" t="n">
-        <v>103.5</v>
+        <v>113.8</v>
       </c>
       <c r="I10" t="n">
-        <v>2329.8</v>
+        <v>2359.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2433.22</v>
+        <v>2373.97</v>
       </c>
       <c r="K10" t="n">
-        <v>2470.15</v>
+        <v>2438.15</v>
       </c>
       <c r="L10" t="n">
-        <v>2507.07</v>
+        <v>2502.32</v>
       </c>
       <c r="M10" t="n">
-        <v>2577.25</v>
+        <v>2541.65</v>
       </c>
       <c r="N10" t="n">
-        <v>2647.43</v>
+        <v>2580.97</v>
       </c>
       <c r="O10" t="n">
-        <v>2651.1</v>
+        <v>2670</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1359,12 +1353,12 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1381,59 +1375,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2489.1</v>
+        <v>2455.2</v>
       </c>
       <c r="C11" t="n">
-        <v>2500.4</v>
+        <v>2487.6</v>
       </c>
       <c r="D11" t="n">
-        <v>2386.6</v>
+        <v>2353.8</v>
       </c>
       <c r="E11" t="n">
-        <v>2440.6</v>
+        <v>2396</v>
       </c>
       <c r="F11" t="n">
-        <v>-49.3</v>
+        <v>-44.6</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0198</v>
+        <v>-0.0183</v>
       </c>
       <c r="H11" t="n">
-        <v>113.8</v>
+        <v>133.8</v>
       </c>
       <c r="I11" t="n">
-        <v>2359.5</v>
+        <v>2272.8</v>
       </c>
       <c r="J11" t="n">
-        <v>2373.97</v>
+        <v>2325.35</v>
       </c>
       <c r="K11" t="n">
-        <v>2438.15</v>
+        <v>2383.7</v>
       </c>
       <c r="L11" t="n">
-        <v>2502.32</v>
+        <v>2442.05</v>
       </c>
       <c r="M11" t="n">
-        <v>2541.65</v>
+        <v>2497.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2580.97</v>
+        <v>2552.95</v>
       </c>
       <c r="O11" t="n">
-        <v>2670</v>
+        <v>2614.2</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1470,50 +1460,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2455.2</v>
+        <v>2397</v>
       </c>
       <c r="C12" t="n">
-        <v>2487.6</v>
+        <v>2411.9</v>
       </c>
       <c r="D12" t="n">
-        <v>2353.8</v>
+        <v>2300.7</v>
       </c>
       <c r="E12" t="n">
-        <v>2396</v>
+        <v>2375.3</v>
       </c>
       <c r="F12" t="n">
-        <v>-44.6</v>
+        <v>-20.7</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.0086</v>
       </c>
       <c r="H12" t="n">
-        <v>133.8</v>
+        <v>111.2</v>
       </c>
       <c r="I12" t="n">
-        <v>2272.8</v>
+        <v>2220</v>
       </c>
       <c r="J12" t="n">
-        <v>2325.35</v>
+        <v>2249.85</v>
       </c>
       <c r="K12" t="n">
-        <v>2383.7</v>
+        <v>2329.1</v>
       </c>
       <c r="L12" t="n">
-        <v>2442.05</v>
+        <v>2408.35</v>
       </c>
       <c r="M12" t="n">
-        <v>2497.5</v>
+        <v>2462.9</v>
       </c>
       <c r="N12" t="n">
-        <v>2552.95</v>
+        <v>2517.45</v>
       </c>
       <c r="O12" t="n">
-        <v>2614.2</v>
+        <v>2621.4</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1523,12 +1513,12 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1550,50 +1540,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2397</v>
+        <v>2387.8</v>
       </c>
       <c r="C13" t="n">
-        <v>2411.9</v>
+        <v>2508.1</v>
       </c>
       <c r="D13" t="n">
-        <v>2300.7</v>
+        <v>2370.3</v>
       </c>
       <c r="E13" t="n">
-        <v>2375.3</v>
+        <v>2505.1</v>
       </c>
       <c r="F13" t="n">
-        <v>-20.7</v>
+        <v>129.8</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0546</v>
       </c>
       <c r="H13" t="n">
-        <v>111.2</v>
+        <v>137.8</v>
       </c>
       <c r="I13" t="n">
-        <v>2220</v>
+        <v>2189.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2249.85</v>
+        <v>2273.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2329.1</v>
+        <v>2319.7</v>
       </c>
       <c r="L13" t="n">
-        <v>2408.35</v>
+        <v>2365.8</v>
       </c>
       <c r="M13" t="n">
-        <v>2462.9</v>
+        <v>2430.9</v>
       </c>
       <c r="N13" t="n">
-        <v>2517.45</v>
+        <v>2496</v>
       </c>
       <c r="O13" t="n">
-        <v>2621.4</v>
+        <v>2523.1</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1601,28 +1591,30 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -1630,50 +1622,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2387.8</v>
+        <v>2501</v>
       </c>
       <c r="C14" t="n">
-        <v>2508.1</v>
+        <v>2544.2</v>
       </c>
       <c r="D14" t="n">
-        <v>2370.3</v>
+        <v>2468.1</v>
       </c>
       <c r="E14" t="n">
-        <v>2505.1</v>
+        <v>2524.4</v>
       </c>
       <c r="F14" t="n">
-        <v>129.8</v>
+        <v>19.3</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0077</v>
       </c>
       <c r="H14" t="n">
-        <v>137.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>2189.5</v>
+        <v>2232.5</v>
       </c>
       <c r="J14" t="n">
-        <v>2273.6</v>
+        <v>2400.25</v>
       </c>
       <c r="K14" t="n">
-        <v>2319.7</v>
+        <v>2436.2</v>
       </c>
       <c r="L14" t="n">
-        <v>2365.8</v>
+        <v>2472.15</v>
       </c>
       <c r="M14" t="n">
-        <v>2430.9</v>
+        <v>2574</v>
       </c>
       <c r="N14" t="n">
-        <v>2496</v>
+        <v>2675.85</v>
       </c>
       <c r="O14" t="n">
-        <v>2523.1</v>
+        <v>2645.9</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1691,13 +1683,11 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1712,50 +1702,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2501</v>
+        <v>2528</v>
       </c>
       <c r="C15" t="n">
-        <v>2544.2</v>
+        <v>2605</v>
       </c>
       <c r="D15" t="n">
-        <v>2468.1</v>
+        <v>2516.6</v>
       </c>
       <c r="E15" t="n">
-        <v>2524.4</v>
+        <v>2553.7</v>
       </c>
       <c r="F15" t="n">
-        <v>19.3</v>
+        <v>29.3</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0116</v>
       </c>
       <c r="H15" t="n">
-        <v>76.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2232.5</v>
+        <v>2392</v>
       </c>
       <c r="J15" t="n">
-        <v>2400.25</v>
+        <v>2457.42</v>
       </c>
       <c r="K15" t="n">
-        <v>2436.2</v>
+        <v>2486.35</v>
       </c>
       <c r="L15" t="n">
-        <v>2472.15</v>
+        <v>2515.27</v>
       </c>
       <c r="M15" t="n">
-        <v>2574</v>
+        <v>2562.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2675.85</v>
+        <v>2609.62</v>
       </c>
       <c r="O15" t="n">
-        <v>2645.9</v>
+        <v>2620.3</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1792,50 +1782,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2528</v>
+        <v>2552.8</v>
       </c>
       <c r="C16" t="n">
-        <v>2605</v>
+        <v>2577.3</v>
       </c>
       <c r="D16" t="n">
-        <v>2516.6</v>
+        <v>2489.4</v>
       </c>
       <c r="E16" t="n">
-        <v>2553.7</v>
+        <v>2509.56</v>
       </c>
       <c r="F16" t="n">
-        <v>29.3</v>
+        <v>-44.14</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0116</v>
+        <v>-0.0173</v>
       </c>
       <c r="H16" t="n">
-        <v>88.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>2392</v>
+        <v>2428.2</v>
       </c>
       <c r="J16" t="n">
-        <v>2457.42</v>
+        <v>2461.75</v>
       </c>
       <c r="K16" t="n">
-        <v>2486.35</v>
+        <v>2509.5</v>
       </c>
       <c r="L16" t="n">
-        <v>2515.27</v>
+        <v>2557.25</v>
       </c>
       <c r="M16" t="n">
-        <v>2562.45</v>
+        <v>2597.9</v>
       </c>
       <c r="N16" t="n">
-        <v>2609.62</v>
+        <v>2638.55</v>
       </c>
       <c r="O16" t="n">
-        <v>2620.3</v>
+        <v>2693.4</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1843,19 +1833,19 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1867,55 +1857,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2552.8</v>
+        <v>2550</v>
       </c>
       <c r="C17" t="n">
-        <v>2577.3</v>
+        <v>2590.3</v>
       </c>
       <c r="D17" t="n">
-        <v>2489.4</v>
+        <v>2540.8</v>
       </c>
       <c r="E17" t="n">
-        <v>2509.56</v>
+        <v>2551.4</v>
       </c>
       <c r="F17" t="n">
-        <v>-44.14</v>
+        <v>41.84</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0173</v>
+        <v>0.0167</v>
       </c>
       <c r="H17" t="n">
-        <v>87.90000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="I17" t="n">
-        <v>2428.2</v>
+        <v>2401.5</v>
       </c>
       <c r="J17" t="n">
-        <v>2461.75</v>
+        <v>2409.76</v>
       </c>
       <c r="K17" t="n">
-        <v>2509.5</v>
+        <v>2465.61</v>
       </c>
       <c r="L17" t="n">
-        <v>2557.25</v>
+        <v>2521.46</v>
       </c>
       <c r="M17" t="n">
-        <v>2597.9</v>
+        <v>2553.51</v>
       </c>
       <c r="N17" t="n">
-        <v>2638.55</v>
+        <v>2585.57</v>
       </c>
       <c r="O17" t="n">
-        <v>2693.4</v>
+        <v>2665.2</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1923,21 +1917,23 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1947,83 +1943,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2550</v>
+        <v>2551.6</v>
       </c>
       <c r="C18" t="n">
-        <v>2590.3</v>
+        <v>2556.9</v>
       </c>
       <c r="D18" t="n">
-        <v>2540.8</v>
+        <v>2493.5</v>
       </c>
       <c r="E18" t="n">
-        <v>2551.4</v>
+        <v>2522.5</v>
       </c>
       <c r="F18" t="n">
-        <v>41.84</v>
+        <v>-28.9</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0167</v>
+        <v>-0.0113</v>
       </c>
       <c r="H18" t="n">
-        <v>49.5</v>
+        <v>63.4</v>
       </c>
       <c r="I18" t="n">
-        <v>2401.5</v>
+        <v>2491.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2409.76</v>
+        <v>2494.82</v>
       </c>
       <c r="K18" t="n">
-        <v>2465.61</v>
+        <v>2526.65</v>
       </c>
       <c r="L18" t="n">
-        <v>2521.46</v>
+        <v>2558.47</v>
       </c>
       <c r="M18" t="n">
-        <v>2553.51</v>
+        <v>2576.15</v>
       </c>
       <c r="N18" t="n">
-        <v>2585.57</v>
+        <v>2593.82</v>
       </c>
       <c r="O18" t="n">
-        <v>2665.2</v>
+        <v>2639.8</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2033,141 +2025,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2551.6</v>
+        <v>2524.2</v>
       </c>
       <c r="C19" t="n">
-        <v>2556.9</v>
+        <v>2650.3</v>
       </c>
       <c r="D19" t="n">
-        <v>2493.5</v>
+        <v>2517.2</v>
       </c>
       <c r="E19" t="n">
-        <v>2522.5</v>
+        <v>2636.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-28.9</v>
+        <v>114.4</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0113</v>
+        <v>0.0454</v>
       </c>
       <c r="H19" t="n">
-        <v>63.4</v>
+        <v>133.1</v>
       </c>
       <c r="I19" t="n">
-        <v>2491.3</v>
+        <v>2430.1</v>
       </c>
       <c r="J19" t="n">
-        <v>2494.82</v>
+        <v>2457.75</v>
       </c>
       <c r="K19" t="n">
-        <v>2526.65</v>
+        <v>2490.8</v>
       </c>
       <c r="L19" t="n">
-        <v>2558.47</v>
+        <v>2523.85</v>
       </c>
       <c r="M19" t="n">
-        <v>2576.15</v>
+        <v>2554.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2593.82</v>
+        <v>2584.55</v>
       </c>
       <c r="O19" t="n">
-        <v>2639.8</v>
+        <v>2620.3</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2524.2</v>
+        <v>2638.9</v>
       </c>
       <c r="C20" t="n">
-        <v>2650.3</v>
+        <v>2705.6</v>
       </c>
       <c r="D20" t="n">
-        <v>2517.2</v>
+        <v>2616.3</v>
       </c>
       <c r="E20" t="n">
-        <v>2636.9</v>
+        <v>2691.2</v>
       </c>
       <c r="F20" t="n">
-        <v>114.4</v>
+        <v>54.3</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0454</v>
+        <v>0.0206</v>
       </c>
       <c r="H20" t="n">
-        <v>133.1</v>
+        <v>89.3</v>
       </c>
       <c r="I20" t="n">
-        <v>2430.1</v>
+        <v>2384.1</v>
       </c>
       <c r="J20" t="n">
-        <v>2457.75</v>
+        <v>2530.37</v>
       </c>
       <c r="K20" t="n">
-        <v>2490.8</v>
+        <v>2570.35</v>
       </c>
       <c r="L20" t="n">
-        <v>2523.85</v>
+        <v>2610.32</v>
       </c>
       <c r="M20" t="n">
-        <v>2554.2</v>
+        <v>2703.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2584.55</v>
+        <v>2796.57</v>
       </c>
       <c r="O20" t="n">
-        <v>2620.3</v>
+        <v>2783.4</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2185,18 +2179,14 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2208,50 +2198,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2638.9</v>
+        <v>2670</v>
       </c>
       <c r="C21" t="n">
-        <v>2705.6</v>
+        <v>2749.2</v>
       </c>
       <c r="D21" t="n">
-        <v>2616.3</v>
+        <v>2631</v>
       </c>
       <c r="E21" t="n">
-        <v>2691.2</v>
+        <v>2679.6</v>
       </c>
       <c r="F21" t="n">
-        <v>54.3</v>
+        <v>-11.6</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0206</v>
+        <v>-0.0043</v>
       </c>
       <c r="H21" t="n">
-        <v>89.3</v>
+        <v>118.2</v>
       </c>
       <c r="I21" t="n">
-        <v>2384.1</v>
+        <v>2527</v>
       </c>
       <c r="J21" t="n">
-        <v>2530.37</v>
+        <v>2617.02</v>
       </c>
       <c r="K21" t="n">
-        <v>2570.35</v>
+        <v>2646.55</v>
       </c>
       <c r="L21" t="n">
-        <v>2610.32</v>
+        <v>2676.08</v>
       </c>
       <c r="M21" t="n">
-        <v>2703.45</v>
+        <v>2735.85</v>
       </c>
       <c r="N21" t="n">
-        <v>2796.57</v>
+        <v>2795.62</v>
       </c>
       <c r="O21" t="n">
-        <v>2783.4</v>
+        <v>2794.9</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2259,17 +2249,19 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U21" s="8" t="n">
@@ -2283,55 +2275,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2670</v>
+        <v>2661</v>
       </c>
       <c r="C22" t="n">
-        <v>2749.2</v>
+        <v>2697.9</v>
       </c>
       <c r="D22" t="n">
-        <v>2631</v>
+        <v>2607.5</v>
       </c>
       <c r="E22" t="n">
-        <v>2679.6</v>
+        <v>2624.6</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.6</v>
+        <v>-55</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0205</v>
       </c>
       <c r="H22" t="n">
-        <v>118.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>2527</v>
+        <v>2512.8</v>
       </c>
       <c r="J22" t="n">
-        <v>2617.02</v>
+        <v>2556.15</v>
       </c>
       <c r="K22" t="n">
-        <v>2646.55</v>
+        <v>2620.5</v>
       </c>
       <c r="L22" t="n">
-        <v>2676.08</v>
+        <v>2684.85</v>
       </c>
       <c r="M22" t="n">
-        <v>2735.85</v>
+        <v>2738.7</v>
       </c>
       <c r="N22" t="n">
-        <v>2795.62</v>
+        <v>2792.55</v>
       </c>
       <c r="O22" t="n">
-        <v>2794.9</v>
+        <v>2867.4</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2341,18 +2337,16 @@
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2367,57 +2361,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2661</v>
+        <v>2615</v>
       </c>
       <c r="C23" t="n">
-        <v>2697.9</v>
+        <v>2684.1</v>
       </c>
       <c r="D23" t="n">
-        <v>2607.5</v>
+        <v>2566.8</v>
       </c>
       <c r="E23" t="n">
-        <v>2624.6</v>
+        <v>2677.9</v>
       </c>
       <c r="F23" t="n">
-        <v>-55</v>
+        <v>53.3</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0205</v>
+        <v>0.0203</v>
       </c>
       <c r="H23" t="n">
-        <v>90.40000000000001</v>
+        <v>117.3</v>
       </c>
       <c r="I23" t="n">
-        <v>2512.8</v>
+        <v>2517.1</v>
       </c>
       <c r="J23" t="n">
-        <v>2556.15</v>
+        <v>2520.15</v>
       </c>
       <c r="K23" t="n">
-        <v>2620.5</v>
+        <v>2579.4</v>
       </c>
       <c r="L23" t="n">
-        <v>2684.85</v>
+        <v>2638.65</v>
       </c>
       <c r="M23" t="n">
-        <v>2738.7</v>
+        <v>2669.8</v>
       </c>
       <c r="N23" t="n">
-        <v>2792.55</v>
+        <v>2700.95</v>
       </c>
       <c r="O23" t="n">
-        <v>2867.4</v>
+        <v>2788.3</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2427,17 +2421,19 @@
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2451,57 +2447,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2615</v>
+        <v>2677</v>
       </c>
       <c r="C24" t="n">
-        <v>2684.1</v>
+        <v>2720</v>
       </c>
       <c r="D24" t="n">
-        <v>2566.8</v>
+        <v>2607.3</v>
       </c>
       <c r="E24" t="n">
-        <v>2677.9</v>
+        <v>2653.1</v>
       </c>
       <c r="F24" t="n">
-        <v>53.3</v>
+        <v>-24.8</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0203</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>117.3</v>
+        <v>112.7</v>
       </c>
       <c r="I24" t="n">
-        <v>2517.1</v>
+        <v>2449.5</v>
       </c>
       <c r="J24" t="n">
-        <v>2520.15</v>
+        <v>2586.82</v>
       </c>
       <c r="K24" t="n">
-        <v>2579.4</v>
+        <v>2619.25</v>
       </c>
       <c r="L24" t="n">
-        <v>2638.65</v>
+        <v>2651.67</v>
       </c>
       <c r="M24" t="n">
-        <v>2669.8</v>
+        <v>2736.55</v>
       </c>
       <c r="N24" t="n">
-        <v>2700.95</v>
+        <v>2821.42</v>
       </c>
       <c r="O24" t="n">
-        <v>2788.3</v>
+        <v>2801.4</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2516,13 +2512,11 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2537,57 +2531,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2677</v>
+        <v>2650.9</v>
       </c>
       <c r="C25" t="n">
-        <v>2720</v>
+        <v>2696</v>
       </c>
       <c r="D25" t="n">
-        <v>2607.3</v>
+        <v>2613.7</v>
       </c>
       <c r="E25" t="n">
-        <v>2653.1</v>
+        <v>2668.8</v>
       </c>
       <c r="F25" t="n">
-        <v>-24.8</v>
+        <v>15.7</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H25" t="n">
-        <v>112.7</v>
+        <v>82.3</v>
       </c>
       <c r="I25" t="n">
-        <v>2449.5</v>
+        <v>2494.6</v>
       </c>
       <c r="J25" t="n">
-        <v>2586.82</v>
+        <v>2535.13</v>
       </c>
       <c r="K25" t="n">
-        <v>2619.25</v>
+        <v>2596.75</v>
       </c>
       <c r="L25" t="n">
-        <v>2651.67</v>
+        <v>2658.38</v>
       </c>
       <c r="M25" t="n">
-        <v>2736.55</v>
+        <v>2709.45</v>
       </c>
       <c r="N25" t="n">
-        <v>2821.42</v>
+        <v>2760.53</v>
       </c>
       <c r="O25" t="n">
-        <v>2801.4</v>
+        <v>2832.7</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2595,10 +2589,8 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
@@ -2628,50 +2620,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2650.9</v>
+        <v>2666.5</v>
       </c>
       <c r="C26" t="n">
-        <v>2696</v>
+        <v>2683.4</v>
       </c>
       <c r="D26" t="n">
-        <v>2613.7</v>
+        <v>2602.7</v>
       </c>
       <c r="E26" t="n">
-        <v>2668.8</v>
+        <v>2634.7</v>
       </c>
       <c r="F26" t="n">
-        <v>15.7</v>
+        <v>-34.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0128</v>
       </c>
       <c r="H26" t="n">
-        <v>82.3</v>
+        <v>80.7</v>
       </c>
       <c r="I26" t="n">
-        <v>2494.6</v>
+        <v>2531.4</v>
       </c>
       <c r="J26" t="n">
-        <v>2535.13</v>
+        <v>2593.48</v>
       </c>
       <c r="K26" t="n">
-        <v>2596.75</v>
+        <v>2627.65</v>
       </c>
       <c r="L26" t="n">
-        <v>2658.38</v>
+        <v>2661.83</v>
       </c>
       <c r="M26" t="n">
-        <v>2709.45</v>
+        <v>2709.95</v>
       </c>
       <c r="N26" t="n">
-        <v>2760.53</v>
+        <v>2758.08</v>
       </c>
       <c r="O26" t="n">
-        <v>2832.7</v>
+        <v>2778.3</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2679,12 +2671,14 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2703,67 +2697,71 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2666.5</v>
+        <v>2608.8</v>
       </c>
       <c r="C27" t="n">
-        <v>2683.4</v>
+        <v>2663.3</v>
       </c>
       <c r="D27" t="n">
-        <v>2602.7</v>
+        <v>2516.6</v>
       </c>
       <c r="E27" t="n">
-        <v>2634.7</v>
+        <v>2526.7</v>
       </c>
       <c r="F27" t="n">
-        <v>-34.1</v>
+        <v>-108</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0128</v>
+        <v>-0.041</v>
       </c>
       <c r="H27" t="n">
-        <v>80.7</v>
+        <v>146.7</v>
       </c>
       <c r="I27" t="n">
-        <v>2531.4</v>
+        <v>2522</v>
       </c>
       <c r="J27" t="n">
-        <v>2593.48</v>
+        <v>2549.83</v>
       </c>
       <c r="K27" t="n">
-        <v>2627.65</v>
+        <v>2594.35</v>
       </c>
       <c r="L27" t="n">
-        <v>2661.83</v>
+        <v>2638.87</v>
       </c>
       <c r="M27" t="n">
-        <v>2709.95</v>
+        <v>2675.05</v>
       </c>
       <c r="N27" t="n">
-        <v>2758.08</v>
+        <v>2711.22</v>
       </c>
       <c r="O27" t="n">
-        <v>2778.3</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+        <v>2764.1</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
@@ -2780,78 +2778,70 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2608.8</v>
+        <v>2499.2</v>
       </c>
       <c r="C28" t="n">
-        <v>2663.3</v>
+        <v>2594.4</v>
       </c>
       <c r="D28" t="n">
-        <v>2516.6</v>
+        <v>2416.9</v>
       </c>
       <c r="E28" t="n">
-        <v>2526.7</v>
+        <v>2480.9</v>
       </c>
       <c r="F28" t="n">
-        <v>-108</v>
+        <v>-45.8</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.041</v>
+        <v>-0.0181</v>
       </c>
       <c r="H28" t="n">
-        <v>146.7</v>
+        <v>177.5</v>
       </c>
       <c r="I28" t="n">
-        <v>2522</v>
+        <v>2369.9</v>
       </c>
       <c r="J28" t="n">
-        <v>2549.83</v>
+        <v>2348.37</v>
       </c>
       <c r="K28" t="n">
-        <v>2594.35</v>
+        <v>2453.35</v>
       </c>
       <c r="L28" t="n">
-        <v>2638.87</v>
+        <v>2558.33</v>
       </c>
       <c r="M28" t="n">
-        <v>2675.05</v>
+        <v>2600.05</v>
       </c>
       <c r="N28" t="n">
-        <v>2711.22</v>
+        <v>2641.77</v>
       </c>
       <c r="O28" t="n">
-        <v>2764.1</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
+        <v>2810</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
@@ -2878,50 +2868,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2499.2</v>
+        <v>2468.5</v>
       </c>
       <c r="C29" t="n">
-        <v>2594.4</v>
+        <v>2547.9</v>
       </c>
       <c r="D29" t="n">
-        <v>2416.9</v>
+        <v>2442</v>
       </c>
       <c r="E29" t="n">
-        <v>2480.9</v>
+        <v>2496.4</v>
       </c>
       <c r="F29" t="n">
-        <v>-45.8</v>
+        <v>15.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0181</v>
+        <v>0.0062</v>
       </c>
       <c r="H29" t="n">
-        <v>177.5</v>
+        <v>105.9</v>
       </c>
       <c r="I29" t="n">
-        <v>2369.9</v>
+        <v>2239.4</v>
       </c>
       <c r="J29" t="n">
-        <v>2348.37</v>
+        <v>2291.02</v>
       </c>
       <c r="K29" t="n">
-        <v>2453.35</v>
+        <v>2392.15</v>
       </c>
       <c r="L29" t="n">
-        <v>2558.33</v>
+        <v>2493.27</v>
       </c>
       <c r="M29" t="n">
-        <v>2600.05</v>
+        <v>2569.65</v>
       </c>
       <c r="N29" t="n">
-        <v>2641.77</v>
+        <v>2646.02</v>
       </c>
       <c r="O29" t="n">
-        <v>2810</v>
+        <v>2771.9</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2929,14 +2919,12 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2953,55 +2941,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2468.5</v>
+        <v>2429.1</v>
       </c>
       <c r="C30" t="n">
-        <v>2547.9</v>
+        <v>2574.5</v>
       </c>
       <c r="D30" t="n">
-        <v>2442</v>
+        <v>2415.3</v>
       </c>
       <c r="E30" t="n">
-        <v>2496.4</v>
+        <v>2464</v>
       </c>
       <c r="F30" t="n">
-        <v>15.5</v>
+        <v>-32.4</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.013</v>
       </c>
       <c r="H30" t="n">
-        <v>105.9</v>
+        <v>159.2</v>
       </c>
       <c r="I30" t="n">
-        <v>2239.4</v>
+        <v>2336.1</v>
       </c>
       <c r="J30" t="n">
-        <v>2291.02</v>
+        <v>2391.22</v>
       </c>
       <c r="K30" t="n">
-        <v>2392.15</v>
+        <v>2443.45</v>
       </c>
       <c r="L30" t="n">
-        <v>2493.27</v>
+        <v>2495.67</v>
       </c>
       <c r="M30" t="n">
-        <v>2569.65</v>
+        <v>2549.35</v>
       </c>
       <c r="N30" t="n">
-        <v>2646.02</v>
+        <v>2603.02</v>
       </c>
       <c r="O30" t="n">
-        <v>2771.9</v>
+        <v>2653.8</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3009,16 +3001,20 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3033,57 +3029,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2429.1</v>
+        <v>2445</v>
       </c>
       <c r="C31" t="n">
-        <v>2574.5</v>
+        <v>2557</v>
       </c>
       <c r="D31" t="n">
-        <v>2415.3</v>
+        <v>2409.4</v>
       </c>
       <c r="E31" t="n">
-        <v>2464</v>
+        <v>2531.7</v>
       </c>
       <c r="F31" t="n">
-        <v>-32.4</v>
+        <v>67.7</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.013</v>
+        <v>0.0275</v>
       </c>
       <c r="H31" t="n">
-        <v>159.2</v>
+        <v>147.6</v>
       </c>
       <c r="I31" t="n">
-        <v>2336.1</v>
+        <v>2256.1</v>
       </c>
       <c r="J31" t="n">
-        <v>2391.22</v>
+        <v>2289.35</v>
       </c>
       <c r="K31" t="n">
-        <v>2443.45</v>
+        <v>2384.4</v>
       </c>
       <c r="L31" t="n">
-        <v>2495.67</v>
+        <v>2479.45</v>
       </c>
       <c r="M31" t="n">
-        <v>2549.35</v>
+        <v>2543.6</v>
       </c>
       <c r="N31" t="n">
-        <v>2603.02</v>
+        <v>2607.75</v>
       </c>
       <c r="O31" t="n">
-        <v>2653.8</v>
+        <v>2733.7</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3091,19 +3087,17 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="U31" s="8" t="n">
@@ -3126,50 +3120,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2445</v>
+        <v>2527.9</v>
       </c>
       <c r="C32" t="n">
-        <v>2557</v>
+        <v>2674.5</v>
       </c>
       <c r="D32" t="n">
-        <v>2409.4</v>
+        <v>2511.4</v>
       </c>
       <c r="E32" t="n">
-        <v>2531.7</v>
+        <v>2644.4</v>
       </c>
       <c r="F32" t="n">
-        <v>67.7</v>
+        <v>112.7</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0445</v>
       </c>
       <c r="H32" t="n">
-        <v>147.6</v>
+        <v>163.1</v>
       </c>
       <c r="I32" t="n">
-        <v>2256.1</v>
+        <v>2261.8</v>
       </c>
       <c r="J32" t="n">
-        <v>2289.35</v>
+        <v>2408.35</v>
       </c>
       <c r="K32" t="n">
-        <v>2384.4</v>
+        <v>2457.9</v>
       </c>
       <c r="L32" t="n">
-        <v>2479.45</v>
+        <v>2507.45</v>
       </c>
       <c r="M32" t="n">
-        <v>2543.6</v>
+        <v>2605.5</v>
       </c>
       <c r="N32" t="n">
-        <v>2607.75</v>
+        <v>2703.55</v>
       </c>
       <c r="O32" t="n">
-        <v>2733.7</v>
+        <v>2704.6</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3203,57 +3197,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2527.9</v>
+        <v>2607.8</v>
       </c>
       <c r="C33" t="n">
-        <v>2674.5</v>
+        <v>2807.8</v>
       </c>
       <c r="D33" t="n">
-        <v>2511.4</v>
+        <v>2591.8</v>
       </c>
       <c r="E33" t="n">
-        <v>2644.4</v>
+        <v>2788.9</v>
       </c>
       <c r="F33" t="n">
-        <v>112.7</v>
+        <v>144.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0445</v>
+        <v>0.0546</v>
       </c>
       <c r="H33" t="n">
-        <v>163.1</v>
+        <v>216</v>
       </c>
       <c r="I33" t="n">
-        <v>2261.8</v>
+        <v>2348.3</v>
       </c>
       <c r="J33" t="n">
-        <v>2408.35</v>
+        <v>2507.02</v>
       </c>
       <c r="K33" t="n">
-        <v>2457.9</v>
+        <v>2562.85</v>
       </c>
       <c r="L33" t="n">
-        <v>2507.45</v>
+        <v>2618.67</v>
       </c>
       <c r="M33" t="n">
-        <v>2605.5</v>
+        <v>2725.95</v>
       </c>
       <c r="N33" t="n">
-        <v>2703.55</v>
+        <v>2833.22</v>
       </c>
       <c r="O33" t="n">
-        <v>2704.6</v>
+        <v>2837.6</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3271,11 +3265,13 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3294,50 +3290,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2607.8</v>
+        <v>2758.7</v>
       </c>
       <c r="C34" t="n">
-        <v>2807.8</v>
+        <v>2828.7</v>
       </c>
       <c r="D34" t="n">
-        <v>2591.8</v>
+        <v>2745.9</v>
       </c>
       <c r="E34" t="n">
-        <v>2788.9</v>
+        <v>2796.1</v>
       </c>
       <c r="F34" t="n">
-        <v>144.5</v>
+        <v>7.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0026</v>
       </c>
       <c r="H34" t="n">
-        <v>216</v>
+        <v>82.8</v>
       </c>
       <c r="I34" t="n">
-        <v>2348.3</v>
+        <v>2375.8</v>
       </c>
       <c r="J34" t="n">
-        <v>2507.02</v>
+        <v>2617.45</v>
       </c>
       <c r="K34" t="n">
-        <v>2562.85</v>
+        <v>2680.9</v>
       </c>
       <c r="L34" t="n">
-        <v>2618.67</v>
+        <v>2744.35</v>
       </c>
       <c r="M34" t="n">
-        <v>2725.95</v>
+        <v>2896.9</v>
       </c>
       <c r="N34" t="n">
-        <v>2833.22</v>
+        <v>3049.45</v>
       </c>
       <c r="O34" t="n">
-        <v>2837.6</v>
+        <v>3023.8</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3350,18 +3346,14 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3380,50 +3372,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2758.7</v>
+        <v>2792.7</v>
       </c>
       <c r="C35" t="n">
-        <v>2828.7</v>
+        <v>2825</v>
       </c>
       <c r="D35" t="n">
-        <v>2745.9</v>
+        <v>2726.1</v>
       </c>
       <c r="E35" t="n">
-        <v>2796.1</v>
+        <v>2819.3</v>
       </c>
       <c r="F35" t="n">
-        <v>7.2</v>
+        <v>23.2</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0083</v>
       </c>
       <c r="H35" t="n">
-        <v>82.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>2375.8</v>
+        <v>2663.1</v>
       </c>
       <c r="J35" t="n">
-        <v>2617.45</v>
+        <v>2717.7</v>
       </c>
       <c r="K35" t="n">
-        <v>2680.9</v>
+        <v>2754.7</v>
       </c>
       <c r="L35" t="n">
-        <v>2744.35</v>
+        <v>2791.7</v>
       </c>
       <c r="M35" t="n">
-        <v>2896.9</v>
+        <v>2837.5</v>
       </c>
       <c r="N35" t="n">
-        <v>3049.45</v>
+        <v>2883.3</v>
       </c>
       <c r="O35" t="n">
-        <v>3023.8</v>
+        <v>2911.5</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3431,16 +3423,20 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3455,57 +3451,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2792.7</v>
+        <v>2825.9</v>
       </c>
       <c r="C36" t="n">
-        <v>2825</v>
+        <v>2918.4</v>
       </c>
       <c r="D36" t="n">
-        <v>2726.1</v>
+        <v>2786.8</v>
       </c>
       <c r="E36" t="n">
-        <v>2819.3</v>
+        <v>2867.6</v>
       </c>
       <c r="F36" t="n">
-        <v>23.2</v>
+        <v>48.3</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0171</v>
       </c>
       <c r="H36" t="n">
-        <v>98.90000000000001</v>
+        <v>131.6</v>
       </c>
       <c r="I36" t="n">
-        <v>2663.1</v>
+        <v>2627.2</v>
       </c>
       <c r="J36" t="n">
-        <v>2717.7</v>
+        <v>2742.28</v>
       </c>
       <c r="K36" t="n">
-        <v>2754.7</v>
+        <v>2769.85</v>
       </c>
       <c r="L36" t="n">
-        <v>2791.7</v>
+        <v>2797.43</v>
       </c>
       <c r="M36" t="n">
-        <v>2837.5</v>
+        <v>2868.75</v>
       </c>
       <c r="N36" t="n">
-        <v>2883.3</v>
+        <v>2940.07</v>
       </c>
       <c r="O36" t="n">
-        <v>2911.5</v>
+        <v>2923.9</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3513,10 +3509,8 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
@@ -3541,57 +3535,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2825.9</v>
+        <v>2863</v>
       </c>
       <c r="C37" t="n">
-        <v>2918.4</v>
+        <v>2896.2</v>
       </c>
       <c r="D37" t="n">
-        <v>2786.8</v>
+        <v>2787.9</v>
       </c>
       <c r="E37" t="n">
-        <v>2867.6</v>
+        <v>2799.6</v>
       </c>
       <c r="F37" t="n">
-        <v>48.3</v>
+        <v>-68</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0171</v>
+        <v>-0.0237</v>
       </c>
       <c r="H37" t="n">
-        <v>131.6</v>
+        <v>108.3</v>
       </c>
       <c r="I37" t="n">
-        <v>2627.2</v>
+        <v>2655.2</v>
       </c>
       <c r="J37" t="n">
-        <v>2742.28</v>
+        <v>2743.5</v>
       </c>
       <c r="K37" t="n">
-        <v>2769.85</v>
+        <v>2801.8</v>
       </c>
       <c r="L37" t="n">
-        <v>2797.43</v>
+        <v>2860.1</v>
       </c>
       <c r="M37" t="n">
-        <v>2868.75</v>
+        <v>2933.4</v>
       </c>
       <c r="N37" t="n">
-        <v>2940.07</v>
+        <v>3006.7</v>
       </c>
       <c r="O37" t="n">
-        <v>2923.9</v>
+        <v>3050</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3599,19 +3593,19 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3625,57 +3619,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2863</v>
+        <v>2788.8</v>
       </c>
       <c r="C38" t="n">
-        <v>2896.2</v>
+        <v>2887</v>
       </c>
       <c r="D38" t="n">
-        <v>2787.9</v>
+        <v>2728.4</v>
       </c>
       <c r="E38" t="n">
-        <v>2799.6</v>
+        <v>2872.1</v>
       </c>
       <c r="F38" t="n">
-        <v>-68</v>
+        <v>72.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0259</v>
       </c>
       <c r="H38" t="n">
-        <v>108.3</v>
+        <v>158.6</v>
       </c>
       <c r="I38" t="n">
-        <v>2655.2</v>
+        <v>2679.6</v>
       </c>
       <c r="J38" t="n">
-        <v>2743.5</v>
+        <v>2670.08</v>
       </c>
       <c r="K38" t="n">
-        <v>2801.8</v>
+        <v>2745.45</v>
       </c>
       <c r="L38" t="n">
-        <v>2860.1</v>
+        <v>2820.83</v>
       </c>
       <c r="M38" t="n">
-        <v>2933.4</v>
+        <v>2853.75</v>
       </c>
       <c r="N38" t="n">
-        <v>3006.7</v>
+        <v>2886.68</v>
       </c>
       <c r="O38" t="n">
-        <v>3050</v>
+        <v>3004.5</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3685,19 +3679,23 @@
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3716,50 +3714,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2788.8</v>
+        <v>2888</v>
       </c>
       <c r="C39" t="n">
-        <v>2887</v>
+        <v>2952</v>
       </c>
       <c r="D39" t="n">
-        <v>2728.4</v>
+        <v>2887.9</v>
       </c>
       <c r="E39" t="n">
-        <v>2872.1</v>
+        <v>2924.3</v>
       </c>
       <c r="F39" t="n">
-        <v>72.5</v>
+        <v>52.2</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0259</v>
+        <v>0.0182</v>
       </c>
       <c r="H39" t="n">
-        <v>158.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>2679.6</v>
+        <v>2569.8</v>
       </c>
       <c r="J39" t="n">
-        <v>2670.08</v>
+        <v>2745.7</v>
       </c>
       <c r="K39" t="n">
-        <v>2745.45</v>
+        <v>2792.8</v>
       </c>
       <c r="L39" t="n">
-        <v>2820.83</v>
+        <v>2839.9</v>
       </c>
       <c r="M39" t="n">
-        <v>2853.75</v>
+        <v>2951.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2886.68</v>
+        <v>3062.9</v>
       </c>
       <c r="O39" t="n">
-        <v>3004.5</v>
+        <v>3045.6</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3767,10 +3765,8 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
@@ -3779,14 +3775,12 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3797,77 +3791,81 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2888</v>
+        <v>2920.5</v>
       </c>
       <c r="C40" t="n">
-        <v>2952</v>
+        <v>2948.3</v>
       </c>
       <c r="D40" t="n">
-        <v>2887.9</v>
+        <v>2812.4</v>
       </c>
       <c r="E40" t="n">
-        <v>2924.3</v>
+        <v>2834.8</v>
       </c>
       <c r="F40" t="n">
-        <v>52.2</v>
+        <v>-89.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0182</v>
+        <v>-0.0306</v>
       </c>
       <c r="H40" t="n">
-        <v>64.09999999999999</v>
+        <v>135.9</v>
       </c>
       <c r="I40" t="n">
-        <v>2569.8</v>
+        <v>2823.8</v>
       </c>
       <c r="J40" t="n">
-        <v>2745.7</v>
+        <v>2862.38</v>
       </c>
       <c r="K40" t="n">
-        <v>2792.8</v>
+        <v>2892.25</v>
       </c>
       <c r="L40" t="n">
-        <v>2839.9</v>
+        <v>2922.12</v>
       </c>
       <c r="M40" t="n">
-        <v>2951.4</v>
+        <v>2956.35</v>
       </c>
       <c r="N40" t="n">
-        <v>3062.9</v>
+        <v>2990.58</v>
       </c>
       <c r="O40" t="n">
-        <v>3045.6</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+        <v>3016.1</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3879,86 +3877,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2920.5</v>
+        <v>2816.3</v>
       </c>
       <c r="C41" t="n">
-        <v>2948.3</v>
+        <v>2974.2</v>
       </c>
       <c r="D41" t="n">
-        <v>2812.4</v>
+        <v>2793.7</v>
       </c>
       <c r="E41" t="n">
-        <v>2834.8</v>
+        <v>2947</v>
       </c>
       <c r="F41" t="n">
-        <v>-89.5</v>
+        <v>112.2</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0306</v>
+        <v>0.0396</v>
       </c>
       <c r="H41" t="n">
-        <v>135.9</v>
+        <v>180.5</v>
       </c>
       <c r="I41" t="n">
-        <v>2823.8</v>
+        <v>2676.5</v>
       </c>
       <c r="J41" t="n">
-        <v>2862.38</v>
+        <v>2676.12</v>
       </c>
       <c r="K41" t="n">
-        <v>2892.25</v>
+        <v>2766.85</v>
       </c>
       <c r="L41" t="n">
-        <v>2922.12</v>
+        <v>2857.58</v>
       </c>
       <c r="M41" t="n">
-        <v>2956.35</v>
+        <v>2902.75</v>
       </c>
       <c r="N41" t="n">
-        <v>2990.58</v>
+        <v>2947.93</v>
       </c>
       <c r="O41" t="n">
-        <v>3016.1</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
+        <v>3084.2</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
@@ -3967,55 +3959,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2816.3</v>
+        <v>2984</v>
       </c>
       <c r="C42" t="n">
-        <v>2974.2</v>
+        <v>3005</v>
       </c>
       <c r="D42" t="n">
-        <v>2793.7</v>
+        <v>2910.3</v>
       </c>
       <c r="E42" t="n">
-        <v>2947</v>
+        <v>2995.6</v>
       </c>
       <c r="F42" t="n">
-        <v>112.2</v>
+        <v>48.6</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.0165</v>
       </c>
       <c r="H42" t="n">
-        <v>180.5</v>
+        <v>94.7</v>
       </c>
       <c r="I42" t="n">
-        <v>2676.5</v>
+        <v>2613.2</v>
       </c>
       <c r="J42" t="n">
-        <v>2676.12</v>
+        <v>2798.03</v>
       </c>
       <c r="K42" t="n">
-        <v>2766.85</v>
+        <v>2856.75</v>
       </c>
       <c r="L42" t="n">
-        <v>2857.58</v>
+        <v>2915.47</v>
       </c>
       <c r="M42" t="n">
-        <v>2902.75</v>
+        <v>3037.25</v>
       </c>
       <c r="N42" t="n">
-        <v>2947.93</v>
+        <v>3159.03</v>
       </c>
       <c r="O42" t="n">
-        <v>3084.2</v>
+        <v>3154.7</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4033,14 +4029,12 @@
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4051,57 +4045,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2984</v>
+        <v>2989.9</v>
       </c>
       <c r="C43" t="n">
-        <v>3005</v>
+        <v>3062.4</v>
       </c>
       <c r="D43" t="n">
-        <v>2910.3</v>
+        <v>2965.2</v>
       </c>
       <c r="E43" t="n">
-        <v>2995.6</v>
+        <v>3022.6</v>
       </c>
       <c r="F43" t="n">
-        <v>48.6</v>
+        <v>27</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>94.7</v>
+        <v>97.2</v>
       </c>
       <c r="I43" t="n">
-        <v>2613.2</v>
+        <v>2815.6</v>
       </c>
       <c r="J43" t="n">
-        <v>2798.03</v>
+        <v>2919.88</v>
       </c>
       <c r="K43" t="n">
-        <v>2856.75</v>
+        <v>2948.25</v>
       </c>
       <c r="L43" t="n">
-        <v>2915.47</v>
+        <v>2976.63</v>
       </c>
       <c r="M43" t="n">
-        <v>3037.25</v>
+        <v>3042.95</v>
       </c>
       <c r="N43" t="n">
-        <v>3159.03</v>
+        <v>3109.28</v>
       </c>
       <c r="O43" t="n">
-        <v>3154.7</v>
+        <v>3099.7</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4142,50 +4136,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2989.9</v>
+        <v>3020.9</v>
       </c>
       <c r="C44" t="n">
-        <v>3062.4</v>
+        <v>3068.4</v>
       </c>
       <c r="D44" t="n">
-        <v>2965.2</v>
+        <v>2987.8</v>
       </c>
       <c r="E44" t="n">
-        <v>3022.6</v>
+        <v>3023.5</v>
       </c>
       <c r="F44" t="n">
-        <v>27</v>
+        <v>0.9</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0003</v>
       </c>
       <c r="H44" t="n">
-        <v>97.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>2815.6</v>
+        <v>2868</v>
       </c>
       <c r="J44" t="n">
-        <v>2919.88</v>
+        <v>2929.8</v>
       </c>
       <c r="K44" t="n">
-        <v>2948.25</v>
+        <v>2974</v>
       </c>
       <c r="L44" t="n">
-        <v>2976.63</v>
+        <v>3018.2</v>
       </c>
       <c r="M44" t="n">
-        <v>3042.95</v>
+        <v>3071.2</v>
       </c>
       <c r="N44" t="n">
-        <v>3109.28</v>
+        <v>3124.2</v>
       </c>
       <c r="O44" t="n">
-        <v>3099.7</v>
+        <v>3159.6</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4198,13 +4192,11 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4226,50 +4218,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3020.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C45" t="n">
-        <v>3068.4</v>
+        <v>3042.6</v>
       </c>
       <c r="D45" t="n">
-        <v>2987.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E45" t="n">
-        <v>3023.5</v>
+        <v>2994</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9</v>
+        <v>-29.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0098</v>
       </c>
       <c r="H45" t="n">
-        <v>80.59999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="I45" t="n">
-        <v>2868</v>
+        <v>2907.2</v>
       </c>
       <c r="J45" t="n">
-        <v>2929.8</v>
+        <v>2940.6</v>
       </c>
       <c r="K45" t="n">
-        <v>2974</v>
+        <v>2983.2</v>
       </c>
       <c r="L45" t="n">
-        <v>3018.2</v>
+        <v>3025.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3071.2</v>
+        <v>3063.8</v>
       </c>
       <c r="N45" t="n">
-        <v>3124.2</v>
+        <v>3101.8</v>
       </c>
       <c r="O45" t="n">
-        <v>3159.6</v>
+        <v>3149</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4277,12 +4269,14 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4299,59 +4293,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3019.7</v>
+        <v>2984.7</v>
       </c>
       <c r="C46" t="n">
-        <v>3042.6</v>
+        <v>3029.8</v>
       </c>
       <c r="D46" t="n">
-        <v>2943.4</v>
+        <v>2949.3</v>
       </c>
       <c r="E46" t="n">
-        <v>2994</v>
+        <v>2973.5</v>
       </c>
       <c r="F46" t="n">
-        <v>-29.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0068</v>
       </c>
       <c r="H46" t="n">
-        <v>99.2</v>
+        <v>80.5</v>
       </c>
       <c r="I46" t="n">
-        <v>2907.2</v>
+        <v>2844.2</v>
       </c>
       <c r="J46" t="n">
-        <v>2940.6</v>
+        <v>2895.3</v>
       </c>
       <c r="K46" t="n">
-        <v>2983.2</v>
+        <v>2944.4</v>
       </c>
       <c r="L46" t="n">
-        <v>3025.8</v>
+        <v>2993.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3063.8</v>
+        <v>3043.6</v>
       </c>
       <c r="N46" t="n">
-        <v>3101.8</v>
+        <v>3093.7</v>
       </c>
       <c r="O46" t="n">
-        <v>3149</v>
+        <v>3141.8</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4359,14 +4349,12 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4383,55 +4371,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2984.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C47" t="n">
-        <v>3029.8</v>
+        <v>2999.8</v>
       </c>
       <c r="D47" t="n">
-        <v>2949.3</v>
+        <v>2932.1</v>
       </c>
       <c r="E47" t="n">
-        <v>2973.5</v>
+        <v>2941.3</v>
       </c>
       <c r="F47" t="n">
-        <v>-20.5</v>
+        <v>-32.2</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0068</v>
+        <v>-0.0108</v>
       </c>
       <c r="H47" t="n">
-        <v>80.5</v>
+        <v>67.7</v>
       </c>
       <c r="I47" t="n">
-        <v>2844.2</v>
+        <v>2868.8</v>
       </c>
       <c r="J47" t="n">
-        <v>2895.3</v>
+        <v>2884.97</v>
       </c>
       <c r="K47" t="n">
-        <v>2944.4</v>
+        <v>2933.25</v>
       </c>
       <c r="L47" t="n">
-        <v>2993.5</v>
+        <v>2981.53</v>
       </c>
       <c r="M47" t="n">
-        <v>3043.6</v>
+        <v>3013.75</v>
       </c>
       <c r="N47" t="n">
-        <v>3093.7</v>
+        <v>3045.97</v>
       </c>
       <c r="O47" t="n">
-        <v>3141.8</v>
+        <v>3110.3</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4439,12 +4431,14 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4461,59 +4455,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2964.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C48" t="n">
-        <v>2999.8</v>
+        <v>2985.9</v>
       </c>
       <c r="D48" t="n">
-        <v>2932.1</v>
+        <v>2902.3</v>
       </c>
       <c r="E48" t="n">
-        <v>2941.3</v>
+        <v>2938</v>
       </c>
       <c r="F48" t="n">
-        <v>-32.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0011</v>
       </c>
       <c r="H48" t="n">
-        <v>67.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>2868.8</v>
+        <v>2864.4</v>
       </c>
       <c r="J48" t="n">
-        <v>2884.97</v>
+        <v>2861.28</v>
       </c>
       <c r="K48" t="n">
-        <v>2933.25</v>
+        <v>2907.45</v>
       </c>
       <c r="L48" t="n">
-        <v>2981.53</v>
+        <v>2953.63</v>
       </c>
       <c r="M48" t="n">
-        <v>3013.75</v>
+        <v>2975.15</v>
       </c>
       <c r="N48" t="n">
-        <v>3045.97</v>
+        <v>2996.67</v>
       </c>
       <c r="O48" t="n">
-        <v>3110.3</v>
+        <v>3067.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4523,16 +4513,18 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4550,50 +4542,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2955.5</v>
+        <v>2950</v>
       </c>
       <c r="C49" t="n">
-        <v>2985.9</v>
+        <v>3058.3</v>
       </c>
       <c r="D49" t="n">
-        <v>2902.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E49" t="n">
-        <v>2938</v>
+        <v>3041.6</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.3</v>
+        <v>103.6</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0353</v>
       </c>
       <c r="H49" t="n">
-        <v>83.59999999999999</v>
+        <v>109.9</v>
       </c>
       <c r="I49" t="n">
-        <v>2864.4</v>
+        <v>2818.7</v>
       </c>
       <c r="J49" t="n">
-        <v>2861.28</v>
+        <v>2851.35</v>
       </c>
       <c r="K49" t="n">
-        <v>2907.45</v>
+        <v>2896.2</v>
       </c>
       <c r="L49" t="n">
-        <v>2953.63</v>
+        <v>2941.05</v>
       </c>
       <c r="M49" t="n">
-        <v>2975.15</v>
+        <v>2979.8</v>
       </c>
       <c r="N49" t="n">
-        <v>2996.67</v>
+        <v>3018.55</v>
       </c>
       <c r="O49" t="n">
-        <v>3067.5</v>
+        <v>3069.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4601,30 +4593,30 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr"/>
@@ -4632,50 +4624,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2950</v>
+        <v>3038.9</v>
       </c>
       <c r="C50" t="n">
-        <v>3058.3</v>
+        <v>3076.3</v>
       </c>
       <c r="D50" t="n">
-        <v>2948.4</v>
+        <v>3016</v>
       </c>
       <c r="E50" t="n">
-        <v>3041.6</v>
+        <v>3074.9</v>
       </c>
       <c r="F50" t="n">
-        <v>103.6</v>
+        <v>33.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.0109</v>
       </c>
       <c r="H50" t="n">
-        <v>109.9</v>
+        <v>60.3</v>
       </c>
       <c r="I50" t="n">
-        <v>2818.7</v>
+        <v>2838.5</v>
       </c>
       <c r="J50" t="n">
-        <v>2851.35</v>
+        <v>2950.83</v>
       </c>
       <c r="K50" t="n">
-        <v>2896.2</v>
+        <v>2986.65</v>
       </c>
       <c r="L50" t="n">
-        <v>2941.05</v>
+        <v>3022.48</v>
       </c>
       <c r="M50" t="n">
-        <v>2979.8</v>
+        <v>3096.55</v>
       </c>
       <c r="N50" t="n">
-        <v>3018.55</v>
+        <v>3170.63</v>
       </c>
       <c r="O50" t="n">
-        <v>3069.5</v>
+        <v>3168.2</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4693,13 +4685,11 @@
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4714,144 +4704,148 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3038.9</v>
+        <v>3073.5</v>
       </c>
       <c r="C51" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D51" t="n">
-        <v>3016</v>
+        <v>2993.2</v>
       </c>
       <c r="E51" t="n">
-        <v>3074.9</v>
+        <v>3022.1</v>
       </c>
       <c r="F51" t="n">
-        <v>33.3</v>
+        <v>-52.8</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.0172</v>
       </c>
       <c r="H51" t="n">
-        <v>60.3</v>
+        <v>86.7</v>
       </c>
       <c r="I51" t="n">
-        <v>2838.5</v>
+        <v>2955.7</v>
       </c>
       <c r="J51" t="n">
-        <v>2950.83</v>
+        <v>3028.97</v>
       </c>
       <c r="K51" t="n">
-        <v>2986.65</v>
+        <v>3044.75</v>
       </c>
       <c r="L51" t="n">
-        <v>3022.48</v>
+        <v>3060.52</v>
       </c>
       <c r="M51" t="n">
-        <v>3096.55</v>
+        <v>3105.05</v>
       </c>
       <c r="N51" t="n">
-        <v>3170.63</v>
+        <v>3149.57</v>
       </c>
       <c r="O51" t="n">
-        <v>3168.2</v>
+        <v>3136.6</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
+      <c r="Q51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="W51" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3073.5</v>
+        <v>3023</v>
       </c>
       <c r="C52" t="n">
-        <v>3079.9</v>
+        <v>3028.9</v>
       </c>
       <c r="D52" t="n">
-        <v>2993.2</v>
+        <v>2976.6</v>
       </c>
       <c r="E52" t="n">
-        <v>3022.1</v>
+        <v>2977.5</v>
       </c>
       <c r="F52" t="n">
-        <v>-52.8</v>
+        <v>-44.6</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0172</v>
+        <v>-0.0148</v>
       </c>
       <c r="H52" t="n">
-        <v>86.7</v>
+        <v>52.3</v>
       </c>
       <c r="I52" t="n">
-        <v>2955.7</v>
+        <v>2906.5</v>
       </c>
       <c r="J52" t="n">
-        <v>3028.97</v>
+        <v>2928.18</v>
       </c>
       <c r="K52" t="n">
-        <v>3044.75</v>
+        <v>2978.75</v>
       </c>
       <c r="L52" t="n">
-        <v>3060.52</v>
+        <v>3029.33</v>
       </c>
       <c r="M52" t="n">
-        <v>3105.05</v>
+        <v>3065.45</v>
       </c>
       <c r="N52" t="n">
-        <v>3149.57</v>
+        <v>3101.58</v>
       </c>
       <c r="O52" t="n">
-        <v>3136.6</v>
+        <v>3166.6</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4871,74 +4865,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3023</v>
+        <v>2971</v>
       </c>
       <c r="C53" t="n">
-        <v>3028.9</v>
+        <v>2983.3</v>
       </c>
       <c r="D53" t="n">
+        <v>2914.5</v>
+      </c>
+      <c r="E53" t="n">
         <v>2976.6</v>
       </c>
-      <c r="E53" t="n">
-        <v>2977.5</v>
-      </c>
       <c r="F53" t="n">
-        <v>-44.6</v>
+        <v>-0.9</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0148</v>
+        <v>-0.0003</v>
       </c>
       <c r="H53" t="n">
-        <v>52.3</v>
+        <v>68.8</v>
       </c>
       <c r="I53" t="n">
-        <v>2906.5</v>
+        <v>2924.3</v>
       </c>
       <c r="J53" t="n">
-        <v>2928.18</v>
+        <v>2912.58</v>
       </c>
       <c r="K53" t="n">
-        <v>2978.75</v>
+        <v>2951.35</v>
       </c>
       <c r="L53" t="n">
-        <v>3029.33</v>
+        <v>2990.12</v>
       </c>
       <c r="M53" t="n">
-        <v>3065.45</v>
+        <v>3003.65</v>
       </c>
       <c r="N53" t="n">
-        <v>3101.58</v>
+        <v>3017.17</v>
       </c>
       <c r="O53" t="n">
-        <v>3166.6</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
+        <v>3081.2</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4960,67 +4952,67 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2971</v>
+        <v>2974.7</v>
       </c>
       <c r="C54" t="n">
-        <v>2983.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D54" t="n">
-        <v>2914.5</v>
+        <v>2887.6</v>
       </c>
       <c r="E54" t="n">
-        <v>2976.6</v>
+        <v>2904.5</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.9</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0242</v>
       </c>
       <c r="H54" t="n">
-        <v>68.8</v>
+        <v>90.3</v>
       </c>
       <c r="I54" t="n">
-        <v>2924.3</v>
+        <v>2845.7</v>
       </c>
       <c r="J54" t="n">
-        <v>2912.58</v>
+        <v>2921.65</v>
       </c>
       <c r="K54" t="n">
-        <v>2951.35</v>
+        <v>2942.2</v>
       </c>
       <c r="L54" t="n">
-        <v>2990.12</v>
+        <v>2962.75</v>
       </c>
       <c r="M54" t="n">
-        <v>3003.65</v>
+        <v>3011</v>
       </c>
       <c r="N54" t="n">
-        <v>3017.17</v>
+        <v>3059.25</v>
       </c>
       <c r="O54" t="n">
-        <v>3081.2</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
+        <v>3052.1</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5042,62 +5034,60 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2974.7</v>
+        <v>2892.7</v>
       </c>
       <c r="C55" t="n">
-        <v>2977.9</v>
+        <v>2913.5</v>
       </c>
       <c r="D55" t="n">
-        <v>2887.6</v>
+        <v>2831.9</v>
       </c>
       <c r="E55" t="n">
-        <v>2904.5</v>
+        <v>2873.23</v>
       </c>
       <c r="F55" t="n">
-        <v>-72.09999999999999</v>
+        <v>-31.27</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0242</v>
+        <v>-0.0108</v>
       </c>
       <c r="H55" t="n">
-        <v>90.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>2845.7</v>
+        <v>2797.3</v>
       </c>
       <c r="J55" t="n">
-        <v>2921.65</v>
+        <v>2800.08</v>
       </c>
       <c r="K55" t="n">
-        <v>2942.2</v>
+        <v>2859.35</v>
       </c>
       <c r="L55" t="n">
-        <v>2962.75</v>
+        <v>2918.62</v>
       </c>
       <c r="M55" t="n">
-        <v>3011</v>
+        <v>2949.65</v>
       </c>
       <c r="N55" t="n">
-        <v>3059.25</v>
+        <v>2980.67</v>
       </c>
       <c r="O55" t="n">
-        <v>3052.1</v>
+        <v>3068.2</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
@@ -5124,50 +5114,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2892.7</v>
+        <v>2879.5</v>
       </c>
       <c r="C56" t="n">
-        <v>2913.5</v>
+        <v>2931.2</v>
       </c>
       <c r="D56" t="n">
-        <v>2831.9</v>
+        <v>2829.9</v>
       </c>
       <c r="E56" t="n">
-        <v>2873.23</v>
+        <v>2859.3</v>
       </c>
       <c r="F56" t="n">
-        <v>-31.27</v>
+        <v>-13.93</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0048</v>
       </c>
       <c r="H56" t="n">
-        <v>81.59999999999999</v>
+        <v>101.3</v>
       </c>
       <c r="I56" t="n">
-        <v>2797.3</v>
+        <v>2750.3</v>
       </c>
       <c r="J56" t="n">
-        <v>2800.08</v>
+        <v>2791.89</v>
       </c>
       <c r="K56" t="n">
-        <v>2859.35</v>
+        <v>2832.43</v>
       </c>
       <c r="L56" t="n">
-        <v>2918.62</v>
+        <v>2872.96</v>
       </c>
       <c r="M56" t="n">
-        <v>2949.65</v>
+        <v>2914.03</v>
       </c>
       <c r="N56" t="n">
-        <v>2980.67</v>
+        <v>2955.1</v>
       </c>
       <c r="O56" t="n">
-        <v>3068.2</v>
+        <v>2995.1</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5177,16 +5167,18 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5199,55 +5191,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2879.5</v>
+        <v>2857.7</v>
       </c>
       <c r="C57" t="n">
-        <v>2931.2</v>
+        <v>2875.3</v>
       </c>
       <c r="D57" t="n">
-        <v>2829.9</v>
+        <v>2791.5</v>
       </c>
       <c r="E57" t="n">
-        <v>2859.3</v>
+        <v>2850.9</v>
       </c>
       <c r="F57" t="n">
-        <v>-13.93</v>
+        <v>-8.4</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0029</v>
       </c>
       <c r="H57" t="n">
-        <v>101.3</v>
+        <v>83.8</v>
       </c>
       <c r="I57" t="n">
-        <v>2750.3</v>
+        <v>2728.6</v>
       </c>
       <c r="J57" t="n">
-        <v>2791.89</v>
+        <v>2747.38</v>
       </c>
       <c r="K57" t="n">
-        <v>2832.43</v>
+        <v>2808.65</v>
       </c>
       <c r="L57" t="n">
-        <v>2872.96</v>
+        <v>2869.92</v>
       </c>
       <c r="M57" t="n">
-        <v>2914.03</v>
+        <v>2909.95</v>
       </c>
       <c r="N57" t="n">
-        <v>2955.1</v>
+        <v>2949.98</v>
       </c>
       <c r="O57" t="n">
-        <v>2995.1</v>
+        <v>3032.5</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5265,10 +5261,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5281,91 +5275,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2857.7</v>
-      </c>
-      <c r="C58" t="n">
-        <v>2858.8</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2811.9</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2830.4</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-28.9</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0101</v>
-      </c>
-      <c r="H58" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2728.6</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2747.38</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2808.65</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2869.92</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2909.95</v>
-      </c>
-      <c r="N58" t="n">
-        <v>2949.98</v>
-      </c>
-      <c r="O58" t="n">
-        <v>3032.5</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5277,6 +5277,90 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2869.4</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2871.8</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2869.2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2869.8</v>
+      </c>
+      <c r="F58" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2707.7</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2775.85</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2809</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2842.15</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2892.8</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2943.45</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2959.1</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>54.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2238.7</v>
+        <v>2263.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2317.95</v>
+        <v>2327.17</v>
       </c>
       <c r="K2" t="n">
-        <v>2349.8</v>
+        <v>2355.95</v>
       </c>
       <c r="L2" t="n">
-        <v>2381.65</v>
+        <v>2384.72</v>
       </c>
       <c r="M2" t="n">
-        <v>2437.2</v>
+        <v>2431.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2492.75</v>
+        <v>2477.38</v>
       </c>
       <c r="O2" t="n">
-        <v>2500.9</v>
+        <v>2488.6</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5284,25 +5284,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2869.4</v>
+        <v>2850.6</v>
       </c>
       <c r="C58" t="n">
-        <v>2871.8</v>
+        <v>2878.4</v>
       </c>
       <c r="D58" t="n">
-        <v>2869.2</v>
+        <v>2835.8</v>
       </c>
       <c r="E58" t="n">
-        <v>2869.8</v>
+        <v>2843.9</v>
       </c>
       <c r="F58" t="n">
-        <v>18.9</v>
+        <v>-7</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0066</v>
+        <v>-0.0025</v>
       </c>
       <c r="H58" t="n">
-        <v>2.6</v>
+        <v>42.6</v>
       </c>
       <c r="I58" t="n">
         <v>2707.7</v>
@@ -5336,13 +5336,11 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>54.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2263.3</v>
+        <v>2292.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2327.17</v>
+        <v>2338.05</v>
       </c>
       <c r="K2" t="n">
-        <v>2355.95</v>
+        <v>2363.2</v>
       </c>
       <c r="L2" t="n">
-        <v>2384.72</v>
+        <v>2388.35</v>
       </c>
       <c r="M2" t="n">
-        <v>2431.05</v>
+        <v>2423.8</v>
       </c>
       <c r="N2" t="n">
-        <v>2477.38</v>
+        <v>2459.25</v>
       </c>
       <c r="O2" t="n">
-        <v>2488.6</v>
+        <v>2474.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -693,8 +693,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -5287,22 +5289,22 @@
         <v>2850.6</v>
       </c>
       <c r="C58" t="n">
-        <v>2878.4</v>
+        <v>2887.2</v>
       </c>
       <c r="D58" t="n">
-        <v>2835.8</v>
+        <v>2809</v>
       </c>
       <c r="E58" t="n">
-        <v>2843.9</v>
+        <v>2810</v>
       </c>
       <c r="F58" t="n">
-        <v>-7</v>
+        <v>-40.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0143</v>
       </c>
       <c r="H58" t="n">
-        <v>42.6</v>
+        <v>78.2</v>
       </c>
       <c r="I58" t="n">
         <v>2707.7</v>
@@ -5331,12 +5333,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5292,19 +5292,19 @@
         <v>2887.2</v>
       </c>
       <c r="D58" t="n">
-        <v>2809</v>
+        <v>2806.6</v>
       </c>
       <c r="E58" t="n">
-        <v>2810</v>
+        <v>2808</v>
       </c>
       <c r="F58" t="n">
-        <v>-40.9</v>
+        <v>-42.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0143</v>
+        <v>-0.015</v>
       </c>
       <c r="H58" t="n">
-        <v>78.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I58" t="n">
         <v>2707.7</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>54.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2292.3</v>
+        <v>2317.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2338.05</v>
+        <v>2347.58</v>
       </c>
       <c r="K2" t="n">
-        <v>2363.2</v>
+        <v>2369.55</v>
       </c>
       <c r="L2" t="n">
-        <v>2388.35</v>
+        <v>2391.53</v>
       </c>
       <c r="M2" t="n">
-        <v>2423.8</v>
+        <v>2417.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2459.25</v>
+        <v>2443.37</v>
       </c>
       <c r="O2" t="n">
-        <v>2474.1</v>
+        <v>2461.4</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5292,19 +5292,19 @@
         <v>2887.2</v>
       </c>
       <c r="D58" t="n">
-        <v>2806.6</v>
+        <v>2804.2</v>
       </c>
       <c r="E58" t="n">
-        <v>2808</v>
+        <v>2818.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-42.9</v>
+        <v>-32.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.015</v>
+        <v>-0.0114</v>
       </c>
       <c r="H58" t="n">
-        <v>80.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="I58" t="n">
         <v>2707.7</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2391.8</v>
+        <v>2398</v>
       </c>
       <c r="C2" t="n">
-        <v>2424.7</v>
+        <v>2485.1</v>
       </c>
       <c r="D2" t="n">
-        <v>2369.9</v>
+        <v>2388.3</v>
       </c>
       <c r="E2" t="n">
-        <v>2397.9</v>
+        <v>2472.04</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4</v>
+        <v>74.14</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0309</v>
       </c>
       <c r="H2" t="n">
-        <v>54.8</v>
+        <v>96.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2317.7</v>
+        <v>2315.1</v>
       </c>
       <c r="J2" t="n">
-        <v>2347.58</v>
+        <v>2343.4</v>
       </c>
       <c r="K2" t="n">
-        <v>2369.55</v>
+        <v>2370.5</v>
       </c>
       <c r="L2" t="n">
-        <v>2391.53</v>
+        <v>2397.6</v>
       </c>
       <c r="M2" t="n">
-        <v>2417.45</v>
+        <v>2425.3</v>
       </c>
       <c r="N2" t="n">
-        <v>2443.37</v>
+        <v>2453</v>
       </c>
       <c r="O2" t="n">
-        <v>2461.4</v>
+        <v>2479.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,7 +690,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -698,11 +698,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -714,50 +718,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2398</v>
+        <v>2469.5</v>
       </c>
       <c r="C3" t="n">
-        <v>2485.1</v>
+        <v>2510.3</v>
       </c>
       <c r="D3" t="n">
-        <v>2388.3</v>
+        <v>2412.1</v>
       </c>
       <c r="E3" t="n">
-        <v>2472.04</v>
+        <v>2450.4</v>
       </c>
       <c r="F3" t="n">
-        <v>74.14</v>
+        <v>-21.64</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0309</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>96.8</v>
+        <v>98.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2315.1</v>
+        <v>2291.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2343.4</v>
+        <v>2392.91</v>
       </c>
       <c r="K3" t="n">
-        <v>2370.5</v>
+        <v>2423.64</v>
       </c>
       <c r="L3" t="n">
-        <v>2397.6</v>
+        <v>2454.37</v>
       </c>
       <c r="M3" t="n">
-        <v>2425.3</v>
+        <v>2520.44</v>
       </c>
       <c r="N3" t="n">
-        <v>2453</v>
+        <v>2586.51</v>
       </c>
       <c r="O3" t="n">
-        <v>2479.5</v>
+        <v>2581.9</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -765,83 +769,83 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2469.5</v>
+        <v>2449.2</v>
       </c>
       <c r="C4" t="n">
-        <v>2510.3</v>
+        <v>2515</v>
       </c>
       <c r="D4" t="n">
-        <v>2412.1</v>
+        <v>2424.7</v>
       </c>
       <c r="E4" t="n">
-        <v>2450.4</v>
+        <v>2492.1</v>
       </c>
       <c r="F4" t="n">
-        <v>-21.64</v>
+        <v>41.7</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="H4" t="n">
-        <v>98.2</v>
+        <v>90.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2291.5</v>
+        <v>2313.9</v>
       </c>
       <c r="J4" t="n">
-        <v>2392.91</v>
+        <v>2346.8</v>
       </c>
       <c r="K4" t="n">
-        <v>2423.64</v>
+        <v>2401.3</v>
       </c>
       <c r="L4" t="n">
-        <v>2454.37</v>
+        <v>2455.8</v>
       </c>
       <c r="M4" t="n">
-        <v>2520.44</v>
+        <v>2499.5</v>
       </c>
       <c r="N4" t="n">
-        <v>2586.51</v>
+        <v>2543.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2581.9</v>
+        <v>2608.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -849,18 +853,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -873,164 +877,166 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2449.2</v>
+        <v>2491.9</v>
       </c>
       <c r="C5" t="n">
-        <v>2515</v>
+        <v>2518.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2424.7</v>
+        <v>2381.8</v>
       </c>
       <c r="E5" t="n">
-        <v>2492.1</v>
+        <v>2408.5</v>
       </c>
       <c r="F5" t="n">
-        <v>41.7</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.017</v>
+        <v>-0.0335</v>
       </c>
       <c r="H5" t="n">
-        <v>90.3</v>
+        <v>136.7</v>
       </c>
       <c r="I5" t="n">
-        <v>2313.9</v>
+        <v>2334.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2346.8</v>
+        <v>2412.93</v>
       </c>
       <c r="K5" t="n">
-        <v>2401.3</v>
+        <v>2446.95</v>
       </c>
       <c r="L5" t="n">
-        <v>2455.8</v>
+        <v>2480.98</v>
       </c>
       <c r="M5" t="n">
-        <v>2499.5</v>
+        <v>2537.25</v>
       </c>
       <c r="N5" t="n">
-        <v>2543.2</v>
+        <v>2593.53</v>
       </c>
       <c r="O5" t="n">
-        <v>2608.5</v>
+        <v>2605.3</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2491.9</v>
+        <v>2421.6</v>
       </c>
       <c r="C6" t="n">
-        <v>2518.5</v>
+        <v>2559.9</v>
       </c>
       <c r="D6" t="n">
-        <v>2381.8</v>
+        <v>2421.6</v>
       </c>
       <c r="E6" t="n">
-        <v>2408.5</v>
+        <v>2464.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-83.59999999999999</v>
+        <v>55.9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0335</v>
+        <v>0.0232</v>
       </c>
       <c r="H6" t="n">
-        <v>136.7</v>
+        <v>138.3</v>
       </c>
       <c r="I6" t="n">
-        <v>2334.4</v>
+        <v>2245.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2412.93</v>
+        <v>2250.98</v>
       </c>
       <c r="K6" t="n">
-        <v>2446.95</v>
+        <v>2340.15</v>
       </c>
       <c r="L6" t="n">
-        <v>2480.98</v>
+        <v>2429.33</v>
       </c>
       <c r="M6" t="n">
-        <v>2537.25</v>
+        <v>2476.85</v>
       </c>
       <c r="N6" t="n">
-        <v>2593.53</v>
+        <v>2524.37</v>
       </c>
       <c r="O6" t="n">
-        <v>2605.3</v>
+        <v>2655.2</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
@@ -1041,57 +1047,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2421.6</v>
+        <v>2473.7</v>
       </c>
       <c r="C7" t="n">
-        <v>2559.9</v>
+        <v>2544</v>
       </c>
       <c r="D7" t="n">
-        <v>2421.6</v>
+        <v>2436.9</v>
       </c>
       <c r="E7" t="n">
-        <v>2464.4</v>
+        <v>2523.7</v>
       </c>
       <c r="F7" t="n">
-        <v>55.9</v>
+        <v>59.3</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0232</v>
+        <v>0.0241</v>
       </c>
       <c r="H7" t="n">
-        <v>138.3</v>
+        <v>107.1</v>
       </c>
       <c r="I7" t="n">
-        <v>2245.1</v>
+        <v>2283.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2250.98</v>
+        <v>2312.93</v>
       </c>
       <c r="K7" t="n">
-        <v>2340.15</v>
+        <v>2395.25</v>
       </c>
       <c r="L7" t="n">
-        <v>2429.33</v>
+        <v>2477.57</v>
       </c>
       <c r="M7" t="n">
-        <v>2476.85</v>
+        <v>2533.55</v>
       </c>
       <c r="N7" t="n">
-        <v>2524.37</v>
+        <v>2589.52</v>
       </c>
       <c r="O7" t="n">
-        <v>2655.2</v>
+        <v>2698.2</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1112,10 +1118,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1127,57 +1131,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2473.7</v>
+        <v>2551.8</v>
       </c>
       <c r="C8" t="n">
-        <v>2544</v>
+        <v>2566.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2436.9</v>
+        <v>2463</v>
       </c>
       <c r="E8" t="n">
-        <v>2523.7</v>
+        <v>2489.9</v>
       </c>
       <c r="F8" t="n">
-        <v>59.3</v>
+        <v>-33.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0241</v>
+        <v>-0.0134</v>
       </c>
       <c r="H8" t="n">
-        <v>107.1</v>
+        <v>103.5</v>
       </c>
       <c r="I8" t="n">
-        <v>2283.3</v>
+        <v>2329.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2312.93</v>
+        <v>2433.22</v>
       </c>
       <c r="K8" t="n">
-        <v>2395.25</v>
+        <v>2470.15</v>
       </c>
       <c r="L8" t="n">
-        <v>2477.57</v>
+        <v>2507.07</v>
       </c>
       <c r="M8" t="n">
-        <v>2533.55</v>
+        <v>2577.25</v>
       </c>
       <c r="N8" t="n">
-        <v>2589.52</v>
+        <v>2647.43</v>
       </c>
       <c r="O8" t="n">
-        <v>2698.2</v>
+        <v>2651.1</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1185,18 +1189,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1218,50 +1222,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2551.8</v>
+        <v>2489.1</v>
       </c>
       <c r="C9" t="n">
-        <v>2566.5</v>
+        <v>2500.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2463</v>
+        <v>2386.6</v>
       </c>
       <c r="E9" t="n">
-        <v>2489.9</v>
+        <v>2440.6</v>
       </c>
       <c r="F9" t="n">
-        <v>-33.8</v>
+        <v>-49.3</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0134</v>
+        <v>-0.0198</v>
       </c>
       <c r="H9" t="n">
-        <v>103.5</v>
+        <v>113.8</v>
       </c>
       <c r="I9" t="n">
-        <v>2329.8</v>
+        <v>2359.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2433.22</v>
+        <v>2373.97</v>
       </c>
       <c r="K9" t="n">
-        <v>2470.15</v>
+        <v>2438.15</v>
       </c>
       <c r="L9" t="n">
-        <v>2507.07</v>
+        <v>2502.32</v>
       </c>
       <c r="M9" t="n">
-        <v>2577.25</v>
+        <v>2541.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2647.43</v>
+        <v>2580.97</v>
       </c>
       <c r="O9" t="n">
-        <v>2651.1</v>
+        <v>2670</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,12 +1275,12 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1293,59 +1297,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2489.1</v>
+        <v>2455.2</v>
       </c>
       <c r="C10" t="n">
-        <v>2500.4</v>
+        <v>2487.6</v>
       </c>
       <c r="D10" t="n">
-        <v>2386.6</v>
+        <v>2353.8</v>
       </c>
       <c r="E10" t="n">
-        <v>2440.6</v>
+        <v>2396</v>
       </c>
       <c r="F10" t="n">
-        <v>-49.3</v>
+        <v>-44.6</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0198</v>
+        <v>-0.0183</v>
       </c>
       <c r="H10" t="n">
-        <v>113.8</v>
+        <v>133.8</v>
       </c>
       <c r="I10" t="n">
-        <v>2359.5</v>
+        <v>2272.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2373.97</v>
+        <v>2325.35</v>
       </c>
       <c r="K10" t="n">
-        <v>2438.15</v>
+        <v>2383.7</v>
       </c>
       <c r="L10" t="n">
-        <v>2502.32</v>
+        <v>2442.05</v>
       </c>
       <c r="M10" t="n">
-        <v>2541.65</v>
+        <v>2497.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2580.97</v>
+        <v>2552.95</v>
       </c>
       <c r="O10" t="n">
-        <v>2670</v>
+        <v>2614.2</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1382,50 +1382,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2455.2</v>
+        <v>2397</v>
       </c>
       <c r="C11" t="n">
-        <v>2487.6</v>
+        <v>2411.9</v>
       </c>
       <c r="D11" t="n">
-        <v>2353.8</v>
+        <v>2300.7</v>
       </c>
       <c r="E11" t="n">
-        <v>2396</v>
+        <v>2375.3</v>
       </c>
       <c r="F11" t="n">
-        <v>-44.6</v>
+        <v>-20.7</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.0086</v>
       </c>
       <c r="H11" t="n">
-        <v>133.8</v>
+        <v>111.2</v>
       </c>
       <c r="I11" t="n">
-        <v>2272.8</v>
+        <v>2220</v>
       </c>
       <c r="J11" t="n">
-        <v>2325.35</v>
+        <v>2249.85</v>
       </c>
       <c r="K11" t="n">
-        <v>2383.7</v>
+        <v>2329.1</v>
       </c>
       <c r="L11" t="n">
-        <v>2442.05</v>
+        <v>2408.35</v>
       </c>
       <c r="M11" t="n">
-        <v>2497.5</v>
+        <v>2462.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2552.95</v>
+        <v>2517.45</v>
       </c>
       <c r="O11" t="n">
-        <v>2614.2</v>
+        <v>2621.4</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1462,50 +1462,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2397</v>
+        <v>2387.8</v>
       </c>
       <c r="C12" t="n">
-        <v>2411.9</v>
+        <v>2508.1</v>
       </c>
       <c r="D12" t="n">
-        <v>2300.7</v>
+        <v>2370.3</v>
       </c>
       <c r="E12" t="n">
-        <v>2375.3</v>
+        <v>2505.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-20.7</v>
+        <v>129.8</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0546</v>
       </c>
       <c r="H12" t="n">
-        <v>111.2</v>
+        <v>137.8</v>
       </c>
       <c r="I12" t="n">
-        <v>2220</v>
+        <v>2189.5</v>
       </c>
       <c r="J12" t="n">
-        <v>2249.85</v>
+        <v>2273.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2329.1</v>
+        <v>2319.7</v>
       </c>
       <c r="L12" t="n">
-        <v>2408.35</v>
+        <v>2365.8</v>
       </c>
       <c r="M12" t="n">
-        <v>2462.9</v>
+        <v>2430.9</v>
       </c>
       <c r="N12" t="n">
-        <v>2517.45</v>
+        <v>2496</v>
       </c>
       <c r="O12" t="n">
-        <v>2621.4</v>
+        <v>2523.1</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1513,28 +1513,30 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1542,50 +1544,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2387.8</v>
+        <v>2501</v>
       </c>
       <c r="C13" t="n">
-        <v>2508.1</v>
+        <v>2544.2</v>
       </c>
       <c r="D13" t="n">
-        <v>2370.3</v>
+        <v>2468.1</v>
       </c>
       <c r="E13" t="n">
-        <v>2505.1</v>
+        <v>2524.4</v>
       </c>
       <c r="F13" t="n">
-        <v>129.8</v>
+        <v>19.3</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0077</v>
       </c>
       <c r="H13" t="n">
-        <v>137.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>2189.5</v>
+        <v>2232.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2273.6</v>
+        <v>2400.25</v>
       </c>
       <c r="K13" t="n">
-        <v>2319.7</v>
+        <v>2436.2</v>
       </c>
       <c r="L13" t="n">
-        <v>2365.8</v>
+        <v>2472.15</v>
       </c>
       <c r="M13" t="n">
-        <v>2430.9</v>
+        <v>2574</v>
       </c>
       <c r="N13" t="n">
-        <v>2496</v>
+        <v>2675.85</v>
       </c>
       <c r="O13" t="n">
-        <v>2523.1</v>
+        <v>2645.9</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1603,13 +1605,11 @@
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1624,50 +1624,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2501</v>
+        <v>2528</v>
       </c>
       <c r="C14" t="n">
-        <v>2544.2</v>
+        <v>2605</v>
       </c>
       <c r="D14" t="n">
-        <v>2468.1</v>
+        <v>2516.6</v>
       </c>
       <c r="E14" t="n">
-        <v>2524.4</v>
+        <v>2553.7</v>
       </c>
       <c r="F14" t="n">
-        <v>19.3</v>
+        <v>29.3</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0116</v>
       </c>
       <c r="H14" t="n">
-        <v>76.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>2232.5</v>
+        <v>2392</v>
       </c>
       <c r="J14" t="n">
-        <v>2400.25</v>
+        <v>2457.42</v>
       </c>
       <c r="K14" t="n">
-        <v>2436.2</v>
+        <v>2486.35</v>
       </c>
       <c r="L14" t="n">
-        <v>2472.15</v>
+        <v>2515.27</v>
       </c>
       <c r="M14" t="n">
-        <v>2574</v>
+        <v>2562.45</v>
       </c>
       <c r="N14" t="n">
-        <v>2675.85</v>
+        <v>2609.62</v>
       </c>
       <c r="O14" t="n">
-        <v>2645.9</v>
+        <v>2620.3</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1704,50 +1704,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2528</v>
+        <v>2552.8</v>
       </c>
       <c r="C15" t="n">
-        <v>2605</v>
+        <v>2577.3</v>
       </c>
       <c r="D15" t="n">
-        <v>2516.6</v>
+        <v>2489.4</v>
       </c>
       <c r="E15" t="n">
-        <v>2553.7</v>
+        <v>2509.56</v>
       </c>
       <c r="F15" t="n">
-        <v>29.3</v>
+        <v>-44.14</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0116</v>
+        <v>-0.0173</v>
       </c>
       <c r="H15" t="n">
-        <v>88.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2392</v>
+        <v>2428.2</v>
       </c>
       <c r="J15" t="n">
-        <v>2457.42</v>
+        <v>2461.75</v>
       </c>
       <c r="K15" t="n">
-        <v>2486.35</v>
+        <v>2509.5</v>
       </c>
       <c r="L15" t="n">
-        <v>2515.27</v>
+        <v>2557.25</v>
       </c>
       <c r="M15" t="n">
-        <v>2562.45</v>
+        <v>2597.9</v>
       </c>
       <c r="N15" t="n">
-        <v>2609.62</v>
+        <v>2638.55</v>
       </c>
       <c r="O15" t="n">
-        <v>2620.3</v>
+        <v>2693.4</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1755,19 +1755,19 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1779,55 +1779,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2552.8</v>
+        <v>2550</v>
       </c>
       <c r="C16" t="n">
-        <v>2577.3</v>
+        <v>2590.3</v>
       </c>
       <c r="D16" t="n">
-        <v>2489.4</v>
+        <v>2540.8</v>
       </c>
       <c r="E16" t="n">
-        <v>2509.56</v>
+        <v>2551.4</v>
       </c>
       <c r="F16" t="n">
-        <v>-44.14</v>
+        <v>41.84</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0173</v>
+        <v>0.0167</v>
       </c>
       <c r="H16" t="n">
-        <v>87.90000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="I16" t="n">
-        <v>2428.2</v>
+        <v>2401.5</v>
       </c>
       <c r="J16" t="n">
-        <v>2461.75</v>
+        <v>2409.76</v>
       </c>
       <c r="K16" t="n">
-        <v>2509.5</v>
+        <v>2465.61</v>
       </c>
       <c r="L16" t="n">
-        <v>2557.25</v>
+        <v>2521.46</v>
       </c>
       <c r="M16" t="n">
-        <v>2597.9</v>
+        <v>2553.51</v>
       </c>
       <c r="N16" t="n">
-        <v>2638.55</v>
+        <v>2585.57</v>
       </c>
       <c r="O16" t="n">
-        <v>2693.4</v>
+        <v>2665.2</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1835,21 +1839,23 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1859,83 +1865,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2550</v>
+        <v>2551.6</v>
       </c>
       <c r="C17" t="n">
-        <v>2590.3</v>
+        <v>2556.9</v>
       </c>
       <c r="D17" t="n">
-        <v>2540.8</v>
+        <v>2493.5</v>
       </c>
       <c r="E17" t="n">
-        <v>2551.4</v>
+        <v>2522.5</v>
       </c>
       <c r="F17" t="n">
-        <v>41.84</v>
+        <v>-28.9</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0167</v>
+        <v>-0.0113</v>
       </c>
       <c r="H17" t="n">
-        <v>49.5</v>
+        <v>63.4</v>
       </c>
       <c r="I17" t="n">
-        <v>2401.5</v>
+        <v>2491.3</v>
       </c>
       <c r="J17" t="n">
-        <v>2409.76</v>
+        <v>2494.82</v>
       </c>
       <c r="K17" t="n">
-        <v>2465.61</v>
+        <v>2526.65</v>
       </c>
       <c r="L17" t="n">
-        <v>2521.46</v>
+        <v>2558.47</v>
       </c>
       <c r="M17" t="n">
-        <v>2553.51</v>
+        <v>2576.15</v>
       </c>
       <c r="N17" t="n">
-        <v>2585.57</v>
+        <v>2593.82</v>
       </c>
       <c r="O17" t="n">
-        <v>2665.2</v>
+        <v>2639.8</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1945,141 +1947,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2551.6</v>
+        <v>2524.2</v>
       </c>
       <c r="C18" t="n">
-        <v>2556.9</v>
+        <v>2650.3</v>
       </c>
       <c r="D18" t="n">
-        <v>2493.5</v>
+        <v>2517.2</v>
       </c>
       <c r="E18" t="n">
-        <v>2522.5</v>
+        <v>2636.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-28.9</v>
+        <v>114.4</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0113</v>
+        <v>0.0454</v>
       </c>
       <c r="H18" t="n">
-        <v>63.4</v>
+        <v>133.1</v>
       </c>
       <c r="I18" t="n">
-        <v>2491.3</v>
+        <v>2430.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2494.82</v>
+        <v>2457.75</v>
       </c>
       <c r="K18" t="n">
-        <v>2526.65</v>
+        <v>2490.8</v>
       </c>
       <c r="L18" t="n">
-        <v>2558.47</v>
+        <v>2523.85</v>
       </c>
       <c r="M18" t="n">
-        <v>2576.15</v>
+        <v>2554.2</v>
       </c>
       <c r="N18" t="n">
-        <v>2593.82</v>
+        <v>2584.55</v>
       </c>
       <c r="O18" t="n">
-        <v>2639.8</v>
+        <v>2620.3</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2524.2</v>
+        <v>2638.9</v>
       </c>
       <c r="C19" t="n">
-        <v>2650.3</v>
+        <v>2705.6</v>
       </c>
       <c r="D19" t="n">
-        <v>2517.2</v>
+        <v>2616.3</v>
       </c>
       <c r="E19" t="n">
-        <v>2636.9</v>
+        <v>2691.2</v>
       </c>
       <c r="F19" t="n">
-        <v>114.4</v>
+        <v>54.3</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0454</v>
+        <v>0.0206</v>
       </c>
       <c r="H19" t="n">
-        <v>133.1</v>
+        <v>89.3</v>
       </c>
       <c r="I19" t="n">
-        <v>2430.1</v>
+        <v>2384.1</v>
       </c>
       <c r="J19" t="n">
-        <v>2457.75</v>
+        <v>2530.37</v>
       </c>
       <c r="K19" t="n">
-        <v>2490.8</v>
+        <v>2570.35</v>
       </c>
       <c r="L19" t="n">
-        <v>2523.85</v>
+        <v>2610.32</v>
       </c>
       <c r="M19" t="n">
-        <v>2554.2</v>
+        <v>2703.45</v>
       </c>
       <c r="N19" t="n">
-        <v>2584.55</v>
+        <v>2796.57</v>
       </c>
       <c r="O19" t="n">
-        <v>2620.3</v>
+        <v>2783.4</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2097,18 +2101,14 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2120,50 +2120,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2638.9</v>
+        <v>2670</v>
       </c>
       <c r="C20" t="n">
-        <v>2705.6</v>
+        <v>2749.2</v>
       </c>
       <c r="D20" t="n">
-        <v>2616.3</v>
+        <v>2631</v>
       </c>
       <c r="E20" t="n">
-        <v>2691.2</v>
+        <v>2679.6</v>
       </c>
       <c r="F20" t="n">
-        <v>54.3</v>
+        <v>-11.6</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0206</v>
+        <v>-0.0043</v>
       </c>
       <c r="H20" t="n">
-        <v>89.3</v>
+        <v>118.2</v>
       </c>
       <c r="I20" t="n">
-        <v>2384.1</v>
+        <v>2527</v>
       </c>
       <c r="J20" t="n">
-        <v>2530.37</v>
+        <v>2617.02</v>
       </c>
       <c r="K20" t="n">
-        <v>2570.35</v>
+        <v>2646.55</v>
       </c>
       <c r="L20" t="n">
-        <v>2610.32</v>
+        <v>2676.08</v>
       </c>
       <c r="M20" t="n">
-        <v>2703.45</v>
+        <v>2735.85</v>
       </c>
       <c r="N20" t="n">
-        <v>2796.57</v>
+        <v>2795.62</v>
       </c>
       <c r="O20" t="n">
-        <v>2783.4</v>
+        <v>2794.9</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2171,17 +2171,19 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U20" s="8" t="n">
@@ -2195,55 +2197,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2670</v>
+        <v>2661</v>
       </c>
       <c r="C21" t="n">
-        <v>2749.2</v>
+        <v>2697.9</v>
       </c>
       <c r="D21" t="n">
-        <v>2631</v>
+        <v>2607.5</v>
       </c>
       <c r="E21" t="n">
-        <v>2679.6</v>
+        <v>2624.6</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.6</v>
+        <v>-55</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0205</v>
       </c>
       <c r="H21" t="n">
-        <v>118.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>2527</v>
+        <v>2512.8</v>
       </c>
       <c r="J21" t="n">
-        <v>2617.02</v>
+        <v>2556.15</v>
       </c>
       <c r="K21" t="n">
-        <v>2646.55</v>
+        <v>2620.5</v>
       </c>
       <c r="L21" t="n">
-        <v>2676.08</v>
+        <v>2684.85</v>
       </c>
       <c r="M21" t="n">
-        <v>2735.85</v>
+        <v>2738.7</v>
       </c>
       <c r="N21" t="n">
-        <v>2795.62</v>
+        <v>2792.55</v>
       </c>
       <c r="O21" t="n">
-        <v>2794.9</v>
+        <v>2867.4</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2253,18 +2259,16 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2279,57 +2283,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2661</v>
+        <v>2615</v>
       </c>
       <c r="C22" t="n">
-        <v>2697.9</v>
+        <v>2684.1</v>
       </c>
       <c r="D22" t="n">
-        <v>2607.5</v>
+        <v>2566.8</v>
       </c>
       <c r="E22" t="n">
-        <v>2624.6</v>
+        <v>2677.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-55</v>
+        <v>53.3</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0205</v>
+        <v>0.0203</v>
       </c>
       <c r="H22" t="n">
-        <v>90.40000000000001</v>
+        <v>117.3</v>
       </c>
       <c r="I22" t="n">
-        <v>2512.8</v>
+        <v>2517.1</v>
       </c>
       <c r="J22" t="n">
-        <v>2556.15</v>
+        <v>2520.15</v>
       </c>
       <c r="K22" t="n">
-        <v>2620.5</v>
+        <v>2579.4</v>
       </c>
       <c r="L22" t="n">
-        <v>2684.85</v>
+        <v>2638.65</v>
       </c>
       <c r="M22" t="n">
-        <v>2738.7</v>
+        <v>2669.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2792.55</v>
+        <v>2700.95</v>
       </c>
       <c r="O22" t="n">
-        <v>2867.4</v>
+        <v>2788.3</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2339,17 +2343,19 @@
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2363,57 +2369,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2615</v>
+        <v>2677</v>
       </c>
       <c r="C23" t="n">
-        <v>2684.1</v>
+        <v>2720</v>
       </c>
       <c r="D23" t="n">
-        <v>2566.8</v>
+        <v>2607.3</v>
       </c>
       <c r="E23" t="n">
-        <v>2677.9</v>
+        <v>2653.1</v>
       </c>
       <c r="F23" t="n">
-        <v>53.3</v>
+        <v>-24.8</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0203</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>117.3</v>
+        <v>112.7</v>
       </c>
       <c r="I23" t="n">
-        <v>2517.1</v>
+        <v>2449.5</v>
       </c>
       <c r="J23" t="n">
-        <v>2520.15</v>
+        <v>2586.82</v>
       </c>
       <c r="K23" t="n">
-        <v>2579.4</v>
+        <v>2619.25</v>
       </c>
       <c r="L23" t="n">
-        <v>2638.65</v>
+        <v>2651.67</v>
       </c>
       <c r="M23" t="n">
-        <v>2669.8</v>
+        <v>2736.55</v>
       </c>
       <c r="N23" t="n">
-        <v>2700.95</v>
+        <v>2821.42</v>
       </c>
       <c r="O23" t="n">
-        <v>2788.3</v>
+        <v>2801.4</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2428,13 +2434,11 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2449,57 +2453,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2677</v>
+        <v>2650.9</v>
       </c>
       <c r="C24" t="n">
-        <v>2720</v>
+        <v>2696</v>
       </c>
       <c r="D24" t="n">
-        <v>2607.3</v>
+        <v>2613.7</v>
       </c>
       <c r="E24" t="n">
-        <v>2653.1</v>
+        <v>2668.8</v>
       </c>
       <c r="F24" t="n">
-        <v>-24.8</v>
+        <v>15.7</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H24" t="n">
-        <v>112.7</v>
+        <v>82.3</v>
       </c>
       <c r="I24" t="n">
-        <v>2449.5</v>
+        <v>2494.6</v>
       </c>
       <c r="J24" t="n">
-        <v>2586.82</v>
+        <v>2535.13</v>
       </c>
       <c r="K24" t="n">
-        <v>2619.25</v>
+        <v>2596.75</v>
       </c>
       <c r="L24" t="n">
-        <v>2651.67</v>
+        <v>2658.38</v>
       </c>
       <c r="M24" t="n">
-        <v>2736.55</v>
+        <v>2709.45</v>
       </c>
       <c r="N24" t="n">
-        <v>2821.42</v>
+        <v>2760.53</v>
       </c>
       <c r="O24" t="n">
-        <v>2801.4</v>
+        <v>2832.7</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2507,10 +2511,8 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
@@ -2540,50 +2542,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2650.9</v>
+        <v>2666.5</v>
       </c>
       <c r="C25" t="n">
-        <v>2696</v>
+        <v>2683.4</v>
       </c>
       <c r="D25" t="n">
-        <v>2613.7</v>
+        <v>2602.7</v>
       </c>
       <c r="E25" t="n">
-        <v>2668.8</v>
+        <v>2634.7</v>
       </c>
       <c r="F25" t="n">
-        <v>15.7</v>
+        <v>-34.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0128</v>
       </c>
       <c r="H25" t="n">
-        <v>82.3</v>
+        <v>80.7</v>
       </c>
       <c r="I25" t="n">
-        <v>2494.6</v>
+        <v>2531.4</v>
       </c>
       <c r="J25" t="n">
-        <v>2535.13</v>
+        <v>2593.48</v>
       </c>
       <c r="K25" t="n">
-        <v>2596.75</v>
+        <v>2627.65</v>
       </c>
       <c r="L25" t="n">
-        <v>2658.38</v>
+        <v>2661.83</v>
       </c>
       <c r="M25" t="n">
-        <v>2709.45</v>
+        <v>2709.95</v>
       </c>
       <c r="N25" t="n">
-        <v>2760.53</v>
+        <v>2758.08</v>
       </c>
       <c r="O25" t="n">
-        <v>2832.7</v>
+        <v>2778.3</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2591,12 +2593,14 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2615,67 +2619,71 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2666.5</v>
+        <v>2608.8</v>
       </c>
       <c r="C26" t="n">
-        <v>2683.4</v>
+        <v>2663.3</v>
       </c>
       <c r="D26" t="n">
-        <v>2602.7</v>
+        <v>2516.6</v>
       </c>
       <c r="E26" t="n">
-        <v>2634.7</v>
+        <v>2526.7</v>
       </c>
       <c r="F26" t="n">
-        <v>-34.1</v>
+        <v>-108</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0128</v>
+        <v>-0.041</v>
       </c>
       <c r="H26" t="n">
-        <v>80.7</v>
+        <v>146.7</v>
       </c>
       <c r="I26" t="n">
-        <v>2531.4</v>
+        <v>2522</v>
       </c>
       <c r="J26" t="n">
-        <v>2593.48</v>
+        <v>2549.83</v>
       </c>
       <c r="K26" t="n">
-        <v>2627.65</v>
+        <v>2594.35</v>
       </c>
       <c r="L26" t="n">
-        <v>2661.83</v>
+        <v>2638.87</v>
       </c>
       <c r="M26" t="n">
-        <v>2709.95</v>
+        <v>2675.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2758.08</v>
+        <v>2711.22</v>
       </c>
       <c r="O26" t="n">
-        <v>2778.3</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+        <v>2764.1</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
@@ -2692,78 +2700,70 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2608.8</v>
+        <v>2499.2</v>
       </c>
       <c r="C27" t="n">
-        <v>2663.3</v>
+        <v>2594.4</v>
       </c>
       <c r="D27" t="n">
-        <v>2516.6</v>
+        <v>2416.9</v>
       </c>
       <c r="E27" t="n">
-        <v>2526.7</v>
+        <v>2480.9</v>
       </c>
       <c r="F27" t="n">
-        <v>-108</v>
+        <v>-45.8</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.041</v>
+        <v>-0.0181</v>
       </c>
       <c r="H27" t="n">
-        <v>146.7</v>
+        <v>177.5</v>
       </c>
       <c r="I27" t="n">
-        <v>2522</v>
+        <v>2369.9</v>
       </c>
       <c r="J27" t="n">
-        <v>2549.83</v>
+        <v>2348.37</v>
       </c>
       <c r="K27" t="n">
-        <v>2594.35</v>
+        <v>2453.35</v>
       </c>
       <c r="L27" t="n">
-        <v>2638.87</v>
+        <v>2558.33</v>
       </c>
       <c r="M27" t="n">
-        <v>2675.05</v>
+        <v>2600.05</v>
       </c>
       <c r="N27" t="n">
-        <v>2711.22</v>
+        <v>2641.77</v>
       </c>
       <c r="O27" t="n">
-        <v>2764.1</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>2810</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
@@ -2790,50 +2790,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2499.2</v>
+        <v>2468.5</v>
       </c>
       <c r="C28" t="n">
-        <v>2594.4</v>
+        <v>2547.9</v>
       </c>
       <c r="D28" t="n">
-        <v>2416.9</v>
+        <v>2442</v>
       </c>
       <c r="E28" t="n">
-        <v>2480.9</v>
+        <v>2496.4</v>
       </c>
       <c r="F28" t="n">
-        <v>-45.8</v>
+        <v>15.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0181</v>
+        <v>0.0062</v>
       </c>
       <c r="H28" t="n">
-        <v>177.5</v>
+        <v>105.9</v>
       </c>
       <c r="I28" t="n">
-        <v>2369.9</v>
+        <v>2239.4</v>
       </c>
       <c r="J28" t="n">
-        <v>2348.37</v>
+        <v>2291.02</v>
       </c>
       <c r="K28" t="n">
-        <v>2453.35</v>
+        <v>2392.15</v>
       </c>
       <c r="L28" t="n">
-        <v>2558.33</v>
+        <v>2493.27</v>
       </c>
       <c r="M28" t="n">
-        <v>2600.05</v>
+        <v>2569.65</v>
       </c>
       <c r="N28" t="n">
-        <v>2641.77</v>
+        <v>2646.02</v>
       </c>
       <c r="O28" t="n">
-        <v>2810</v>
+        <v>2771.9</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2841,14 +2841,12 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2865,55 +2863,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2468.5</v>
+        <v>2429.1</v>
       </c>
       <c r="C29" t="n">
-        <v>2547.9</v>
+        <v>2574.5</v>
       </c>
       <c r="D29" t="n">
-        <v>2442</v>
+        <v>2415.3</v>
       </c>
       <c r="E29" t="n">
-        <v>2496.4</v>
+        <v>2464</v>
       </c>
       <c r="F29" t="n">
-        <v>15.5</v>
+        <v>-32.4</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.013</v>
       </c>
       <c r="H29" t="n">
-        <v>105.9</v>
+        <v>159.2</v>
       </c>
       <c r="I29" t="n">
-        <v>2239.4</v>
+        <v>2336.1</v>
       </c>
       <c r="J29" t="n">
-        <v>2291.02</v>
+        <v>2391.22</v>
       </c>
       <c r="K29" t="n">
-        <v>2392.15</v>
+        <v>2443.45</v>
       </c>
       <c r="L29" t="n">
-        <v>2493.27</v>
+        <v>2495.67</v>
       </c>
       <c r="M29" t="n">
-        <v>2569.65</v>
+        <v>2549.35</v>
       </c>
       <c r="N29" t="n">
-        <v>2646.02</v>
+        <v>2603.02</v>
       </c>
       <c r="O29" t="n">
-        <v>2771.9</v>
+        <v>2653.8</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2921,16 +2923,20 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2945,57 +2951,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2429.1</v>
+        <v>2445</v>
       </c>
       <c r="C30" t="n">
-        <v>2574.5</v>
+        <v>2557</v>
       </c>
       <c r="D30" t="n">
-        <v>2415.3</v>
+        <v>2409.4</v>
       </c>
       <c r="E30" t="n">
-        <v>2464</v>
+        <v>2531.7</v>
       </c>
       <c r="F30" t="n">
-        <v>-32.4</v>
+        <v>67.7</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.013</v>
+        <v>0.0275</v>
       </c>
       <c r="H30" t="n">
-        <v>159.2</v>
+        <v>147.6</v>
       </c>
       <c r="I30" t="n">
-        <v>2336.1</v>
+        <v>2256.1</v>
       </c>
       <c r="J30" t="n">
-        <v>2391.22</v>
+        <v>2289.35</v>
       </c>
       <c r="K30" t="n">
-        <v>2443.45</v>
+        <v>2384.4</v>
       </c>
       <c r="L30" t="n">
-        <v>2495.67</v>
+        <v>2479.45</v>
       </c>
       <c r="M30" t="n">
-        <v>2549.35</v>
+        <v>2543.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2603.02</v>
+        <v>2607.75</v>
       </c>
       <c r="O30" t="n">
-        <v>2653.8</v>
+        <v>2733.7</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3003,19 +3009,17 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="U30" s="8" t="n">
@@ -3038,50 +3042,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2445</v>
+        <v>2527.9</v>
       </c>
       <c r="C31" t="n">
-        <v>2557</v>
+        <v>2674.5</v>
       </c>
       <c r="D31" t="n">
-        <v>2409.4</v>
+        <v>2511.4</v>
       </c>
       <c r="E31" t="n">
-        <v>2531.7</v>
+        <v>2644.4</v>
       </c>
       <c r="F31" t="n">
-        <v>67.7</v>
+        <v>112.7</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0445</v>
       </c>
       <c r="H31" t="n">
-        <v>147.6</v>
+        <v>163.1</v>
       </c>
       <c r="I31" t="n">
-        <v>2256.1</v>
+        <v>2261.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2289.35</v>
+        <v>2408.35</v>
       </c>
       <c r="K31" t="n">
-        <v>2384.4</v>
+        <v>2457.9</v>
       </c>
       <c r="L31" t="n">
-        <v>2479.45</v>
+        <v>2507.45</v>
       </c>
       <c r="M31" t="n">
-        <v>2543.6</v>
+        <v>2605.5</v>
       </c>
       <c r="N31" t="n">
-        <v>2607.75</v>
+        <v>2703.55</v>
       </c>
       <c r="O31" t="n">
-        <v>2733.7</v>
+        <v>2704.6</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3115,57 +3119,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2527.9</v>
+        <v>2607.8</v>
       </c>
       <c r="C32" t="n">
-        <v>2674.5</v>
+        <v>2807.8</v>
       </c>
       <c r="D32" t="n">
-        <v>2511.4</v>
+        <v>2591.8</v>
       </c>
       <c r="E32" t="n">
-        <v>2644.4</v>
+        <v>2788.9</v>
       </c>
       <c r="F32" t="n">
-        <v>112.7</v>
+        <v>144.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0445</v>
+        <v>0.0546</v>
       </c>
       <c r="H32" t="n">
-        <v>163.1</v>
+        <v>216</v>
       </c>
       <c r="I32" t="n">
-        <v>2261.8</v>
+        <v>2348.3</v>
       </c>
       <c r="J32" t="n">
-        <v>2408.35</v>
+        <v>2507.02</v>
       </c>
       <c r="K32" t="n">
-        <v>2457.9</v>
+        <v>2562.85</v>
       </c>
       <c r="L32" t="n">
-        <v>2507.45</v>
+        <v>2618.67</v>
       </c>
       <c r="M32" t="n">
-        <v>2605.5</v>
+        <v>2725.95</v>
       </c>
       <c r="N32" t="n">
-        <v>2703.55</v>
+        <v>2833.22</v>
       </c>
       <c r="O32" t="n">
-        <v>2704.6</v>
+        <v>2837.6</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3183,11 +3187,13 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3206,50 +3212,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2607.8</v>
+        <v>2758.7</v>
       </c>
       <c r="C33" t="n">
-        <v>2807.8</v>
+        <v>2828.7</v>
       </c>
       <c r="D33" t="n">
-        <v>2591.8</v>
+        <v>2745.9</v>
       </c>
       <c r="E33" t="n">
-        <v>2788.9</v>
+        <v>2796.1</v>
       </c>
       <c r="F33" t="n">
-        <v>144.5</v>
+        <v>7.2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0026</v>
       </c>
       <c r="H33" t="n">
-        <v>216</v>
+        <v>82.8</v>
       </c>
       <c r="I33" t="n">
-        <v>2348.3</v>
+        <v>2375.8</v>
       </c>
       <c r="J33" t="n">
-        <v>2507.02</v>
+        <v>2617.45</v>
       </c>
       <c r="K33" t="n">
-        <v>2562.85</v>
+        <v>2680.9</v>
       </c>
       <c r="L33" t="n">
-        <v>2618.67</v>
+        <v>2744.35</v>
       </c>
       <c r="M33" t="n">
-        <v>2725.95</v>
+        <v>2896.9</v>
       </c>
       <c r="N33" t="n">
-        <v>2833.22</v>
+        <v>3049.45</v>
       </c>
       <c r="O33" t="n">
-        <v>2837.6</v>
+        <v>3023.8</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3262,18 +3268,14 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3292,50 +3294,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2758.7</v>
+        <v>2792.7</v>
       </c>
       <c r="C34" t="n">
-        <v>2828.7</v>
+        <v>2825</v>
       </c>
       <c r="D34" t="n">
-        <v>2745.9</v>
+        <v>2726.1</v>
       </c>
       <c r="E34" t="n">
-        <v>2796.1</v>
+        <v>2819.3</v>
       </c>
       <c r="F34" t="n">
-        <v>7.2</v>
+        <v>23.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0083</v>
       </c>
       <c r="H34" t="n">
-        <v>82.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>2375.8</v>
+        <v>2663.1</v>
       </c>
       <c r="J34" t="n">
-        <v>2617.45</v>
+        <v>2717.7</v>
       </c>
       <c r="K34" t="n">
-        <v>2680.9</v>
+        <v>2754.7</v>
       </c>
       <c r="L34" t="n">
-        <v>2744.35</v>
+        <v>2791.7</v>
       </c>
       <c r="M34" t="n">
-        <v>2896.9</v>
+        <v>2837.5</v>
       </c>
       <c r="N34" t="n">
-        <v>3049.45</v>
+        <v>2883.3</v>
       </c>
       <c r="O34" t="n">
-        <v>3023.8</v>
+        <v>2911.5</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3343,16 +3345,20 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3367,57 +3373,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2792.7</v>
+        <v>2825.9</v>
       </c>
       <c r="C35" t="n">
-        <v>2825</v>
+        <v>2918.4</v>
       </c>
       <c r="D35" t="n">
-        <v>2726.1</v>
+        <v>2786.8</v>
       </c>
       <c r="E35" t="n">
-        <v>2819.3</v>
+        <v>2867.6</v>
       </c>
       <c r="F35" t="n">
-        <v>23.2</v>
+        <v>48.3</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0171</v>
       </c>
       <c r="H35" t="n">
-        <v>98.90000000000001</v>
+        <v>131.6</v>
       </c>
       <c r="I35" t="n">
-        <v>2663.1</v>
+        <v>2627.2</v>
       </c>
       <c r="J35" t="n">
-        <v>2717.7</v>
+        <v>2742.28</v>
       </c>
       <c r="K35" t="n">
-        <v>2754.7</v>
+        <v>2769.85</v>
       </c>
       <c r="L35" t="n">
-        <v>2791.7</v>
+        <v>2797.43</v>
       </c>
       <c r="M35" t="n">
-        <v>2837.5</v>
+        <v>2868.75</v>
       </c>
       <c r="N35" t="n">
-        <v>2883.3</v>
+        <v>2940.07</v>
       </c>
       <c r="O35" t="n">
-        <v>2911.5</v>
+        <v>2923.9</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3425,10 +3431,8 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
@@ -3453,57 +3457,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2825.9</v>
+        <v>2863</v>
       </c>
       <c r="C36" t="n">
-        <v>2918.4</v>
+        <v>2896.2</v>
       </c>
       <c r="D36" t="n">
-        <v>2786.8</v>
+        <v>2787.9</v>
       </c>
       <c r="E36" t="n">
-        <v>2867.6</v>
+        <v>2799.6</v>
       </c>
       <c r="F36" t="n">
-        <v>48.3</v>
+        <v>-68</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0171</v>
+        <v>-0.0237</v>
       </c>
       <c r="H36" t="n">
-        <v>131.6</v>
+        <v>108.3</v>
       </c>
       <c r="I36" t="n">
-        <v>2627.2</v>
+        <v>2655.2</v>
       </c>
       <c r="J36" t="n">
-        <v>2742.28</v>
+        <v>2743.5</v>
       </c>
       <c r="K36" t="n">
-        <v>2769.85</v>
+        <v>2801.8</v>
       </c>
       <c r="L36" t="n">
-        <v>2797.43</v>
+        <v>2860.1</v>
       </c>
       <c r="M36" t="n">
-        <v>2868.75</v>
+        <v>2933.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2940.07</v>
+        <v>3006.7</v>
       </c>
       <c r="O36" t="n">
-        <v>2923.9</v>
+        <v>3050</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3511,19 +3515,19 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3537,57 +3541,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2863</v>
+        <v>2788.8</v>
       </c>
       <c r="C37" t="n">
-        <v>2896.2</v>
+        <v>2887</v>
       </c>
       <c r="D37" t="n">
-        <v>2787.9</v>
+        <v>2728.4</v>
       </c>
       <c r="E37" t="n">
-        <v>2799.6</v>
+        <v>2872.1</v>
       </c>
       <c r="F37" t="n">
-        <v>-68</v>
+        <v>72.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0259</v>
       </c>
       <c r="H37" t="n">
-        <v>108.3</v>
+        <v>158.6</v>
       </c>
       <c r="I37" t="n">
-        <v>2655.2</v>
+        <v>2679.6</v>
       </c>
       <c r="J37" t="n">
-        <v>2743.5</v>
+        <v>2670.08</v>
       </c>
       <c r="K37" t="n">
-        <v>2801.8</v>
+        <v>2745.45</v>
       </c>
       <c r="L37" t="n">
-        <v>2860.1</v>
+        <v>2820.83</v>
       </c>
       <c r="M37" t="n">
-        <v>2933.4</v>
+        <v>2853.75</v>
       </c>
       <c r="N37" t="n">
-        <v>3006.7</v>
+        <v>2886.68</v>
       </c>
       <c r="O37" t="n">
-        <v>3050</v>
+        <v>3004.5</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3597,19 +3601,23 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3628,50 +3636,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2788.8</v>
+        <v>2888</v>
       </c>
       <c r="C38" t="n">
-        <v>2887</v>
+        <v>2952</v>
       </c>
       <c r="D38" t="n">
-        <v>2728.4</v>
+        <v>2887.9</v>
       </c>
       <c r="E38" t="n">
-        <v>2872.1</v>
+        <v>2924.3</v>
       </c>
       <c r="F38" t="n">
-        <v>72.5</v>
+        <v>52.2</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0259</v>
+        <v>0.0182</v>
       </c>
       <c r="H38" t="n">
-        <v>158.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>2679.6</v>
+        <v>2569.8</v>
       </c>
       <c r="J38" t="n">
-        <v>2670.08</v>
+        <v>2745.7</v>
       </c>
       <c r="K38" t="n">
-        <v>2745.45</v>
+        <v>2792.8</v>
       </c>
       <c r="L38" t="n">
-        <v>2820.83</v>
+        <v>2839.9</v>
       </c>
       <c r="M38" t="n">
-        <v>2853.75</v>
+        <v>2951.4</v>
       </c>
       <c r="N38" t="n">
-        <v>2886.68</v>
+        <v>3062.9</v>
       </c>
       <c r="O38" t="n">
-        <v>3004.5</v>
+        <v>3045.6</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3679,10 +3687,8 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
@@ -3691,14 +3697,12 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
@@ -3709,77 +3713,81 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2888</v>
+        <v>2920.5</v>
       </c>
       <c r="C39" t="n">
-        <v>2952</v>
+        <v>2948.3</v>
       </c>
       <c r="D39" t="n">
-        <v>2887.9</v>
+        <v>2812.4</v>
       </c>
       <c r="E39" t="n">
-        <v>2924.3</v>
+        <v>2834.8</v>
       </c>
       <c r="F39" t="n">
-        <v>52.2</v>
+        <v>-89.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0182</v>
+        <v>-0.0306</v>
       </c>
       <c r="H39" t="n">
-        <v>64.09999999999999</v>
+        <v>135.9</v>
       </c>
       <c r="I39" t="n">
-        <v>2569.8</v>
+        <v>2823.8</v>
       </c>
       <c r="J39" t="n">
-        <v>2745.7</v>
+        <v>2862.38</v>
       </c>
       <c r="K39" t="n">
-        <v>2792.8</v>
+        <v>2892.25</v>
       </c>
       <c r="L39" t="n">
-        <v>2839.9</v>
+        <v>2922.12</v>
       </c>
       <c r="M39" t="n">
-        <v>2951.4</v>
+        <v>2956.35</v>
       </c>
       <c r="N39" t="n">
-        <v>3062.9</v>
+        <v>2990.58</v>
       </c>
       <c r="O39" t="n">
-        <v>3045.6</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+        <v>3016.1</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3791,86 +3799,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2920.5</v>
+        <v>2816.3</v>
       </c>
       <c r="C40" t="n">
-        <v>2948.3</v>
+        <v>2974.2</v>
       </c>
       <c r="D40" t="n">
-        <v>2812.4</v>
+        <v>2793.7</v>
       </c>
       <c r="E40" t="n">
-        <v>2834.8</v>
+        <v>2947</v>
       </c>
       <c r="F40" t="n">
-        <v>-89.5</v>
+        <v>112.2</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0306</v>
+        <v>0.0396</v>
       </c>
       <c r="H40" t="n">
-        <v>135.9</v>
+        <v>180.5</v>
       </c>
       <c r="I40" t="n">
-        <v>2823.8</v>
+        <v>2676.5</v>
       </c>
       <c r="J40" t="n">
-        <v>2862.38</v>
+        <v>2676.12</v>
       </c>
       <c r="K40" t="n">
-        <v>2892.25</v>
+        <v>2766.85</v>
       </c>
       <c r="L40" t="n">
-        <v>2922.12</v>
+        <v>2857.58</v>
       </c>
       <c r="M40" t="n">
-        <v>2956.35</v>
+        <v>2902.75</v>
       </c>
       <c r="N40" t="n">
-        <v>2990.58</v>
+        <v>2947.93</v>
       </c>
       <c r="O40" t="n">
-        <v>3016.1</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
+        <v>3084.2</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3879,55 +3881,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2816.3</v>
+        <v>2984</v>
       </c>
       <c r="C41" t="n">
-        <v>2974.2</v>
+        <v>3005</v>
       </c>
       <c r="D41" t="n">
-        <v>2793.7</v>
+        <v>2910.3</v>
       </c>
       <c r="E41" t="n">
-        <v>2947</v>
+        <v>2995.6</v>
       </c>
       <c r="F41" t="n">
-        <v>112.2</v>
+        <v>48.6</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.0165</v>
       </c>
       <c r="H41" t="n">
-        <v>180.5</v>
+        <v>94.7</v>
       </c>
       <c r="I41" t="n">
-        <v>2676.5</v>
+        <v>2613.2</v>
       </c>
       <c r="J41" t="n">
-        <v>2676.12</v>
+        <v>2798.03</v>
       </c>
       <c r="K41" t="n">
-        <v>2766.85</v>
+        <v>2856.75</v>
       </c>
       <c r="L41" t="n">
-        <v>2857.58</v>
+        <v>2915.47</v>
       </c>
       <c r="M41" t="n">
-        <v>2902.75</v>
+        <v>3037.25</v>
       </c>
       <c r="N41" t="n">
-        <v>2947.93</v>
+        <v>3159.03</v>
       </c>
       <c r="O41" t="n">
-        <v>3084.2</v>
+        <v>3154.7</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3945,14 +3951,12 @@
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
@@ -3963,57 +3967,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2984</v>
+        <v>2989.9</v>
       </c>
       <c r="C42" t="n">
-        <v>3005</v>
+        <v>3062.4</v>
       </c>
       <c r="D42" t="n">
-        <v>2910.3</v>
+        <v>2965.2</v>
       </c>
       <c r="E42" t="n">
-        <v>2995.6</v>
+        <v>3022.6</v>
       </c>
       <c r="F42" t="n">
-        <v>48.6</v>
+        <v>27</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>94.7</v>
+        <v>97.2</v>
       </c>
       <c r="I42" t="n">
-        <v>2613.2</v>
+        <v>2815.6</v>
       </c>
       <c r="J42" t="n">
-        <v>2798.03</v>
+        <v>2919.88</v>
       </c>
       <c r="K42" t="n">
-        <v>2856.75</v>
+        <v>2948.25</v>
       </c>
       <c r="L42" t="n">
-        <v>2915.47</v>
+        <v>2976.63</v>
       </c>
       <c r="M42" t="n">
-        <v>3037.25</v>
+        <v>3042.95</v>
       </c>
       <c r="N42" t="n">
-        <v>3159.03</v>
+        <v>3109.28</v>
       </c>
       <c r="O42" t="n">
-        <v>3154.7</v>
+        <v>3099.7</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4054,50 +4058,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2989.9</v>
+        <v>3020.9</v>
       </c>
       <c r="C43" t="n">
-        <v>3062.4</v>
+        <v>3068.4</v>
       </c>
       <c r="D43" t="n">
-        <v>2965.2</v>
+        <v>2987.8</v>
       </c>
       <c r="E43" t="n">
-        <v>3022.6</v>
+        <v>3023.5</v>
       </c>
       <c r="F43" t="n">
-        <v>27</v>
+        <v>0.9</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0003</v>
       </c>
       <c r="H43" t="n">
-        <v>97.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>2815.6</v>
+        <v>2868</v>
       </c>
       <c r="J43" t="n">
-        <v>2919.88</v>
+        <v>2929.8</v>
       </c>
       <c r="K43" t="n">
-        <v>2948.25</v>
+        <v>2974</v>
       </c>
       <c r="L43" t="n">
-        <v>2976.63</v>
+        <v>3018.2</v>
       </c>
       <c r="M43" t="n">
-        <v>3042.95</v>
+        <v>3071.2</v>
       </c>
       <c r="N43" t="n">
-        <v>3109.28</v>
+        <v>3124.2</v>
       </c>
       <c r="O43" t="n">
-        <v>3099.7</v>
+        <v>3159.6</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4110,13 +4114,11 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4138,50 +4140,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3020.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C44" t="n">
-        <v>3068.4</v>
+        <v>3042.6</v>
       </c>
       <c r="D44" t="n">
-        <v>2987.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E44" t="n">
-        <v>3023.5</v>
+        <v>2994</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9</v>
+        <v>-29.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0098</v>
       </c>
       <c r="H44" t="n">
-        <v>80.59999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="I44" t="n">
-        <v>2868</v>
+        <v>2907.2</v>
       </c>
       <c r="J44" t="n">
-        <v>2929.8</v>
+        <v>2940.6</v>
       </c>
       <c r="K44" t="n">
-        <v>2974</v>
+        <v>2983.2</v>
       </c>
       <c r="L44" t="n">
-        <v>3018.2</v>
+        <v>3025.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3071.2</v>
+        <v>3063.8</v>
       </c>
       <c r="N44" t="n">
-        <v>3124.2</v>
+        <v>3101.8</v>
       </c>
       <c r="O44" t="n">
-        <v>3159.6</v>
+        <v>3149</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4189,12 +4191,14 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4211,59 +4215,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3019.7</v>
+        <v>2984.7</v>
       </c>
       <c r="C45" t="n">
-        <v>3042.6</v>
+        <v>3029.8</v>
       </c>
       <c r="D45" t="n">
-        <v>2943.4</v>
+        <v>2949.3</v>
       </c>
       <c r="E45" t="n">
-        <v>2994</v>
+        <v>2973.5</v>
       </c>
       <c r="F45" t="n">
-        <v>-29.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0068</v>
       </c>
       <c r="H45" t="n">
-        <v>99.2</v>
+        <v>80.5</v>
       </c>
       <c r="I45" t="n">
-        <v>2907.2</v>
+        <v>2844.2</v>
       </c>
       <c r="J45" t="n">
-        <v>2940.6</v>
+        <v>2895.3</v>
       </c>
       <c r="K45" t="n">
-        <v>2983.2</v>
+        <v>2944.4</v>
       </c>
       <c r="L45" t="n">
-        <v>3025.8</v>
+        <v>2993.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3063.8</v>
+        <v>3043.6</v>
       </c>
       <c r="N45" t="n">
-        <v>3101.8</v>
+        <v>3093.7</v>
       </c>
       <c r="O45" t="n">
-        <v>3149</v>
+        <v>3141.8</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4271,14 +4271,12 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4295,55 +4293,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2984.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C46" t="n">
-        <v>3029.8</v>
+        <v>2999.8</v>
       </c>
       <c r="D46" t="n">
-        <v>2949.3</v>
+        <v>2932.1</v>
       </c>
       <c r="E46" t="n">
-        <v>2973.5</v>
+        <v>2941.3</v>
       </c>
       <c r="F46" t="n">
-        <v>-20.5</v>
+        <v>-32.2</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0068</v>
+        <v>-0.0108</v>
       </c>
       <c r="H46" t="n">
-        <v>80.5</v>
+        <v>67.7</v>
       </c>
       <c r="I46" t="n">
-        <v>2844.2</v>
+        <v>2868.8</v>
       </c>
       <c r="J46" t="n">
-        <v>2895.3</v>
+        <v>2884.97</v>
       </c>
       <c r="K46" t="n">
-        <v>2944.4</v>
+        <v>2933.25</v>
       </c>
       <c r="L46" t="n">
-        <v>2993.5</v>
+        <v>2981.53</v>
       </c>
       <c r="M46" t="n">
-        <v>3043.6</v>
+        <v>3013.75</v>
       </c>
       <c r="N46" t="n">
-        <v>3093.7</v>
+        <v>3045.97</v>
       </c>
       <c r="O46" t="n">
-        <v>3141.8</v>
+        <v>3110.3</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4351,12 +4353,14 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4373,59 +4377,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2964.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C47" t="n">
-        <v>2999.8</v>
+        <v>2985.9</v>
       </c>
       <c r="D47" t="n">
-        <v>2932.1</v>
+        <v>2902.3</v>
       </c>
       <c r="E47" t="n">
-        <v>2941.3</v>
+        <v>2938</v>
       </c>
       <c r="F47" t="n">
-        <v>-32.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0011</v>
       </c>
       <c r="H47" t="n">
-        <v>67.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>2868.8</v>
+        <v>2864.4</v>
       </c>
       <c r="J47" t="n">
-        <v>2884.97</v>
+        <v>2861.28</v>
       </c>
       <c r="K47" t="n">
-        <v>2933.25</v>
+        <v>2907.45</v>
       </c>
       <c r="L47" t="n">
-        <v>2981.53</v>
+        <v>2953.63</v>
       </c>
       <c r="M47" t="n">
-        <v>3013.75</v>
+        <v>2975.15</v>
       </c>
       <c r="N47" t="n">
-        <v>3045.97</v>
+        <v>2996.67</v>
       </c>
       <c r="O47" t="n">
-        <v>3110.3</v>
+        <v>3067.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4435,16 +4435,18 @@
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4462,50 +4464,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2955.5</v>
+        <v>2950</v>
       </c>
       <c r="C48" t="n">
-        <v>2985.9</v>
+        <v>3058.3</v>
       </c>
       <c r="D48" t="n">
-        <v>2902.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E48" t="n">
-        <v>2938</v>
+        <v>3041.6</v>
       </c>
       <c r="F48" t="n">
-        <v>-3.3</v>
+        <v>103.6</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0353</v>
       </c>
       <c r="H48" t="n">
-        <v>83.59999999999999</v>
+        <v>109.9</v>
       </c>
       <c r="I48" t="n">
-        <v>2864.4</v>
+        <v>2818.7</v>
       </c>
       <c r="J48" t="n">
-        <v>2861.28</v>
+        <v>2851.35</v>
       </c>
       <c r="K48" t="n">
-        <v>2907.45</v>
+        <v>2896.2</v>
       </c>
       <c r="L48" t="n">
-        <v>2953.63</v>
+        <v>2941.05</v>
       </c>
       <c r="M48" t="n">
-        <v>2975.15</v>
+        <v>2979.8</v>
       </c>
       <c r="N48" t="n">
-        <v>2996.67</v>
+        <v>3018.55</v>
       </c>
       <c r="O48" t="n">
-        <v>3067.5</v>
+        <v>3069.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4513,30 +4515,30 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W48" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr"/>
@@ -4544,50 +4546,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2950</v>
+        <v>3038.9</v>
       </c>
       <c r="C49" t="n">
-        <v>3058.3</v>
+        <v>3076.3</v>
       </c>
       <c r="D49" t="n">
-        <v>2948.4</v>
+        <v>3016</v>
       </c>
       <c r="E49" t="n">
-        <v>3041.6</v>
+        <v>3074.9</v>
       </c>
       <c r="F49" t="n">
-        <v>103.6</v>
+        <v>33.3</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.0109</v>
       </c>
       <c r="H49" t="n">
-        <v>109.9</v>
+        <v>60.3</v>
       </c>
       <c r="I49" t="n">
-        <v>2818.7</v>
+        <v>2838.5</v>
       </c>
       <c r="J49" t="n">
-        <v>2851.35</v>
+        <v>2950.83</v>
       </c>
       <c r="K49" t="n">
-        <v>2896.2</v>
+        <v>2986.65</v>
       </c>
       <c r="L49" t="n">
-        <v>2941.05</v>
+        <v>3022.48</v>
       </c>
       <c r="M49" t="n">
-        <v>2979.8</v>
+        <v>3096.55</v>
       </c>
       <c r="N49" t="n">
-        <v>3018.55</v>
+        <v>3170.63</v>
       </c>
       <c r="O49" t="n">
-        <v>3069.5</v>
+        <v>3168.2</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4605,13 +4607,11 @@
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4626,144 +4626,148 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3038.9</v>
+        <v>3073.5</v>
       </c>
       <c r="C50" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D50" t="n">
-        <v>3016</v>
+        <v>2993.2</v>
       </c>
       <c r="E50" t="n">
-        <v>3074.9</v>
+        <v>3022.1</v>
       </c>
       <c r="F50" t="n">
-        <v>33.3</v>
+        <v>-52.8</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.0172</v>
       </c>
       <c r="H50" t="n">
-        <v>60.3</v>
+        <v>86.7</v>
       </c>
       <c r="I50" t="n">
-        <v>2838.5</v>
+        <v>2955.7</v>
       </c>
       <c r="J50" t="n">
-        <v>2950.83</v>
+        <v>3028.97</v>
       </c>
       <c r="K50" t="n">
-        <v>2986.65</v>
+        <v>3044.75</v>
       </c>
       <c r="L50" t="n">
-        <v>3022.48</v>
+        <v>3060.52</v>
       </c>
       <c r="M50" t="n">
-        <v>3096.55</v>
+        <v>3105.05</v>
       </c>
       <c r="N50" t="n">
-        <v>3170.63</v>
+        <v>3149.57</v>
       </c>
       <c r="O50" t="n">
-        <v>3168.2</v>
+        <v>3136.6</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
+      <c r="Q50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3073.5</v>
+        <v>3023</v>
       </c>
       <c r="C51" t="n">
-        <v>3079.9</v>
+        <v>3028.9</v>
       </c>
       <c r="D51" t="n">
-        <v>2993.2</v>
+        <v>2976.6</v>
       </c>
       <c r="E51" t="n">
-        <v>3022.1</v>
+        <v>2977.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-52.8</v>
+        <v>-44.6</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0172</v>
+        <v>-0.0148</v>
       </c>
       <c r="H51" t="n">
-        <v>86.7</v>
+        <v>52.3</v>
       </c>
       <c r="I51" t="n">
-        <v>2955.7</v>
+        <v>2906.5</v>
       </c>
       <c r="J51" t="n">
-        <v>3028.97</v>
+        <v>2928.18</v>
       </c>
       <c r="K51" t="n">
-        <v>3044.75</v>
+        <v>2978.75</v>
       </c>
       <c r="L51" t="n">
-        <v>3060.52</v>
+        <v>3029.33</v>
       </c>
       <c r="M51" t="n">
-        <v>3105.05</v>
+        <v>3065.45</v>
       </c>
       <c r="N51" t="n">
-        <v>3149.57</v>
+        <v>3101.58</v>
       </c>
       <c r="O51" t="n">
-        <v>3136.6</v>
+        <v>3166.6</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4783,74 +4787,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3023</v>
+        <v>2971</v>
       </c>
       <c r="C52" t="n">
-        <v>3028.9</v>
+        <v>2983.3</v>
       </c>
       <c r="D52" t="n">
+        <v>2914.5</v>
+      </c>
+      <c r="E52" t="n">
         <v>2976.6</v>
       </c>
-      <c r="E52" t="n">
-        <v>2977.5</v>
-      </c>
       <c r="F52" t="n">
-        <v>-44.6</v>
+        <v>-0.9</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0148</v>
+        <v>-0.0003</v>
       </c>
       <c r="H52" t="n">
-        <v>52.3</v>
+        <v>68.8</v>
       </c>
       <c r="I52" t="n">
-        <v>2906.5</v>
+        <v>2924.3</v>
       </c>
       <c r="J52" t="n">
-        <v>2928.18</v>
+        <v>2912.58</v>
       </c>
       <c r="K52" t="n">
-        <v>2978.75</v>
+        <v>2951.35</v>
       </c>
       <c r="L52" t="n">
-        <v>3029.33</v>
+        <v>2990.12</v>
       </c>
       <c r="M52" t="n">
-        <v>3065.45</v>
+        <v>3003.65</v>
       </c>
       <c r="N52" t="n">
-        <v>3101.58</v>
+        <v>3017.17</v>
       </c>
       <c r="O52" t="n">
-        <v>3166.6</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
+        <v>3081.2</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4872,67 +4874,67 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2971</v>
+        <v>2974.7</v>
       </c>
       <c r="C53" t="n">
-        <v>2983.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D53" t="n">
-        <v>2914.5</v>
+        <v>2887.6</v>
       </c>
       <c r="E53" t="n">
-        <v>2976.6</v>
+        <v>2904.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.9</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0242</v>
       </c>
       <c r="H53" t="n">
-        <v>68.8</v>
+        <v>90.3</v>
       </c>
       <c r="I53" t="n">
-        <v>2924.3</v>
+        <v>2845.7</v>
       </c>
       <c r="J53" t="n">
-        <v>2912.58</v>
+        <v>2921.65</v>
       </c>
       <c r="K53" t="n">
-        <v>2951.35</v>
+        <v>2942.2</v>
       </c>
       <c r="L53" t="n">
-        <v>2990.12</v>
+        <v>2962.75</v>
       </c>
       <c r="M53" t="n">
-        <v>3003.65</v>
+        <v>3011</v>
       </c>
       <c r="N53" t="n">
-        <v>3017.17</v>
+        <v>3059.25</v>
       </c>
       <c r="O53" t="n">
-        <v>3081.2</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
+        <v>3052.1</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4954,62 +4956,60 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2974.7</v>
+        <v>2892.7</v>
       </c>
       <c r="C54" t="n">
-        <v>2977.9</v>
+        <v>2913.5</v>
       </c>
       <c r="D54" t="n">
-        <v>2887.6</v>
+        <v>2831.9</v>
       </c>
       <c r="E54" t="n">
-        <v>2904.5</v>
+        <v>2873.23</v>
       </c>
       <c r="F54" t="n">
-        <v>-72.09999999999999</v>
+        <v>-31.27</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0242</v>
+        <v>-0.0108</v>
       </c>
       <c r="H54" t="n">
-        <v>90.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>2845.7</v>
+        <v>2797.3</v>
       </c>
       <c r="J54" t="n">
-        <v>2921.65</v>
+        <v>2800.08</v>
       </c>
       <c r="K54" t="n">
-        <v>2942.2</v>
+        <v>2859.35</v>
       </c>
       <c r="L54" t="n">
-        <v>2962.75</v>
+        <v>2918.62</v>
       </c>
       <c r="M54" t="n">
-        <v>3011</v>
+        <v>2949.65</v>
       </c>
       <c r="N54" t="n">
-        <v>3059.25</v>
+        <v>2980.67</v>
       </c>
       <c r="O54" t="n">
-        <v>3052.1</v>
+        <v>3068.2</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
@@ -5036,50 +5036,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2892.7</v>
+        <v>2879.5</v>
       </c>
       <c r="C55" t="n">
-        <v>2913.5</v>
+        <v>2931.2</v>
       </c>
       <c r="D55" t="n">
-        <v>2831.9</v>
+        <v>2829.9</v>
       </c>
       <c r="E55" t="n">
-        <v>2873.23</v>
+        <v>2859.3</v>
       </c>
       <c r="F55" t="n">
-        <v>-31.27</v>
+        <v>-13.93</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0048</v>
       </c>
       <c r="H55" t="n">
-        <v>81.59999999999999</v>
+        <v>101.3</v>
       </c>
       <c r="I55" t="n">
-        <v>2797.3</v>
+        <v>2750.3</v>
       </c>
       <c r="J55" t="n">
-        <v>2800.08</v>
+        <v>2791.89</v>
       </c>
       <c r="K55" t="n">
-        <v>2859.35</v>
+        <v>2832.43</v>
       </c>
       <c r="L55" t="n">
-        <v>2918.62</v>
+        <v>2872.96</v>
       </c>
       <c r="M55" t="n">
-        <v>2949.65</v>
+        <v>2914.03</v>
       </c>
       <c r="N55" t="n">
-        <v>2980.67</v>
+        <v>2955.1</v>
       </c>
       <c r="O55" t="n">
-        <v>3068.2</v>
+        <v>2995.1</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5089,16 +5089,18 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5111,55 +5113,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2879.5</v>
+        <v>2857.7</v>
       </c>
       <c r="C56" t="n">
-        <v>2931.2</v>
+        <v>2875.3</v>
       </c>
       <c r="D56" t="n">
-        <v>2829.9</v>
+        <v>2791.5</v>
       </c>
       <c r="E56" t="n">
-        <v>2859.3</v>
+        <v>2850.9</v>
       </c>
       <c r="F56" t="n">
-        <v>-13.93</v>
+        <v>-8.4</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0029</v>
       </c>
       <c r="H56" t="n">
-        <v>101.3</v>
+        <v>83.8</v>
       </c>
       <c r="I56" t="n">
-        <v>2750.3</v>
+        <v>2728.6</v>
       </c>
       <c r="J56" t="n">
-        <v>2791.89</v>
+        <v>2747.38</v>
       </c>
       <c r="K56" t="n">
-        <v>2832.43</v>
+        <v>2808.65</v>
       </c>
       <c r="L56" t="n">
-        <v>2872.96</v>
+        <v>2869.92</v>
       </c>
       <c r="M56" t="n">
-        <v>2914.03</v>
+        <v>2909.95</v>
       </c>
       <c r="N56" t="n">
-        <v>2955.1</v>
+        <v>2949.98</v>
       </c>
       <c r="O56" t="n">
-        <v>2995.1</v>
+        <v>3032.5</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5177,10 +5183,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5193,59 +5197,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2857.7</v>
+        <v>2850.6</v>
       </c>
       <c r="C57" t="n">
-        <v>2875.3</v>
+        <v>2887.2</v>
       </c>
       <c r="D57" t="n">
-        <v>2791.5</v>
+        <v>2778.6</v>
       </c>
       <c r="E57" t="n">
-        <v>2850.9</v>
+        <v>2822.1</v>
       </c>
       <c r="F57" t="n">
-        <v>-8.4</v>
+        <v>-28.8</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0101</v>
       </c>
       <c r="H57" t="n">
-        <v>83.8</v>
+        <v>108.6</v>
       </c>
       <c r="I57" t="n">
-        <v>2728.6</v>
+        <v>2707.7</v>
       </c>
       <c r="J57" t="n">
-        <v>2747.38</v>
+        <v>2775.85</v>
       </c>
       <c r="K57" t="n">
-        <v>2808.65</v>
+        <v>2809</v>
       </c>
       <c r="L57" t="n">
-        <v>2869.92</v>
+        <v>2842.15</v>
       </c>
       <c r="M57" t="n">
-        <v>2909.95</v>
+        <v>2892.8</v>
       </c>
       <c r="N57" t="n">
-        <v>2949.98</v>
+        <v>2943.45</v>
       </c>
       <c r="O57" t="n">
-        <v>3032.5</v>
+        <v>2959.1</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5255,12 +5255,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5277,89 +5277,9 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2850.6</v>
-      </c>
-      <c r="C58" t="n">
-        <v>2887.2</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2804.2</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2818.5</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-32.4</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0114</v>
-      </c>
-      <c r="H58" t="n">
-        <v>83</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2707.7</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2775.85</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2809</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2842.15</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2892.8</v>
-      </c>
-      <c r="N58" t="n">
-        <v>2943.45</v>
-      </c>
-      <c r="O58" t="n">
-        <v>2959.1</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5215,13 +5215,13 @@
         <v>2778.6</v>
       </c>
       <c r="E57" t="n">
-        <v>2822.1</v>
+        <v>2829.9</v>
       </c>
       <c r="F57" t="n">
-        <v>-28.8</v>
+        <v>-21</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0101</v>
+        <v>-0.0074</v>
       </c>
       <c r="H57" t="n">
         <v>108.6</v>
@@ -5255,12 +5255,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5215,13 +5215,13 @@
         <v>2778.6</v>
       </c>
       <c r="E57" t="n">
-        <v>2829.9</v>
+        <v>2831.8</v>
       </c>
       <c r="F57" t="n">
-        <v>-21</v>
+        <v>-19.1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0067</v>
       </c>
       <c r="H57" t="n">
         <v>108.6</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5215,13 +5215,13 @@
         <v>2778.6</v>
       </c>
       <c r="E57" t="n">
-        <v>2831.8</v>
+        <v>2822.1</v>
       </c>
       <c r="F57" t="n">
-        <v>-19.1</v>
+        <v>-28.8</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0067</v>
+        <v>-0.0101</v>
       </c>
       <c r="H57" t="n">
         <v>108.6</v>
@@ -5255,29 +5255,111 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2822.9</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2834.3</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2810.4</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2812.2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="H58" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2670</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2708.1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2767.8</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2827.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2876.4</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2925.3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2995.8</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>96.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2315.1</v>
+        <v>2315.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2343.4</v>
+        <v>2343.47</v>
       </c>
       <c r="K2" t="n">
-        <v>2370.5</v>
+        <v>2370.55</v>
       </c>
       <c r="L2" t="n">
-        <v>2397.6</v>
+        <v>2397.62</v>
       </c>
       <c r="M2" t="n">
-        <v>2425.3</v>
+        <v>2425.25</v>
       </c>
       <c r="N2" t="n">
-        <v>2453</v>
+        <v>2452.87</v>
       </c>
       <c r="O2" t="n">
-        <v>2479.5</v>
+        <v>2479.4</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5296,19 +5296,19 @@
         <v>2834.3</v>
       </c>
       <c r="D58" t="n">
-        <v>2810.4</v>
+        <v>2798.6</v>
       </c>
       <c r="E58" t="n">
-        <v>2812.2</v>
+        <v>2803.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-9.9</v>
+        <v>-18.6</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0035</v>
+        <v>-0.0066</v>
       </c>
       <c r="H58" t="n">
-        <v>23.9</v>
+        <v>35.7</v>
       </c>
       <c r="I58" t="n">
         <v>2670</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5296,19 +5296,19 @@
         <v>2834.3</v>
       </c>
       <c r="D58" t="n">
-        <v>2798.6</v>
+        <v>2739.8</v>
       </c>
       <c r="E58" t="n">
-        <v>2803.5</v>
+        <v>2747.3</v>
       </c>
       <c r="F58" t="n">
-        <v>-18.6</v>
+        <v>-74.8</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0066</v>
+        <v>-0.0265</v>
       </c>
       <c r="H58" t="n">
-        <v>35.7</v>
+        <v>94.5</v>
       </c>
       <c r="I58" t="n">
         <v>2670</v>
@@ -5337,12 +5337,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5359,11 +5361,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5296,19 +5296,19 @@
         <v>2834.3</v>
       </c>
       <c r="D58" t="n">
-        <v>2739.8</v>
+        <v>2739.5</v>
       </c>
       <c r="E58" t="n">
-        <v>2747.3</v>
+        <v>2745</v>
       </c>
       <c r="F58" t="n">
-        <v>-74.8</v>
+        <v>-77.09999999999999</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0265</v>
+        <v>-0.0273</v>
       </c>
       <c r="H58" t="n">
-        <v>94.5</v>
+        <v>94.8</v>
       </c>
       <c r="I58" t="n">
         <v>2670</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5299,13 +5299,13 @@
         <v>2739.5</v>
       </c>
       <c r="E58" t="n">
-        <v>2745</v>
+        <v>2747.6</v>
       </c>
       <c r="F58" t="n">
-        <v>-77.09999999999999</v>
+        <v>-74.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0273</v>
+        <v>-0.0264</v>
       </c>
       <c r="H58" t="n">
         <v>94.8</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>96.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2315.3</v>
+        <v>2371.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2343.47</v>
+        <v>2368.43</v>
       </c>
       <c r="K2" t="n">
-        <v>2370.55</v>
+        <v>2385.75</v>
       </c>
       <c r="L2" t="n">
-        <v>2397.62</v>
+        <v>2403.07</v>
       </c>
       <c r="M2" t="n">
-        <v>2425.25</v>
+        <v>2410.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2452.87</v>
+        <v>2417.02</v>
       </c>
       <c r="O2" t="n">
-        <v>2479.4</v>
+        <v>2444.7</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -713,7 +713,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5296,19 +5300,19 @@
         <v>2834.3</v>
       </c>
       <c r="D58" t="n">
-        <v>2739.5</v>
+        <v>2734.9</v>
       </c>
       <c r="E58" t="n">
-        <v>2747.6</v>
+        <v>2781.7</v>
       </c>
       <c r="F58" t="n">
-        <v>-74.5</v>
+        <v>-40.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0264</v>
+        <v>-0.0143</v>
       </c>
       <c r="H58" t="n">
-        <v>94.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I58" t="n">
         <v>2670</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2398</v>
+        <v>2469.5</v>
       </c>
       <c r="C2" t="n">
-        <v>2485.1</v>
+        <v>2510.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2388.3</v>
+        <v>2412.1</v>
       </c>
       <c r="E2" t="n">
-        <v>2472.04</v>
+        <v>2450.4</v>
       </c>
       <c r="F2" t="n">
-        <v>74.14</v>
+        <v>-21.64</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0309</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>96.8</v>
+        <v>98.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2371.8</v>
+        <v>2291.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2368.43</v>
+        <v>2392.91</v>
       </c>
       <c r="K2" t="n">
-        <v>2385.75</v>
+        <v>2423.64</v>
       </c>
       <c r="L2" t="n">
-        <v>2403.07</v>
+        <v>2454.37</v>
       </c>
       <c r="M2" t="n">
-        <v>2410.05</v>
+        <v>2520.44</v>
       </c>
       <c r="N2" t="n">
-        <v>2417.02</v>
+        <v>2586.51</v>
       </c>
       <c r="O2" t="n">
-        <v>2444.7</v>
+        <v>2581.9</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,28 +685,24 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -722,50 +718,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2469.5</v>
+        <v>2449.2</v>
       </c>
       <c r="C3" t="n">
-        <v>2510.3</v>
+        <v>2515</v>
       </c>
       <c r="D3" t="n">
-        <v>2412.1</v>
+        <v>2424.7</v>
       </c>
       <c r="E3" t="n">
-        <v>2450.4</v>
+        <v>2492.1</v>
       </c>
       <c r="F3" t="n">
-        <v>-21.64</v>
+        <v>41.7</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="H3" t="n">
-        <v>98.2</v>
+        <v>90.3</v>
       </c>
       <c r="I3" t="n">
-        <v>2291.5</v>
+        <v>2313.9</v>
       </c>
       <c r="J3" t="n">
-        <v>2392.91</v>
+        <v>2346.8</v>
       </c>
       <c r="K3" t="n">
-        <v>2423.64</v>
+        <v>2401.3</v>
       </c>
       <c r="L3" t="n">
-        <v>2454.37</v>
+        <v>2455.8</v>
       </c>
       <c r="M3" t="n">
-        <v>2520.44</v>
+        <v>2499.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2586.51</v>
+        <v>2543.2</v>
       </c>
       <c r="O3" t="n">
-        <v>2581.9</v>
+        <v>2608.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,18 +769,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -797,78 +793,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2449.2</v>
+        <v>2491.9</v>
       </c>
       <c r="C4" t="n">
-        <v>2515</v>
+        <v>2518.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2424.7</v>
+        <v>2381.8</v>
       </c>
       <c r="E4" t="n">
-        <v>2492.1</v>
+        <v>2408.5</v>
       </c>
       <c r="F4" t="n">
-        <v>41.7</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.017</v>
+        <v>-0.0335</v>
       </c>
       <c r="H4" t="n">
-        <v>90.3</v>
+        <v>136.7</v>
       </c>
       <c r="I4" t="n">
-        <v>2313.9</v>
+        <v>2334.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2346.8</v>
+        <v>2412.93</v>
       </c>
       <c r="K4" t="n">
-        <v>2401.3</v>
+        <v>2446.95</v>
       </c>
       <c r="L4" t="n">
-        <v>2455.8</v>
+        <v>2480.98</v>
       </c>
       <c r="M4" t="n">
-        <v>2499.5</v>
+        <v>2537.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2543.2</v>
+        <v>2593.53</v>
       </c>
       <c r="O4" t="n">
-        <v>2608.5</v>
+        <v>2605.3</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -876,85 +870,89 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2491.9</v>
+        <v>2421.6</v>
       </c>
       <c r="C5" t="n">
-        <v>2518.5</v>
+        <v>2559.9</v>
       </c>
       <c r="D5" t="n">
-        <v>2381.8</v>
+        <v>2421.6</v>
       </c>
       <c r="E5" t="n">
-        <v>2408.5</v>
+        <v>2464.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-83.59999999999999</v>
+        <v>55.9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0335</v>
+        <v>0.0232</v>
       </c>
       <c r="H5" t="n">
-        <v>136.7</v>
+        <v>138.3</v>
       </c>
       <c r="I5" t="n">
-        <v>2334.4</v>
+        <v>2245.1</v>
       </c>
       <c r="J5" t="n">
-        <v>2412.93</v>
+        <v>2250.98</v>
       </c>
       <c r="K5" t="n">
-        <v>2446.95</v>
+        <v>2340.15</v>
       </c>
       <c r="L5" t="n">
-        <v>2480.98</v>
+        <v>2429.33</v>
       </c>
       <c r="M5" t="n">
-        <v>2537.25</v>
+        <v>2476.85</v>
       </c>
       <c r="N5" t="n">
-        <v>2593.53</v>
+        <v>2524.37</v>
       </c>
       <c r="O5" t="n">
-        <v>2605.3</v>
+        <v>2655.2</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
@@ -965,57 +963,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2421.6</v>
+        <v>2473.7</v>
       </c>
       <c r="C6" t="n">
-        <v>2559.9</v>
+        <v>2544</v>
       </c>
       <c r="D6" t="n">
-        <v>2421.6</v>
+        <v>2436.9</v>
       </c>
       <c r="E6" t="n">
-        <v>2464.4</v>
+        <v>2523.7</v>
       </c>
       <c r="F6" t="n">
-        <v>55.9</v>
+        <v>59.3</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0232</v>
+        <v>0.0241</v>
       </c>
       <c r="H6" t="n">
-        <v>138.3</v>
+        <v>107.1</v>
       </c>
       <c r="I6" t="n">
-        <v>2245.1</v>
+        <v>2283.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2250.98</v>
+        <v>2312.93</v>
       </c>
       <c r="K6" t="n">
-        <v>2340.15</v>
+        <v>2395.25</v>
       </c>
       <c r="L6" t="n">
-        <v>2429.33</v>
+        <v>2477.57</v>
       </c>
       <c r="M6" t="n">
-        <v>2476.85</v>
+        <v>2533.55</v>
       </c>
       <c r="N6" t="n">
-        <v>2524.37</v>
+        <v>2589.52</v>
       </c>
       <c r="O6" t="n">
-        <v>2655.2</v>
+        <v>2698.2</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1026,7 +1024,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1036,10 +1034,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1051,57 +1047,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2473.7</v>
+        <v>2551.8</v>
       </c>
       <c r="C7" t="n">
-        <v>2544</v>
+        <v>2566.5</v>
       </c>
       <c r="D7" t="n">
-        <v>2436.9</v>
+        <v>2463</v>
       </c>
       <c r="E7" t="n">
-        <v>2523.7</v>
+        <v>2489.9</v>
       </c>
       <c r="F7" t="n">
-        <v>59.3</v>
+        <v>-33.8</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0241</v>
+        <v>-0.0134</v>
       </c>
       <c r="H7" t="n">
-        <v>107.1</v>
+        <v>103.5</v>
       </c>
       <c r="I7" t="n">
-        <v>2283.3</v>
+        <v>2329.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2312.93</v>
+        <v>2433.22</v>
       </c>
       <c r="K7" t="n">
-        <v>2395.25</v>
+        <v>2470.15</v>
       </c>
       <c r="L7" t="n">
-        <v>2477.57</v>
+        <v>2507.07</v>
       </c>
       <c r="M7" t="n">
-        <v>2533.55</v>
+        <v>2577.25</v>
       </c>
       <c r="N7" t="n">
-        <v>2589.52</v>
+        <v>2647.43</v>
       </c>
       <c r="O7" t="n">
-        <v>2698.2</v>
+        <v>2651.1</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1109,18 +1105,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1142,50 +1138,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2551.8</v>
+        <v>2489.1</v>
       </c>
       <c r="C8" t="n">
-        <v>2566.5</v>
+        <v>2500.4</v>
       </c>
       <c r="D8" t="n">
-        <v>2463</v>
+        <v>2386.6</v>
       </c>
       <c r="E8" t="n">
-        <v>2489.9</v>
+        <v>2440.6</v>
       </c>
       <c r="F8" t="n">
-        <v>-33.8</v>
+        <v>-49.3</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0134</v>
+        <v>-0.0198</v>
       </c>
       <c r="H8" t="n">
-        <v>103.5</v>
+        <v>113.8</v>
       </c>
       <c r="I8" t="n">
-        <v>2329.8</v>
+        <v>2359.5</v>
       </c>
       <c r="J8" t="n">
-        <v>2433.22</v>
+        <v>2373.97</v>
       </c>
       <c r="K8" t="n">
-        <v>2470.15</v>
+        <v>2438.15</v>
       </c>
       <c r="L8" t="n">
-        <v>2507.07</v>
+        <v>2502.32</v>
       </c>
       <c r="M8" t="n">
-        <v>2577.25</v>
+        <v>2541.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2647.43</v>
+        <v>2580.97</v>
       </c>
       <c r="O8" t="n">
-        <v>2651.1</v>
+        <v>2670</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1195,12 +1191,12 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1217,59 +1213,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2489.1</v>
+        <v>2455.2</v>
       </c>
       <c r="C9" t="n">
-        <v>2500.4</v>
+        <v>2487.6</v>
       </c>
       <c r="D9" t="n">
-        <v>2386.6</v>
+        <v>2353.8</v>
       </c>
       <c r="E9" t="n">
-        <v>2440.6</v>
+        <v>2396</v>
       </c>
       <c r="F9" t="n">
-        <v>-49.3</v>
+        <v>-44.6</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0198</v>
+        <v>-0.0183</v>
       </c>
       <c r="H9" t="n">
-        <v>113.8</v>
+        <v>133.8</v>
       </c>
       <c r="I9" t="n">
-        <v>2359.5</v>
+        <v>2272.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2373.97</v>
+        <v>2325.35</v>
       </c>
       <c r="K9" t="n">
-        <v>2438.15</v>
+        <v>2383.7</v>
       </c>
       <c r="L9" t="n">
-        <v>2502.32</v>
+        <v>2442.05</v>
       </c>
       <c r="M9" t="n">
-        <v>2541.65</v>
+        <v>2497.5</v>
       </c>
       <c r="N9" t="n">
-        <v>2580.97</v>
+        <v>2552.95</v>
       </c>
       <c r="O9" t="n">
-        <v>2670</v>
+        <v>2614.2</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1282,7 +1274,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1306,50 +1298,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2455.2</v>
+        <v>2397</v>
       </c>
       <c r="C10" t="n">
-        <v>2487.6</v>
+        <v>2411.9</v>
       </c>
       <c r="D10" t="n">
-        <v>2353.8</v>
+        <v>2300.7</v>
       </c>
       <c r="E10" t="n">
-        <v>2396</v>
+        <v>2375.3</v>
       </c>
       <c r="F10" t="n">
-        <v>-44.6</v>
+        <v>-20.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.0086</v>
       </c>
       <c r="H10" t="n">
-        <v>133.8</v>
+        <v>111.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2272.8</v>
+        <v>2220</v>
       </c>
       <c r="J10" t="n">
-        <v>2325.35</v>
+        <v>2249.85</v>
       </c>
       <c r="K10" t="n">
-        <v>2383.7</v>
+        <v>2329.1</v>
       </c>
       <c r="L10" t="n">
-        <v>2442.05</v>
+        <v>2408.35</v>
       </c>
       <c r="M10" t="n">
-        <v>2497.5</v>
+        <v>2462.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2552.95</v>
+        <v>2517.45</v>
       </c>
       <c r="O10" t="n">
-        <v>2614.2</v>
+        <v>2621.4</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1359,12 +1351,12 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1386,50 +1378,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2397</v>
+        <v>2387.8</v>
       </c>
       <c r="C11" t="n">
-        <v>2411.9</v>
+        <v>2508.1</v>
       </c>
       <c r="D11" t="n">
-        <v>2300.7</v>
+        <v>2370.3</v>
       </c>
       <c r="E11" t="n">
-        <v>2375.3</v>
+        <v>2505.1</v>
       </c>
       <c r="F11" t="n">
-        <v>-20.7</v>
+        <v>129.8</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0546</v>
       </c>
       <c r="H11" t="n">
-        <v>111.2</v>
+        <v>137.8</v>
       </c>
       <c r="I11" t="n">
-        <v>2220</v>
+        <v>2189.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2249.85</v>
+        <v>2273.6</v>
       </c>
       <c r="K11" t="n">
-        <v>2329.1</v>
+        <v>2319.7</v>
       </c>
       <c r="L11" t="n">
-        <v>2408.35</v>
+        <v>2365.8</v>
       </c>
       <c r="M11" t="n">
-        <v>2462.9</v>
+        <v>2430.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2517.45</v>
+        <v>2496</v>
       </c>
       <c r="O11" t="n">
-        <v>2621.4</v>
+        <v>2523.1</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1437,28 +1429,30 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W11" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -1466,50 +1460,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2387.8</v>
+        <v>2501</v>
       </c>
       <c r="C12" t="n">
-        <v>2508.1</v>
+        <v>2544.2</v>
       </c>
       <c r="D12" t="n">
-        <v>2370.3</v>
+        <v>2468.1</v>
       </c>
       <c r="E12" t="n">
-        <v>2505.1</v>
+        <v>2524.4</v>
       </c>
       <c r="F12" t="n">
-        <v>129.8</v>
+        <v>19.3</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0077</v>
       </c>
       <c r="H12" t="n">
-        <v>137.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>2189.5</v>
+        <v>2232.5</v>
       </c>
       <c r="J12" t="n">
-        <v>2273.6</v>
+        <v>2400.25</v>
       </c>
       <c r="K12" t="n">
-        <v>2319.7</v>
+        <v>2436.2</v>
       </c>
       <c r="L12" t="n">
-        <v>2365.8</v>
+        <v>2472.15</v>
       </c>
       <c r="M12" t="n">
-        <v>2430.9</v>
+        <v>2574</v>
       </c>
       <c r="N12" t="n">
-        <v>2496</v>
+        <v>2675.85</v>
       </c>
       <c r="O12" t="n">
-        <v>2523.1</v>
+        <v>2645.9</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1520,20 +1514,18 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1548,50 +1540,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2501</v>
+        <v>2528</v>
       </c>
       <c r="C13" t="n">
-        <v>2544.2</v>
+        <v>2605</v>
       </c>
       <c r="D13" t="n">
-        <v>2468.1</v>
+        <v>2516.6</v>
       </c>
       <c r="E13" t="n">
-        <v>2524.4</v>
+        <v>2553.7</v>
       </c>
       <c r="F13" t="n">
-        <v>19.3</v>
+        <v>29.3</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0116</v>
       </c>
       <c r="H13" t="n">
-        <v>76.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2232.5</v>
+        <v>2392</v>
       </c>
       <c r="J13" t="n">
-        <v>2400.25</v>
+        <v>2457.42</v>
       </c>
       <c r="K13" t="n">
-        <v>2436.2</v>
+        <v>2486.35</v>
       </c>
       <c r="L13" t="n">
-        <v>2472.15</v>
+        <v>2515.27</v>
       </c>
       <c r="M13" t="n">
-        <v>2574</v>
+        <v>2562.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2675.85</v>
+        <v>2609.62</v>
       </c>
       <c r="O13" t="n">
-        <v>2645.9</v>
+        <v>2620.3</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1602,7 +1594,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1628,50 +1620,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2528</v>
+        <v>2552.8</v>
       </c>
       <c r="C14" t="n">
-        <v>2605</v>
+        <v>2577.3</v>
       </c>
       <c r="D14" t="n">
-        <v>2516.6</v>
+        <v>2489.4</v>
       </c>
       <c r="E14" t="n">
-        <v>2553.7</v>
+        <v>2509.56</v>
       </c>
       <c r="F14" t="n">
-        <v>29.3</v>
+        <v>-44.14</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0116</v>
+        <v>-0.0173</v>
       </c>
       <c r="H14" t="n">
-        <v>88.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>2392</v>
+        <v>2428.2</v>
       </c>
       <c r="J14" t="n">
-        <v>2457.42</v>
+        <v>2461.75</v>
       </c>
       <c r="K14" t="n">
-        <v>2486.35</v>
+        <v>2509.5</v>
       </c>
       <c r="L14" t="n">
-        <v>2515.27</v>
+        <v>2557.25</v>
       </c>
       <c r="M14" t="n">
-        <v>2562.45</v>
+        <v>2597.9</v>
       </c>
       <c r="N14" t="n">
-        <v>2609.62</v>
+        <v>2638.55</v>
       </c>
       <c r="O14" t="n">
-        <v>2620.3</v>
+        <v>2693.4</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1679,18 +1671,18 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1703,55 +1695,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2552.8</v>
+        <v>2550</v>
       </c>
       <c r="C15" t="n">
-        <v>2577.3</v>
+        <v>2590.3</v>
       </c>
       <c r="D15" t="n">
-        <v>2489.4</v>
+        <v>2540.8</v>
       </c>
       <c r="E15" t="n">
-        <v>2509.56</v>
+        <v>2551.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-44.14</v>
+        <v>41.84</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0173</v>
+        <v>0.0167</v>
       </c>
       <c r="H15" t="n">
-        <v>87.90000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="I15" t="n">
-        <v>2428.2</v>
+        <v>2401.5</v>
       </c>
       <c r="J15" t="n">
-        <v>2461.75</v>
+        <v>2409.76</v>
       </c>
       <c r="K15" t="n">
-        <v>2509.5</v>
+        <v>2465.61</v>
       </c>
       <c r="L15" t="n">
-        <v>2557.25</v>
+        <v>2521.46</v>
       </c>
       <c r="M15" t="n">
-        <v>2597.9</v>
+        <v>2553.51</v>
       </c>
       <c r="N15" t="n">
-        <v>2638.55</v>
+        <v>2585.57</v>
       </c>
       <c r="O15" t="n">
-        <v>2693.4</v>
+        <v>2665.2</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1759,21 +1755,23 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1783,83 +1781,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2550</v>
+        <v>2551.6</v>
       </c>
       <c r="C16" t="n">
-        <v>2590.3</v>
+        <v>2556.9</v>
       </c>
       <c r="D16" t="n">
-        <v>2540.8</v>
+        <v>2493.5</v>
       </c>
       <c r="E16" t="n">
-        <v>2551.4</v>
+        <v>2522.5</v>
       </c>
       <c r="F16" t="n">
-        <v>41.84</v>
+        <v>-28.9</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0167</v>
+        <v>-0.0113</v>
       </c>
       <c r="H16" t="n">
-        <v>49.5</v>
+        <v>63.4</v>
       </c>
       <c r="I16" t="n">
-        <v>2401.5</v>
+        <v>2491.3</v>
       </c>
       <c r="J16" t="n">
-        <v>2409.76</v>
+        <v>2494.82</v>
       </c>
       <c r="K16" t="n">
-        <v>2465.61</v>
+        <v>2526.65</v>
       </c>
       <c r="L16" t="n">
-        <v>2521.46</v>
+        <v>2558.47</v>
       </c>
       <c r="M16" t="n">
-        <v>2553.51</v>
+        <v>2576.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2585.57</v>
+        <v>2593.82</v>
       </c>
       <c r="O16" t="n">
-        <v>2665.2</v>
+        <v>2639.8</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1869,141 +1863,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2551.6</v>
+        <v>2524.2</v>
       </c>
       <c r="C17" t="n">
-        <v>2556.9</v>
+        <v>2650.3</v>
       </c>
       <c r="D17" t="n">
-        <v>2493.5</v>
+        <v>2517.2</v>
       </c>
       <c r="E17" t="n">
-        <v>2522.5</v>
+        <v>2636.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-28.9</v>
+        <v>114.4</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0113</v>
+        <v>0.0454</v>
       </c>
       <c r="H17" t="n">
-        <v>63.4</v>
+        <v>133.1</v>
       </c>
       <c r="I17" t="n">
-        <v>2491.3</v>
+        <v>2430.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2494.82</v>
+        <v>2457.75</v>
       </c>
       <c r="K17" t="n">
-        <v>2526.65</v>
+        <v>2490.8</v>
       </c>
       <c r="L17" t="n">
-        <v>2558.47</v>
+        <v>2523.85</v>
       </c>
       <c r="M17" t="n">
-        <v>2576.15</v>
+        <v>2554.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2593.82</v>
+        <v>2584.55</v>
       </c>
       <c r="O17" t="n">
-        <v>2639.8</v>
+        <v>2620.3</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2524.2</v>
+        <v>2638.9</v>
       </c>
       <c r="C18" t="n">
-        <v>2650.3</v>
+        <v>2705.6</v>
       </c>
       <c r="D18" t="n">
-        <v>2517.2</v>
+        <v>2616.3</v>
       </c>
       <c r="E18" t="n">
-        <v>2636.9</v>
+        <v>2691.2</v>
       </c>
       <c r="F18" t="n">
-        <v>114.4</v>
+        <v>54.3</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0454</v>
+        <v>0.0206</v>
       </c>
       <c r="H18" t="n">
-        <v>133.1</v>
+        <v>89.3</v>
       </c>
       <c r="I18" t="n">
-        <v>2430.1</v>
+        <v>2384.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2457.75</v>
+        <v>2530.37</v>
       </c>
       <c r="K18" t="n">
-        <v>2490.8</v>
+        <v>2570.35</v>
       </c>
       <c r="L18" t="n">
-        <v>2523.85</v>
+        <v>2610.32</v>
       </c>
       <c r="M18" t="n">
-        <v>2554.2</v>
+        <v>2703.45</v>
       </c>
       <c r="N18" t="n">
-        <v>2584.55</v>
+        <v>2796.57</v>
       </c>
       <c r="O18" t="n">
-        <v>2620.3</v>
+        <v>2783.4</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2014,25 +2010,21 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2044,50 +2036,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2638.9</v>
+        <v>2670</v>
       </c>
       <c r="C19" t="n">
-        <v>2705.6</v>
+        <v>2749.2</v>
       </c>
       <c r="D19" t="n">
-        <v>2616.3</v>
+        <v>2631</v>
       </c>
       <c r="E19" t="n">
-        <v>2691.2</v>
+        <v>2679.6</v>
       </c>
       <c r="F19" t="n">
-        <v>54.3</v>
+        <v>-11.6</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0206</v>
+        <v>-0.0043</v>
       </c>
       <c r="H19" t="n">
-        <v>89.3</v>
+        <v>118.2</v>
       </c>
       <c r="I19" t="n">
-        <v>2384.1</v>
+        <v>2527</v>
       </c>
       <c r="J19" t="n">
-        <v>2530.37</v>
+        <v>2617.02</v>
       </c>
       <c r="K19" t="n">
-        <v>2570.35</v>
+        <v>2646.55</v>
       </c>
       <c r="L19" t="n">
-        <v>2610.32</v>
+        <v>2676.08</v>
       </c>
       <c r="M19" t="n">
-        <v>2703.45</v>
+        <v>2735.85</v>
       </c>
       <c r="N19" t="n">
-        <v>2796.57</v>
+        <v>2795.62</v>
       </c>
       <c r="O19" t="n">
-        <v>2783.4</v>
+        <v>2794.9</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2095,17 +2087,19 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U19" s="8" t="n">
@@ -2119,55 +2113,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2670</v>
+        <v>2661</v>
       </c>
       <c r="C20" t="n">
-        <v>2749.2</v>
+        <v>2697.9</v>
       </c>
       <c r="D20" t="n">
-        <v>2631</v>
+        <v>2607.5</v>
       </c>
       <c r="E20" t="n">
-        <v>2679.6</v>
+        <v>2624.6</v>
       </c>
       <c r="F20" t="n">
-        <v>-11.6</v>
+        <v>-55</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0205</v>
       </c>
       <c r="H20" t="n">
-        <v>118.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>2527</v>
+        <v>2512.8</v>
       </c>
       <c r="J20" t="n">
-        <v>2617.02</v>
+        <v>2556.15</v>
       </c>
       <c r="K20" t="n">
-        <v>2646.55</v>
+        <v>2620.5</v>
       </c>
       <c r="L20" t="n">
-        <v>2676.08</v>
+        <v>2684.85</v>
       </c>
       <c r="M20" t="n">
-        <v>2735.85</v>
+        <v>2738.7</v>
       </c>
       <c r="N20" t="n">
-        <v>2795.62</v>
+        <v>2792.55</v>
       </c>
       <c r="O20" t="n">
-        <v>2794.9</v>
+        <v>2867.4</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2177,18 +2175,16 @@
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2203,57 +2199,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2661</v>
+        <v>2615</v>
       </c>
       <c r="C21" t="n">
-        <v>2697.9</v>
+        <v>2684.1</v>
       </c>
       <c r="D21" t="n">
-        <v>2607.5</v>
+        <v>2566.8</v>
       </c>
       <c r="E21" t="n">
-        <v>2624.6</v>
+        <v>2677.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-55</v>
+        <v>53.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0205</v>
+        <v>0.0203</v>
       </c>
       <c r="H21" t="n">
-        <v>90.40000000000001</v>
+        <v>117.3</v>
       </c>
       <c r="I21" t="n">
-        <v>2512.8</v>
+        <v>2517.1</v>
       </c>
       <c r="J21" t="n">
-        <v>2556.15</v>
+        <v>2520.15</v>
       </c>
       <c r="K21" t="n">
-        <v>2620.5</v>
+        <v>2579.4</v>
       </c>
       <c r="L21" t="n">
-        <v>2684.85</v>
+        <v>2638.65</v>
       </c>
       <c r="M21" t="n">
-        <v>2738.7</v>
+        <v>2669.8</v>
       </c>
       <c r="N21" t="n">
-        <v>2792.55</v>
+        <v>2700.95</v>
       </c>
       <c r="O21" t="n">
-        <v>2867.4</v>
+        <v>2788.3</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2263,17 +2259,19 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2287,57 +2285,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2615</v>
+        <v>2677</v>
       </c>
       <c r="C22" t="n">
-        <v>2684.1</v>
+        <v>2720</v>
       </c>
       <c r="D22" t="n">
-        <v>2566.8</v>
+        <v>2607.3</v>
       </c>
       <c r="E22" t="n">
-        <v>2677.9</v>
+        <v>2653.1</v>
       </c>
       <c r="F22" t="n">
-        <v>53.3</v>
+        <v>-24.8</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0203</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>117.3</v>
+        <v>112.7</v>
       </c>
       <c r="I22" t="n">
-        <v>2517.1</v>
+        <v>2449.5</v>
       </c>
       <c r="J22" t="n">
-        <v>2520.15</v>
+        <v>2586.82</v>
       </c>
       <c r="K22" t="n">
-        <v>2579.4</v>
+        <v>2619.25</v>
       </c>
       <c r="L22" t="n">
-        <v>2638.65</v>
+        <v>2651.67</v>
       </c>
       <c r="M22" t="n">
-        <v>2669.8</v>
+        <v>2736.55</v>
       </c>
       <c r="N22" t="n">
-        <v>2700.95</v>
+        <v>2821.42</v>
       </c>
       <c r="O22" t="n">
-        <v>2788.3</v>
+        <v>2801.4</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2350,15 +2348,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2373,57 +2369,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2677</v>
+        <v>2650.9</v>
       </c>
       <c r="C23" t="n">
-        <v>2720</v>
+        <v>2696</v>
       </c>
       <c r="D23" t="n">
-        <v>2607.3</v>
+        <v>2613.7</v>
       </c>
       <c r="E23" t="n">
-        <v>2653.1</v>
+        <v>2668.8</v>
       </c>
       <c r="F23" t="n">
-        <v>-24.8</v>
+        <v>15.7</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H23" t="n">
-        <v>112.7</v>
+        <v>82.3</v>
       </c>
       <c r="I23" t="n">
-        <v>2449.5</v>
+        <v>2494.6</v>
       </c>
       <c r="J23" t="n">
-        <v>2586.82</v>
+        <v>2535.13</v>
       </c>
       <c r="K23" t="n">
-        <v>2619.25</v>
+        <v>2596.75</v>
       </c>
       <c r="L23" t="n">
-        <v>2651.67</v>
+        <v>2658.38</v>
       </c>
       <c r="M23" t="n">
-        <v>2736.55</v>
+        <v>2709.45</v>
       </c>
       <c r="N23" t="n">
-        <v>2821.42</v>
+        <v>2760.53</v>
       </c>
       <c r="O23" t="n">
-        <v>2801.4</v>
+        <v>2832.7</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2431,12 +2427,10 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2464,50 +2458,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2650.9</v>
+        <v>2666.5</v>
       </c>
       <c r="C24" t="n">
-        <v>2696</v>
+        <v>2683.4</v>
       </c>
       <c r="D24" t="n">
-        <v>2613.7</v>
+        <v>2602.7</v>
       </c>
       <c r="E24" t="n">
-        <v>2668.8</v>
+        <v>2634.7</v>
       </c>
       <c r="F24" t="n">
-        <v>15.7</v>
+        <v>-34.1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0128</v>
       </c>
       <c r="H24" t="n">
-        <v>82.3</v>
+        <v>80.7</v>
       </c>
       <c r="I24" t="n">
-        <v>2494.6</v>
+        <v>2531.4</v>
       </c>
       <c r="J24" t="n">
-        <v>2535.13</v>
+        <v>2593.48</v>
       </c>
       <c r="K24" t="n">
-        <v>2596.75</v>
+        <v>2627.65</v>
       </c>
       <c r="L24" t="n">
-        <v>2658.38</v>
+        <v>2661.83</v>
       </c>
       <c r="M24" t="n">
-        <v>2709.45</v>
+        <v>2709.95</v>
       </c>
       <c r="N24" t="n">
-        <v>2760.53</v>
+        <v>2758.08</v>
       </c>
       <c r="O24" t="n">
-        <v>2832.7</v>
+        <v>2778.3</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2515,12 +2509,14 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2539,70 +2535,74 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2666.5</v>
+        <v>2608.8</v>
       </c>
       <c r="C25" t="n">
-        <v>2683.4</v>
+        <v>2663.3</v>
       </c>
       <c r="D25" t="n">
-        <v>2602.7</v>
+        <v>2516.6</v>
       </c>
       <c r="E25" t="n">
-        <v>2634.7</v>
+        <v>2526.7</v>
       </c>
       <c r="F25" t="n">
-        <v>-34.1</v>
+        <v>-108</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0128</v>
+        <v>-0.041</v>
       </c>
       <c r="H25" t="n">
-        <v>80.7</v>
+        <v>146.7</v>
       </c>
       <c r="I25" t="n">
-        <v>2531.4</v>
+        <v>2522</v>
       </c>
       <c r="J25" t="n">
-        <v>2593.48</v>
+        <v>2549.83</v>
       </c>
       <c r="K25" t="n">
-        <v>2627.65</v>
+        <v>2594.35</v>
       </c>
       <c r="L25" t="n">
-        <v>2661.83</v>
+        <v>2638.87</v>
       </c>
       <c r="M25" t="n">
-        <v>2709.95</v>
+        <v>2675.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2758.08</v>
+        <v>2711.22</v>
       </c>
       <c r="O25" t="n">
-        <v>2778.3</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+        <v>2764.1</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2616,81 +2616,73 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2608.8</v>
+        <v>2499.2</v>
       </c>
       <c r="C26" t="n">
-        <v>2663.3</v>
+        <v>2594.4</v>
       </c>
       <c r="D26" t="n">
-        <v>2516.6</v>
+        <v>2416.9</v>
       </c>
       <c r="E26" t="n">
-        <v>2526.7</v>
+        <v>2480.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-108</v>
+        <v>-45.8</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.041</v>
+        <v>-0.0181</v>
       </c>
       <c r="H26" t="n">
-        <v>146.7</v>
+        <v>177.5</v>
       </c>
       <c r="I26" t="n">
-        <v>2522</v>
+        <v>2369.9</v>
       </c>
       <c r="J26" t="n">
-        <v>2549.83</v>
+        <v>2348.37</v>
       </c>
       <c r="K26" t="n">
-        <v>2594.35</v>
+        <v>2453.35</v>
       </c>
       <c r="L26" t="n">
-        <v>2638.87</v>
+        <v>2558.33</v>
       </c>
       <c r="M26" t="n">
-        <v>2675.05</v>
+        <v>2600.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2711.22</v>
+        <v>2641.77</v>
       </c>
       <c r="O26" t="n">
-        <v>2764.1</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>2810</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2714,50 +2706,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2499.2</v>
+        <v>2468.5</v>
       </c>
       <c r="C27" t="n">
-        <v>2594.4</v>
+        <v>2547.9</v>
       </c>
       <c r="D27" t="n">
-        <v>2416.9</v>
+        <v>2442</v>
       </c>
       <c r="E27" t="n">
-        <v>2480.9</v>
+        <v>2496.4</v>
       </c>
       <c r="F27" t="n">
-        <v>-45.8</v>
+        <v>15.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0181</v>
+        <v>0.0062</v>
       </c>
       <c r="H27" t="n">
-        <v>177.5</v>
+        <v>105.9</v>
       </c>
       <c r="I27" t="n">
-        <v>2369.9</v>
+        <v>2239.4</v>
       </c>
       <c r="J27" t="n">
-        <v>2348.37</v>
+        <v>2291.02</v>
       </c>
       <c r="K27" t="n">
-        <v>2453.35</v>
+        <v>2392.15</v>
       </c>
       <c r="L27" t="n">
-        <v>2558.33</v>
+        <v>2493.27</v>
       </c>
       <c r="M27" t="n">
-        <v>2600.05</v>
+        <v>2569.65</v>
       </c>
       <c r="N27" t="n">
-        <v>2641.77</v>
+        <v>2646.02</v>
       </c>
       <c r="O27" t="n">
-        <v>2810</v>
+        <v>2771.9</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2765,14 +2757,12 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2789,55 +2779,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2468.5</v>
+        <v>2429.1</v>
       </c>
       <c r="C28" t="n">
-        <v>2547.9</v>
+        <v>2574.5</v>
       </c>
       <c r="D28" t="n">
-        <v>2442</v>
+        <v>2415.3</v>
       </c>
       <c r="E28" t="n">
-        <v>2496.4</v>
+        <v>2464</v>
       </c>
       <c r="F28" t="n">
-        <v>15.5</v>
+        <v>-32.4</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.013</v>
       </c>
       <c r="H28" t="n">
-        <v>105.9</v>
+        <v>159.2</v>
       </c>
       <c r="I28" t="n">
-        <v>2239.4</v>
+        <v>2336.1</v>
       </c>
       <c r="J28" t="n">
-        <v>2291.02</v>
+        <v>2391.22</v>
       </c>
       <c r="K28" t="n">
-        <v>2392.15</v>
+        <v>2443.45</v>
       </c>
       <c r="L28" t="n">
-        <v>2493.27</v>
+        <v>2495.67</v>
       </c>
       <c r="M28" t="n">
-        <v>2569.65</v>
+        <v>2549.35</v>
       </c>
       <c r="N28" t="n">
-        <v>2646.02</v>
+        <v>2603.02</v>
       </c>
       <c r="O28" t="n">
-        <v>2771.9</v>
+        <v>2653.8</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2845,16 +2839,20 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2869,57 +2867,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2429.1</v>
+        <v>2445</v>
       </c>
       <c r="C29" t="n">
-        <v>2574.5</v>
+        <v>2557</v>
       </c>
       <c r="D29" t="n">
-        <v>2415.3</v>
+        <v>2409.4</v>
       </c>
       <c r="E29" t="n">
-        <v>2464</v>
+        <v>2531.7</v>
       </c>
       <c r="F29" t="n">
-        <v>-32.4</v>
+        <v>67.7</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.013</v>
+        <v>0.0275</v>
       </c>
       <c r="H29" t="n">
-        <v>159.2</v>
+        <v>147.6</v>
       </c>
       <c r="I29" t="n">
-        <v>2336.1</v>
+        <v>2256.1</v>
       </c>
       <c r="J29" t="n">
-        <v>2391.22</v>
+        <v>2289.35</v>
       </c>
       <c r="K29" t="n">
-        <v>2443.45</v>
+        <v>2384.4</v>
       </c>
       <c r="L29" t="n">
-        <v>2495.67</v>
+        <v>2479.45</v>
       </c>
       <c r="M29" t="n">
-        <v>2549.35</v>
+        <v>2543.6</v>
       </c>
       <c r="N29" t="n">
-        <v>2603.02</v>
+        <v>2607.75</v>
       </c>
       <c r="O29" t="n">
-        <v>2653.8</v>
+        <v>2733.7</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2927,19 +2925,17 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="U29" s="8" t="n">
@@ -2962,50 +2958,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2445</v>
+        <v>2527.9</v>
       </c>
       <c r="C30" t="n">
-        <v>2557</v>
+        <v>2674.5</v>
       </c>
       <c r="D30" t="n">
-        <v>2409.4</v>
+        <v>2511.4</v>
       </c>
       <c r="E30" t="n">
-        <v>2531.7</v>
+        <v>2644.4</v>
       </c>
       <c r="F30" t="n">
-        <v>67.7</v>
+        <v>112.7</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0445</v>
       </c>
       <c r="H30" t="n">
-        <v>147.6</v>
+        <v>163.1</v>
       </c>
       <c r="I30" t="n">
-        <v>2256.1</v>
+        <v>2261.8</v>
       </c>
       <c r="J30" t="n">
-        <v>2289.35</v>
+        <v>2408.35</v>
       </c>
       <c r="K30" t="n">
-        <v>2384.4</v>
+        <v>2457.9</v>
       </c>
       <c r="L30" t="n">
-        <v>2479.45</v>
+        <v>2507.45</v>
       </c>
       <c r="M30" t="n">
-        <v>2543.6</v>
+        <v>2605.5</v>
       </c>
       <c r="N30" t="n">
-        <v>2607.75</v>
+        <v>2703.55</v>
       </c>
       <c r="O30" t="n">
-        <v>2733.7</v>
+        <v>2704.6</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3016,7 +3012,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3039,57 +3035,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2527.9</v>
+        <v>2607.8</v>
       </c>
       <c r="C31" t="n">
-        <v>2674.5</v>
+        <v>2807.8</v>
       </c>
       <c r="D31" t="n">
-        <v>2511.4</v>
+        <v>2591.8</v>
       </c>
       <c r="E31" t="n">
-        <v>2644.4</v>
+        <v>2788.9</v>
       </c>
       <c r="F31" t="n">
-        <v>112.7</v>
+        <v>144.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0445</v>
+        <v>0.0546</v>
       </c>
       <c r="H31" t="n">
-        <v>163.1</v>
+        <v>216</v>
       </c>
       <c r="I31" t="n">
-        <v>2261.8</v>
+        <v>2348.3</v>
       </c>
       <c r="J31" t="n">
-        <v>2408.35</v>
+        <v>2507.02</v>
       </c>
       <c r="K31" t="n">
-        <v>2457.9</v>
+        <v>2562.85</v>
       </c>
       <c r="L31" t="n">
-        <v>2507.45</v>
+        <v>2618.67</v>
       </c>
       <c r="M31" t="n">
-        <v>2605.5</v>
+        <v>2725.95</v>
       </c>
       <c r="N31" t="n">
-        <v>2703.55</v>
+        <v>2833.22</v>
       </c>
       <c r="O31" t="n">
-        <v>2704.6</v>
+        <v>2837.6</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3100,18 +3096,20 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3130,50 +3128,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2607.8</v>
+        <v>2758.7</v>
       </c>
       <c r="C32" t="n">
-        <v>2807.8</v>
+        <v>2828.7</v>
       </c>
       <c r="D32" t="n">
-        <v>2591.8</v>
+        <v>2745.9</v>
       </c>
       <c r="E32" t="n">
-        <v>2788.9</v>
+        <v>2796.1</v>
       </c>
       <c r="F32" t="n">
-        <v>144.5</v>
+        <v>7.2</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0026</v>
       </c>
       <c r="H32" t="n">
-        <v>216</v>
+        <v>82.8</v>
       </c>
       <c r="I32" t="n">
-        <v>2348.3</v>
+        <v>2375.8</v>
       </c>
       <c r="J32" t="n">
-        <v>2507.02</v>
+        <v>2617.45</v>
       </c>
       <c r="K32" t="n">
-        <v>2562.85</v>
+        <v>2680.9</v>
       </c>
       <c r="L32" t="n">
-        <v>2618.67</v>
+        <v>2744.35</v>
       </c>
       <c r="M32" t="n">
-        <v>2725.95</v>
+        <v>2896.9</v>
       </c>
       <c r="N32" t="n">
-        <v>2833.22</v>
+        <v>3049.45</v>
       </c>
       <c r="O32" t="n">
-        <v>2837.6</v>
+        <v>3023.8</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3184,20 +3182,16 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3216,50 +3210,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2758.7</v>
+        <v>2792.7</v>
       </c>
       <c r="C33" t="n">
-        <v>2828.7</v>
+        <v>2825</v>
       </c>
       <c r="D33" t="n">
-        <v>2745.9</v>
+        <v>2726.1</v>
       </c>
       <c r="E33" t="n">
-        <v>2796.1</v>
+        <v>2819.3</v>
       </c>
       <c r="F33" t="n">
-        <v>7.2</v>
+        <v>23.2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0083</v>
       </c>
       <c r="H33" t="n">
-        <v>82.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>2375.8</v>
+        <v>2663.1</v>
       </c>
       <c r="J33" t="n">
-        <v>2617.45</v>
+        <v>2717.7</v>
       </c>
       <c r="K33" t="n">
-        <v>2680.9</v>
+        <v>2754.7</v>
       </c>
       <c r="L33" t="n">
-        <v>2744.35</v>
+        <v>2791.7</v>
       </c>
       <c r="M33" t="n">
-        <v>2896.9</v>
+        <v>2837.5</v>
       </c>
       <c r="N33" t="n">
-        <v>3049.45</v>
+        <v>2883.3</v>
       </c>
       <c r="O33" t="n">
-        <v>3023.8</v>
+        <v>2911.5</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3267,16 +3261,20 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3291,57 +3289,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2792.7</v>
+        <v>2825.9</v>
       </c>
       <c r="C34" t="n">
-        <v>2825</v>
+        <v>2918.4</v>
       </c>
       <c r="D34" t="n">
-        <v>2726.1</v>
+        <v>2786.8</v>
       </c>
       <c r="E34" t="n">
-        <v>2819.3</v>
+        <v>2867.6</v>
       </c>
       <c r="F34" t="n">
-        <v>23.2</v>
+        <v>48.3</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0171</v>
       </c>
       <c r="H34" t="n">
-        <v>98.90000000000001</v>
+        <v>131.6</v>
       </c>
       <c r="I34" t="n">
-        <v>2663.1</v>
+        <v>2627.2</v>
       </c>
       <c r="J34" t="n">
-        <v>2717.7</v>
+        <v>2742.28</v>
       </c>
       <c r="K34" t="n">
-        <v>2754.7</v>
+        <v>2769.85</v>
       </c>
       <c r="L34" t="n">
-        <v>2791.7</v>
+        <v>2797.43</v>
       </c>
       <c r="M34" t="n">
-        <v>2837.5</v>
+        <v>2868.75</v>
       </c>
       <c r="N34" t="n">
-        <v>2883.3</v>
+        <v>2940.07</v>
       </c>
       <c r="O34" t="n">
-        <v>2911.5</v>
+        <v>2923.9</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3349,12 +3347,10 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3377,57 +3373,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2825.9</v>
+        <v>2863</v>
       </c>
       <c r="C35" t="n">
-        <v>2918.4</v>
+        <v>2896.2</v>
       </c>
       <c r="D35" t="n">
-        <v>2786.8</v>
+        <v>2787.9</v>
       </c>
       <c r="E35" t="n">
-        <v>2867.6</v>
+        <v>2799.6</v>
       </c>
       <c r="F35" t="n">
-        <v>48.3</v>
+        <v>-68</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0171</v>
+        <v>-0.0237</v>
       </c>
       <c r="H35" t="n">
-        <v>131.6</v>
+        <v>108.3</v>
       </c>
       <c r="I35" t="n">
-        <v>2627.2</v>
+        <v>2655.2</v>
       </c>
       <c r="J35" t="n">
-        <v>2742.28</v>
+        <v>2743.5</v>
       </c>
       <c r="K35" t="n">
-        <v>2769.85</v>
+        <v>2801.8</v>
       </c>
       <c r="L35" t="n">
-        <v>2797.43</v>
+        <v>2860.1</v>
       </c>
       <c r="M35" t="n">
-        <v>2868.75</v>
+        <v>2933.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2940.07</v>
+        <v>3006.7</v>
       </c>
       <c r="O35" t="n">
-        <v>2923.9</v>
+        <v>3050</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3435,18 +3431,18 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3461,57 +3457,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2863</v>
+        <v>2788.8</v>
       </c>
       <c r="C36" t="n">
-        <v>2896.2</v>
+        <v>2887</v>
       </c>
       <c r="D36" t="n">
-        <v>2787.9</v>
+        <v>2728.4</v>
       </c>
       <c r="E36" t="n">
-        <v>2799.6</v>
+        <v>2872.1</v>
       </c>
       <c r="F36" t="n">
-        <v>-68</v>
+        <v>72.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0259</v>
       </c>
       <c r="H36" t="n">
-        <v>108.3</v>
+        <v>158.6</v>
       </c>
       <c r="I36" t="n">
-        <v>2655.2</v>
+        <v>2679.6</v>
       </c>
       <c r="J36" t="n">
-        <v>2743.5</v>
+        <v>2670.08</v>
       </c>
       <c r="K36" t="n">
-        <v>2801.8</v>
+        <v>2745.45</v>
       </c>
       <c r="L36" t="n">
-        <v>2860.1</v>
+        <v>2820.83</v>
       </c>
       <c r="M36" t="n">
-        <v>2933.4</v>
+        <v>2853.75</v>
       </c>
       <c r="N36" t="n">
-        <v>3006.7</v>
+        <v>2886.68</v>
       </c>
       <c r="O36" t="n">
-        <v>3050</v>
+        <v>3004.5</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3521,19 +3517,23 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3552,50 +3552,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2788.8</v>
+        <v>2888</v>
       </c>
       <c r="C37" t="n">
-        <v>2887</v>
+        <v>2952</v>
       </c>
       <c r="D37" t="n">
-        <v>2728.4</v>
+        <v>2887.9</v>
       </c>
       <c r="E37" t="n">
-        <v>2872.1</v>
+        <v>2924.3</v>
       </c>
       <c r="F37" t="n">
-        <v>72.5</v>
+        <v>52.2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0259</v>
+        <v>0.0182</v>
       </c>
       <c r="H37" t="n">
-        <v>158.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>2679.6</v>
+        <v>2569.8</v>
       </c>
       <c r="J37" t="n">
-        <v>2670.08</v>
+        <v>2745.7</v>
       </c>
       <c r="K37" t="n">
-        <v>2745.45</v>
+        <v>2792.8</v>
       </c>
       <c r="L37" t="n">
-        <v>2820.83</v>
+        <v>2839.9</v>
       </c>
       <c r="M37" t="n">
-        <v>2853.75</v>
+        <v>2951.4</v>
       </c>
       <c r="N37" t="n">
-        <v>2886.68</v>
+        <v>3062.9</v>
       </c>
       <c r="O37" t="n">
-        <v>3004.5</v>
+        <v>3045.6</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3603,26 +3603,22 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
@@ -3633,76 +3629,80 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2888</v>
+        <v>2920.5</v>
       </c>
       <c r="C38" t="n">
-        <v>2952</v>
+        <v>2948.3</v>
       </c>
       <c r="D38" t="n">
-        <v>2887.9</v>
+        <v>2812.4</v>
       </c>
       <c r="E38" t="n">
-        <v>2924.3</v>
+        <v>2834.8</v>
       </c>
       <c r="F38" t="n">
-        <v>52.2</v>
+        <v>-89.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0182</v>
+        <v>-0.0306</v>
       </c>
       <c r="H38" t="n">
-        <v>64.09999999999999</v>
+        <v>135.9</v>
       </c>
       <c r="I38" t="n">
-        <v>2569.8</v>
+        <v>2823.8</v>
       </c>
       <c r="J38" t="n">
-        <v>2745.7</v>
+        <v>2862.38</v>
       </c>
       <c r="K38" t="n">
-        <v>2792.8</v>
+        <v>2892.25</v>
       </c>
       <c r="L38" t="n">
-        <v>2839.9</v>
+        <v>2922.12</v>
       </c>
       <c r="M38" t="n">
-        <v>2951.4</v>
+        <v>2956.35</v>
       </c>
       <c r="N38" t="n">
-        <v>3062.9</v>
+        <v>2990.58</v>
       </c>
       <c r="O38" t="n">
-        <v>3045.6</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+        <v>3016.1</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3715,86 +3715,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2920.5</v>
+        <v>2816.3</v>
       </c>
       <c r="C39" t="n">
-        <v>2948.3</v>
+        <v>2974.2</v>
       </c>
       <c r="D39" t="n">
-        <v>2812.4</v>
+        <v>2793.7</v>
       </c>
       <c r="E39" t="n">
-        <v>2834.8</v>
+        <v>2947</v>
       </c>
       <c r="F39" t="n">
-        <v>-89.5</v>
+        <v>112.2</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0306</v>
+        <v>0.0396</v>
       </c>
       <c r="H39" t="n">
-        <v>135.9</v>
+        <v>180.5</v>
       </c>
       <c r="I39" t="n">
-        <v>2823.8</v>
+        <v>2676.5</v>
       </c>
       <c r="J39" t="n">
-        <v>2862.38</v>
+        <v>2676.12</v>
       </c>
       <c r="K39" t="n">
-        <v>2892.25</v>
+        <v>2766.85</v>
       </c>
       <c r="L39" t="n">
-        <v>2922.12</v>
+        <v>2857.58</v>
       </c>
       <c r="M39" t="n">
-        <v>2956.35</v>
+        <v>2902.75</v>
       </c>
       <c r="N39" t="n">
-        <v>2990.58</v>
+        <v>2947.93</v>
       </c>
       <c r="O39" t="n">
-        <v>3016.1</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
+        <v>3084.2</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3803,55 +3797,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2816.3</v>
+        <v>2984</v>
       </c>
       <c r="C40" t="n">
-        <v>2974.2</v>
+        <v>3005</v>
       </c>
       <c r="D40" t="n">
-        <v>2793.7</v>
+        <v>2910.3</v>
       </c>
       <c r="E40" t="n">
-        <v>2947</v>
+        <v>2995.6</v>
       </c>
       <c r="F40" t="n">
-        <v>112.2</v>
+        <v>48.6</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.0165</v>
       </c>
       <c r="H40" t="n">
-        <v>180.5</v>
+        <v>94.7</v>
       </c>
       <c r="I40" t="n">
-        <v>2676.5</v>
+        <v>2613.2</v>
       </c>
       <c r="J40" t="n">
-        <v>2676.12</v>
+        <v>2798.03</v>
       </c>
       <c r="K40" t="n">
-        <v>2766.85</v>
+        <v>2856.75</v>
       </c>
       <c r="L40" t="n">
-        <v>2857.58</v>
+        <v>2915.47</v>
       </c>
       <c r="M40" t="n">
-        <v>2902.75</v>
+        <v>3037.25</v>
       </c>
       <c r="N40" t="n">
-        <v>2947.93</v>
+        <v>3159.03</v>
       </c>
       <c r="O40" t="n">
-        <v>3084.2</v>
+        <v>3154.7</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3862,21 +3860,19 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3887,57 +3883,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2984</v>
+        <v>2989.9</v>
       </c>
       <c r="C41" t="n">
-        <v>3005</v>
+        <v>3062.4</v>
       </c>
       <c r="D41" t="n">
-        <v>2910.3</v>
+        <v>2965.2</v>
       </c>
       <c r="E41" t="n">
-        <v>2995.6</v>
+        <v>3022.6</v>
       </c>
       <c r="F41" t="n">
-        <v>48.6</v>
+        <v>27</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>94.7</v>
+        <v>97.2</v>
       </c>
       <c r="I41" t="n">
-        <v>2613.2</v>
+        <v>2815.6</v>
       </c>
       <c r="J41" t="n">
-        <v>2798.03</v>
+        <v>2919.88</v>
       </c>
       <c r="K41" t="n">
-        <v>2856.75</v>
+        <v>2948.25</v>
       </c>
       <c r="L41" t="n">
-        <v>2915.47</v>
+        <v>2976.63</v>
       </c>
       <c r="M41" t="n">
-        <v>3037.25</v>
+        <v>3042.95</v>
       </c>
       <c r="N41" t="n">
-        <v>3159.03</v>
+        <v>3109.28</v>
       </c>
       <c r="O41" t="n">
-        <v>3154.7</v>
+        <v>3099.7</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3948,7 +3944,7 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3978,50 +3974,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2989.9</v>
+        <v>3020.9</v>
       </c>
       <c r="C42" t="n">
-        <v>3062.4</v>
+        <v>3068.4</v>
       </c>
       <c r="D42" t="n">
-        <v>2965.2</v>
+        <v>2987.8</v>
       </c>
       <c r="E42" t="n">
-        <v>3022.6</v>
+        <v>3023.5</v>
       </c>
       <c r="F42" t="n">
-        <v>27</v>
+        <v>0.9</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0003</v>
       </c>
       <c r="H42" t="n">
-        <v>97.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>2815.6</v>
+        <v>2868</v>
       </c>
       <c r="J42" t="n">
-        <v>2919.88</v>
+        <v>2929.8</v>
       </c>
       <c r="K42" t="n">
-        <v>2948.25</v>
+        <v>2974</v>
       </c>
       <c r="L42" t="n">
-        <v>2976.63</v>
+        <v>3018.2</v>
       </c>
       <c r="M42" t="n">
-        <v>3042.95</v>
+        <v>3071.2</v>
       </c>
       <c r="N42" t="n">
-        <v>3109.28</v>
+        <v>3124.2</v>
       </c>
       <c r="O42" t="n">
-        <v>3099.7</v>
+        <v>3159.6</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4032,15 +4028,13 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4062,50 +4056,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3020.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C43" t="n">
-        <v>3068.4</v>
+        <v>3042.6</v>
       </c>
       <c r="D43" t="n">
-        <v>2987.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E43" t="n">
-        <v>3023.5</v>
+        <v>2994</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9</v>
+        <v>-29.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0098</v>
       </c>
       <c r="H43" t="n">
-        <v>80.59999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="I43" t="n">
-        <v>2868</v>
+        <v>2907.2</v>
       </c>
       <c r="J43" t="n">
-        <v>2929.8</v>
+        <v>2940.6</v>
       </c>
       <c r="K43" t="n">
-        <v>2974</v>
+        <v>2983.2</v>
       </c>
       <c r="L43" t="n">
-        <v>3018.2</v>
+        <v>3025.8</v>
       </c>
       <c r="M43" t="n">
-        <v>3071.2</v>
+        <v>3063.8</v>
       </c>
       <c r="N43" t="n">
-        <v>3124.2</v>
+        <v>3101.8</v>
       </c>
       <c r="O43" t="n">
-        <v>3159.6</v>
+        <v>3149</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4113,12 +4107,14 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4135,59 +4131,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3019.7</v>
+        <v>2984.7</v>
       </c>
       <c r="C44" t="n">
-        <v>3042.6</v>
+        <v>3029.8</v>
       </c>
       <c r="D44" t="n">
-        <v>2943.4</v>
+        <v>2949.3</v>
       </c>
       <c r="E44" t="n">
-        <v>2994</v>
+        <v>2973.5</v>
       </c>
       <c r="F44" t="n">
-        <v>-29.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0068</v>
       </c>
       <c r="H44" t="n">
-        <v>99.2</v>
+        <v>80.5</v>
       </c>
       <c r="I44" t="n">
-        <v>2907.2</v>
+        <v>2844.2</v>
       </c>
       <c r="J44" t="n">
-        <v>2940.6</v>
+        <v>2895.3</v>
       </c>
       <c r="K44" t="n">
-        <v>2983.2</v>
+        <v>2944.4</v>
       </c>
       <c r="L44" t="n">
-        <v>3025.8</v>
+        <v>2993.5</v>
       </c>
       <c r="M44" t="n">
-        <v>3063.8</v>
+        <v>3043.6</v>
       </c>
       <c r="N44" t="n">
-        <v>3101.8</v>
+        <v>3093.7</v>
       </c>
       <c r="O44" t="n">
-        <v>3149</v>
+        <v>3141.8</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4195,14 +4187,12 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4219,55 +4209,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2984.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C45" t="n">
-        <v>3029.8</v>
+        <v>2999.8</v>
       </c>
       <c r="D45" t="n">
-        <v>2949.3</v>
+        <v>2932.1</v>
       </c>
       <c r="E45" t="n">
-        <v>2973.5</v>
+        <v>2941.3</v>
       </c>
       <c r="F45" t="n">
-        <v>-20.5</v>
+        <v>-32.2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0068</v>
+        <v>-0.0108</v>
       </c>
       <c r="H45" t="n">
-        <v>80.5</v>
+        <v>67.7</v>
       </c>
       <c r="I45" t="n">
-        <v>2844.2</v>
+        <v>2868.8</v>
       </c>
       <c r="J45" t="n">
-        <v>2895.3</v>
+        <v>2884.97</v>
       </c>
       <c r="K45" t="n">
-        <v>2944.4</v>
+        <v>2933.25</v>
       </c>
       <c r="L45" t="n">
-        <v>2993.5</v>
+        <v>2981.53</v>
       </c>
       <c r="M45" t="n">
-        <v>3043.6</v>
+        <v>3013.75</v>
       </c>
       <c r="N45" t="n">
-        <v>3093.7</v>
+        <v>3045.97</v>
       </c>
       <c r="O45" t="n">
-        <v>3141.8</v>
+        <v>3110.3</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4275,12 +4269,14 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4297,59 +4293,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2964.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C46" t="n">
-        <v>2999.8</v>
+        <v>2985.9</v>
       </c>
       <c r="D46" t="n">
-        <v>2932.1</v>
+        <v>2902.3</v>
       </c>
       <c r="E46" t="n">
-        <v>2941.3</v>
+        <v>2938</v>
       </c>
       <c r="F46" t="n">
-        <v>-32.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0011</v>
       </c>
       <c r="H46" t="n">
-        <v>67.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>2868.8</v>
+        <v>2864.4</v>
       </c>
       <c r="J46" t="n">
-        <v>2884.97</v>
+        <v>2861.28</v>
       </c>
       <c r="K46" t="n">
-        <v>2933.25</v>
+        <v>2907.45</v>
       </c>
       <c r="L46" t="n">
-        <v>2981.53</v>
+        <v>2953.63</v>
       </c>
       <c r="M46" t="n">
-        <v>3013.75</v>
+        <v>2975.15</v>
       </c>
       <c r="N46" t="n">
-        <v>3045.97</v>
+        <v>2996.67</v>
       </c>
       <c r="O46" t="n">
-        <v>3110.3</v>
+        <v>3067.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4359,16 +4351,18 @@
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4386,50 +4380,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2955.5</v>
+        <v>2950</v>
       </c>
       <c r="C47" t="n">
-        <v>2985.9</v>
+        <v>3058.3</v>
       </c>
       <c r="D47" t="n">
-        <v>2902.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E47" t="n">
-        <v>2938</v>
+        <v>3041.6</v>
       </c>
       <c r="F47" t="n">
-        <v>-3.3</v>
+        <v>103.6</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0353</v>
       </c>
       <c r="H47" t="n">
-        <v>83.59999999999999</v>
+        <v>109.9</v>
       </c>
       <c r="I47" t="n">
-        <v>2864.4</v>
+        <v>2818.7</v>
       </c>
       <c r="J47" t="n">
-        <v>2861.28</v>
+        <v>2851.35</v>
       </c>
       <c r="K47" t="n">
-        <v>2907.45</v>
+        <v>2896.2</v>
       </c>
       <c r="L47" t="n">
-        <v>2953.63</v>
+        <v>2941.05</v>
       </c>
       <c r="M47" t="n">
-        <v>2975.15</v>
+        <v>2979.8</v>
       </c>
       <c r="N47" t="n">
-        <v>2996.67</v>
+        <v>3018.55</v>
       </c>
       <c r="O47" t="n">
-        <v>3067.5</v>
+        <v>3069.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4437,30 +4431,30 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr"/>
@@ -4468,50 +4462,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2950</v>
+        <v>3038.9</v>
       </c>
       <c r="C48" t="n">
-        <v>3058.3</v>
+        <v>3076.3</v>
       </c>
       <c r="D48" t="n">
-        <v>2948.4</v>
+        <v>3016</v>
       </c>
       <c r="E48" t="n">
-        <v>3041.6</v>
+        <v>3074.9</v>
       </c>
       <c r="F48" t="n">
-        <v>103.6</v>
+        <v>33.3</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.0109</v>
       </c>
       <c r="H48" t="n">
-        <v>109.9</v>
+        <v>60.3</v>
       </c>
       <c r="I48" t="n">
-        <v>2818.7</v>
+        <v>2838.5</v>
       </c>
       <c r="J48" t="n">
-        <v>2851.35</v>
+        <v>2950.83</v>
       </c>
       <c r="K48" t="n">
-        <v>2896.2</v>
+        <v>2986.65</v>
       </c>
       <c r="L48" t="n">
-        <v>2941.05</v>
+        <v>3022.48</v>
       </c>
       <c r="M48" t="n">
-        <v>2979.8</v>
+        <v>3096.55</v>
       </c>
       <c r="N48" t="n">
-        <v>3018.55</v>
+        <v>3170.63</v>
       </c>
       <c r="O48" t="n">
-        <v>3069.5</v>
+        <v>3168.2</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4522,20 +4516,18 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4550,69 +4542,71 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3038.9</v>
+        <v>3073.5</v>
       </c>
       <c r="C49" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D49" t="n">
-        <v>3016</v>
+        <v>2993.2</v>
       </c>
       <c r="E49" t="n">
-        <v>3074.9</v>
+        <v>3022.1</v>
       </c>
       <c r="F49" t="n">
-        <v>33.3</v>
+        <v>-52.8</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.0172</v>
       </c>
       <c r="H49" t="n">
-        <v>60.3</v>
+        <v>86.7</v>
       </c>
       <c r="I49" t="n">
-        <v>2838.5</v>
+        <v>2955.7</v>
       </c>
       <c r="J49" t="n">
-        <v>2950.83</v>
+        <v>3028.97</v>
       </c>
       <c r="K49" t="n">
-        <v>2986.65</v>
+        <v>3044.75</v>
       </c>
       <c r="L49" t="n">
-        <v>3022.48</v>
+        <v>3060.52</v>
       </c>
       <c r="M49" t="n">
-        <v>3096.55</v>
+        <v>3105.05</v>
       </c>
       <c r="N49" t="n">
-        <v>3170.63</v>
+        <v>3149.57</v>
       </c>
       <c r="O49" t="n">
-        <v>3168.2</v>
+        <v>3136.6</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4620,75 +4614,77 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3073.5</v>
+        <v>3023</v>
       </c>
       <c r="C50" t="n">
-        <v>3079.9</v>
+        <v>3028.9</v>
       </c>
       <c r="D50" t="n">
-        <v>2993.2</v>
+        <v>2976.6</v>
       </c>
       <c r="E50" t="n">
-        <v>3022.1</v>
+        <v>2977.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-52.8</v>
+        <v>-44.6</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0172</v>
+        <v>-0.0148</v>
       </c>
       <c r="H50" t="n">
-        <v>86.7</v>
+        <v>52.3</v>
       </c>
       <c r="I50" t="n">
-        <v>2955.7</v>
+        <v>2906.5</v>
       </c>
       <c r="J50" t="n">
-        <v>3028.97</v>
+        <v>2928.18</v>
       </c>
       <c r="K50" t="n">
-        <v>3044.75</v>
+        <v>2978.75</v>
       </c>
       <c r="L50" t="n">
-        <v>3060.52</v>
+        <v>3029.33</v>
       </c>
       <c r="M50" t="n">
-        <v>3105.05</v>
+        <v>3065.45</v>
       </c>
       <c r="N50" t="n">
-        <v>3149.57</v>
+        <v>3101.58</v>
       </c>
       <c r="O50" t="n">
-        <v>3136.6</v>
+        <v>3166.6</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4707,74 +4703,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3023</v>
+        <v>2971</v>
       </c>
       <c r="C51" t="n">
-        <v>3028.9</v>
+        <v>2983.3</v>
       </c>
       <c r="D51" t="n">
+        <v>2914.5</v>
+      </c>
+      <c r="E51" t="n">
         <v>2976.6</v>
       </c>
-      <c r="E51" t="n">
-        <v>2977.5</v>
-      </c>
       <c r="F51" t="n">
-        <v>-44.6</v>
+        <v>-0.9</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0148</v>
+        <v>-0.0003</v>
       </c>
       <c r="H51" t="n">
-        <v>52.3</v>
+        <v>68.8</v>
       </c>
       <c r="I51" t="n">
-        <v>2906.5</v>
+        <v>2924.3</v>
       </c>
       <c r="J51" t="n">
-        <v>2928.18</v>
+        <v>2912.58</v>
       </c>
       <c r="K51" t="n">
-        <v>2978.75</v>
+        <v>2951.35</v>
       </c>
       <c r="L51" t="n">
-        <v>3029.33</v>
+        <v>2990.12</v>
       </c>
       <c r="M51" t="n">
-        <v>3065.45</v>
+        <v>3003.65</v>
       </c>
       <c r="N51" t="n">
-        <v>3101.58</v>
+        <v>3017.17</v>
       </c>
       <c r="O51" t="n">
-        <v>3166.6</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
+        <v>3081.2</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4796,67 +4790,67 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2971</v>
+        <v>2974.7</v>
       </c>
       <c r="C52" t="n">
-        <v>2983.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D52" t="n">
-        <v>2914.5</v>
+        <v>2887.6</v>
       </c>
       <c r="E52" t="n">
-        <v>2976.6</v>
+        <v>2904.5</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.9</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0242</v>
       </c>
       <c r="H52" t="n">
-        <v>68.8</v>
+        <v>90.3</v>
       </c>
       <c r="I52" t="n">
-        <v>2924.3</v>
+        <v>2845.7</v>
       </c>
       <c r="J52" t="n">
-        <v>2912.58</v>
+        <v>2921.65</v>
       </c>
       <c r="K52" t="n">
-        <v>2951.35</v>
+        <v>2942.2</v>
       </c>
       <c r="L52" t="n">
-        <v>2990.12</v>
+        <v>2962.75</v>
       </c>
       <c r="M52" t="n">
-        <v>3003.65</v>
+        <v>3011</v>
       </c>
       <c r="N52" t="n">
-        <v>3017.17</v>
+        <v>3059.25</v>
       </c>
       <c r="O52" t="n">
-        <v>3081.2</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
+        <v>3052.1</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4878,65 +4872,63 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2974.7</v>
+        <v>2892.7</v>
       </c>
       <c r="C53" t="n">
-        <v>2977.9</v>
+        <v>2913.5</v>
       </c>
       <c r="D53" t="n">
-        <v>2887.6</v>
+        <v>2831.9</v>
       </c>
       <c r="E53" t="n">
-        <v>2904.5</v>
+        <v>2873.23</v>
       </c>
       <c r="F53" t="n">
-        <v>-72.09999999999999</v>
+        <v>-31.27</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0242</v>
+        <v>-0.0108</v>
       </c>
       <c r="H53" t="n">
-        <v>90.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>2845.7</v>
+        <v>2797.3</v>
       </c>
       <c r="J53" t="n">
-        <v>2921.65</v>
+        <v>2800.08</v>
       </c>
       <c r="K53" t="n">
-        <v>2942.2</v>
+        <v>2859.35</v>
       </c>
       <c r="L53" t="n">
-        <v>2962.75</v>
+        <v>2918.62</v>
       </c>
       <c r="M53" t="n">
-        <v>3011</v>
+        <v>2949.65</v>
       </c>
       <c r="N53" t="n">
-        <v>3059.25</v>
+        <v>2980.67</v>
       </c>
       <c r="O53" t="n">
-        <v>3052.1</v>
+        <v>3068.2</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4960,50 +4952,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2892.7</v>
+        <v>2879.5</v>
       </c>
       <c r="C54" t="n">
-        <v>2913.5</v>
+        <v>2931.2</v>
       </c>
       <c r="D54" t="n">
-        <v>2831.9</v>
+        <v>2829.9</v>
       </c>
       <c r="E54" t="n">
-        <v>2873.23</v>
+        <v>2859.3</v>
       </c>
       <c r="F54" t="n">
-        <v>-31.27</v>
+        <v>-13.93</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0048</v>
       </c>
       <c r="H54" t="n">
-        <v>81.59999999999999</v>
+        <v>101.3</v>
       </c>
       <c r="I54" t="n">
-        <v>2797.3</v>
+        <v>2750.3</v>
       </c>
       <c r="J54" t="n">
-        <v>2800.08</v>
+        <v>2791.89</v>
       </c>
       <c r="K54" t="n">
-        <v>2859.35</v>
+        <v>2832.43</v>
       </c>
       <c r="L54" t="n">
-        <v>2918.62</v>
+        <v>2872.96</v>
       </c>
       <c r="M54" t="n">
-        <v>2949.65</v>
+        <v>2914.03</v>
       </c>
       <c r="N54" t="n">
-        <v>2980.67</v>
+        <v>2955.1</v>
       </c>
       <c r="O54" t="n">
-        <v>3068.2</v>
+        <v>2995.1</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5013,16 +5005,18 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5035,55 +5029,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2879.5</v>
+        <v>2857.7</v>
       </c>
       <c r="C55" t="n">
-        <v>2931.2</v>
+        <v>2875.3</v>
       </c>
       <c r="D55" t="n">
-        <v>2829.9</v>
+        <v>2791.5</v>
       </c>
       <c r="E55" t="n">
-        <v>2859.3</v>
+        <v>2850.9</v>
       </c>
       <c r="F55" t="n">
-        <v>-13.93</v>
+        <v>-8.4</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0029</v>
       </c>
       <c r="H55" t="n">
-        <v>101.3</v>
+        <v>83.8</v>
       </c>
       <c r="I55" t="n">
-        <v>2750.3</v>
+        <v>2728.6</v>
       </c>
       <c r="J55" t="n">
-        <v>2791.89</v>
+        <v>2747.38</v>
       </c>
       <c r="K55" t="n">
-        <v>2832.43</v>
+        <v>2808.65</v>
       </c>
       <c r="L55" t="n">
-        <v>2872.96</v>
+        <v>2869.92</v>
       </c>
       <c r="M55" t="n">
-        <v>2914.03</v>
+        <v>2909.95</v>
       </c>
       <c r="N55" t="n">
-        <v>2955.1</v>
+        <v>2949.98</v>
       </c>
       <c r="O55" t="n">
-        <v>2995.1</v>
+        <v>3032.5</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5096,15 +5094,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5117,59 +5113,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2857.7</v>
+        <v>2850.6</v>
       </c>
       <c r="C56" t="n">
-        <v>2875.3</v>
+        <v>2887.2</v>
       </c>
       <c r="D56" t="n">
-        <v>2791.5</v>
+        <v>2778.6</v>
       </c>
       <c r="E56" t="n">
-        <v>2850.9</v>
+        <v>2822.1</v>
       </c>
       <c r="F56" t="n">
-        <v>-8.4</v>
+        <v>-28.8</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0101</v>
       </c>
       <c r="H56" t="n">
-        <v>83.8</v>
+        <v>108.6</v>
       </c>
       <c r="I56" t="n">
-        <v>2728.6</v>
+        <v>2707.7</v>
       </c>
       <c r="J56" t="n">
-        <v>2747.38</v>
+        <v>2775.85</v>
       </c>
       <c r="K56" t="n">
-        <v>2808.65</v>
+        <v>2809</v>
       </c>
       <c r="L56" t="n">
-        <v>2869.92</v>
+        <v>2842.15</v>
       </c>
       <c r="M56" t="n">
-        <v>2909.95</v>
+        <v>2892.8</v>
       </c>
       <c r="N56" t="n">
-        <v>2949.98</v>
+        <v>2943.45</v>
       </c>
       <c r="O56" t="n">
-        <v>3032.5</v>
+        <v>2959.1</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5179,12 +5171,12 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5201,68 +5193,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2850.6</v>
+        <v>2822.9</v>
       </c>
       <c r="C57" t="n">
-        <v>2887.2</v>
+        <v>2834.3</v>
       </c>
       <c r="D57" t="n">
-        <v>2778.6</v>
+        <v>2728.9</v>
       </c>
       <c r="E57" t="n">
-        <v>2822.1</v>
+        <v>2737</v>
       </c>
       <c r="F57" t="n">
-        <v>-28.8</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0101</v>
+        <v>-0.0302</v>
       </c>
       <c r="H57" t="n">
-        <v>108.6</v>
+        <v>105.4</v>
       </c>
       <c r="I57" t="n">
-        <v>2707.7</v>
+        <v>2670</v>
       </c>
       <c r="J57" t="n">
-        <v>2775.85</v>
+        <v>2708.1</v>
       </c>
       <c r="K57" t="n">
-        <v>2809</v>
+        <v>2767.8</v>
       </c>
       <c r="L57" t="n">
-        <v>2842.15</v>
+        <v>2827.5</v>
       </c>
       <c r="M57" t="n">
-        <v>2892.8</v>
+        <v>2876.4</v>
       </c>
       <c r="N57" t="n">
-        <v>2943.45</v>
+        <v>2925.3</v>
       </c>
       <c r="O57" t="n">
-        <v>2959.1</v>
+        <v>2995.8</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5281,91 +5279,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2822.9</v>
-      </c>
-      <c r="C58" t="n">
-        <v>2834.3</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2734.9</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2781.7</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-40.4</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0143</v>
-      </c>
-      <c r="H58" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2670</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2708.1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2767.8</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2827.5</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2876.4</v>
-      </c>
-      <c r="N58" t="n">
-        <v>2925.3</v>
-      </c>
-      <c r="O58" t="n">
-        <v>2995.8</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5215,13 +5215,13 @@
         <v>2728.9</v>
       </c>
       <c r="E57" t="n">
-        <v>2737</v>
+        <v>2735.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-85.09999999999999</v>
+        <v>-86.59999999999999</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0302</v>
+        <v>-0.0307</v>
       </c>
       <c r="H57" t="n">
         <v>105.4</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5212,19 +5212,19 @@
         <v>2834.3</v>
       </c>
       <c r="D57" t="n">
-        <v>2728.9</v>
+        <v>2723.3</v>
       </c>
       <c r="E57" t="n">
-        <v>2735.5</v>
+        <v>2752.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-86.59999999999999</v>
+        <v>-69.59999999999999</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0307</v>
+        <v>-0.0247</v>
       </c>
       <c r="H57" t="n">
-        <v>105.4</v>
+        <v>111</v>
       </c>
       <c r="I57" t="n">
         <v>2670</v>
@@ -5250,14 +5250,12 @@
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S57" s="7" t="inlineStr">

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5215,13 +5215,13 @@
         <v>2723.3</v>
       </c>
       <c r="E57" t="n">
-        <v>2752.5</v>
+        <v>2751.7</v>
       </c>
       <c r="F57" t="n">
-        <v>-69.59999999999999</v>
+        <v>-70.40000000000001</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0247</v>
+        <v>-0.0249</v>
       </c>
       <c r="H57" t="n">
         <v>111</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5212,19 +5215,19 @@
         <v>2834.3</v>
       </c>
       <c r="D57" t="n">
-        <v>2723.3</v>
+        <v>2728.9</v>
       </c>
       <c r="E57" t="n">
-        <v>2751.7</v>
+        <v>2735.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-70.40000000000001</v>
+        <v>-86.59999999999999</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0249</v>
+        <v>-0.0307</v>
       </c>
       <c r="H57" t="n">
-        <v>111</v>
+        <v>105.4</v>
       </c>
       <c r="I57" t="n">
         <v>2670</v>
@@ -5250,34 +5253,120 @@
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2744.2</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2747</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2739.4</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2623.5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2607.05</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2682.8</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2758.55</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2788.2</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2817.85</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2939.7</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5297,7 +5297,7 @@
         <v>2747</v>
       </c>
       <c r="D58" t="n">
-        <v>2739.4</v>
+        <v>2738.2</v>
       </c>
       <c r="E58" t="n">
         <v/>
@@ -5309,7 +5309,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I58" t="n">
         <v>2623.5</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>98.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2291.5</v>
+        <v>2296.9</v>
       </c>
       <c r="J2" t="n">
-        <v>2392.91</v>
+        <v>2394.93</v>
       </c>
       <c r="K2" t="n">
-        <v>2423.64</v>
+        <v>2424.99</v>
       </c>
       <c r="L2" t="n">
-        <v>2454.37</v>
+        <v>2455.05</v>
       </c>
       <c r="M2" t="n">
-        <v>2520.44</v>
+        <v>2519.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2586.51</v>
+        <v>2583.14</v>
       </c>
       <c r="O2" t="n">
-        <v>2581.9</v>
+        <v>2579.2</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5291,25 +5288,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2744.2</v>
+        <v>2723.3</v>
       </c>
       <c r="C58" t="n">
-        <v>2747</v>
+        <v>2793.5</v>
       </c>
       <c r="D58" t="n">
-        <v>2738.2</v>
+        <v>2723.3</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>2785.5</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>50</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0183</v>
       </c>
       <c r="H58" t="n">
-        <v>8.800000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="I58" t="n">
         <v>2623.5</v>
@@ -5332,24 +5329,24 @@
       <c r="O58" t="n">
         <v>2939.7</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>98.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2296.9</v>
+        <v>2338.9</v>
       </c>
       <c r="J2" t="n">
-        <v>2394.93</v>
+        <v>2410.68</v>
       </c>
       <c r="K2" t="n">
-        <v>2424.99</v>
+        <v>2435.49</v>
       </c>
       <c r="L2" t="n">
-        <v>2455.05</v>
+        <v>2460.3</v>
       </c>
       <c r="M2" t="n">
-        <v>2519.09</v>
+        <v>2508.59</v>
       </c>
       <c r="N2" t="n">
-        <v>2583.14</v>
+        <v>2556.89</v>
       </c>
       <c r="O2" t="n">
-        <v>2579.2</v>
+        <v>2558.2</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,8 +695,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -5291,22 +5293,22 @@
         <v>2723.3</v>
       </c>
       <c r="C58" t="n">
-        <v>2793.5</v>
+        <v>2799</v>
       </c>
       <c r="D58" t="n">
         <v>2723.3</v>
       </c>
       <c r="E58" t="n">
-        <v>2785.5</v>
+        <v>2782.9</v>
       </c>
       <c r="F58" t="n">
-        <v>50</v>
+        <v>47.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0183</v>
+        <v>0.0173</v>
       </c>
       <c r="H58" t="n">
-        <v>70.2</v>
+        <v>75.7</v>
       </c>
       <c r="I58" t="n">
         <v>2623.5</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5293,22 +5293,22 @@
         <v>2723.3</v>
       </c>
       <c r="C58" t="n">
-        <v>2799</v>
+        <v>2806.2</v>
       </c>
       <c r="D58" t="n">
         <v>2723.3</v>
       </c>
       <c r="E58" t="n">
-        <v>2782.9</v>
+        <v>2781.2</v>
       </c>
       <c r="F58" t="n">
-        <v>47.4</v>
+        <v>45.7</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0173</v>
+        <v>0.0167</v>
       </c>
       <c r="H58" t="n">
-        <v>75.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I58" t="n">
         <v>2623.5</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -659,31 +659,35 @@
         <v>98.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2338.9</v>
+        <v>2438.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2410.68</v>
+        <v>2447.96</v>
       </c>
       <c r="K2" t="n">
-        <v>2435.49</v>
+        <v>2460.34</v>
       </c>
       <c r="L2" t="n">
-        <v>2460.3</v>
+        <v>2472.72</v>
       </c>
       <c r="M2" t="n">
-        <v>2508.59</v>
+        <v>2483.74</v>
       </c>
       <c r="N2" t="n">
-        <v>2556.89</v>
+        <v>2494.76</v>
       </c>
       <c r="O2" t="n">
-        <v>2558.2</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>2508.5</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -692,7 +696,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -700,11 +704,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -713,7 +721,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5299,13 +5307,13 @@
         <v>2723.3</v>
       </c>
       <c r="E58" t="n">
-        <v>2781.2</v>
+        <v>2792.5</v>
       </c>
       <c r="F58" t="n">
-        <v>45.7</v>
+        <v>57</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0208</v>
       </c>
       <c r="H58" t="n">
         <v>82.90000000000001</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,163 +634,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2469.5</v>
+        <v>2449.2</v>
       </c>
       <c r="C2" t="n">
-        <v>2510.3</v>
+        <v>2515</v>
       </c>
       <c r="D2" t="n">
-        <v>2412.1</v>
+        <v>2424.7</v>
       </c>
       <c r="E2" t="n">
-        <v>2450.4</v>
+        <v>2492.1</v>
       </c>
       <c r="F2" t="n">
-        <v>-21.64</v>
+        <v>41.7</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="H2" t="n">
-        <v>98.2</v>
+        <v>90.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2438.3</v>
+        <v>2313.9</v>
       </c>
       <c r="J2" t="n">
-        <v>2447.96</v>
+        <v>2346.8</v>
       </c>
       <c r="K2" t="n">
-        <v>2460.34</v>
+        <v>2401.3</v>
       </c>
       <c r="L2" t="n">
-        <v>2472.72</v>
+        <v>2455.8</v>
       </c>
       <c r="M2" t="n">
-        <v>2483.74</v>
+        <v>2499.5</v>
       </c>
       <c r="N2" t="n">
-        <v>2494.76</v>
+        <v>2543.2</v>
       </c>
       <c r="O2" t="n">
-        <v>2508.5</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
+        <v>2608.5</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2449.2</v>
+        <v>2491.9</v>
       </c>
       <c r="C3" t="n">
-        <v>2515</v>
+        <v>2518.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2424.7</v>
+        <v>2381.8</v>
       </c>
       <c r="E3" t="n">
-        <v>2492.1</v>
+        <v>2408.5</v>
       </c>
       <c r="F3" t="n">
-        <v>41.7</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.017</v>
+        <v>-0.0335</v>
       </c>
       <c r="H3" t="n">
-        <v>90.3</v>
+        <v>136.7</v>
       </c>
       <c r="I3" t="n">
-        <v>2313.9</v>
+        <v>2334.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2346.8</v>
+        <v>2412.93</v>
       </c>
       <c r="K3" t="n">
-        <v>2401.3</v>
+        <v>2446.95</v>
       </c>
       <c r="L3" t="n">
-        <v>2455.8</v>
+        <v>2480.98</v>
       </c>
       <c r="M3" t="n">
-        <v>2499.5</v>
+        <v>2537.25</v>
       </c>
       <c r="N3" t="n">
-        <v>2543.2</v>
+        <v>2593.53</v>
       </c>
       <c r="O3" t="n">
-        <v>2608.5</v>
+        <v>2605.3</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -798,85 +786,89 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2491.9</v>
+        <v>2421.6</v>
       </c>
       <c r="C4" t="n">
-        <v>2518.5</v>
+        <v>2559.9</v>
       </c>
       <c r="D4" t="n">
-        <v>2381.8</v>
+        <v>2421.6</v>
       </c>
       <c r="E4" t="n">
-        <v>2408.5</v>
+        <v>2464.4</v>
       </c>
       <c r="F4" t="n">
-        <v>-83.59999999999999</v>
+        <v>55.9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0335</v>
+        <v>0.0232</v>
       </c>
       <c r="H4" t="n">
-        <v>136.7</v>
+        <v>138.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2334.4</v>
+        <v>2245.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2412.93</v>
+        <v>2250.98</v>
       </c>
       <c r="K4" t="n">
-        <v>2446.95</v>
+        <v>2340.15</v>
       </c>
       <c r="L4" t="n">
-        <v>2480.98</v>
+        <v>2429.33</v>
       </c>
       <c r="M4" t="n">
-        <v>2537.25</v>
+        <v>2476.85</v>
       </c>
       <c r="N4" t="n">
-        <v>2593.53</v>
+        <v>2524.37</v>
       </c>
       <c r="O4" t="n">
-        <v>2605.3</v>
+        <v>2655.2</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
@@ -887,57 +879,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2421.6</v>
+        <v>2473.7</v>
       </c>
       <c r="C5" t="n">
-        <v>2559.9</v>
+        <v>2544</v>
       </c>
       <c r="D5" t="n">
-        <v>2421.6</v>
+        <v>2436.9</v>
       </c>
       <c r="E5" t="n">
-        <v>2464.4</v>
+        <v>2523.7</v>
       </c>
       <c r="F5" t="n">
-        <v>55.9</v>
+        <v>59.3</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0232</v>
+        <v>0.0241</v>
       </c>
       <c r="H5" t="n">
-        <v>138.3</v>
+        <v>107.1</v>
       </c>
       <c r="I5" t="n">
-        <v>2245.1</v>
+        <v>2283.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2250.98</v>
+        <v>2312.93</v>
       </c>
       <c r="K5" t="n">
-        <v>2340.15</v>
+        <v>2395.25</v>
       </c>
       <c r="L5" t="n">
-        <v>2429.33</v>
+        <v>2477.57</v>
       </c>
       <c r="M5" t="n">
-        <v>2476.85</v>
+        <v>2533.55</v>
       </c>
       <c r="N5" t="n">
-        <v>2524.37</v>
+        <v>2589.52</v>
       </c>
       <c r="O5" t="n">
-        <v>2655.2</v>
+        <v>2698.2</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -948,7 +940,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -958,10 +950,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -973,57 +963,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2473.7</v>
+        <v>2551.8</v>
       </c>
       <c r="C6" t="n">
-        <v>2544</v>
+        <v>2566.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2436.9</v>
+        <v>2463</v>
       </c>
       <c r="E6" t="n">
-        <v>2523.7</v>
+        <v>2489.9</v>
       </c>
       <c r="F6" t="n">
-        <v>59.3</v>
+        <v>-33.8</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0241</v>
+        <v>-0.0134</v>
       </c>
       <c r="H6" t="n">
-        <v>107.1</v>
+        <v>103.5</v>
       </c>
       <c r="I6" t="n">
-        <v>2283.3</v>
+        <v>2329.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2312.93</v>
+        <v>2433.22</v>
       </c>
       <c r="K6" t="n">
-        <v>2395.25</v>
+        <v>2470.15</v>
       </c>
       <c r="L6" t="n">
-        <v>2477.57</v>
+        <v>2507.07</v>
       </c>
       <c r="M6" t="n">
-        <v>2533.55</v>
+        <v>2577.25</v>
       </c>
       <c r="N6" t="n">
-        <v>2589.52</v>
+        <v>2647.43</v>
       </c>
       <c r="O6" t="n">
-        <v>2698.2</v>
+        <v>2651.1</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1031,18 +1021,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1064,50 +1054,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2551.8</v>
+        <v>2489.1</v>
       </c>
       <c r="C7" t="n">
-        <v>2566.5</v>
+        <v>2500.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2463</v>
+        <v>2386.6</v>
       </c>
       <c r="E7" t="n">
-        <v>2489.9</v>
+        <v>2440.6</v>
       </c>
       <c r="F7" t="n">
-        <v>-33.8</v>
+        <v>-49.3</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0134</v>
+        <v>-0.0198</v>
       </c>
       <c r="H7" t="n">
-        <v>103.5</v>
+        <v>113.8</v>
       </c>
       <c r="I7" t="n">
-        <v>2329.8</v>
+        <v>2359.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2433.22</v>
+        <v>2373.97</v>
       </c>
       <c r="K7" t="n">
-        <v>2470.15</v>
+        <v>2438.15</v>
       </c>
       <c r="L7" t="n">
-        <v>2507.07</v>
+        <v>2502.32</v>
       </c>
       <c r="M7" t="n">
-        <v>2577.25</v>
+        <v>2541.65</v>
       </c>
       <c r="N7" t="n">
-        <v>2647.43</v>
+        <v>2580.97</v>
       </c>
       <c r="O7" t="n">
-        <v>2651.1</v>
+        <v>2670</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1117,12 +1107,12 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1139,59 +1129,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2489.1</v>
+        <v>2455.2</v>
       </c>
       <c r="C8" t="n">
-        <v>2500.4</v>
+        <v>2487.6</v>
       </c>
       <c r="D8" t="n">
-        <v>2386.6</v>
+        <v>2353.8</v>
       </c>
       <c r="E8" t="n">
-        <v>2440.6</v>
+        <v>2396</v>
       </c>
       <c r="F8" t="n">
-        <v>-49.3</v>
+        <v>-44.6</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0198</v>
+        <v>-0.0183</v>
       </c>
       <c r="H8" t="n">
-        <v>113.8</v>
+        <v>133.8</v>
       </c>
       <c r="I8" t="n">
-        <v>2359.5</v>
+        <v>2272.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2373.97</v>
+        <v>2325.35</v>
       </c>
       <c r="K8" t="n">
-        <v>2438.15</v>
+        <v>2383.7</v>
       </c>
       <c r="L8" t="n">
-        <v>2502.32</v>
+        <v>2442.05</v>
       </c>
       <c r="M8" t="n">
-        <v>2541.65</v>
+        <v>2497.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2580.97</v>
+        <v>2552.95</v>
       </c>
       <c r="O8" t="n">
-        <v>2670</v>
+        <v>2614.2</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1204,7 +1190,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1228,50 +1214,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2455.2</v>
+        <v>2397</v>
       </c>
       <c r="C9" t="n">
-        <v>2487.6</v>
+        <v>2411.9</v>
       </c>
       <c r="D9" t="n">
-        <v>2353.8</v>
+        <v>2300.7</v>
       </c>
       <c r="E9" t="n">
-        <v>2396</v>
+        <v>2375.3</v>
       </c>
       <c r="F9" t="n">
-        <v>-44.6</v>
+        <v>-20.7</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.0086</v>
       </c>
       <c r="H9" t="n">
-        <v>133.8</v>
+        <v>111.2</v>
       </c>
       <c r="I9" t="n">
-        <v>2272.8</v>
+        <v>2220</v>
       </c>
       <c r="J9" t="n">
-        <v>2325.35</v>
+        <v>2249.85</v>
       </c>
       <c r="K9" t="n">
-        <v>2383.7</v>
+        <v>2329.1</v>
       </c>
       <c r="L9" t="n">
-        <v>2442.05</v>
+        <v>2408.35</v>
       </c>
       <c r="M9" t="n">
-        <v>2497.5</v>
+        <v>2462.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2552.95</v>
+        <v>2517.45</v>
       </c>
       <c r="O9" t="n">
-        <v>2614.2</v>
+        <v>2621.4</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1281,12 +1267,12 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1308,50 +1294,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2397</v>
+        <v>2387.8</v>
       </c>
       <c r="C10" t="n">
-        <v>2411.9</v>
+        <v>2508.1</v>
       </c>
       <c r="D10" t="n">
-        <v>2300.7</v>
+        <v>2370.3</v>
       </c>
       <c r="E10" t="n">
-        <v>2375.3</v>
+        <v>2505.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-20.7</v>
+        <v>129.8</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0546</v>
       </c>
       <c r="H10" t="n">
-        <v>111.2</v>
+        <v>137.8</v>
       </c>
       <c r="I10" t="n">
-        <v>2220</v>
+        <v>2189.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2249.85</v>
+        <v>2273.6</v>
       </c>
       <c r="K10" t="n">
-        <v>2329.1</v>
+        <v>2319.7</v>
       </c>
       <c r="L10" t="n">
-        <v>2408.35</v>
+        <v>2365.8</v>
       </c>
       <c r="M10" t="n">
-        <v>2462.9</v>
+        <v>2430.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2517.45</v>
+        <v>2496</v>
       </c>
       <c r="O10" t="n">
-        <v>2621.4</v>
+        <v>2523.1</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1359,28 +1345,30 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W10" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1388,50 +1376,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2387.8</v>
+        <v>2501</v>
       </c>
       <c r="C11" t="n">
-        <v>2508.1</v>
+        <v>2544.2</v>
       </c>
       <c r="D11" t="n">
-        <v>2370.3</v>
+        <v>2468.1</v>
       </c>
       <c r="E11" t="n">
-        <v>2505.1</v>
+        <v>2524.4</v>
       </c>
       <c r="F11" t="n">
-        <v>129.8</v>
+        <v>19.3</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0077</v>
       </c>
       <c r="H11" t="n">
-        <v>137.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>2189.5</v>
+        <v>2232.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2273.6</v>
+        <v>2400.25</v>
       </c>
       <c r="K11" t="n">
-        <v>2319.7</v>
+        <v>2436.2</v>
       </c>
       <c r="L11" t="n">
-        <v>2365.8</v>
+        <v>2472.15</v>
       </c>
       <c r="M11" t="n">
-        <v>2430.9</v>
+        <v>2574</v>
       </c>
       <c r="N11" t="n">
-        <v>2496</v>
+        <v>2675.85</v>
       </c>
       <c r="O11" t="n">
-        <v>2523.1</v>
+        <v>2645.9</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1442,20 +1430,18 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1470,50 +1456,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2501</v>
+        <v>2528</v>
       </c>
       <c r="C12" t="n">
-        <v>2544.2</v>
+        <v>2605</v>
       </c>
       <c r="D12" t="n">
-        <v>2468.1</v>
+        <v>2516.6</v>
       </c>
       <c r="E12" t="n">
-        <v>2524.4</v>
+        <v>2553.7</v>
       </c>
       <c r="F12" t="n">
-        <v>19.3</v>
+        <v>29.3</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0116</v>
       </c>
       <c r="H12" t="n">
-        <v>76.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>2232.5</v>
+        <v>2392</v>
       </c>
       <c r="J12" t="n">
-        <v>2400.25</v>
+        <v>2457.42</v>
       </c>
       <c r="K12" t="n">
-        <v>2436.2</v>
+        <v>2486.35</v>
       </c>
       <c r="L12" t="n">
-        <v>2472.15</v>
+        <v>2515.27</v>
       </c>
       <c r="M12" t="n">
-        <v>2574</v>
+        <v>2562.45</v>
       </c>
       <c r="N12" t="n">
-        <v>2675.85</v>
+        <v>2609.62</v>
       </c>
       <c r="O12" t="n">
-        <v>2645.9</v>
+        <v>2620.3</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1524,7 +1510,7 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1550,50 +1536,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2528</v>
+        <v>2552.8</v>
       </c>
       <c r="C13" t="n">
-        <v>2605</v>
+        <v>2577.3</v>
       </c>
       <c r="D13" t="n">
-        <v>2516.6</v>
+        <v>2489.4</v>
       </c>
       <c r="E13" t="n">
-        <v>2553.7</v>
+        <v>2509.56</v>
       </c>
       <c r="F13" t="n">
-        <v>29.3</v>
+        <v>-44.14</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0116</v>
+        <v>-0.0173</v>
       </c>
       <c r="H13" t="n">
-        <v>88.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2392</v>
+        <v>2428.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2457.42</v>
+        <v>2461.75</v>
       </c>
       <c r="K13" t="n">
-        <v>2486.35</v>
+        <v>2509.5</v>
       </c>
       <c r="L13" t="n">
-        <v>2515.27</v>
+        <v>2557.25</v>
       </c>
       <c r="M13" t="n">
-        <v>2562.45</v>
+        <v>2597.9</v>
       </c>
       <c r="N13" t="n">
-        <v>2609.62</v>
+        <v>2638.55</v>
       </c>
       <c r="O13" t="n">
-        <v>2620.3</v>
+        <v>2693.4</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1601,18 +1587,18 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1625,55 +1611,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2552.8</v>
+        <v>2550</v>
       </c>
       <c r="C14" t="n">
-        <v>2577.3</v>
+        <v>2590.3</v>
       </c>
       <c r="D14" t="n">
-        <v>2489.4</v>
+        <v>2540.8</v>
       </c>
       <c r="E14" t="n">
-        <v>2509.56</v>
+        <v>2551.4</v>
       </c>
       <c r="F14" t="n">
-        <v>-44.14</v>
+        <v>41.84</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0173</v>
+        <v>0.0167</v>
       </c>
       <c r="H14" t="n">
-        <v>87.90000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="I14" t="n">
-        <v>2428.2</v>
+        <v>2401.5</v>
       </c>
       <c r="J14" t="n">
-        <v>2461.75</v>
+        <v>2409.76</v>
       </c>
       <c r="K14" t="n">
-        <v>2509.5</v>
+        <v>2465.61</v>
       </c>
       <c r="L14" t="n">
-        <v>2557.25</v>
+        <v>2521.46</v>
       </c>
       <c r="M14" t="n">
-        <v>2597.9</v>
+        <v>2553.51</v>
       </c>
       <c r="N14" t="n">
-        <v>2638.55</v>
+        <v>2585.57</v>
       </c>
       <c r="O14" t="n">
-        <v>2693.4</v>
+        <v>2665.2</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1681,21 +1671,23 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1705,83 +1697,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2550</v>
+        <v>2551.6</v>
       </c>
       <c r="C15" t="n">
-        <v>2590.3</v>
+        <v>2556.9</v>
       </c>
       <c r="D15" t="n">
-        <v>2540.8</v>
+        <v>2493.5</v>
       </c>
       <c r="E15" t="n">
-        <v>2551.4</v>
+        <v>2522.5</v>
       </c>
       <c r="F15" t="n">
-        <v>41.84</v>
+        <v>-28.9</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0167</v>
+        <v>-0.0113</v>
       </c>
       <c r="H15" t="n">
-        <v>49.5</v>
+        <v>63.4</v>
       </c>
       <c r="I15" t="n">
-        <v>2401.5</v>
+        <v>2491.3</v>
       </c>
       <c r="J15" t="n">
-        <v>2409.76</v>
+        <v>2494.82</v>
       </c>
       <c r="K15" t="n">
-        <v>2465.61</v>
+        <v>2526.65</v>
       </c>
       <c r="L15" t="n">
-        <v>2521.46</v>
+        <v>2558.47</v>
       </c>
       <c r="M15" t="n">
-        <v>2553.51</v>
+        <v>2576.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2585.57</v>
+        <v>2593.82</v>
       </c>
       <c r="O15" t="n">
-        <v>2665.2</v>
+        <v>2639.8</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1791,141 +1779,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2551.6</v>
+        <v>2524.2</v>
       </c>
       <c r="C16" t="n">
-        <v>2556.9</v>
+        <v>2650.3</v>
       </c>
       <c r="D16" t="n">
-        <v>2493.5</v>
+        <v>2517.2</v>
       </c>
       <c r="E16" t="n">
-        <v>2522.5</v>
+        <v>2636.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-28.9</v>
+        <v>114.4</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0113</v>
+        <v>0.0454</v>
       </c>
       <c r="H16" t="n">
-        <v>63.4</v>
+        <v>133.1</v>
       </c>
       <c r="I16" t="n">
-        <v>2491.3</v>
+        <v>2430.1</v>
       </c>
       <c r="J16" t="n">
-        <v>2494.82</v>
+        <v>2457.75</v>
       </c>
       <c r="K16" t="n">
-        <v>2526.65</v>
+        <v>2490.8</v>
       </c>
       <c r="L16" t="n">
-        <v>2558.47</v>
+        <v>2523.85</v>
       </c>
       <c r="M16" t="n">
-        <v>2576.15</v>
+        <v>2554.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2593.82</v>
+        <v>2584.55</v>
       </c>
       <c r="O16" t="n">
-        <v>2639.8</v>
+        <v>2620.3</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
-      </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2524.2</v>
+        <v>2638.9</v>
       </c>
       <c r="C17" t="n">
-        <v>2650.3</v>
+        <v>2705.6</v>
       </c>
       <c r="D17" t="n">
-        <v>2517.2</v>
+        <v>2616.3</v>
       </c>
       <c r="E17" t="n">
-        <v>2636.9</v>
+        <v>2691.2</v>
       </c>
       <c r="F17" t="n">
-        <v>114.4</v>
+        <v>54.3</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0454</v>
+        <v>0.0206</v>
       </c>
       <c r="H17" t="n">
-        <v>133.1</v>
+        <v>89.3</v>
       </c>
       <c r="I17" t="n">
-        <v>2430.1</v>
+        <v>2384.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2457.75</v>
+        <v>2530.37</v>
       </c>
       <c r="K17" t="n">
-        <v>2490.8</v>
+        <v>2570.35</v>
       </c>
       <c r="L17" t="n">
-        <v>2523.85</v>
+        <v>2610.32</v>
       </c>
       <c r="M17" t="n">
-        <v>2554.2</v>
+        <v>2703.45</v>
       </c>
       <c r="N17" t="n">
-        <v>2584.55</v>
+        <v>2796.57</v>
       </c>
       <c r="O17" t="n">
-        <v>2620.3</v>
+        <v>2783.4</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1936,25 +1926,21 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1966,50 +1952,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2638.9</v>
+        <v>2670</v>
       </c>
       <c r="C18" t="n">
-        <v>2705.6</v>
+        <v>2749.2</v>
       </c>
       <c r="D18" t="n">
-        <v>2616.3</v>
+        <v>2631</v>
       </c>
       <c r="E18" t="n">
-        <v>2691.2</v>
+        <v>2679.6</v>
       </c>
       <c r="F18" t="n">
-        <v>54.3</v>
+        <v>-11.6</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0206</v>
+        <v>-0.0043</v>
       </c>
       <c r="H18" t="n">
-        <v>89.3</v>
+        <v>118.2</v>
       </c>
       <c r="I18" t="n">
-        <v>2384.1</v>
+        <v>2527</v>
       </c>
       <c r="J18" t="n">
-        <v>2530.37</v>
+        <v>2617.02</v>
       </c>
       <c r="K18" t="n">
-        <v>2570.35</v>
+        <v>2646.55</v>
       </c>
       <c r="L18" t="n">
-        <v>2610.32</v>
+        <v>2676.08</v>
       </c>
       <c r="M18" t="n">
-        <v>2703.45</v>
+        <v>2735.85</v>
       </c>
       <c r="N18" t="n">
-        <v>2796.57</v>
+        <v>2795.62</v>
       </c>
       <c r="O18" t="n">
-        <v>2783.4</v>
+        <v>2794.9</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2017,17 +2003,19 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U18" s="8" t="n">
@@ -2041,55 +2029,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2670</v>
+        <v>2661</v>
       </c>
       <c r="C19" t="n">
-        <v>2749.2</v>
+        <v>2697.9</v>
       </c>
       <c r="D19" t="n">
-        <v>2631</v>
+        <v>2607.5</v>
       </c>
       <c r="E19" t="n">
-        <v>2679.6</v>
+        <v>2624.6</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.6</v>
+        <v>-55</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0205</v>
       </c>
       <c r="H19" t="n">
-        <v>118.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>2527</v>
+        <v>2512.8</v>
       </c>
       <c r="J19" t="n">
-        <v>2617.02</v>
+        <v>2556.15</v>
       </c>
       <c r="K19" t="n">
-        <v>2646.55</v>
+        <v>2620.5</v>
       </c>
       <c r="L19" t="n">
-        <v>2676.08</v>
+        <v>2684.85</v>
       </c>
       <c r="M19" t="n">
-        <v>2735.85</v>
+        <v>2738.7</v>
       </c>
       <c r="N19" t="n">
-        <v>2795.62</v>
+        <v>2792.55</v>
       </c>
       <c r="O19" t="n">
-        <v>2794.9</v>
+        <v>2867.4</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2099,18 +2091,16 @@
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2125,57 +2115,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2661</v>
+        <v>2615</v>
       </c>
       <c r="C20" t="n">
-        <v>2697.9</v>
+        <v>2684.1</v>
       </c>
       <c r="D20" t="n">
-        <v>2607.5</v>
+        <v>2566.8</v>
       </c>
       <c r="E20" t="n">
-        <v>2624.6</v>
+        <v>2677.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-55</v>
+        <v>53.3</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0205</v>
+        <v>0.0203</v>
       </c>
       <c r="H20" t="n">
-        <v>90.40000000000001</v>
+        <v>117.3</v>
       </c>
       <c r="I20" t="n">
-        <v>2512.8</v>
+        <v>2517.1</v>
       </c>
       <c r="J20" t="n">
-        <v>2556.15</v>
+        <v>2520.15</v>
       </c>
       <c r="K20" t="n">
-        <v>2620.5</v>
+        <v>2579.4</v>
       </c>
       <c r="L20" t="n">
-        <v>2684.85</v>
+        <v>2638.65</v>
       </c>
       <c r="M20" t="n">
-        <v>2738.7</v>
+        <v>2669.8</v>
       </c>
       <c r="N20" t="n">
-        <v>2792.55</v>
+        <v>2700.95</v>
       </c>
       <c r="O20" t="n">
-        <v>2867.4</v>
+        <v>2788.3</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2185,17 +2175,19 @@
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2209,57 +2201,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2615</v>
+        <v>2677</v>
       </c>
       <c r="C21" t="n">
-        <v>2684.1</v>
+        <v>2720</v>
       </c>
       <c r="D21" t="n">
-        <v>2566.8</v>
+        <v>2607.3</v>
       </c>
       <c r="E21" t="n">
-        <v>2677.9</v>
+        <v>2653.1</v>
       </c>
       <c r="F21" t="n">
-        <v>53.3</v>
+        <v>-24.8</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0203</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>117.3</v>
+        <v>112.7</v>
       </c>
       <c r="I21" t="n">
-        <v>2517.1</v>
+        <v>2449.5</v>
       </c>
       <c r="J21" t="n">
-        <v>2520.15</v>
+        <v>2586.82</v>
       </c>
       <c r="K21" t="n">
-        <v>2579.4</v>
+        <v>2619.25</v>
       </c>
       <c r="L21" t="n">
-        <v>2638.65</v>
+        <v>2651.67</v>
       </c>
       <c r="M21" t="n">
-        <v>2669.8</v>
+        <v>2736.55</v>
       </c>
       <c r="N21" t="n">
-        <v>2700.95</v>
+        <v>2821.42</v>
       </c>
       <c r="O21" t="n">
-        <v>2788.3</v>
+        <v>2801.4</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2272,15 +2264,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2295,57 +2285,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2677</v>
+        <v>2650.9</v>
       </c>
       <c r="C22" t="n">
-        <v>2720</v>
+        <v>2696</v>
       </c>
       <c r="D22" t="n">
-        <v>2607.3</v>
+        <v>2613.7</v>
       </c>
       <c r="E22" t="n">
-        <v>2653.1</v>
+        <v>2668.8</v>
       </c>
       <c r="F22" t="n">
-        <v>-24.8</v>
+        <v>15.7</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H22" t="n">
-        <v>112.7</v>
+        <v>82.3</v>
       </c>
       <c r="I22" t="n">
-        <v>2449.5</v>
+        <v>2494.6</v>
       </c>
       <c r="J22" t="n">
-        <v>2586.82</v>
+        <v>2535.13</v>
       </c>
       <c r="K22" t="n">
-        <v>2619.25</v>
+        <v>2596.75</v>
       </c>
       <c r="L22" t="n">
-        <v>2651.67</v>
+        <v>2658.38</v>
       </c>
       <c r="M22" t="n">
-        <v>2736.55</v>
+        <v>2709.45</v>
       </c>
       <c r="N22" t="n">
-        <v>2821.42</v>
+        <v>2760.53</v>
       </c>
       <c r="O22" t="n">
-        <v>2801.4</v>
+        <v>2832.7</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2353,12 +2343,10 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2386,50 +2374,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2650.9</v>
+        <v>2666.5</v>
       </c>
       <c r="C23" t="n">
-        <v>2696</v>
+        <v>2683.4</v>
       </c>
       <c r="D23" t="n">
-        <v>2613.7</v>
+        <v>2602.7</v>
       </c>
       <c r="E23" t="n">
-        <v>2668.8</v>
+        <v>2634.7</v>
       </c>
       <c r="F23" t="n">
-        <v>15.7</v>
+        <v>-34.1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0128</v>
       </c>
       <c r="H23" t="n">
-        <v>82.3</v>
+        <v>80.7</v>
       </c>
       <c r="I23" t="n">
-        <v>2494.6</v>
+        <v>2531.4</v>
       </c>
       <c r="J23" t="n">
-        <v>2535.13</v>
+        <v>2593.48</v>
       </c>
       <c r="K23" t="n">
-        <v>2596.75</v>
+        <v>2627.65</v>
       </c>
       <c r="L23" t="n">
-        <v>2658.38</v>
+        <v>2661.83</v>
       </c>
       <c r="M23" t="n">
-        <v>2709.45</v>
+        <v>2709.95</v>
       </c>
       <c r="N23" t="n">
-        <v>2760.53</v>
+        <v>2758.08</v>
       </c>
       <c r="O23" t="n">
-        <v>2832.7</v>
+        <v>2778.3</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2437,12 +2425,14 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2461,70 +2451,74 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2666.5</v>
+        <v>2608.8</v>
       </c>
       <c r="C24" t="n">
-        <v>2683.4</v>
+        <v>2663.3</v>
       </c>
       <c r="D24" t="n">
-        <v>2602.7</v>
+        <v>2516.6</v>
       </c>
       <c r="E24" t="n">
-        <v>2634.7</v>
+        <v>2526.7</v>
       </c>
       <c r="F24" t="n">
-        <v>-34.1</v>
+        <v>-108</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0128</v>
+        <v>-0.041</v>
       </c>
       <c r="H24" t="n">
-        <v>80.7</v>
+        <v>146.7</v>
       </c>
       <c r="I24" t="n">
-        <v>2531.4</v>
+        <v>2522</v>
       </c>
       <c r="J24" t="n">
-        <v>2593.48</v>
+        <v>2549.83</v>
       </c>
       <c r="K24" t="n">
-        <v>2627.65</v>
+        <v>2594.35</v>
       </c>
       <c r="L24" t="n">
-        <v>2661.83</v>
+        <v>2638.87</v>
       </c>
       <c r="M24" t="n">
-        <v>2709.95</v>
+        <v>2675.05</v>
       </c>
       <c r="N24" t="n">
-        <v>2758.08</v>
+        <v>2711.22</v>
       </c>
       <c r="O24" t="n">
-        <v>2778.3</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
+        <v>2764.1</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2538,81 +2532,73 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2608.8</v>
+        <v>2499.2</v>
       </c>
       <c r="C25" t="n">
-        <v>2663.3</v>
+        <v>2594.4</v>
       </c>
       <c r="D25" t="n">
-        <v>2516.6</v>
+        <v>2416.9</v>
       </c>
       <c r="E25" t="n">
-        <v>2526.7</v>
+        <v>2480.9</v>
       </c>
       <c r="F25" t="n">
-        <v>-108</v>
+        <v>-45.8</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.041</v>
+        <v>-0.0181</v>
       </c>
       <c r="H25" t="n">
-        <v>146.7</v>
+        <v>177.5</v>
       </c>
       <c r="I25" t="n">
-        <v>2522</v>
+        <v>2369.9</v>
       </c>
       <c r="J25" t="n">
-        <v>2549.83</v>
+        <v>2348.37</v>
       </c>
       <c r="K25" t="n">
-        <v>2594.35</v>
+        <v>2453.35</v>
       </c>
       <c r="L25" t="n">
-        <v>2638.87</v>
+        <v>2558.33</v>
       </c>
       <c r="M25" t="n">
-        <v>2675.05</v>
+        <v>2600.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2711.22</v>
+        <v>2641.77</v>
       </c>
       <c r="O25" t="n">
-        <v>2764.1</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>2810</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2636,50 +2622,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2499.2</v>
+        <v>2468.5</v>
       </c>
       <c r="C26" t="n">
-        <v>2594.4</v>
+        <v>2547.9</v>
       </c>
       <c r="D26" t="n">
-        <v>2416.9</v>
+        <v>2442</v>
       </c>
       <c r="E26" t="n">
-        <v>2480.9</v>
+        <v>2496.4</v>
       </c>
       <c r="F26" t="n">
-        <v>-45.8</v>
+        <v>15.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0181</v>
+        <v>0.0062</v>
       </c>
       <c r="H26" t="n">
-        <v>177.5</v>
+        <v>105.9</v>
       </c>
       <c r="I26" t="n">
-        <v>2369.9</v>
+        <v>2239.4</v>
       </c>
       <c r="J26" t="n">
-        <v>2348.37</v>
+        <v>2291.02</v>
       </c>
       <c r="K26" t="n">
-        <v>2453.35</v>
+        <v>2392.15</v>
       </c>
       <c r="L26" t="n">
-        <v>2558.33</v>
+        <v>2493.27</v>
       </c>
       <c r="M26" t="n">
-        <v>2600.05</v>
+        <v>2569.65</v>
       </c>
       <c r="N26" t="n">
-        <v>2641.77</v>
+        <v>2646.02</v>
       </c>
       <c r="O26" t="n">
-        <v>2810</v>
+        <v>2771.9</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2687,14 +2673,12 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2711,55 +2695,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2468.5</v>
+        <v>2429.1</v>
       </c>
       <c r="C27" t="n">
-        <v>2547.9</v>
+        <v>2574.5</v>
       </c>
       <c r="D27" t="n">
-        <v>2442</v>
+        <v>2415.3</v>
       </c>
       <c r="E27" t="n">
-        <v>2496.4</v>
+        <v>2464</v>
       </c>
       <c r="F27" t="n">
-        <v>15.5</v>
+        <v>-32.4</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.013</v>
       </c>
       <c r="H27" t="n">
-        <v>105.9</v>
+        <v>159.2</v>
       </c>
       <c r="I27" t="n">
-        <v>2239.4</v>
+        <v>2336.1</v>
       </c>
       <c r="J27" t="n">
-        <v>2291.02</v>
+        <v>2391.22</v>
       </c>
       <c r="K27" t="n">
-        <v>2392.15</v>
+        <v>2443.45</v>
       </c>
       <c r="L27" t="n">
-        <v>2493.27</v>
+        <v>2495.67</v>
       </c>
       <c r="M27" t="n">
-        <v>2569.65</v>
+        <v>2549.35</v>
       </c>
       <c r="N27" t="n">
-        <v>2646.02</v>
+        <v>2603.02</v>
       </c>
       <c r="O27" t="n">
-        <v>2771.9</v>
+        <v>2653.8</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2767,16 +2755,20 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2791,57 +2783,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2429.1</v>
+        <v>2445</v>
       </c>
       <c r="C28" t="n">
-        <v>2574.5</v>
+        <v>2557</v>
       </c>
       <c r="D28" t="n">
-        <v>2415.3</v>
+        <v>2409.4</v>
       </c>
       <c r="E28" t="n">
-        <v>2464</v>
+        <v>2531.7</v>
       </c>
       <c r="F28" t="n">
-        <v>-32.4</v>
+        <v>67.7</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.013</v>
+        <v>0.0275</v>
       </c>
       <c r="H28" t="n">
-        <v>159.2</v>
+        <v>147.6</v>
       </c>
       <c r="I28" t="n">
-        <v>2336.1</v>
+        <v>2256.1</v>
       </c>
       <c r="J28" t="n">
-        <v>2391.22</v>
+        <v>2289.35</v>
       </c>
       <c r="K28" t="n">
-        <v>2443.45</v>
+        <v>2384.4</v>
       </c>
       <c r="L28" t="n">
-        <v>2495.67</v>
+        <v>2479.45</v>
       </c>
       <c r="M28" t="n">
-        <v>2549.35</v>
+        <v>2543.6</v>
       </c>
       <c r="N28" t="n">
-        <v>2603.02</v>
+        <v>2607.75</v>
       </c>
       <c r="O28" t="n">
-        <v>2653.8</v>
+        <v>2733.7</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2849,19 +2841,17 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="U28" s="8" t="n">
@@ -2884,50 +2874,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2445</v>
+        <v>2527.9</v>
       </c>
       <c r="C29" t="n">
-        <v>2557</v>
+        <v>2674.5</v>
       </c>
       <c r="D29" t="n">
-        <v>2409.4</v>
+        <v>2511.4</v>
       </c>
       <c r="E29" t="n">
-        <v>2531.7</v>
+        <v>2644.4</v>
       </c>
       <c r="F29" t="n">
-        <v>67.7</v>
+        <v>112.7</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0445</v>
       </c>
       <c r="H29" t="n">
-        <v>147.6</v>
+        <v>163.1</v>
       </c>
       <c r="I29" t="n">
-        <v>2256.1</v>
+        <v>2261.8</v>
       </c>
       <c r="J29" t="n">
-        <v>2289.35</v>
+        <v>2408.35</v>
       </c>
       <c r="K29" t="n">
-        <v>2384.4</v>
+        <v>2457.9</v>
       </c>
       <c r="L29" t="n">
-        <v>2479.45</v>
+        <v>2507.45</v>
       </c>
       <c r="M29" t="n">
-        <v>2543.6</v>
+        <v>2605.5</v>
       </c>
       <c r="N29" t="n">
-        <v>2607.75</v>
+        <v>2703.55</v>
       </c>
       <c r="O29" t="n">
-        <v>2733.7</v>
+        <v>2704.6</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2938,7 +2928,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2961,57 +2951,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2527.9</v>
+        <v>2607.8</v>
       </c>
       <c r="C30" t="n">
-        <v>2674.5</v>
+        <v>2807.8</v>
       </c>
       <c r="D30" t="n">
-        <v>2511.4</v>
+        <v>2591.8</v>
       </c>
       <c r="E30" t="n">
-        <v>2644.4</v>
+        <v>2788.9</v>
       </c>
       <c r="F30" t="n">
-        <v>112.7</v>
+        <v>144.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0445</v>
+        <v>0.0546</v>
       </c>
       <c r="H30" t="n">
-        <v>163.1</v>
+        <v>216</v>
       </c>
       <c r="I30" t="n">
-        <v>2261.8</v>
+        <v>2348.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2408.35</v>
+        <v>2507.02</v>
       </c>
       <c r="K30" t="n">
-        <v>2457.9</v>
+        <v>2562.85</v>
       </c>
       <c r="L30" t="n">
-        <v>2507.45</v>
+        <v>2618.67</v>
       </c>
       <c r="M30" t="n">
-        <v>2605.5</v>
+        <v>2725.95</v>
       </c>
       <c r="N30" t="n">
-        <v>2703.55</v>
+        <v>2833.22</v>
       </c>
       <c r="O30" t="n">
-        <v>2704.6</v>
+        <v>2837.6</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3022,18 +3012,20 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3052,50 +3044,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2607.8</v>
+        <v>2758.7</v>
       </c>
       <c r="C31" t="n">
-        <v>2807.8</v>
+        <v>2828.7</v>
       </c>
       <c r="D31" t="n">
-        <v>2591.8</v>
+        <v>2745.9</v>
       </c>
       <c r="E31" t="n">
-        <v>2788.9</v>
+        <v>2796.1</v>
       </c>
       <c r="F31" t="n">
-        <v>144.5</v>
+        <v>7.2</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0026</v>
       </c>
       <c r="H31" t="n">
-        <v>216</v>
+        <v>82.8</v>
       </c>
       <c r="I31" t="n">
-        <v>2348.3</v>
+        <v>2375.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2507.02</v>
+        <v>2617.45</v>
       </c>
       <c r="K31" t="n">
-        <v>2562.85</v>
+        <v>2680.9</v>
       </c>
       <c r="L31" t="n">
-        <v>2618.67</v>
+        <v>2744.35</v>
       </c>
       <c r="M31" t="n">
-        <v>2725.95</v>
+        <v>2896.9</v>
       </c>
       <c r="N31" t="n">
-        <v>2833.22</v>
+        <v>3049.45</v>
       </c>
       <c r="O31" t="n">
-        <v>2837.6</v>
+        <v>3023.8</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3106,20 +3098,16 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3138,50 +3126,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2758.7</v>
+        <v>2792.7</v>
       </c>
       <c r="C32" t="n">
-        <v>2828.7</v>
+        <v>2825</v>
       </c>
       <c r="D32" t="n">
-        <v>2745.9</v>
+        <v>2726.1</v>
       </c>
       <c r="E32" t="n">
-        <v>2796.1</v>
+        <v>2819.3</v>
       </c>
       <c r="F32" t="n">
-        <v>7.2</v>
+        <v>23.2</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0083</v>
       </c>
       <c r="H32" t="n">
-        <v>82.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>2375.8</v>
+        <v>2663.1</v>
       </c>
       <c r="J32" t="n">
-        <v>2617.45</v>
+        <v>2717.7</v>
       </c>
       <c r="K32" t="n">
-        <v>2680.9</v>
+        <v>2754.7</v>
       </c>
       <c r="L32" t="n">
-        <v>2744.35</v>
+        <v>2791.7</v>
       </c>
       <c r="M32" t="n">
-        <v>2896.9</v>
+        <v>2837.5</v>
       </c>
       <c r="N32" t="n">
-        <v>3049.45</v>
+        <v>2883.3</v>
       </c>
       <c r="O32" t="n">
-        <v>3023.8</v>
+        <v>2911.5</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3189,16 +3177,20 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3213,57 +3205,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2792.7</v>
+        <v>2825.9</v>
       </c>
       <c r="C33" t="n">
-        <v>2825</v>
+        <v>2918.4</v>
       </c>
       <c r="D33" t="n">
-        <v>2726.1</v>
+        <v>2786.8</v>
       </c>
       <c r="E33" t="n">
-        <v>2819.3</v>
+        <v>2867.6</v>
       </c>
       <c r="F33" t="n">
-        <v>23.2</v>
+        <v>48.3</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0171</v>
       </c>
       <c r="H33" t="n">
-        <v>98.90000000000001</v>
+        <v>131.6</v>
       </c>
       <c r="I33" t="n">
-        <v>2663.1</v>
+        <v>2627.2</v>
       </c>
       <c r="J33" t="n">
-        <v>2717.7</v>
+        <v>2742.28</v>
       </c>
       <c r="K33" t="n">
-        <v>2754.7</v>
+        <v>2769.85</v>
       </c>
       <c r="L33" t="n">
-        <v>2791.7</v>
+        <v>2797.43</v>
       </c>
       <c r="M33" t="n">
-        <v>2837.5</v>
+        <v>2868.75</v>
       </c>
       <c r="N33" t="n">
-        <v>2883.3</v>
+        <v>2940.07</v>
       </c>
       <c r="O33" t="n">
-        <v>2911.5</v>
+        <v>2923.9</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3271,12 +3263,10 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3299,57 +3289,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2825.9</v>
+        <v>2863</v>
       </c>
       <c r="C34" t="n">
-        <v>2918.4</v>
+        <v>2896.2</v>
       </c>
       <c r="D34" t="n">
-        <v>2786.8</v>
+        <v>2787.9</v>
       </c>
       <c r="E34" t="n">
-        <v>2867.6</v>
+        <v>2799.6</v>
       </c>
       <c r="F34" t="n">
-        <v>48.3</v>
+        <v>-68</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0171</v>
+        <v>-0.0237</v>
       </c>
       <c r="H34" t="n">
-        <v>131.6</v>
+        <v>108.3</v>
       </c>
       <c r="I34" t="n">
-        <v>2627.2</v>
+        <v>2655.2</v>
       </c>
       <c r="J34" t="n">
-        <v>2742.28</v>
+        <v>2743.5</v>
       </c>
       <c r="K34" t="n">
-        <v>2769.85</v>
+        <v>2801.8</v>
       </c>
       <c r="L34" t="n">
-        <v>2797.43</v>
+        <v>2860.1</v>
       </c>
       <c r="M34" t="n">
-        <v>2868.75</v>
+        <v>2933.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2940.07</v>
+        <v>3006.7</v>
       </c>
       <c r="O34" t="n">
-        <v>2923.9</v>
+        <v>3050</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3357,18 +3347,18 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3383,57 +3373,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2863</v>
+        <v>2788.8</v>
       </c>
       <c r="C35" t="n">
-        <v>2896.2</v>
+        <v>2887</v>
       </c>
       <c r="D35" t="n">
-        <v>2787.9</v>
+        <v>2728.4</v>
       </c>
       <c r="E35" t="n">
-        <v>2799.6</v>
+        <v>2872.1</v>
       </c>
       <c r="F35" t="n">
-        <v>-68</v>
+        <v>72.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0259</v>
       </c>
       <c r="H35" t="n">
-        <v>108.3</v>
+        <v>158.6</v>
       </c>
       <c r="I35" t="n">
-        <v>2655.2</v>
+        <v>2679.6</v>
       </c>
       <c r="J35" t="n">
-        <v>2743.5</v>
+        <v>2670.08</v>
       </c>
       <c r="K35" t="n">
-        <v>2801.8</v>
+        <v>2745.45</v>
       </c>
       <c r="L35" t="n">
-        <v>2860.1</v>
+        <v>2820.83</v>
       </c>
       <c r="M35" t="n">
-        <v>2933.4</v>
+        <v>2853.75</v>
       </c>
       <c r="N35" t="n">
-        <v>3006.7</v>
+        <v>2886.68</v>
       </c>
       <c r="O35" t="n">
-        <v>3050</v>
+        <v>3004.5</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3443,19 +3433,23 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3474,50 +3468,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2788.8</v>
+        <v>2888</v>
       </c>
       <c r="C36" t="n">
-        <v>2887</v>
+        <v>2952</v>
       </c>
       <c r="D36" t="n">
-        <v>2728.4</v>
+        <v>2887.9</v>
       </c>
       <c r="E36" t="n">
-        <v>2872.1</v>
+        <v>2924.3</v>
       </c>
       <c r="F36" t="n">
-        <v>72.5</v>
+        <v>52.2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0259</v>
+        <v>0.0182</v>
       </c>
       <c r="H36" t="n">
-        <v>158.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>2679.6</v>
+        <v>2569.8</v>
       </c>
       <c r="J36" t="n">
-        <v>2670.08</v>
+        <v>2745.7</v>
       </c>
       <c r="K36" t="n">
-        <v>2745.45</v>
+        <v>2792.8</v>
       </c>
       <c r="L36" t="n">
-        <v>2820.83</v>
+        <v>2839.9</v>
       </c>
       <c r="M36" t="n">
-        <v>2853.75</v>
+        <v>2951.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2886.68</v>
+        <v>3062.9</v>
       </c>
       <c r="O36" t="n">
-        <v>3004.5</v>
+        <v>3045.6</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3525,26 +3519,22 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
@@ -3555,76 +3545,80 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2888</v>
+        <v>2920.5</v>
       </c>
       <c r="C37" t="n">
-        <v>2952</v>
+        <v>2948.3</v>
       </c>
       <c r="D37" t="n">
-        <v>2887.9</v>
+        <v>2812.4</v>
       </c>
       <c r="E37" t="n">
-        <v>2924.3</v>
+        <v>2834.8</v>
       </c>
       <c r="F37" t="n">
-        <v>52.2</v>
+        <v>-89.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0182</v>
+        <v>-0.0306</v>
       </c>
       <c r="H37" t="n">
-        <v>64.09999999999999</v>
+        <v>135.9</v>
       </c>
       <c r="I37" t="n">
-        <v>2569.8</v>
+        <v>2823.8</v>
       </c>
       <c r="J37" t="n">
-        <v>2745.7</v>
+        <v>2862.38</v>
       </c>
       <c r="K37" t="n">
-        <v>2792.8</v>
+        <v>2892.25</v>
       </c>
       <c r="L37" t="n">
-        <v>2839.9</v>
+        <v>2922.12</v>
       </c>
       <c r="M37" t="n">
-        <v>2951.4</v>
+        <v>2956.35</v>
       </c>
       <c r="N37" t="n">
-        <v>3062.9</v>
+        <v>2990.58</v>
       </c>
       <c r="O37" t="n">
-        <v>3045.6</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+        <v>3016.1</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3637,86 +3631,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2920.5</v>
+        <v>2816.3</v>
       </c>
       <c r="C38" t="n">
-        <v>2948.3</v>
+        <v>2974.2</v>
       </c>
       <c r="D38" t="n">
-        <v>2812.4</v>
+        <v>2793.7</v>
       </c>
       <c r="E38" t="n">
-        <v>2834.8</v>
+        <v>2947</v>
       </c>
       <c r="F38" t="n">
-        <v>-89.5</v>
+        <v>112.2</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0306</v>
+        <v>0.0396</v>
       </c>
       <c r="H38" t="n">
-        <v>135.9</v>
+        <v>180.5</v>
       </c>
       <c r="I38" t="n">
-        <v>2823.8</v>
+        <v>2676.5</v>
       </c>
       <c r="J38" t="n">
-        <v>2862.38</v>
+        <v>2676.12</v>
       </c>
       <c r="K38" t="n">
-        <v>2892.25</v>
+        <v>2766.85</v>
       </c>
       <c r="L38" t="n">
-        <v>2922.12</v>
+        <v>2857.58</v>
       </c>
       <c r="M38" t="n">
-        <v>2956.35</v>
+        <v>2902.75</v>
       </c>
       <c r="N38" t="n">
-        <v>2990.58</v>
+        <v>2947.93</v>
       </c>
       <c r="O38" t="n">
-        <v>3016.1</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
+        <v>3084.2</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
@@ -3725,55 +3713,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2816.3</v>
+        <v>2984</v>
       </c>
       <c r="C39" t="n">
-        <v>2974.2</v>
+        <v>3005</v>
       </c>
       <c r="D39" t="n">
-        <v>2793.7</v>
+        <v>2910.3</v>
       </c>
       <c r="E39" t="n">
-        <v>2947</v>
+        <v>2995.6</v>
       </c>
       <c r="F39" t="n">
-        <v>112.2</v>
+        <v>48.6</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.0165</v>
       </c>
       <c r="H39" t="n">
-        <v>180.5</v>
+        <v>94.7</v>
       </c>
       <c r="I39" t="n">
-        <v>2676.5</v>
+        <v>2613.2</v>
       </c>
       <c r="J39" t="n">
-        <v>2676.12</v>
+        <v>2798.03</v>
       </c>
       <c r="K39" t="n">
-        <v>2766.85</v>
+        <v>2856.75</v>
       </c>
       <c r="L39" t="n">
-        <v>2857.58</v>
+        <v>2915.47</v>
       </c>
       <c r="M39" t="n">
-        <v>2902.75</v>
+        <v>3037.25</v>
       </c>
       <c r="N39" t="n">
-        <v>2947.93</v>
+        <v>3159.03</v>
       </c>
       <c r="O39" t="n">
-        <v>3084.2</v>
+        <v>3154.7</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3784,21 +3776,19 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3809,57 +3799,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2984</v>
+        <v>2989.9</v>
       </c>
       <c r="C40" t="n">
-        <v>3005</v>
+        <v>3062.4</v>
       </c>
       <c r="D40" t="n">
-        <v>2910.3</v>
+        <v>2965.2</v>
       </c>
       <c r="E40" t="n">
-        <v>2995.6</v>
+        <v>3022.6</v>
       </c>
       <c r="F40" t="n">
-        <v>48.6</v>
+        <v>27</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>94.7</v>
+        <v>97.2</v>
       </c>
       <c r="I40" t="n">
-        <v>2613.2</v>
+        <v>2815.6</v>
       </c>
       <c r="J40" t="n">
-        <v>2798.03</v>
+        <v>2919.88</v>
       </c>
       <c r="K40" t="n">
-        <v>2856.75</v>
+        <v>2948.25</v>
       </c>
       <c r="L40" t="n">
-        <v>2915.47</v>
+        <v>2976.63</v>
       </c>
       <c r="M40" t="n">
-        <v>3037.25</v>
+        <v>3042.95</v>
       </c>
       <c r="N40" t="n">
-        <v>3159.03</v>
+        <v>3109.28</v>
       </c>
       <c r="O40" t="n">
-        <v>3154.7</v>
+        <v>3099.7</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3870,7 +3860,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3900,50 +3890,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2989.9</v>
+        <v>3020.9</v>
       </c>
       <c r="C41" t="n">
-        <v>3062.4</v>
+        <v>3068.4</v>
       </c>
       <c r="D41" t="n">
-        <v>2965.2</v>
+        <v>2987.8</v>
       </c>
       <c r="E41" t="n">
-        <v>3022.6</v>
+        <v>3023.5</v>
       </c>
       <c r="F41" t="n">
-        <v>27</v>
+        <v>0.9</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0003</v>
       </c>
       <c r="H41" t="n">
-        <v>97.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>2815.6</v>
+        <v>2868</v>
       </c>
       <c r="J41" t="n">
-        <v>2919.88</v>
+        <v>2929.8</v>
       </c>
       <c r="K41" t="n">
-        <v>2948.25</v>
+        <v>2974</v>
       </c>
       <c r="L41" t="n">
-        <v>2976.63</v>
+        <v>3018.2</v>
       </c>
       <c r="M41" t="n">
-        <v>3042.95</v>
+        <v>3071.2</v>
       </c>
       <c r="N41" t="n">
-        <v>3109.28</v>
+        <v>3124.2</v>
       </c>
       <c r="O41" t="n">
-        <v>3099.7</v>
+        <v>3159.6</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3954,15 +3944,13 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3984,50 +3972,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3020.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C42" t="n">
-        <v>3068.4</v>
+        <v>3042.6</v>
       </c>
       <c r="D42" t="n">
-        <v>2987.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E42" t="n">
-        <v>3023.5</v>
+        <v>2994</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9</v>
+        <v>-29.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0098</v>
       </c>
       <c r="H42" t="n">
-        <v>80.59999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="I42" t="n">
-        <v>2868</v>
+        <v>2907.2</v>
       </c>
       <c r="J42" t="n">
-        <v>2929.8</v>
+        <v>2940.6</v>
       </c>
       <c r="K42" t="n">
-        <v>2974</v>
+        <v>2983.2</v>
       </c>
       <c r="L42" t="n">
-        <v>3018.2</v>
+        <v>3025.8</v>
       </c>
       <c r="M42" t="n">
-        <v>3071.2</v>
+        <v>3063.8</v>
       </c>
       <c r="N42" t="n">
-        <v>3124.2</v>
+        <v>3101.8</v>
       </c>
       <c r="O42" t="n">
-        <v>3159.6</v>
+        <v>3149</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4035,12 +4023,14 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4057,59 +4047,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3019.7</v>
+        <v>2984.7</v>
       </c>
       <c r="C43" t="n">
-        <v>3042.6</v>
+        <v>3029.8</v>
       </c>
       <c r="D43" t="n">
-        <v>2943.4</v>
+        <v>2949.3</v>
       </c>
       <c r="E43" t="n">
-        <v>2994</v>
+        <v>2973.5</v>
       </c>
       <c r="F43" t="n">
-        <v>-29.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0068</v>
       </c>
       <c r="H43" t="n">
-        <v>99.2</v>
+        <v>80.5</v>
       </c>
       <c r="I43" t="n">
-        <v>2907.2</v>
+        <v>2844.2</v>
       </c>
       <c r="J43" t="n">
-        <v>2940.6</v>
+        <v>2895.3</v>
       </c>
       <c r="K43" t="n">
-        <v>2983.2</v>
+        <v>2944.4</v>
       </c>
       <c r="L43" t="n">
-        <v>3025.8</v>
+        <v>2993.5</v>
       </c>
       <c r="M43" t="n">
-        <v>3063.8</v>
+        <v>3043.6</v>
       </c>
       <c r="N43" t="n">
-        <v>3101.8</v>
+        <v>3093.7</v>
       </c>
       <c r="O43" t="n">
-        <v>3149</v>
+        <v>3141.8</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4117,14 +4103,12 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4141,55 +4125,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2984.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C44" t="n">
-        <v>3029.8</v>
+        <v>2999.8</v>
       </c>
       <c r="D44" t="n">
-        <v>2949.3</v>
+        <v>2932.1</v>
       </c>
       <c r="E44" t="n">
-        <v>2973.5</v>
+        <v>2941.3</v>
       </c>
       <c r="F44" t="n">
-        <v>-20.5</v>
+        <v>-32.2</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0068</v>
+        <v>-0.0108</v>
       </c>
       <c r="H44" t="n">
-        <v>80.5</v>
+        <v>67.7</v>
       </c>
       <c r="I44" t="n">
-        <v>2844.2</v>
+        <v>2868.8</v>
       </c>
       <c r="J44" t="n">
-        <v>2895.3</v>
+        <v>2884.97</v>
       </c>
       <c r="K44" t="n">
-        <v>2944.4</v>
+        <v>2933.25</v>
       </c>
       <c r="L44" t="n">
-        <v>2993.5</v>
+        <v>2981.53</v>
       </c>
       <c r="M44" t="n">
-        <v>3043.6</v>
+        <v>3013.75</v>
       </c>
       <c r="N44" t="n">
-        <v>3093.7</v>
+        <v>3045.97</v>
       </c>
       <c r="O44" t="n">
-        <v>3141.8</v>
+        <v>3110.3</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4197,12 +4185,14 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4219,59 +4209,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2964.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C45" t="n">
-        <v>2999.8</v>
+        <v>2985.9</v>
       </c>
       <c r="D45" t="n">
-        <v>2932.1</v>
+        <v>2902.3</v>
       </c>
       <c r="E45" t="n">
-        <v>2941.3</v>
+        <v>2938</v>
       </c>
       <c r="F45" t="n">
-        <v>-32.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0011</v>
       </c>
       <c r="H45" t="n">
-        <v>67.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>2868.8</v>
+        <v>2864.4</v>
       </c>
       <c r="J45" t="n">
-        <v>2884.97</v>
+        <v>2861.28</v>
       </c>
       <c r="K45" t="n">
-        <v>2933.25</v>
+        <v>2907.45</v>
       </c>
       <c r="L45" t="n">
-        <v>2981.53</v>
+        <v>2953.63</v>
       </c>
       <c r="M45" t="n">
-        <v>3013.75</v>
+        <v>2975.15</v>
       </c>
       <c r="N45" t="n">
-        <v>3045.97</v>
+        <v>2996.67</v>
       </c>
       <c r="O45" t="n">
-        <v>3110.3</v>
+        <v>3067.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4281,16 +4267,18 @@
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4308,50 +4296,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2955.5</v>
+        <v>2950</v>
       </c>
       <c r="C46" t="n">
-        <v>2985.9</v>
+        <v>3058.3</v>
       </c>
       <c r="D46" t="n">
-        <v>2902.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E46" t="n">
-        <v>2938</v>
+        <v>3041.6</v>
       </c>
       <c r="F46" t="n">
-        <v>-3.3</v>
+        <v>103.6</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0353</v>
       </c>
       <c r="H46" t="n">
-        <v>83.59999999999999</v>
+        <v>109.9</v>
       </c>
       <c r="I46" t="n">
-        <v>2864.4</v>
+        <v>2818.7</v>
       </c>
       <c r="J46" t="n">
-        <v>2861.28</v>
+        <v>2851.35</v>
       </c>
       <c r="K46" t="n">
-        <v>2907.45</v>
+        <v>2896.2</v>
       </c>
       <c r="L46" t="n">
-        <v>2953.63</v>
+        <v>2941.05</v>
       </c>
       <c r="M46" t="n">
-        <v>2975.15</v>
+        <v>2979.8</v>
       </c>
       <c r="N46" t="n">
-        <v>2996.67</v>
+        <v>3018.55</v>
       </c>
       <c r="O46" t="n">
-        <v>3067.5</v>
+        <v>3069.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4359,30 +4347,30 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr"/>
@@ -4390,50 +4378,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2950</v>
+        <v>3038.9</v>
       </c>
       <c r="C47" t="n">
-        <v>3058.3</v>
+        <v>3076.3</v>
       </c>
       <c r="D47" t="n">
-        <v>2948.4</v>
+        <v>3016</v>
       </c>
       <c r="E47" t="n">
-        <v>3041.6</v>
+        <v>3074.9</v>
       </c>
       <c r="F47" t="n">
-        <v>103.6</v>
+        <v>33.3</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.0109</v>
       </c>
       <c r="H47" t="n">
-        <v>109.9</v>
+        <v>60.3</v>
       </c>
       <c r="I47" t="n">
-        <v>2818.7</v>
+        <v>2838.5</v>
       </c>
       <c r="J47" t="n">
-        <v>2851.35</v>
+        <v>2950.83</v>
       </c>
       <c r="K47" t="n">
-        <v>2896.2</v>
+        <v>2986.65</v>
       </c>
       <c r="L47" t="n">
-        <v>2941.05</v>
+        <v>3022.48</v>
       </c>
       <c r="M47" t="n">
-        <v>2979.8</v>
+        <v>3096.55</v>
       </c>
       <c r="N47" t="n">
-        <v>3018.55</v>
+        <v>3170.63</v>
       </c>
       <c r="O47" t="n">
-        <v>3069.5</v>
+        <v>3168.2</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4444,20 +4432,18 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4472,69 +4458,71 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3038.9</v>
+        <v>3073.5</v>
       </c>
       <c r="C48" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D48" t="n">
-        <v>3016</v>
+        <v>2993.2</v>
       </c>
       <c r="E48" t="n">
-        <v>3074.9</v>
+        <v>3022.1</v>
       </c>
       <c r="F48" t="n">
-        <v>33.3</v>
+        <v>-52.8</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.0172</v>
       </c>
       <c r="H48" t="n">
-        <v>60.3</v>
+        <v>86.7</v>
       </c>
       <c r="I48" t="n">
-        <v>2838.5</v>
+        <v>2955.7</v>
       </c>
       <c r="J48" t="n">
-        <v>2950.83</v>
+        <v>3028.97</v>
       </c>
       <c r="K48" t="n">
-        <v>2986.65</v>
+        <v>3044.75</v>
       </c>
       <c r="L48" t="n">
-        <v>3022.48</v>
+        <v>3060.52</v>
       </c>
       <c r="M48" t="n">
-        <v>3096.55</v>
+        <v>3105.05</v>
       </c>
       <c r="N48" t="n">
-        <v>3170.63</v>
+        <v>3149.57</v>
       </c>
       <c r="O48" t="n">
-        <v>3168.2</v>
+        <v>3136.6</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4542,75 +4530,77 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3073.5</v>
+        <v>3023</v>
       </c>
       <c r="C49" t="n">
-        <v>3079.9</v>
+        <v>3028.9</v>
       </c>
       <c r="D49" t="n">
-        <v>2993.2</v>
+        <v>2976.6</v>
       </c>
       <c r="E49" t="n">
-        <v>3022.1</v>
+        <v>2977.5</v>
       </c>
       <c r="F49" t="n">
-        <v>-52.8</v>
+        <v>-44.6</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0172</v>
+        <v>-0.0148</v>
       </c>
       <c r="H49" t="n">
-        <v>86.7</v>
+        <v>52.3</v>
       </c>
       <c r="I49" t="n">
-        <v>2955.7</v>
+        <v>2906.5</v>
       </c>
       <c r="J49" t="n">
-        <v>3028.97</v>
+        <v>2928.18</v>
       </c>
       <c r="K49" t="n">
-        <v>3044.75</v>
+        <v>2978.75</v>
       </c>
       <c r="L49" t="n">
-        <v>3060.52</v>
+        <v>3029.33</v>
       </c>
       <c r="M49" t="n">
-        <v>3105.05</v>
+        <v>3065.45</v>
       </c>
       <c r="N49" t="n">
-        <v>3149.57</v>
+        <v>3101.58</v>
       </c>
       <c r="O49" t="n">
-        <v>3136.6</v>
+        <v>3166.6</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4629,74 +4619,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3023</v>
+        <v>2971</v>
       </c>
       <c r="C50" t="n">
-        <v>3028.9</v>
+        <v>2983.3</v>
       </c>
       <c r="D50" t="n">
+        <v>2914.5</v>
+      </c>
+      <c r="E50" t="n">
         <v>2976.6</v>
       </c>
-      <c r="E50" t="n">
-        <v>2977.5</v>
-      </c>
       <c r="F50" t="n">
-        <v>-44.6</v>
+        <v>-0.9</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0148</v>
+        <v>-0.0003</v>
       </c>
       <c r="H50" t="n">
-        <v>52.3</v>
+        <v>68.8</v>
       </c>
       <c r="I50" t="n">
-        <v>2906.5</v>
+        <v>2924.3</v>
       </c>
       <c r="J50" t="n">
-        <v>2928.18</v>
+        <v>2912.58</v>
       </c>
       <c r="K50" t="n">
-        <v>2978.75</v>
+        <v>2951.35</v>
       </c>
       <c r="L50" t="n">
-        <v>3029.33</v>
+        <v>2990.12</v>
       </c>
       <c r="M50" t="n">
-        <v>3065.45</v>
+        <v>3003.65</v>
       </c>
       <c r="N50" t="n">
-        <v>3101.58</v>
+        <v>3017.17</v>
       </c>
       <c r="O50" t="n">
-        <v>3166.6</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
+        <v>3081.2</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4718,67 +4706,67 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2971</v>
+        <v>2974.7</v>
       </c>
       <c r="C51" t="n">
-        <v>2983.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D51" t="n">
-        <v>2914.5</v>
+        <v>2887.6</v>
       </c>
       <c r="E51" t="n">
-        <v>2976.6</v>
+        <v>2904.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.9</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0242</v>
       </c>
       <c r="H51" t="n">
-        <v>68.8</v>
+        <v>90.3</v>
       </c>
       <c r="I51" t="n">
-        <v>2924.3</v>
+        <v>2845.7</v>
       </c>
       <c r="J51" t="n">
-        <v>2912.58</v>
+        <v>2921.65</v>
       </c>
       <c r="K51" t="n">
-        <v>2951.35</v>
+        <v>2942.2</v>
       </c>
       <c r="L51" t="n">
-        <v>2990.12</v>
+        <v>2962.75</v>
       </c>
       <c r="M51" t="n">
-        <v>3003.65</v>
+        <v>3011</v>
       </c>
       <c r="N51" t="n">
-        <v>3017.17</v>
+        <v>3059.25</v>
       </c>
       <c r="O51" t="n">
-        <v>3081.2</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
+        <v>3052.1</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4800,65 +4788,63 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2974.7</v>
+        <v>2892.7</v>
       </c>
       <c r="C52" t="n">
-        <v>2977.9</v>
+        <v>2913.5</v>
       </c>
       <c r="D52" t="n">
-        <v>2887.6</v>
+        <v>2831.9</v>
       </c>
       <c r="E52" t="n">
-        <v>2904.5</v>
+        <v>2873.23</v>
       </c>
       <c r="F52" t="n">
-        <v>-72.09999999999999</v>
+        <v>-31.27</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0242</v>
+        <v>-0.0108</v>
       </c>
       <c r="H52" t="n">
-        <v>90.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>2845.7</v>
+        <v>2797.3</v>
       </c>
       <c r="J52" t="n">
-        <v>2921.65</v>
+        <v>2800.08</v>
       </c>
       <c r="K52" t="n">
-        <v>2942.2</v>
+        <v>2859.35</v>
       </c>
       <c r="L52" t="n">
-        <v>2962.75</v>
+        <v>2918.62</v>
       </c>
       <c r="M52" t="n">
-        <v>3011</v>
+        <v>2949.65</v>
       </c>
       <c r="N52" t="n">
-        <v>3059.25</v>
+        <v>2980.67</v>
       </c>
       <c r="O52" t="n">
-        <v>3052.1</v>
+        <v>3068.2</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4882,50 +4868,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2892.7</v>
+        <v>2879.5</v>
       </c>
       <c r="C53" t="n">
-        <v>2913.5</v>
+        <v>2931.2</v>
       </c>
       <c r="D53" t="n">
-        <v>2831.9</v>
+        <v>2829.9</v>
       </c>
       <c r="E53" t="n">
-        <v>2873.23</v>
+        <v>2859.3</v>
       </c>
       <c r="F53" t="n">
-        <v>-31.27</v>
+        <v>-13.93</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0048</v>
       </c>
       <c r="H53" t="n">
-        <v>81.59999999999999</v>
+        <v>101.3</v>
       </c>
       <c r="I53" t="n">
-        <v>2797.3</v>
+        <v>2750.3</v>
       </c>
       <c r="J53" t="n">
-        <v>2800.08</v>
+        <v>2791.89</v>
       </c>
       <c r="K53" t="n">
-        <v>2859.35</v>
+        <v>2832.43</v>
       </c>
       <c r="L53" t="n">
-        <v>2918.62</v>
+        <v>2872.96</v>
       </c>
       <c r="M53" t="n">
-        <v>2949.65</v>
+        <v>2914.03</v>
       </c>
       <c r="N53" t="n">
-        <v>2980.67</v>
+        <v>2955.1</v>
       </c>
       <c r="O53" t="n">
-        <v>3068.2</v>
+        <v>2995.1</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4935,16 +4921,18 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4957,55 +4945,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2879.5</v>
+        <v>2857.7</v>
       </c>
       <c r="C54" t="n">
-        <v>2931.2</v>
+        <v>2875.3</v>
       </c>
       <c r="D54" t="n">
-        <v>2829.9</v>
+        <v>2791.5</v>
       </c>
       <c r="E54" t="n">
-        <v>2859.3</v>
+        <v>2850.9</v>
       </c>
       <c r="F54" t="n">
-        <v>-13.93</v>
+        <v>-8.4</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0029</v>
       </c>
       <c r="H54" t="n">
-        <v>101.3</v>
+        <v>83.8</v>
       </c>
       <c r="I54" t="n">
-        <v>2750.3</v>
+        <v>2728.6</v>
       </c>
       <c r="J54" t="n">
-        <v>2791.89</v>
+        <v>2747.38</v>
       </c>
       <c r="K54" t="n">
-        <v>2832.43</v>
+        <v>2808.65</v>
       </c>
       <c r="L54" t="n">
-        <v>2872.96</v>
+        <v>2869.92</v>
       </c>
       <c r="M54" t="n">
-        <v>2914.03</v>
+        <v>2909.95</v>
       </c>
       <c r="N54" t="n">
-        <v>2955.1</v>
+        <v>2949.98</v>
       </c>
       <c r="O54" t="n">
-        <v>2995.1</v>
+        <v>3032.5</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5018,15 +5010,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5039,59 +5029,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2857.7</v>
+        <v>2850.6</v>
       </c>
       <c r="C55" t="n">
-        <v>2875.3</v>
+        <v>2887.2</v>
       </c>
       <c r="D55" t="n">
-        <v>2791.5</v>
+        <v>2778.6</v>
       </c>
       <c r="E55" t="n">
-        <v>2850.9</v>
+        <v>2822.1</v>
       </c>
       <c r="F55" t="n">
-        <v>-8.4</v>
+        <v>-28.8</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0101</v>
       </c>
       <c r="H55" t="n">
-        <v>83.8</v>
+        <v>108.6</v>
       </c>
       <c r="I55" t="n">
-        <v>2728.6</v>
+        <v>2707.7</v>
       </c>
       <c r="J55" t="n">
-        <v>2747.38</v>
+        <v>2775.85</v>
       </c>
       <c r="K55" t="n">
-        <v>2808.65</v>
+        <v>2809</v>
       </c>
       <c r="L55" t="n">
-        <v>2869.92</v>
+        <v>2842.15</v>
       </c>
       <c r="M55" t="n">
-        <v>2909.95</v>
+        <v>2892.8</v>
       </c>
       <c r="N55" t="n">
-        <v>2949.98</v>
+        <v>2943.45</v>
       </c>
       <c r="O55" t="n">
-        <v>3032.5</v>
+        <v>2959.1</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5101,12 +5087,12 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5123,68 +5109,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2850.6</v>
+        <v>2822.9</v>
       </c>
       <c r="C56" t="n">
-        <v>2887.2</v>
+        <v>2834.3</v>
       </c>
       <c r="D56" t="n">
-        <v>2778.6</v>
+        <v>2728.9</v>
       </c>
       <c r="E56" t="n">
-        <v>2822.1</v>
+        <v>2735.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-28.8</v>
+        <v>-86.59999999999999</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0101</v>
+        <v>-0.0307</v>
       </c>
       <c r="H56" t="n">
-        <v>108.6</v>
+        <v>105.4</v>
       </c>
       <c r="I56" t="n">
-        <v>2707.7</v>
+        <v>2670</v>
       </c>
       <c r="J56" t="n">
-        <v>2775.85</v>
+        <v>2708.1</v>
       </c>
       <c r="K56" t="n">
-        <v>2809</v>
+        <v>2767.8</v>
       </c>
       <c r="L56" t="n">
-        <v>2842.15</v>
+        <v>2827.5</v>
       </c>
       <c r="M56" t="n">
-        <v>2892.8</v>
+        <v>2876.4</v>
       </c>
       <c r="N56" t="n">
-        <v>2943.45</v>
+        <v>2925.3</v>
       </c>
       <c r="O56" t="n">
-        <v>2959.1</v>
+        <v>2995.8</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5203,81 +5195,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2822.9</v>
+        <v>2723.3</v>
       </c>
       <c r="C57" t="n">
-        <v>2834.3</v>
+        <v>2806.2</v>
       </c>
       <c r="D57" t="n">
-        <v>2728.9</v>
+        <v>2723.3</v>
       </c>
       <c r="E57" t="n">
-        <v>2735.5</v>
+        <v>2788.7</v>
       </c>
       <c r="F57" t="n">
-        <v>-86.59999999999999</v>
+        <v>53.2</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0307</v>
+        <v>0.0194</v>
       </c>
       <c r="H57" t="n">
-        <v>105.4</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>2670</v>
+        <v>2623.5</v>
       </c>
       <c r="J57" t="n">
-        <v>2708.1</v>
+        <v>2607.05</v>
       </c>
       <c r="K57" t="n">
-        <v>2767.8</v>
+        <v>2682.8</v>
       </c>
       <c r="L57" t="n">
-        <v>2827.5</v>
+        <v>2758.55</v>
       </c>
       <c r="M57" t="n">
-        <v>2876.4</v>
+        <v>2788.2</v>
       </c>
       <c r="N57" t="n">
-        <v>2925.3</v>
+        <v>2817.85</v>
       </c>
       <c r="O57" t="n">
-        <v>2995.8</v>
+        <v>2939.7</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5289,87 +5275,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2723.3</v>
-      </c>
-      <c r="C58" t="n">
-        <v>2806.2</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2723.3</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2792.5</v>
-      </c>
-      <c r="F58" t="n">
-        <v>57</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0208</v>
-      </c>
-      <c r="H58" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2623.5</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2607.05</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2682.8</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2758.55</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2788.2</v>
-      </c>
-      <c r="N58" t="n">
-        <v>2817.85</v>
-      </c>
-      <c r="O58" t="n">
-        <v>2939.7</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -5213,13 +5213,13 @@
         <v>2723.3</v>
       </c>
       <c r="E57" t="n">
-        <v>2788.7</v>
+        <v>2789</v>
       </c>
       <c r="F57" t="n">
-        <v>53.2</v>
+        <v>53.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0194</v>
+        <v>0.0196</v>
       </c>
       <c r="H57" t="n">
         <v>82.90000000000001</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5213,13 +5216,13 @@
         <v>2723.3</v>
       </c>
       <c r="E57" t="n">
-        <v>2789</v>
+        <v>2784.5</v>
       </c>
       <c r="F57" t="n">
-        <v>53.5</v>
+        <v>49</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.0179</v>
       </c>
       <c r="H57" t="n">
         <v>82.90000000000001</v>
@@ -5276,6 +5279,90 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2794.3</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2802.4</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2790.4</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>12</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2640.4</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2711.48</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2743.05</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2774.62</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2825.95</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2877.27</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2889.1</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>90.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2313.9</v>
+        <v>2340.1</v>
       </c>
       <c r="J2" t="n">
-        <v>2346.8</v>
+        <v>2379.55</v>
       </c>
       <c r="K2" t="n">
-        <v>2401.3</v>
+        <v>2414.4</v>
       </c>
       <c r="L2" t="n">
-        <v>2455.8</v>
+        <v>2449.25</v>
       </c>
       <c r="M2" t="n">
-        <v>2499.5</v>
+        <v>2486.4</v>
       </c>
       <c r="N2" t="n">
-        <v>2543.2</v>
+        <v>2523.55</v>
       </c>
       <c r="O2" t="n">
-        <v>2608.5</v>
+        <v>2556.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5291,25 +5288,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2794.3</v>
+        <v>2793.5</v>
       </c>
       <c r="C58" t="n">
-        <v>2802.4</v>
+        <v>2831.7</v>
       </c>
       <c r="D58" t="n">
-        <v>2790.4</v>
+        <v>2784.9</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>2821.7</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>37.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0134</v>
       </c>
       <c r="H58" t="n">
-        <v>12</v>
+        <v>46.8</v>
       </c>
       <c r="I58" t="n">
         <v>2640.4</v>
@@ -5332,25 +5329,25 @@
       <c r="O58" t="n">
         <v>2889.1</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5364,7 +5361,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>90.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2340.1</v>
+        <v>2361.1</v>
       </c>
       <c r="J2" t="n">
-        <v>2379.55</v>
+        <v>2405.8</v>
       </c>
       <c r="K2" t="n">
-        <v>2414.4</v>
+        <v>2424.9</v>
       </c>
       <c r="L2" t="n">
-        <v>2449.25</v>
+        <v>2444</v>
       </c>
       <c r="M2" t="n">
-        <v>2486.4</v>
+        <v>2475.9</v>
       </c>
       <c r="N2" t="n">
-        <v>2523.55</v>
+        <v>2507.8</v>
       </c>
       <c r="O2" t="n">
-        <v>2556.1</v>
+        <v>2514.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -695,14 +697,18 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5291,22 +5297,22 @@
         <v>2793.5</v>
       </c>
       <c r="C58" t="n">
-        <v>2831.7</v>
+        <v>2859.4</v>
       </c>
       <c r="D58" t="n">
         <v>2784.9</v>
       </c>
       <c r="E58" t="n">
-        <v>2821.7</v>
+        <v>2852.3</v>
       </c>
       <c r="F58" t="n">
-        <v>37.2</v>
+        <v>67.8</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0243</v>
       </c>
       <c r="H58" t="n">
-        <v>46.8</v>
+        <v>74.5</v>
       </c>
       <c r="I58" t="n">
         <v>2640.4</v>
@@ -5345,11 +5351,13 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -659,31 +659,33 @@
         <v>90.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2361.1</v>
+        <v>2388.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2405.8</v>
+        <v>2425.02</v>
       </c>
       <c r="K2" t="n">
-        <v>2424.9</v>
+        <v>2434.35</v>
       </c>
       <c r="L2" t="n">
-        <v>2444</v>
+        <v>2443.67</v>
       </c>
       <c r="M2" t="n">
-        <v>2475.9</v>
+        <v>2466.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2507.8</v>
+        <v>2489.22</v>
       </c>
       <c r="O2" t="n">
-        <v>2514.1</v>
+        <v>2485.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -5297,22 +5299,22 @@
         <v>2793.5</v>
       </c>
       <c r="C58" t="n">
-        <v>2859.4</v>
+        <v>2880.2</v>
       </c>
       <c r="D58" t="n">
         <v>2784.9</v>
       </c>
       <c r="E58" t="n">
-        <v>2852.3</v>
+        <v>2853.2</v>
       </c>
       <c r="F58" t="n">
-        <v>67.8</v>
+        <v>68.7</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0243</v>
+        <v>0.0247</v>
       </c>
       <c r="H58" t="n">
-        <v>74.5</v>
+        <v>95.3</v>
       </c>
       <c r="I58" t="n">
         <v>2640.4</v>

--- a/three_gate/analysis/RTY_weekly.xlsx
+++ b/three_gate/analysis/RTY_weekly.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,224 +634,222 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2449.2</v>
+        <v>2491.9</v>
       </c>
       <c r="C2" t="n">
-        <v>2515</v>
+        <v>2518.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2424.7</v>
+        <v>2381.8</v>
       </c>
       <c r="E2" t="n">
-        <v>2492.1</v>
+        <v>2408.5</v>
       </c>
       <c r="F2" t="n">
-        <v>41.7</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.017</v>
+        <v>-0.0335</v>
       </c>
       <c r="H2" t="n">
-        <v>90.3</v>
+        <v>136.7</v>
       </c>
       <c r="I2" t="n">
-        <v>2388.8</v>
+        <v>2334.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2425.02</v>
+        <v>2412.93</v>
       </c>
       <c r="K2" t="n">
-        <v>2434.35</v>
+        <v>2446.95</v>
       </c>
       <c r="L2" t="n">
-        <v>2443.67</v>
+        <v>2480.98</v>
       </c>
       <c r="M2" t="n">
-        <v>2466.45</v>
+        <v>2537.25</v>
       </c>
       <c r="N2" t="n">
-        <v>2489.22</v>
+        <v>2593.53</v>
       </c>
       <c r="O2" t="n">
-        <v>2485.1</v>
+        <v>2605.3</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2491.9</v>
+        <v>2421.6</v>
       </c>
       <c r="C3" t="n">
-        <v>2518.5</v>
+        <v>2559.9</v>
       </c>
       <c r="D3" t="n">
-        <v>2381.8</v>
+        <v>2421.6</v>
       </c>
       <c r="E3" t="n">
-        <v>2408.5</v>
+        <v>2464.4</v>
       </c>
       <c r="F3" t="n">
-        <v>-83.59999999999999</v>
+        <v>55.9</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0335</v>
+        <v>0.0232</v>
       </c>
       <c r="H3" t="n">
-        <v>136.7</v>
+        <v>138.3</v>
       </c>
       <c r="I3" t="n">
-        <v>2334.4</v>
+        <v>2245.1</v>
       </c>
       <c r="J3" t="n">
-        <v>2412.93</v>
+        <v>2250.98</v>
       </c>
       <c r="K3" t="n">
-        <v>2446.95</v>
+        <v>2340.15</v>
       </c>
       <c r="L3" t="n">
-        <v>2480.98</v>
+        <v>2429.33</v>
       </c>
       <c r="M3" t="n">
-        <v>2537.25</v>
+        <v>2476.85</v>
       </c>
       <c r="N3" t="n">
-        <v>2593.53</v>
+        <v>2524.37</v>
       </c>
       <c r="O3" t="n">
-        <v>2605.3</v>
+        <v>2655.2</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2421.6</v>
+        <v>2473.7</v>
       </c>
       <c r="C4" t="n">
-        <v>2559.9</v>
+        <v>2544</v>
       </c>
       <c r="D4" t="n">
-        <v>2421.6</v>
+        <v>2436.9</v>
       </c>
       <c r="E4" t="n">
-        <v>2464.4</v>
+        <v>2523.7</v>
       </c>
       <c r="F4" t="n">
-        <v>55.9</v>
+        <v>59.3</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0232</v>
+        <v>0.0241</v>
       </c>
       <c r="H4" t="n">
-        <v>138.3</v>
+        <v>107.1</v>
       </c>
       <c r="I4" t="n">
-        <v>2245.1</v>
+        <v>2283.3</v>
       </c>
       <c r="J4" t="n">
-        <v>2250.98</v>
+        <v>2312.93</v>
       </c>
       <c r="K4" t="n">
-        <v>2340.15</v>
+        <v>2395.25</v>
       </c>
       <c r="L4" t="n">
-        <v>2429.33</v>
+        <v>2477.57</v>
       </c>
       <c r="M4" t="n">
-        <v>2476.85</v>
+        <v>2533.55</v>
       </c>
       <c r="N4" t="n">
-        <v>2524.37</v>
+        <v>2589.52</v>
       </c>
       <c r="O4" t="n">
-        <v>2655.2</v>
+        <v>2698.2</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -862,7 +860,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -872,72 +870,70 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2473.7</v>
+        <v>2551.8</v>
       </c>
       <c r="C5" t="n">
-        <v>2544</v>
+        <v>2566.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2436.9</v>
+        <v>2463</v>
       </c>
       <c r="E5" t="n">
-        <v>2523.7</v>
+        <v>2489.9</v>
       </c>
       <c r="F5" t="n">
-        <v>59.3</v>
+        <v>-33.8</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0241</v>
+        <v>-0.0134</v>
       </c>
       <c r="H5" t="n">
-        <v>107.1</v>
+        <v>103.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2283.3</v>
+        <v>2329.8</v>
       </c>
       <c r="J5" t="n">
-        <v>2312.93</v>
+        <v>2433.22</v>
       </c>
       <c r="K5" t="n">
-        <v>2395.25</v>
+        <v>2470.15</v>
       </c>
       <c r="L5" t="n">
-        <v>2477.57</v>
+        <v>2507.07</v>
       </c>
       <c r="M5" t="n">
-        <v>2533.55</v>
+        <v>2577.25</v>
       </c>
       <c r="N5" t="n">
-        <v>2589.52</v>
+        <v>2647.43</v>
       </c>
       <c r="O5" t="n">
-        <v>2698.2</v>
+        <v>2651.1</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -945,18 +941,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -964,7 +960,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -978,50 +974,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2551.8</v>
+        <v>2489.1</v>
       </c>
       <c r="C6" t="n">
-        <v>2566.5</v>
+        <v>2500.4</v>
       </c>
       <c r="D6" t="n">
-        <v>2463</v>
+        <v>2386.6</v>
       </c>
       <c r="E6" t="n">
-        <v>2489.9</v>
+        <v>2440.6</v>
       </c>
       <c r="F6" t="n">
-        <v>-33.8</v>
+        <v>-49.3</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0134</v>
+        <v>-0.0198</v>
       </c>
       <c r="H6" t="n">
-        <v>103.5</v>
+        <v>113.8</v>
       </c>
       <c r="I6" t="n">
-        <v>2329.8</v>
+        <v>2359.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2433.22</v>
+        <v>2373.97</v>
       </c>
       <c r="K6" t="n">
-        <v>2470.15</v>
+        <v>2438.15</v>
       </c>
       <c r="L6" t="n">
-        <v>2507.07</v>
+        <v>2502.32</v>
       </c>
       <c r="M6" t="n">
-        <v>2577.25</v>
+        <v>2541.65</v>
       </c>
       <c r="N6" t="n">
-        <v>2647.43</v>
+        <v>2580.97</v>
       </c>
       <c r="O6" t="n">
-        <v>2651.1</v>
+        <v>2670</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1031,12 +1027,12 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1048,64 +1044,60 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2489.1</v>
+        <v>2455.2</v>
       </c>
       <c r="C7" t="n">
-        <v>2500.4</v>
+        <v>2487.6</v>
       </c>
       <c r="D7" t="n">
-        <v>2386.6</v>
+        <v>2353.8</v>
       </c>
       <c r="E7" t="n">
-        <v>2440.6</v>
+        <v>2396</v>
       </c>
       <c r="F7" t="n">
-        <v>-49.3</v>
+        <v>-44.6</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0198</v>
+        <v>-0.0183</v>
       </c>
       <c r="H7" t="n">
-        <v>113.8</v>
+        <v>133.8</v>
       </c>
       <c r="I7" t="n">
-        <v>2359.5</v>
+        <v>2272.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2373.97</v>
+        <v>2325.35</v>
       </c>
       <c r="K7" t="n">
-        <v>2438.15</v>
+        <v>2383.7</v>
       </c>
       <c r="L7" t="n">
-        <v>2502.32</v>
+        <v>2442.05</v>
       </c>
       <c r="M7" t="n">
-        <v>2541.65</v>
+        <v>2497.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2580.97</v>
+        <v>2552.95</v>
       </c>
       <c r="O7" t="n">
-        <v>2670</v>
+        <v>2614.2</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1118,7 +1110,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1132,7 +1124,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1142,50 +1134,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2455.2</v>
+        <v>2397</v>
       </c>
       <c r="C8" t="n">
-        <v>2487.6</v>
+        <v>2411.9</v>
       </c>
       <c r="D8" t="n">
-        <v>2353.8</v>
+        <v>2300.7</v>
       </c>
       <c r="E8" t="n">
-        <v>2396</v>
+        <v>2375.3</v>
       </c>
       <c r="F8" t="n">
-        <v>-44.6</v>
+        <v>-20.7</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0183</v>
+        <v>-0.0086</v>
       </c>
       <c r="H8" t="n">
-        <v>133.8</v>
+        <v>111.2</v>
       </c>
       <c r="I8" t="n">
-        <v>2272.8</v>
+        <v>2220</v>
       </c>
       <c r="J8" t="n">
-        <v>2325.35</v>
+        <v>2249.85</v>
       </c>
       <c r="K8" t="n">
-        <v>2383.7</v>
+        <v>2329.1</v>
       </c>
       <c r="L8" t="n">
-        <v>2442.05</v>
+        <v>2408.35</v>
       </c>
       <c r="M8" t="n">
-        <v>2497.5</v>
+        <v>2462.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2552.95</v>
+        <v>2517.45</v>
       </c>
       <c r="O8" t="n">
-        <v>2614.2</v>
+        <v>2621.4</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1195,12 +1187,12 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1212,7 +1204,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1222,50 +1214,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2397</v>
+        <v>2387.8</v>
       </c>
       <c r="C9" t="n">
-        <v>2411.9</v>
+        <v>2508.1</v>
       </c>
       <c r="D9" t="n">
-        <v>2300.7</v>
+        <v>2370.3</v>
       </c>
       <c r="E9" t="n">
-        <v>2375.3</v>
+        <v>2505.1</v>
       </c>
       <c r="F9" t="n">
-        <v>-20.7</v>
+        <v>129.8</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0546</v>
       </c>
       <c r="H9" t="n">
-        <v>111.2</v>
+        <v>137.8</v>
       </c>
       <c r="I9" t="n">
-        <v>2220</v>
+        <v>2189.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2249.85</v>
+        <v>2273.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2329.1</v>
+        <v>2319.7</v>
       </c>
       <c r="L9" t="n">
-        <v>2408.35</v>
+        <v>2365.8</v>
       </c>
       <c r="M9" t="n">
-        <v>2462.9</v>
+        <v>2430.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2517.45</v>
+        <v>2496</v>
       </c>
       <c r="O9" t="n">
-        <v>2621.4</v>
+        <v>2523.1</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,28 +1265,30 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
       <c r="W9" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1302,50 +1296,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2387.8</v>
+        <v>2501</v>
       </c>
       <c r="C10" t="n">
-        <v>2508.1</v>
+        <v>2544.2</v>
       </c>
       <c r="D10" t="n">
-        <v>2370.3</v>
+        <v>2468.1</v>
       </c>
       <c r="E10" t="n">
-        <v>2505.1</v>
+        <v>2524.4</v>
       </c>
       <c r="F10" t="n">
-        <v>129.8</v>
+        <v>19.3</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0077</v>
       </c>
       <c r="H10" t="n">
-        <v>137.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>2189.5</v>
+        <v>2232.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2273.6</v>
+        <v>2400.25</v>
       </c>
       <c r="K10" t="n">
-        <v>2319.7</v>
+        <v>2436.2</v>
       </c>
       <c r="L10" t="n">
-        <v>2365.8</v>
+        <v>2472.15</v>
       </c>
       <c r="M10" t="n">
-        <v>2430.9</v>
+        <v>2574</v>
       </c>
       <c r="N10" t="n">
-        <v>2496</v>
+        <v>2675.85</v>
       </c>
       <c r="O10" t="n">
-        <v>2523.1</v>
+        <v>2645.9</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1356,25 +1350,23 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1384,50 +1376,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2501</v>
+        <v>2528</v>
       </c>
       <c r="C11" t="n">
-        <v>2544.2</v>
+        <v>2605</v>
       </c>
       <c r="D11" t="n">
-        <v>2468.1</v>
+        <v>2516.6</v>
       </c>
       <c r="E11" t="n">
-        <v>2524.4</v>
+        <v>2553.7</v>
       </c>
       <c r="F11" t="n">
-        <v>19.3</v>
+        <v>29.3</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0116</v>
       </c>
       <c r="H11" t="n">
-        <v>76.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>2232.5</v>
+        <v>2392</v>
       </c>
       <c r="J11" t="n">
-        <v>2400.25</v>
+        <v>2457.42</v>
       </c>
       <c r="K11" t="n">
-        <v>2436.2</v>
+        <v>2486.35</v>
       </c>
       <c r="L11" t="n">
-        <v>2472.15</v>
+        <v>2515.27</v>
       </c>
       <c r="M11" t="n">
-        <v>2574</v>
+        <v>2562.45</v>
       </c>
       <c r="N11" t="n">
-        <v>2675.85</v>
+        <v>2609.62</v>
       </c>
       <c r="O11" t="n">
-        <v>2645.9</v>
+        <v>2620.3</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1438,7 +1430,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1454,7 +1446,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1464,50 +1456,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2528</v>
+        <v>2552.8</v>
       </c>
       <c r="C12" t="n">
-        <v>2605</v>
+        <v>2577.3</v>
       </c>
       <c r="D12" t="n">
-        <v>2516.6</v>
+        <v>2489.4</v>
       </c>
       <c r="E12" t="n">
-        <v>2553.7</v>
+        <v>2509.56</v>
       </c>
       <c r="F12" t="n">
-        <v>29.3</v>
+        <v>-44.14</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0116</v>
+        <v>-0.0173</v>
       </c>
       <c r="H12" t="n">
-        <v>88.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>2392</v>
+        <v>2428.2</v>
       </c>
       <c r="J12" t="n">
-        <v>2457.42</v>
+        <v>2461.75</v>
       </c>
       <c r="K12" t="n">
-        <v>2486.35</v>
+        <v>2509.5</v>
       </c>
       <c r="L12" t="n">
-        <v>2515.27</v>
+        <v>2557.25</v>
       </c>
       <c r="M12" t="n">
-        <v>2562.45</v>
+        <v>2597.9</v>
       </c>
       <c r="N12" t="n">
-        <v>2609.62</v>
+        <v>2638.55</v>
       </c>
       <c r="O12" t="n">
-        <v>2620.3</v>
+        <v>2693.4</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1515,18 +1507,18 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1534,60 +1526,64 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2552.8</v>
+        <v>2550</v>
       </c>
       <c r="C13" t="n">
-        <v>2577.3</v>
+        <v>2590.3</v>
       </c>
       <c r="D13" t="n">
-        <v>2489.4</v>
+        <v>2540.8</v>
       </c>
       <c r="E13" t="n">
-        <v>2509.56</v>
+        <v>2551.4</v>
       </c>
       <c r="F13" t="n">
-        <v>-44.14</v>
+        <v>41.84</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0173</v>
+        <v>0.0167</v>
       </c>
       <c r="H13" t="n">
-        <v>87.90000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="I13" t="n">
-        <v>2428.2</v>
+        <v>2401.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2461.75</v>
+        <v>2409.76</v>
       </c>
       <c r="K13" t="n">
-        <v>2509.5</v>
+        <v>2465.61</v>
       </c>
       <c r="L13" t="n">
-        <v>2557.25</v>
+        <v>2521.46</v>
       </c>
       <c r="M13" t="n">
-        <v>2597.9</v>
+        <v>2553.51</v>
       </c>
       <c r="N13" t="n">
-        <v>2638.55</v>
+        <v>2585.57</v>
       </c>
       <c r="O13" t="n">
-        <v>2693.4</v>
+        <v>2665.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1595,251 +1591,251 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2550</v>
+        <v>2551.6</v>
       </c>
       <c r="C14" t="n">
-        <v>2590.3</v>
+        <v>2556.9</v>
       </c>
       <c r="D14" t="n">
-        <v>2540.8</v>
+        <v>2493.5</v>
       </c>
       <c r="E14" t="n">
-        <v>2551.4</v>
+        <v>2522.5</v>
       </c>
       <c r="F14" t="n">
-        <v>41.84</v>
+        <v>-28.9</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0167</v>
+        <v>-0.0113</v>
       </c>
       <c r="H14" t="n">
-        <v>49.5</v>
+        <v>63.4</v>
       </c>
       <c r="I14" t="n">
-        <v>2401.5</v>
+        <v>2491.3</v>
       </c>
       <c r="J14" t="n">
-        <v>2409.76</v>
+        <v>2494.82</v>
       </c>
       <c r="K14" t="n">
-        <v>2465.61</v>
+        <v>2526.65</v>
       </c>
       <c r="L14" t="n">
-        <v>2521.46</v>
+        <v>2558.47</v>
       </c>
       <c r="M14" t="n">
-        <v>2553.51</v>
+        <v>2576.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2585.57</v>
+        <v>2593.82</v>
       </c>
       <c r="O14" t="n">
-        <v>2665.2</v>
+        <v>2639.8</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2551.6</v>
+        <v>2524.2</v>
       </c>
       <c r="C15" t="n">
-        <v>2556.9</v>
+        <v>2650.3</v>
       </c>
       <c r="D15" t="n">
-        <v>2493.5</v>
+        <v>2517.2</v>
       </c>
       <c r="E15" t="n">
-        <v>2522.5</v>
+        <v>2636.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-28.9</v>
+        <v>114.4</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0113</v>
+        <v>0.0454</v>
       </c>
       <c r="H15" t="n">
-        <v>63.4</v>
+        <v>133.1</v>
       </c>
       <c r="I15" t="n">
-        <v>2491.3</v>
+        <v>2430.1</v>
       </c>
       <c r="J15" t="n">
-        <v>2494.82</v>
+        <v>2457.75</v>
       </c>
       <c r="K15" t="n">
-        <v>2526.65</v>
+        <v>2490.8</v>
       </c>
       <c r="L15" t="n">
-        <v>2558.47</v>
+        <v>2523.85</v>
       </c>
       <c r="M15" t="n">
-        <v>2576.15</v>
+        <v>2554.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2593.82</v>
+        <v>2584.55</v>
       </c>
       <c r="O15" t="n">
-        <v>2639.8</v>
+        <v>2620.3</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2524.2</v>
+        <v>2638.9</v>
       </c>
       <c r="C16" t="n">
-        <v>2650.3</v>
+        <v>2705.6</v>
       </c>
       <c r="D16" t="n">
-        <v>2517.2</v>
+        <v>2616.3</v>
       </c>
       <c r="E16" t="n">
-        <v>2636.9</v>
+        <v>2691.2</v>
       </c>
       <c r="F16" t="n">
-        <v>114.4</v>
+        <v>54.3</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0454</v>
+        <v>0.0206</v>
       </c>
       <c r="H16" t="n">
-        <v>133.1</v>
+        <v>89.3</v>
       </c>
       <c r="I16" t="n">
-        <v>2430.1</v>
+        <v>2384.1</v>
       </c>
       <c r="J16" t="n">
-        <v>2457.75</v>
+        <v>2530.37</v>
       </c>
       <c r="K16" t="n">
-        <v>2490.8</v>
+        <v>2570.35</v>
       </c>
       <c r="L16" t="n">
-        <v>2523.85</v>
+        <v>2610.32</v>
       </c>
       <c r="M16" t="n">
-        <v>2554.2</v>
+        <v>2703.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2584.55</v>
+        <v>2796.57</v>
       </c>
       <c r="O16" t="n">
-        <v>2620.3</v>
+        <v>2783.4</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1850,27 +1846,23 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1880,50 +1872,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2638.9</v>
+        <v>2670</v>
       </c>
       <c r="C17" t="n">
-        <v>2705.6</v>
+        <v>2749.2</v>
       </c>
       <c r="D17" t="n">
-        <v>2616.3</v>
+        <v>2631</v>
       </c>
       <c r="E17" t="n">
-        <v>2691.2</v>
+        <v>2679.6</v>
       </c>
       <c r="F17" t="n">
-        <v>54.3</v>
+        <v>-11.6</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0206</v>
+        <v>-0.0043</v>
       </c>
       <c r="H17" t="n">
-        <v>89.3</v>
+        <v>118.2</v>
       </c>
       <c r="I17" t="n">
-        <v>2384.1</v>
+        <v>2527</v>
       </c>
       <c r="J17" t="n">
-        <v>2530.37</v>
+        <v>2617.02</v>
       </c>
       <c r="K17" t="n">
-        <v>2570.35</v>
+        <v>2646.55</v>
       </c>
       <c r="L17" t="n">
-        <v>2610.32</v>
+        <v>2676.08</v>
       </c>
       <c r="M17" t="n">
-        <v>2703.45</v>
+        <v>2735.85</v>
       </c>
       <c r="N17" t="n">
-        <v>2796.57</v>
+        <v>2795.62</v>
       </c>
       <c r="O17" t="n">
-        <v>2783.4</v>
+        <v>2794.9</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1931,17 +1923,19 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U17" s="8" t="n">
@@ -1950,60 +1944,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2670</v>
+        <v>2661</v>
       </c>
       <c r="C18" t="n">
-        <v>2749.2</v>
+        <v>2697.9</v>
       </c>
       <c r="D18" t="n">
-        <v>2631</v>
+        <v>2607.5</v>
       </c>
       <c r="E18" t="n">
-        <v>2679.6</v>
+        <v>2624.6</v>
       </c>
       <c r="F18" t="n">
-        <v>-11.6</v>
+        <v>-55</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0205</v>
       </c>
       <c r="H18" t="n">
-        <v>118.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>2527</v>
+        <v>2512.8</v>
       </c>
       <c r="J18" t="n">
-        <v>2617.02</v>
+        <v>2556.15</v>
       </c>
       <c r="K18" t="n">
-        <v>2646.55</v>
+        <v>2620.5</v>
       </c>
       <c r="L18" t="n">
-        <v>2676.08</v>
+        <v>2684.85</v>
       </c>
       <c r="M18" t="n">
-        <v>2735.85</v>
+        <v>2738.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2795.62</v>
+        <v>2792.55</v>
       </c>
       <c r="O18" t="n">
-        <v>2794.9</v>
+        <v>2867.4</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2013,18 +2011,16 @@
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2032,64 +2028,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2661</v>
+        <v>2615</v>
       </c>
       <c r="C19" t="n">
-        <v>2697.9</v>
+        <v>2684.1</v>
       </c>
       <c r="D19" t="n">
-        <v>2607.5</v>
+        <v>2566.8</v>
       </c>
       <c r="E19" t="n">
-        <v>2624.6</v>
+        <v>2677.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-55</v>
+        <v>53.3</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0205</v>
+        <v>0.0203</v>
       </c>
       <c r="H19" t="n">
-        <v>90.40000000000001</v>
+        <v>117.3</v>
       </c>
       <c r="I19" t="n">
-        <v>2512.8</v>
+        <v>2517.1</v>
       </c>
       <c r="J19" t="n">
-        <v>2556.15</v>
+        <v>2520.15</v>
       </c>
       <c r="K19" t="n">
-        <v>2620.5</v>
+        <v>2579.4</v>
       </c>
       <c r="L19" t="n">
-        <v>2684.85</v>
+        <v>2638.65</v>
       </c>
       <c r="M19" t="n">
-        <v>2738.7</v>
+        <v>2669.8</v>
       </c>
       <c r="N19" t="n">
-        <v>2792.55</v>
+        <v>2700.95</v>
       </c>
       <c r="O19" t="n">
-        <v>2867.4</v>
+        <v>2788.3</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2099,81 +2095,83 @@
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2615</v>
+        <v>2677</v>
       </c>
       <c r="C20" t="n">
-        <v>2684.1</v>
+        <v>2720</v>
       </c>
       <c r="D20" t="n">
-        <v>2566.8</v>
+        <v>2607.3</v>
       </c>
       <c r="E20" t="n">
-        <v>2677.9</v>
+        <v>2653.1</v>
       </c>
       <c r="F20" t="n">
-        <v>53.3</v>
+        <v>-24.8</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0203</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>117.3</v>
+        <v>112.7</v>
       </c>
       <c r="I20" t="n">
-        <v>2517.1</v>
+        <v>2449.5</v>
       </c>
       <c r="J20" t="n">
-        <v>2520.15</v>
+        <v>2586.82</v>
       </c>
       <c r="K20" t="n">
-        <v>2579.4</v>
+        <v>2619.25</v>
       </c>
       <c r="L20" t="n">
-        <v>2638.65</v>
+        <v>2651.67</v>
       </c>
       <c r="M20" t="n">
-        <v>2669.8</v>
+        <v>2736.55</v>
       </c>
       <c r="N20" t="n">
-        <v>2700.95</v>
+        <v>2821.42</v>
       </c>
       <c r="O20" t="n">
-        <v>2788.3</v>
+        <v>2801.4</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2186,15 +2184,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2202,64 +2198,64 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2677</v>
+        <v>2650.9</v>
       </c>
       <c r="C21" t="n">
-        <v>2720</v>
+        <v>2696</v>
       </c>
       <c r="D21" t="n">
-        <v>2607.3</v>
+        <v>2613.7</v>
       </c>
       <c r="E21" t="n">
-        <v>2653.1</v>
+        <v>2668.8</v>
       </c>
       <c r="F21" t="n">
-        <v>-24.8</v>
+        <v>15.7</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H21" t="n">
-        <v>112.7</v>
+        <v>82.3</v>
       </c>
       <c r="I21" t="n">
-        <v>2449.5</v>
+        <v>2494.6</v>
       </c>
       <c r="J21" t="n">
-        <v>2586.82</v>
+        <v>2535.13</v>
       </c>
       <c r="K21" t="n">
-        <v>2619.25</v>
+        <v>2596.75</v>
       </c>
       <c r="L21" t="n">
-        <v>2651.67</v>
+        <v>2658.38</v>
       </c>
       <c r="M21" t="n">
-        <v>2736.55</v>
+        <v>2709.45</v>
       </c>
       <c r="N21" t="n">
-        <v>2821.42</v>
+        <v>2760.53</v>
       </c>
       <c r="O21" t="n">
-        <v>2801.4</v>
+        <v>2832.7</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2267,12 +2263,10 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2286,7 +2280,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2300,50 +2294,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2650.9</v>
+        <v>2666.5</v>
       </c>
       <c r="C22" t="n">
-        <v>2696</v>
+        <v>2683.4</v>
       </c>
       <c r="D22" t="n">
-        <v>2613.7</v>
+        <v>2602.7</v>
       </c>
       <c r="E22" t="n">
-        <v>2668.8</v>
+        <v>2634.7</v>
       </c>
       <c r="F22" t="n">
-        <v>15.7</v>
+        <v>-34.1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0128</v>
       </c>
       <c r="H22" t="n">
-        <v>82.3</v>
+        <v>80.7</v>
       </c>
       <c r="I22" t="n">
-        <v>2494.6</v>
+        <v>2531.4</v>
       </c>
       <c r="J22" t="n">
-        <v>2535.13</v>
+        <v>2593.48</v>
       </c>
       <c r="K22" t="n">
-        <v>2596.75</v>
+        <v>2627.65</v>
       </c>
       <c r="L22" t="n">
-        <v>2658.38</v>
+        <v>2661.83</v>
       </c>
       <c r="M22" t="n">
-        <v>2709.45</v>
+        <v>2709.95</v>
       </c>
       <c r="N22" t="n">
-        <v>2760.53</v>
+        <v>2758.08</v>
       </c>
       <c r="O22" t="n">
-        <v>2832.7</v>
+        <v>2778.3</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2351,12 +2345,14 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2368,77 +2364,81 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2666.5</v>
+        <v>2608.8</v>
       </c>
       <c r="C23" t="n">
-        <v>2683.4</v>
+        <v>2663.3</v>
       </c>
       <c r="D23" t="n">
-        <v>2602.7</v>
+        <v>2516.6</v>
       </c>
       <c r="E23" t="n">
-        <v>2634.7</v>
+        <v>2526.7</v>
       </c>
       <c r="F23" t="n">
-        <v>-34.1</v>
+        <v>-108</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0128</v>
+        <v>-0.041</v>
       </c>
       <c r="H23" t="n">
-        <v>80.7</v>
+        <v>146.7</v>
       </c>
       <c r="I23" t="n">
-        <v>2531.4</v>
+        <v>2522</v>
       </c>
       <c r="J23" t="n">
-        <v>2593.48</v>
+        <v>2549.83</v>
       </c>
       <c r="K23" t="n">
-        <v>2627.65</v>
+        <v>2594.35</v>
       </c>
       <c r="L23" t="n">
-        <v>2661.83</v>
+        <v>2638.87</v>
       </c>
       <c r="M23" t="n">
-        <v>2709.95</v>
+        <v>2675.05</v>
       </c>
       <c r="N23" t="n">
-        <v>2758.08</v>
+        <v>2711.22</v>
       </c>
       <c r="O23" t="n">
-        <v>2778.3</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+        <v>2764.1</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2454,79 +2454,71 @@
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2608.8</v>
+        <v>2499.2</v>
       </c>
       <c r="C24" t="n">
-        <v>2663.3</v>
+        <v>2594.4</v>
       </c>
       <c r="D24" t="n">
-        <v>2516.6</v>
+        <v>2416.9</v>
       </c>
       <c r="E24" t="n">
-        <v>2526.7</v>
+        <v>2480.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-108</v>
+        <v>-45.8</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.041</v>
+        <v>-0.0181</v>
       </c>
       <c r="H24" t="n">
-        <v>146.7</v>
+        <v>177.5</v>
       </c>
       <c r="I24" t="n">
-        <v>2522</v>
+        <v>2369.9</v>
       </c>
       <c r="J24" t="n">
-        <v>2549.83</v>
+        <v>2348.37</v>
       </c>
       <c r="K24" t="n">
-        <v>2594.35</v>
+        <v>2453.35</v>
       </c>
       <c r="L24" t="n">
-        <v>2638.87</v>
+        <v>2558.33</v>
       </c>
       <c r="M24" t="n">
-        <v>2675.05</v>
+        <v>2600.05</v>
       </c>
       <c r="N24" t="n">
-        <v>2711.22</v>
+        <v>2641.77</v>
       </c>
       <c r="O24" t="n">
-        <v>2764.1</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>2810</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2540,7 +2532,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2550,50 +2542,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2499.2</v>
+        <v>2468.5</v>
       </c>
       <c r="C25" t="n">
-        <v>2594.4</v>
+        <v>2547.9</v>
       </c>
       <c r="D25" t="n">
-        <v>2416.9</v>
+        <v>2442</v>
       </c>
       <c r="E25" t="n">
-        <v>2480.9</v>
+        <v>2496.4</v>
       </c>
       <c r="F25" t="n">
-        <v>-45.8</v>
+        <v>15.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0181</v>
+        <v>0.0062</v>
       </c>
       <c r="H25" t="n">
-        <v>177.5</v>
+        <v>105.9</v>
       </c>
       <c r="I25" t="n">
-        <v>2369.9</v>
+        <v>2239.4</v>
       </c>
       <c r="J25" t="n">
-        <v>2348.37</v>
+        <v>2291.02</v>
       </c>
       <c r="K25" t="n">
-        <v>2453.35</v>
+        <v>2392.15</v>
       </c>
       <c r="L25" t="n">
-        <v>2558.33</v>
+        <v>2493.27</v>
       </c>
       <c r="M25" t="n">
-        <v>2600.05</v>
+        <v>2569.65</v>
       </c>
       <c r="N25" t="n">
-        <v>2641.77</v>
+        <v>2646.02</v>
       </c>
       <c r="O25" t="n">
-        <v>2810</v>
+        <v>2771.9</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2601,14 +2593,12 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2620,60 +2610,64 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2468.5</v>
+        <v>2429.1</v>
       </c>
       <c r="C26" t="n">
-        <v>2547.9</v>
+        <v>2574.5</v>
       </c>
       <c r="D26" t="n">
-        <v>2442</v>
+        <v>2415.3</v>
       </c>
       <c r="E26" t="n">
-        <v>2496.4</v>
+        <v>2464</v>
       </c>
       <c r="F26" t="n">
-        <v>15.5</v>
+        <v>-32.4</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.013</v>
       </c>
       <c r="H26" t="n">
-        <v>105.9</v>
+        <v>159.2</v>
       </c>
       <c r="I26" t="n">
-        <v>2239.4</v>
+        <v>2336.1</v>
       </c>
       <c r="J26" t="n">
-        <v>2291.02</v>
+        <v>2391.22</v>
       </c>
       <c r="K26" t="n">
-        <v>2392.15</v>
+        <v>2443.45</v>
       </c>
       <c r="L26" t="n">
-        <v>2493.27</v>
+        <v>2495.67</v>
       </c>
       <c r="M26" t="n">
-        <v>2569.65</v>
+        <v>2549.35</v>
       </c>
       <c r="N26" t="n">
-        <v>2646.02</v>
+        <v>2603.02</v>
       </c>
       <c r="O26" t="n">
-        <v>2771.9</v>
+        <v>2653.8</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2681,16 +2675,20 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2698,64 +2696,64 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2429.1</v>
+        <v>2445</v>
       </c>
       <c r="C27" t="n">
-        <v>2574.5</v>
+        <v>2557</v>
       </c>
       <c r="D27" t="n">
-        <v>2415.3</v>
+        <v>2409.4</v>
       </c>
       <c r="E27" t="n">
-        <v>2464</v>
+        <v>2531.7</v>
       </c>
       <c r="F27" t="n">
-        <v>-32.4</v>
+        <v>67.7</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.013</v>
+        <v>0.0275</v>
       </c>
       <c r="H27" t="n">
-        <v>159.2</v>
+        <v>147.6</v>
       </c>
       <c r="I27" t="n">
-        <v>2336.1</v>
+        <v>2256.1</v>
       </c>
       <c r="J27" t="n">
-        <v>2391.22</v>
+        <v>2289.35</v>
       </c>
       <c r="K27" t="n">
-        <v>2443.45</v>
+        <v>2384.4</v>
       </c>
       <c r="L27" t="n">
-        <v>2495.67</v>
+        <v>2479.45</v>
       </c>
       <c r="M27" t="n">
-        <v>2549.35</v>
+        <v>2543.6</v>
       </c>
       <c r="N27" t="n">
-        <v>2603.02</v>
+        <v>2607.75</v>
       </c>
       <c r="O27" t="n">
-        <v>2653.8</v>
+        <v>2733.7</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2763,28 +2761,26 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2798,50 +2794,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2445</v>
+        <v>2527.9</v>
       </c>
       <c r="C28" t="n">
-        <v>2557</v>
+        <v>2674.5</v>
       </c>
       <c r="D28" t="n">
-        <v>2409.4</v>
+        <v>2511.4</v>
       </c>
       <c r="E28" t="n">
-        <v>2531.7</v>
+        <v>2644.4</v>
       </c>
       <c r="F28" t="n">
-        <v>67.7</v>
+        <v>112.7</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0445</v>
       </c>
       <c r="H28" t="n">
-        <v>147.6</v>
+        <v>163.1</v>
       </c>
       <c r="I28" t="n">
-        <v>2256.1</v>
+        <v>2261.8</v>
       </c>
       <c r="J28" t="n">
-        <v>2289.35</v>
+        <v>2408.35</v>
       </c>
       <c r="K28" t="n">
-        <v>2384.4</v>
+        <v>2457.9</v>
       </c>
       <c r="L28" t="n">
-        <v>2479.45</v>
+        <v>2507.45</v>
       </c>
       <c r="M28" t="n">
-        <v>2543.6</v>
+        <v>2605.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2607.75</v>
+        <v>2703.55</v>
       </c>
       <c r="O28" t="n">
-        <v>2733.7</v>
+        <v>2704.6</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2852,7 +2848,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2868,64 +2864,64 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2527.9</v>
+        <v>2607.8</v>
       </c>
       <c r="C29" t="n">
-        <v>2674.5</v>
+        <v>2807.8</v>
       </c>
       <c r="D29" t="n">
-        <v>2511.4</v>
+        <v>2591.8</v>
       </c>
       <c r="E29" t="n">
-        <v>2644.4</v>
+        <v>2788.9</v>
       </c>
       <c r="F29" t="n">
-        <v>112.7</v>
+        <v>144.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0445</v>
+        <v>0.0546</v>
       </c>
       <c r="H29" t="n">
-        <v>163.1</v>
+        <v>216</v>
       </c>
       <c r="I29" t="n">
-        <v>2261.8</v>
+        <v>2348.3</v>
       </c>
       <c r="J29" t="n">
-        <v>2408.35</v>
+        <v>2507.02</v>
       </c>
       <c r="K29" t="n">
-        <v>2457.9</v>
+        <v>2562.85</v>
       </c>
       <c r="L29" t="n">
-        <v>2507.45</v>
+        <v>2618.67</v>
       </c>
       <c r="M29" t="n">
-        <v>2605.5</v>
+        <v>2725.95</v>
       </c>
       <c r="N29" t="n">
-        <v>2703.55</v>
+        <v>2833.22</v>
       </c>
       <c r="O29" t="n">
-        <v>2704.6</v>
+        <v>2837.6</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2936,23 +2932,25 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2966,50 +2964,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2607.8</v>
+        <v>2758.7</v>
       </c>
       <c r="C30" t="n">
-        <v>2807.8</v>
+        <v>2828.7</v>
       </c>
       <c r="D30" t="n">
-        <v>2591.8</v>
+        <v>2745.9</v>
       </c>
       <c r="E30" t="n">
-        <v>2788.9</v>
+        <v>2796.1</v>
       </c>
       <c r="F30" t="n">
-        <v>144.5</v>
+        <v>7.2</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0026</v>
       </c>
       <c r="H30" t="n">
-        <v>216</v>
+        <v>82.8</v>
       </c>
       <c r="I30" t="n">
-        <v>2348.3</v>
+        <v>2375.8</v>
       </c>
       <c r="J30" t="n">
-        <v>2507.02</v>
+        <v>2617.45</v>
       </c>
       <c r="K30" t="n">
-        <v>2562.85</v>
+        <v>2680.9</v>
       </c>
       <c r="L30" t="n">
-        <v>2618.67</v>
+        <v>2744.35</v>
       </c>
       <c r="M30" t="n">
-        <v>2725.95</v>
+        <v>2896.9</v>
       </c>
       <c r="N30" t="n">
-        <v>2833.22</v>
+        <v>3049.45</v>
       </c>
       <c r="O30" t="n">
-        <v>2837.6</v>
+        <v>3023.8</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3020,25 +3018,21 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3052,50 +3046,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2758.7</v>
+        <v>2792.7</v>
       </c>
       <c r="C31" t="n">
-        <v>2828.7</v>
+        <v>2825</v>
       </c>
       <c r="D31" t="n">
-        <v>2745.9</v>
+        <v>2726.1</v>
       </c>
       <c r="E31" t="n">
-        <v>2796.1</v>
+        <v>2819.3</v>
       </c>
       <c r="F31" t="n">
-        <v>7.2</v>
+        <v>23.2</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0083</v>
       </c>
       <c r="H31" t="n">
-        <v>82.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>2375.8</v>
+        <v>2663.1</v>
       </c>
       <c r="J31" t="n">
-        <v>2617.45</v>
+        <v>2717.7</v>
       </c>
       <c r="K31" t="n">
-        <v>2680.9</v>
+        <v>2754.7</v>
       </c>
       <c r="L31" t="n">
-        <v>2744.35</v>
+        <v>2791.7</v>
       </c>
       <c r="M31" t="n">
-        <v>2896.9</v>
+        <v>2837.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3049.45</v>
+        <v>2883.3</v>
       </c>
       <c r="O31" t="n">
-        <v>3023.8</v>
+        <v>2911.5</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3103,16 +3097,20 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3120,64 +3118,64 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2792.7</v>
+        <v>2825.9</v>
       </c>
       <c r="C32" t="n">
-        <v>2825</v>
+        <v>2918.4</v>
       </c>
       <c r="D32" t="n">
-        <v>2726.1</v>
+        <v>2786.8</v>
       </c>
       <c r="E32" t="n">
-        <v>2819.3</v>
+        <v>2867.6</v>
       </c>
       <c r="F32" t="n">
-        <v>23.2</v>
+        <v>48.3</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0171</v>
       </c>
       <c r="H32" t="n">
-        <v>98.90000000000001</v>
+        <v>131.6</v>
       </c>
       <c r="I32" t="n">
-        <v>2663.1</v>
+        <v>2627.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2717.7</v>
+        <v>2742.28</v>
       </c>
       <c r="K32" t="n">
-        <v>2754.7</v>
+        <v>2769.85</v>
       </c>
       <c r="L32" t="n">
-        <v>2791.7</v>
+        <v>2797.43</v>
       </c>
       <c r="M32" t="n">
-        <v>2837.5</v>
+        <v>2868.75</v>
       </c>
       <c r="N32" t="n">
-        <v>2883.3</v>
+        <v>2940.07</v>
       </c>
       <c r="O32" t="n">
-        <v>2911.5</v>
+        <v>2923.9</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3185,12 +3183,10 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3206,64 +3202,64 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2825.9</v>
+        <v>2863</v>
       </c>
       <c r="C33" t="n">
-        <v>2918.4</v>
+        <v>2896.2</v>
       </c>
       <c r="D33" t="n">
-        <v>2786.8</v>
+        <v>2787.9</v>
       </c>
       <c r="E33" t="n">
-        <v>2867.6</v>
+        <v>2799.6</v>
       </c>
       <c r="F33" t="n">
-        <v>48.3</v>
+        <v>-68</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0171</v>
+        <v>-0.0237</v>
       </c>
       <c r="H33" t="n">
-        <v>131.6</v>
+        <v>108.3</v>
       </c>
       <c r="I33" t="n">
-        <v>2627.2</v>
+        <v>2655.2</v>
       </c>
       <c r="J33" t="n">
-        <v>2742.28</v>
+        <v>2743.5</v>
       </c>
       <c r="K33" t="n">
-        <v>2769.85</v>
+        <v>2801.8</v>
       </c>
       <c r="L33" t="n">
-        <v>2797.43</v>
+        <v>2860.1</v>
       </c>
       <c r="M33" t="n">
-        <v>2868.75</v>
+        <v>2933.4</v>
       </c>
       <c r="N33" t="n">
-        <v>2940.07</v>
+        <v>3006.7</v>
       </c>
       <c r="O33" t="n">
-        <v>2923.9</v>
+        <v>3050</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3271,18 +3267,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3290,64 +3286,64 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2863</v>
+        <v>2788.8</v>
       </c>
       <c r="C34" t="n">
-        <v>2896.2</v>
+        <v>2887</v>
       </c>
       <c r="D34" t="n">
-        <v>2787.9</v>
+        <v>2728.4</v>
       </c>
       <c r="E34" t="n">
-        <v>2799.6</v>
+        <v>2872.1</v>
       </c>
       <c r="F34" t="n">
-        <v>-68</v>
+        <v>72.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0259</v>
       </c>
       <c r="H34" t="n">
-        <v>108.3</v>
+        <v>158.6</v>
       </c>
       <c r="I34" t="n">
-        <v>2655.2</v>
+        <v>2679.6</v>
       </c>
       <c r="J34" t="n">
-        <v>2743.5</v>
+        <v>2670.08</v>
       </c>
       <c r="K34" t="n">
-        <v>2801.8</v>
+        <v>2745.45</v>
       </c>
       <c r="L34" t="n">
-        <v>2860.1</v>
+        <v>2820.83</v>
       </c>
       <c r="M34" t="n">
-        <v>2933.4</v>
+        <v>2853.75</v>
       </c>
       <c r="N34" t="n">
-        <v>3006.7</v>
+        <v>2886.68</v>
       </c>
       <c r="O34" t="n">
-        <v>3050</v>
+        <v>3004.5</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3357,24 +3353,28 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3388,50 +3388,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2788.8</v>
+        <v>2888</v>
       </c>
       <c r="C35" t="n">
-        <v>2887</v>
+        <v>2952</v>
       </c>
       <c r="D35" t="n">
-        <v>2728.4</v>
+        <v>2887.9</v>
       </c>
       <c r="E35" t="n">
-        <v>2872.1</v>
+        <v>2924.3</v>
       </c>
       <c r="F35" t="n">
-        <v>72.5</v>
+        <v>52.2</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0259</v>
+        <v>0.0182</v>
       </c>
       <c r="H35" t="n">
-        <v>158.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>2679.6</v>
+        <v>2569.8</v>
       </c>
       <c r="J35" t="n">
-        <v>2670.08</v>
+        <v>2745.7</v>
       </c>
       <c r="K35" t="n">
-        <v>2745.45</v>
+        <v>2792.8</v>
       </c>
       <c r="L35" t="n">
-        <v>2820.83</v>
+        <v>2839.9</v>
       </c>
       <c r="M35" t="n">
-        <v>2853.75</v>
+        <v>2951.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2886.68</v>
+        <v>3062.9</v>
       </c>
       <c r="O35" t="n">
-        <v>3004.5</v>
+        <v>3045.6</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3439,106 +3439,106 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2888</v>
+        <v>2920.5</v>
       </c>
       <c r="C36" t="n">
-        <v>2952</v>
+        <v>2948.3</v>
       </c>
       <c r="D36" t="n">
-        <v>2887.9</v>
+        <v>2812.4</v>
       </c>
       <c r="E36" t="n">
-        <v>2924.3</v>
+        <v>2834.8</v>
       </c>
       <c r="F36" t="n">
-        <v>52.2</v>
+        <v>-89.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0182</v>
+        <v>-0.0306</v>
       </c>
       <c r="H36" t="n">
-        <v>64.09999999999999</v>
+        <v>135.9</v>
       </c>
       <c r="I36" t="n">
-        <v>2569.8</v>
+        <v>2823.8</v>
       </c>
       <c r="J36" t="n">
-        <v>2745.7</v>
+        <v>2862.38</v>
       </c>
       <c r="K36" t="n">
-        <v>2792.8</v>
+        <v>2892.25</v>
       </c>
       <c r="L36" t="n">
-        <v>2839.9</v>
+        <v>2922.12</v>
       </c>
       <c r="M36" t="n">
-        <v>2951.4</v>
+        <v>2956.35</v>
       </c>
       <c r="N36" t="n">
-        <v>3062.9</v>
+        <v>2990.58</v>
       </c>
       <c r="O36" t="n">
-        <v>3045.6</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+        <v>3016.1</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3546,148 +3546,146 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2920.5</v>
+        <v>2816.3</v>
       </c>
       <c r="C37" t="n">
-        <v>2948.3</v>
+        <v>2974.2</v>
       </c>
       <c r="D37" t="n">
-        <v>2812.4</v>
+        <v>2793.7</v>
       </c>
       <c r="E37" t="n">
-        <v>2834.8</v>
+        <v>2947</v>
       </c>
       <c r="F37" t="n">
-        <v>-89.5</v>
+        <v>112.2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0306</v>
+        <v>0.0396</v>
       </c>
       <c r="H37" t="n">
-        <v>135.9</v>
+        <v>180.5</v>
       </c>
       <c r="I37" t="n">
-        <v>2823.8</v>
+        <v>2676.5</v>
       </c>
       <c r="J37" t="n">
-        <v>2862.38</v>
+        <v>2676.12</v>
       </c>
       <c r="K37" t="n">
-        <v>2892.25</v>
+        <v>2766.85</v>
       </c>
       <c r="L37" t="n">
-        <v>2922.12</v>
+        <v>2857.58</v>
       </c>
       <c r="M37" t="n">
-        <v>2956.35</v>
+        <v>2902.75</v>
       </c>
       <c r="N37" t="n">
-        <v>2990.58</v>
+        <v>2947.93</v>
       </c>
       <c r="O37" t="n">
-        <v>3016.1</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
+        <v>3084.2</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2816.3</v>
+        <v>2984</v>
       </c>
       <c r="C38" t="n">
-        <v>2974.2</v>
+        <v>3005</v>
       </c>
       <c r="D38" t="n">
-        <v>2793.7</v>
+        <v>2910.3</v>
       </c>
       <c r="E38" t="n">
-        <v>2947</v>
+        <v>2995.6</v>
       </c>
       <c r="F38" t="n">
-        <v>112.2</v>
+        <v>48.6</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.0165</v>
       </c>
       <c r="H38" t="n">
-        <v>180.5</v>
+        <v>94.7</v>
       </c>
       <c r="I38" t="n">
-        <v>2676.5</v>
+        <v>2613.2</v>
       </c>
       <c r="J38" t="n">
-        <v>2676.12</v>
+        <v>2798.03</v>
       </c>
       <c r="K38" t="n">
-        <v>2766.85</v>
+        <v>2856.75</v>
       </c>
       <c r="L38" t="n">
-        <v>2857.58</v>
+        <v>2915.47</v>
       </c>
       <c r="M38" t="n">
-        <v>2902.75</v>
+        <v>3037.25</v>
       </c>
       <c r="N38" t="n">
-        <v>2947.93</v>
+        <v>3159.03</v>
       </c>
       <c r="O38" t="n">
-        <v>3084.2</v>
+        <v>3154.7</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3698,82 +3696,80 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2984</v>
+        <v>2989.9</v>
       </c>
       <c r="C39" t="n">
-        <v>3005</v>
+        <v>3062.4</v>
       </c>
       <c r="D39" t="n">
-        <v>2910.3</v>
+        <v>2965.2</v>
       </c>
       <c r="E39" t="n">
-        <v>2995.6</v>
+        <v>3022.6</v>
       </c>
       <c r="F39" t="n">
-        <v>48.6</v>
+        <v>27</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>94.7</v>
+        <v>97.2</v>
       </c>
       <c r="I39" t="n">
-        <v>2613.2</v>
+        <v>2815.6</v>
       </c>
       <c r="J39" t="n">
-        <v>2798.03</v>
+        <v>2919.88</v>
       </c>
       <c r="K39" t="n">
-        <v>2856.75</v>
+        <v>2948.25</v>
       </c>
       <c r="L39" t="n">
-        <v>2915.47</v>
+        <v>2976.63</v>
       </c>
       <c r="M39" t="n">
-        <v>3037.25</v>
+        <v>3042.95</v>
       </c>
       <c r="N39" t="n">
-        <v>3159.03</v>
+        <v>3109.28</v>
       </c>
       <c r="O39" t="n">
-        <v>3154.7</v>
+        <v>3099.7</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3784,7 +3780,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3800,7 +3796,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3814,50 +3810,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2989.9</v>
+        <v>3020.9</v>
       </c>
       <c r="C40" t="n">
-        <v>3062.4</v>
+        <v>3068.4</v>
       </c>
       <c r="D40" t="n">
-        <v>2965.2</v>
+        <v>2987.8</v>
       </c>
       <c r="E40" t="n">
-        <v>3022.6</v>
+        <v>3023.5</v>
       </c>
       <c r="F40" t="n">
-        <v>27</v>
+        <v>0.9</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0003</v>
       </c>
       <c r="H40" t="n">
-        <v>97.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>2815.6</v>
+        <v>2868</v>
       </c>
       <c r="J40" t="n">
-        <v>2919.88</v>
+        <v>2929.8</v>
       </c>
       <c r="K40" t="n">
-        <v>2948.25</v>
+        <v>2974</v>
       </c>
       <c r="L40" t="n">
-        <v>2976.63</v>
+        <v>3018.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3042.95</v>
+        <v>3071.2</v>
       </c>
       <c r="N40" t="n">
-        <v>3109.28</v>
+        <v>3124.2</v>
       </c>
       <c r="O40" t="n">
-        <v>3099.7</v>
+        <v>3159.6</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3868,15 +3864,13 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3884,7 +3878,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3898,50 +3892,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3020.9</v>
+        <v>3019.7</v>
       </c>
       <c r="C41" t="n">
-        <v>3068.4</v>
+        <v>3042.6</v>
       </c>
       <c r="D41" t="n">
-        <v>2987.8</v>
+        <v>2943.4</v>
       </c>
       <c r="E41" t="n">
-        <v>3023.5</v>
+        <v>2994</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9</v>
+        <v>-29.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0003</v>
+        <v>-0.0098</v>
       </c>
       <c r="H41" t="n">
-        <v>80.59999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="I41" t="n">
-        <v>2868</v>
+        <v>2907.2</v>
       </c>
       <c r="J41" t="n">
-        <v>2929.8</v>
+        <v>2940.6</v>
       </c>
       <c r="K41" t="n">
-        <v>2974</v>
+        <v>2983.2</v>
       </c>
       <c r="L41" t="n">
-        <v>3018.2</v>
+        <v>3025.8</v>
       </c>
       <c r="M41" t="n">
-        <v>3071.2</v>
+        <v>3063.8</v>
       </c>
       <c r="N41" t="n">
-        <v>3124.2</v>
+        <v>3101.8</v>
       </c>
       <c r="O41" t="n">
-        <v>3159.6</v>
+        <v>3149</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3949,12 +3943,14 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3966,64 +3962,60 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3019.7</v>
+        <v>2984.7</v>
       </c>
       <c r="C42" t="n">
-        <v>3042.6</v>
+        <v>3029.8</v>
       </c>
       <c r="D42" t="n">
-        <v>2943.4</v>
+        <v>2949.3</v>
       </c>
       <c r="E42" t="n">
-        <v>2994</v>
+        <v>2973.5</v>
       </c>
       <c r="F42" t="n">
-        <v>-29.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0068</v>
       </c>
       <c r="H42" t="n">
-        <v>99.2</v>
+        <v>80.5</v>
       </c>
       <c r="I42" t="n">
-        <v>2907.2</v>
+        <v>2844.2</v>
       </c>
       <c r="J42" t="n">
-        <v>2940.6</v>
+        <v>2895.3</v>
       </c>
       <c r="K42" t="n">
-        <v>2983.2</v>
+        <v>2944.4</v>
       </c>
       <c r="L42" t="n">
-        <v>3025.8</v>
+        <v>2993.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3063.8</v>
+        <v>3043.6</v>
       </c>
       <c r="N42" t="n">
-        <v>3101.8</v>
+        <v>3093.7</v>
       </c>
       <c r="O42" t="n">
-        <v>3149</v>
+        <v>3141.8</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4031,14 +4023,12 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4050,60 +4040,64 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2984.7</v>
+        <v>2964.5</v>
       </c>
       <c r="C43" t="n">
-        <v>3029.8</v>
+        <v>2999.8</v>
       </c>
       <c r="D43" t="n">
-        <v>2949.3</v>
+        <v>2932.1</v>
       </c>
       <c r="E43" t="n">
-        <v>2973.5</v>
+        <v>2941.3</v>
       </c>
       <c r="F43" t="n">
-        <v>-20.5</v>
+        <v>-32.2</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0068</v>
+        <v>-0.0108</v>
       </c>
       <c r="H43" t="n">
-        <v>80.5</v>
+        <v>67.7</v>
       </c>
       <c r="I43" t="n">
-        <v>2844.2</v>
+        <v>2868.8</v>
       </c>
       <c r="J43" t="n">
-        <v>2895.3</v>
+        <v>2884.97</v>
       </c>
       <c r="K43" t="n">
-        <v>2944.4</v>
+        <v>2933.25</v>
       </c>
       <c r="L43" t="n">
-        <v>2993.5</v>
+        <v>2981.53</v>
       </c>
       <c r="M43" t="n">
-        <v>3043.6</v>
+        <v>3013.75</v>
       </c>
       <c r="N43" t="n">
-        <v>3093.7</v>
+        <v>3045.97</v>
       </c>
       <c r="O43" t="n">
-        <v>3141.8</v>
+        <v>3110.3</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4111,12 +4105,14 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4128,64 +4124,60 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2964.5</v>
+        <v>2955.5</v>
       </c>
       <c r="C44" t="n">
-        <v>2999.8</v>
+        <v>2985.9</v>
       </c>
       <c r="D44" t="n">
-        <v>2932.1</v>
+        <v>2902.3</v>
       </c>
       <c r="E44" t="n">
-        <v>2941.3</v>
+        <v>2938</v>
       </c>
       <c r="F44" t="n">
-        <v>-32.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0011</v>
       </c>
       <c r="H44" t="n">
-        <v>67.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>2868.8</v>
+        <v>2864.4</v>
       </c>
       <c r="J44" t="n">
-        <v>2884.97</v>
+        <v>2861.28</v>
       </c>
       <c r="K44" t="n">
-        <v>2933.25</v>
+        <v>2907.45</v>
       </c>
       <c r="L44" t="n">
-        <v>2981.53</v>
+        <v>2953.63</v>
       </c>
       <c r="M44" t="n">
-        <v>3013.75</v>
+        <v>2975.15</v>
       </c>
       <c r="N44" t="n">
-        <v>3045.97</v>
+        <v>2996.67</v>
       </c>
       <c r="O44" t="n">
-        <v>3110.3</v>
+        <v>3067.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4195,16 +4187,18 @@
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4212,7 +4206,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4222,50 +4216,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2955.5</v>
+        <v>2950</v>
       </c>
       <c r="C45" t="n">
-        <v>2985.9</v>
+        <v>3058.3</v>
       </c>
       <c r="D45" t="n">
-        <v>2902.3</v>
+        <v>2948.4</v>
       </c>
       <c r="E45" t="n">
-        <v>2938</v>
+        <v>3041.6</v>
       </c>
       <c r="F45" t="n">
-        <v>-3.3</v>
+        <v>103.6</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0353</v>
       </c>
       <c r="H45" t="n">
-        <v>83.59999999999999</v>
+        <v>109.9</v>
       </c>
       <c r="I45" t="n">
-        <v>2864.4</v>
+        <v>2818.7</v>
       </c>
       <c r="J45" t="n">
-        <v>2861.28</v>
+        <v>2851.35</v>
       </c>
       <c r="K45" t="n">
-        <v>2907.45</v>
+        <v>2896.2</v>
       </c>
       <c r="L45" t="n">
-        <v>2953.63</v>
+        <v>2941.05</v>
       </c>
       <c r="M45" t="n">
-        <v>2975.15</v>
+        <v>2979.8</v>
       </c>
       <c r="N45" t="n">
-        <v>2996.67</v>
+        <v>3018.55</v>
       </c>
       <c r="O45" t="n">
-        <v>3067.5</v>
+        <v>3069.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4273,30 +4267,30 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
       <c r="W45" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr"/>
@@ -4304,50 +4298,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2950</v>
+        <v>3038.9</v>
       </c>
       <c r="C46" t="n">
-        <v>3058.3</v>
+        <v>3076.3</v>
       </c>
       <c r="D46" t="n">
-        <v>2948.4</v>
+        <v>3016</v>
       </c>
       <c r="E46" t="n">
-        <v>3041.6</v>
+        <v>3074.9</v>
       </c>
       <c r="F46" t="n">
-        <v>103.6</v>
+        <v>33.3</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.0109</v>
       </c>
       <c r="H46" t="n">
-        <v>109.9</v>
+        <v>60.3</v>
       </c>
       <c r="I46" t="n">
-        <v>2818.7</v>
+        <v>2838.5</v>
       </c>
       <c r="J46" t="n">
-        <v>2851.35</v>
+        <v>2950.83</v>
       </c>
       <c r="K46" t="n">
-        <v>2896.2</v>
+        <v>2986.65</v>
       </c>
       <c r="L46" t="n">
-        <v>2941.05</v>
+        <v>3022.48</v>
       </c>
       <c r="M46" t="n">
-        <v>2979.8</v>
+        <v>3096.55</v>
       </c>
       <c r="N46" t="n">
-        <v>3018.55</v>
+        <v>3170.63</v>
       </c>
       <c r="O46" t="n">
-        <v>3069.5</v>
+        <v>3168.2</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4358,25 +4352,23 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4386,69 +4378,71 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3038.9</v>
+        <v>3073.5</v>
       </c>
       <c r="C47" t="n">
-        <v>3076.3</v>
+        <v>3079.9</v>
       </c>
       <c r="D47" t="n">
-        <v>3016</v>
+        <v>2993.2</v>
       </c>
       <c r="E47" t="n">
-        <v>3074.9</v>
+        <v>3022.1</v>
       </c>
       <c r="F47" t="n">
-        <v>33.3</v>
+        <v>-52.8</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.0172</v>
       </c>
       <c r="H47" t="n">
-        <v>60.3</v>
+        <v>86.7</v>
       </c>
       <c r="I47" t="n">
-        <v>2838.5</v>
+        <v>2955.7</v>
       </c>
       <c r="J47" t="n">
-        <v>2950.83</v>
+        <v>3028.97</v>
       </c>
       <c r="K47" t="n">
-        <v>2986.65</v>
+        <v>3044.75</v>
       </c>
       <c r="L47" t="n">
-        <v>3022.48</v>
+        <v>3060.52</v>
       </c>
       <c r="M47" t="n">
-        <v>3096.55</v>
+        <v>3105.05</v>
       </c>
       <c r="N47" t="n">
-        <v>3170.63</v>
+        <v>3149.57</v>
       </c>
       <c r="O47" t="n">
-        <v>3168.2</v>
+        <v>3136.6</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4458,73 +4452,75 @@
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3073.5</v>
+        <v>3023</v>
       </c>
       <c r="C48" t="n">
-        <v>3079.9</v>
+        <v>3028.9</v>
       </c>
       <c r="D48" t="n">
-        <v>2993.2</v>
+        <v>2976.6</v>
       </c>
       <c r="E48" t="n">
-        <v>3022.1</v>
+        <v>2977.5</v>
       </c>
       <c r="F48" t="n">
-        <v>-52.8</v>
+        <v>-44.6</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0172</v>
+        <v>-0.0148</v>
       </c>
       <c r="H48" t="n">
-        <v>86.7</v>
+        <v>52.3</v>
       </c>
       <c r="I48" t="n">
-        <v>2955.7</v>
+        <v>2906.5</v>
       </c>
       <c r="J48" t="n">
-        <v>3028.97</v>
+        <v>2928.18</v>
       </c>
       <c r="K48" t="n">
-        <v>3044.75</v>
+        <v>2978.75</v>
       </c>
       <c r="L48" t="n">
-        <v>3060.52</v>
+        <v>3029.33</v>
       </c>
       <c r="M48" t="n">
-        <v>3105.05</v>
+        <v>3065.45</v>
       </c>
       <c r="N48" t="n">
-        <v>3149.57</v>
+        <v>3101.58</v>
       </c>
       <c r="O48" t="n">
-        <v>3136.6</v>
+        <v>3166.6</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4538,79 +4534,77 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3023</v>
+        <v>2971</v>
       </c>
       <c r="C49" t="n">
-        <v>3028.9</v>
+        <v>2983.3</v>
       </c>
       <c r="D49" t="n">
+        <v>2914.5</v>
+      </c>
+      <c r="E49" t="n">
         <v>2976.6</v>
       </c>
-      <c r="E49" t="n">
-        <v>2977.5</v>
-      </c>
       <c r="F49" t="n">
-        <v>-44.6</v>
+        <v>-0.9</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0148</v>
+        <v>-0.0003</v>
       </c>
       <c r="H49" t="n">
-        <v>52.3</v>
+        <v>68.8</v>
       </c>
       <c r="I49" t="n">
-        <v>2906.5</v>
+        <v>2924.3</v>
       </c>
       <c r="J49" t="n">
-        <v>2928.18</v>
+        <v>2912.58</v>
       </c>
       <c r="K49" t="n">
-        <v>2978.75</v>
+        <v>2951.35</v>
       </c>
       <c r="L49" t="n">
-        <v>3029.33</v>
+        <v>2990.12</v>
       </c>
       <c r="M49" t="n">
-        <v>3065.45</v>
+        <v>3003.65</v>
       </c>
       <c r="N49" t="n">
-        <v>3101.58</v>
+        <v>3017.17</v>
       </c>
       <c r="O49" t="n">
-        <v>3166.6</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
+        <v>3081.2</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4622,7 +4616,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4632,67 +4626,67 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2971</v>
+        <v>2974.7</v>
       </c>
       <c r="C50" t="n">
-        <v>2983.3</v>
+        <v>2977.9</v>
       </c>
       <c r="D50" t="n">
-        <v>2914.5</v>
+        <v>2887.6</v>
       </c>
       <c r="E50" t="n">
-        <v>2976.6</v>
+        <v>2904.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.9</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0003</v>
+        <v>-0.0242</v>
       </c>
       <c r="H50" t="n">
-        <v>68.8</v>
+        <v>90.3</v>
       </c>
       <c r="I50" t="n">
-        <v>2924.3</v>
+        <v>2845.7</v>
       </c>
       <c r="J50" t="n">
-        <v>2912.58</v>
+        <v>2921.65</v>
       </c>
       <c r="K50" t="n">
-        <v>2951.35</v>
+        <v>2942.2</v>
       </c>
       <c r="L50" t="n">
-        <v>2990.12</v>
+        <v>2962.75</v>
       </c>
       <c r="M50" t="n">
-        <v>3003.65</v>
+        <v>3011</v>
       </c>
       <c r="N50" t="n">
-        <v>3017.17</v>
+        <v>3059.25</v>
       </c>
       <c r="O50" t="n">
-        <v>3081.2</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
+        <v>3052.1</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4704,7 +4698,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4714,65 +4708,63 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2974.7</v>
+        <v>2892.7</v>
       </c>
       <c r="C51" t="n">
-        <v>2977.9</v>
+        <v>2913.5</v>
       </c>
       <c r="D51" t="n">
-        <v>2887.6</v>
+        <v>2831.9</v>
       </c>
       <c r="E51" t="n">
-        <v>2904.5</v>
+        <v>2873.23</v>
       </c>
       <c r="F51" t="n">
-        <v>-72.09999999999999</v>
+        <v>-31.27</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0242</v>
+        <v>-0.0108</v>
       </c>
       <c r="H51" t="n">
-        <v>90.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>2845.7</v>
+        <v>2797.3</v>
       </c>
       <c r="J51" t="n">
-        <v>2921.65</v>
+        <v>2800.08</v>
       </c>
       <c r="K51" t="n">
-        <v>2942.2</v>
+        <v>2859.35</v>
       </c>
       <c r="L51" t="n">
-        <v>2962.75</v>
+        <v>2918.62</v>
       </c>
       <c r="M51" t="n">
-        <v>3011</v>
+        <v>2949.65</v>
       </c>
       <c r="N51" t="n">
-        <v>3059.25</v>
+        <v>2980.67</v>
       </c>
       <c r="O51" t="n">
-        <v>3052.1</v>
+        <v>3068.2</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4786,7 +4778,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4796,50 +4788,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2892.7</v>
+        <v>2879.5</v>
       </c>
       <c r="C52" t="n">
-        <v>2913.5</v>
+        <v>2931.2</v>
       </c>
       <c r="D52" t="n">
-        <v>2831.9</v>
+        <v>2829.9</v>
       </c>
       <c r="E52" t="n">
-        <v>2873.23</v>
+        <v>2859.3</v>
       </c>
       <c r="F52" t="n">
-        <v>-31.27</v>
+        <v>-13.93</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0048</v>
       </c>
       <c r="H52" t="n">
-        <v>81.59999999999999</v>
+        <v>101.3</v>
       </c>
       <c r="I52" t="n">
-        <v>2797.3</v>
+        <v>2750.3</v>
       </c>
       <c r="J52" t="n">
-        <v>2800.08</v>
+        <v>2791.89</v>
       </c>
       <c r="K52" t="n">
-        <v>2859.35</v>
+        <v>2832.43</v>
       </c>
       <c r="L52" t="n">
-        <v>2918.62</v>
+        <v>2872.96</v>
       </c>
       <c r="M52" t="n">
-        <v>2949.65</v>
+        <v>2914.03</v>
       </c>
       <c r="N52" t="n">
-        <v>2980.67</v>
+        <v>2955.1</v>
       </c>
       <c r="O52" t="n">
-        <v>3068.2</v>
+        <v>2995.1</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4849,16 +4841,18 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4866,60 +4860,64 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2879.5</v>
+        <v>2857.7</v>
       </c>
       <c r="C53" t="n">
-        <v>2931.2</v>
+        <v>2875.3</v>
       </c>
       <c r="D53" t="n">
-        <v>2829.9</v>
+        <v>2791.5</v>
       </c>
       <c r="E53" t="n">
-        <v>2859.3</v>
+        <v>2850.9</v>
       </c>
       <c r="F53" t="n">
-        <v>-13.93</v>
+        <v>-8.4</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0029</v>
       </c>
       <c r="H53" t="n">
-        <v>101.3</v>
+        <v>83.8</v>
       </c>
       <c r="I53" t="n">
-        <v>2750.3</v>
+        <v>2728.6</v>
       </c>
       <c r="J53" t="n">
-        <v>2791.89</v>
+        <v>2747.38</v>
       </c>
       <c r="K53" t="n">
-        <v>2832.43</v>
+        <v>2808.65</v>
       </c>
       <c r="L53" t="n">
-        <v>2872.96</v>
+        <v>2869.92</v>
       </c>
       <c r="M53" t="n">
-        <v>2914.03</v>
+        <v>2909.95</v>
       </c>
       <c r="N53" t="n">
-        <v>2955.1</v>
+        <v>2949.98</v>
       </c>
       <c r="O53" t="n">
-        <v>2995.1</v>
+        <v>3032.5</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4932,15 +4930,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4948,64 +4944,60 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2857.7</v>
+        <v>2850.6</v>
       </c>
       <c r="C54" t="n">
-        <v>2875.3</v>
+        <v>2887.2</v>
       </c>
       <c r="D54" t="n">
-        <v>2791.5</v>
+        <v>2778.6</v>
       </c>
       <c r="E54" t="n">
-        <v>2850.9</v>
+        <v>2822.1</v>
       </c>
       <c r="F54" t="n">
-        <v>-8.4</v>
+        <v>-28.8</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0101</v>
       </c>
       <c r="H54" t="n">
-        <v>83.8</v>
+        <v>108.6</v>
       </c>
       <c r="I54" t="n">
-        <v>2728.6</v>
+        <v>2707.7</v>
       </c>
       <c r="J54" t="n">
-        <v>2747.38</v>
+        <v>2775.85</v>
       </c>
       <c r="K54" t="n">
-        <v>2808.65</v>
+        <v>2809</v>
       </c>
       <c r="L54" t="n">
-        <v>2869.92</v>
+        <v>2842.15</v>
       </c>
       <c r="M54" t="n">
-        <v>2909.95</v>
+        <v>2892.8</v>
       </c>
       <c r="N54" t="n">
-        <v>2949.98</v>
+        <v>2943.45</v>
       </c>
       <c r="O54" t="n">
-        <v>3032.5</v>
+        <v>2959.1</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5015,12 +5007,12 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5032,73 +5024,79 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2850.6</v>
+        <v>2822.9</v>
       </c>
       <c r="C55" t="n">
-        <v>2887.2</v>
+        <v>2834.3</v>
       </c>
       <c r="D55" t="n">
-        <v>2778.6</v>
+        <v>2728.9</v>
       </c>
       <c r="E55" t="n">
-        <v>2822.1</v>
+        <v>2735.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-28.8</v>
+        <v>-86.59999999999999</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0101</v>
+        <v>-0.0307</v>
       </c>
       <c r="H55" t="n">
-        <v>108.6</v>
+        <v>105.4</v>
       </c>
       <c r="I55" t="n">
-        <v>2707.7</v>
+        <v>2670</v>
       </c>
       <c r="J55" t="n">
-        <v>2775.85</v>
+        <v>2708.1</v>
       </c>
       <c r="K55" t="n">
-        <v>2809</v>
+        <v>2767.8</v>
       </c>
       <c r="L55" t="n">
-        <v>2842.15</v>
+        <v>2827.5</v>
       </c>
       <c r="M55" t="n">
-        <v>2892.8</v>
+        <v>2876.4</v>
       </c>
       <c r="N55" t="n">
-        <v>2943.45</v>
+        <v>2925.3</v>
       </c>
       <c r="O55" t="n">
-        <v>2959.1</v>
+        <v>2995.8</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5112,146 +5110,144 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2822.9</v>
+        <v>2723.3</v>
       </c>
       <c r="C56" t="n">
-        <v>2834.3</v>
+        <v>2806.2</v>
       </c>
       <c r="D56" t="n">
-        <v>2728.9</v>
+        <v>2723.3</v>
       </c>
       <c r="E56" t="n">
-        <v>2735.5</v>
+        <v>2784.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-86.59999999999999</v>
+        <v>49</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0307</v>
+        <v>0.0179</v>
       </c>
       <c r="H56" t="n">
-        <v>105.4</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>2670</v>
+        <v>2623.5</v>
       </c>
       <c r="J56" t="n">
-        <v>2708.1</v>
+        <v>2607.05</v>
       </c>
       <c r="K56" t="n">
-        <v>2767.8</v>
+        <v>2682.8</v>
       </c>
       <c r="L56" t="n">
-        <v>2827.5</v>
+        <v>2758.55</v>
       </c>
       <c r="M56" t="n">
-        <v>2876.4</v>
+        <v>2788.2</v>
       </c>
       <c r="N56" t="n">
-        <v>2925.3</v>
+        <v>2817.85</v>
       </c>
       <c r="O56" t="n">
-        <v>2995.8</v>
+        <v>2939.7</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2723.3</v>
+        <v>2793.5</v>
       </c>
       <c r="C57" t="n">
-        <v>2806.2</v>
+        <v>2880.2</v>
       </c>
       <c r="D57" t="n">
-        <v>2723.3</v>
+        <v>2784.9</v>
       </c>
       <c r="E57" t="n">
-        <v>2784.5</v>
+        <v>2821.9</v>
       </c>
       <c r="F57" t="n">
-        <v>49</v>
+        <v>37.4</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0134</v>
       </c>
       <c r="H57" t="n">
-        <v>82.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="I57" t="n">
-        <v>2623.5</v>
+        <v>2640.4</v>
       </c>
       <c r="J57" t="n">
-        <v>2607.05</v>
+        <v>2711.48</v>
       </c>
       <c r="K57" t="n">
-        <v>2682.8</v>
+        <v>2743.05</v>
       </c>
       <c r="L57" t="n">
-        <v>2758.55</v>
+        <v>2774.62</v>
       </c>
       <c r="M57" t="n">
-        <v>2788.2</v>
+        <v>2825.95</v>
       </c>
       <c r="N57" t="n">
-        <v>2817.85</v>
+        <v>2877.27</v>
       </c>
       <c r="O57" t="n">
-        <v>2939.7</v>
+        <v>2889.1</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5262,7 +5258,7 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5272,104 +5268,20 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2793.5</v>
-      </c>
-      <c r="C58" t="n">
-        <v>2880.2</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2784.9</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2853.2</v>
-      </c>
-      <c r="F58" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0247</v>
-      </c>
-      <c r="H58" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2640.4</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2711.48</v>
-      </c>
-      <c r="K58" t="n">
-        <v>2743.05</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2774.62</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2825.95</v>
-      </c>
-      <c r="N58" t="n">
-        <v>2877.27</v>
-      </c>
-      <c r="O58" t="n">
-        <v>2889.1</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>
